--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62519F1-92AB-43F7-9D6F-D5B42E0D065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834887AF-6771-44B1-B42A-213B1EE58C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,24 +19,11 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -222,6 +209,48 @@
   </si>
   <si>
     <t xml:space="preserve">Client Name </t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD Total </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/7 Mart </t>
+  </si>
+  <si>
+    <t>7591263-6</t>
+  </si>
+  <si>
+    <t>Rafaqat &amp; Sons (Risen) sbzaZar</t>
+  </si>
+  <si>
+    <t>(Risen) Rehman Garden</t>
+  </si>
+  <si>
+    <t>Pak Madina (Jharan wala)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafaqat &amp; Sons </t>
+  </si>
+  <si>
+    <t>Rehman Garden (Risen)</t>
+  </si>
+  <si>
+    <t>Pak Madina (Jharawala)</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Last Month Sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Month Sale </t>
   </si>
 </sst>
 </file>
@@ -311,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,8 +377,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -806,29 +847,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -936,6 +955,45 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -945,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -964,7 +1022,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1040,9 +1097,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1052,7 +1106,6 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1104,25 +1157,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1138,37 +1184,31 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1183,16 +1223,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="6" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1223,40 +1336,16 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1567,7 +1656,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B7:D19"/>
+  <dimension ref="B7:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.453125" bestFit="1" customWidth="1"/>
@@ -1583,13 +1672,13 @@
     <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="92" t="s">
+      <c r="C9" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="80" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1600,7 +1689,7 @@
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="79">
         <v>3520247902365</v>
       </c>
     </row>
@@ -1618,7 +1707,7 @@
       <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="79">
         <v>300426949714</v>
       </c>
     </row>
@@ -1629,7 +1718,7 @@
       <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="79">
         <v>3277876126916</v>
       </c>
     </row>
@@ -1640,7 +1729,7 @@
       <c r="C14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="79">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1651,7 +1740,7 @@
       <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="91">
+      <c r="D15" s="79">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1662,7 +1751,7 @@
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="91">
+      <c r="D16" s="79">
         <v>3520268948847</v>
       </c>
     </row>
@@ -1686,7 +1775,29 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="93" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="93" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="93" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="77" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1695,1596 +1806,2090 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="103">
+      <c r="B1" s="120">
         <v>46174</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="13">
         <v>60</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>60</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>60</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="16">
         <v>70</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="17">
         <v>70</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="15">
         <v>70</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="16">
         <v>120</v>
       </c>
-      <c r="K2" s="18">
+      <c r="K2" s="17">
         <v>120</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="115"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="118" t="s">
+      <c r="M2" s="109"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="19">
+      <c r="Q2" s="113"/>
+      <c r="R2" s="18">
         <v>0.05</v>
       </c>
-      <c r="S2" s="20">
+      <c r="S2" s="19">
         <v>0.08</v>
       </c>
-      <c r="T2" s="20">
+      <c r="T2" s="19">
         <v>0.08</v>
       </c>
-      <c r="U2" s="21"/>
-      <c r="V2" s="22">
+      <c r="U2" s="20"/>
+      <c r="V2" s="21">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="21"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="123"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="24" t="s">
+      <c r="A3" s="117"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="24">
         <v>39.230000000000004</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="25">
         <v>39.230000000000004</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="26">
         <v>39.230000000000004</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>52.462499999999999</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="28">
         <v>52.462499999999999</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="29">
         <v>52.462499999999999</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="27">
         <v>72.64</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="28">
         <v>72.64</v>
       </c>
-      <c r="L3" s="30">
+      <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="120" t="s">
+      <c r="M3" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="121"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="107" t="s">
+      <c r="N3" s="115"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="110" t="s">
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="126"/>
+      <c r="V3" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="112"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="129"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="123"/>
-      <c r="B4" s="106"/>
-      <c r="C4" s="31" t="s">
+      <c r="A4" s="117"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="34" t="s">
+      <c r="O4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="27">
         <v>70</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="34">
         <v>120</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="31">
         <v>60</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="28">
         <v>70</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="28">
         <v>120</v>
       </c>
-      <c r="U4" s="36" t="s">
+      <c r="U4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="V4" s="32">
+      <c r="V4" s="31">
         <v>60</v>
       </c>
-      <c r="W4" s="29">
+      <c r="W4" s="28">
         <v>70</v>
       </c>
-      <c r="X4" s="29">
+      <c r="X4" s="28">
         <v>120</v>
       </c>
-      <c r="Y4" s="36" t="s">
+      <c r="Y4" s="35" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="93">
+      <c r="A5" s="81">
         <v>46179</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="97" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="98">
+        <v>1003</v>
+      </c>
+      <c r="E5" s="99"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="101">
+        <v>1613</v>
+      </c>
+      <c r="H5" s="99">
+        <v>2442</v>
+      </c>
+      <c r="I5" s="100">
+        <v>1036</v>
+      </c>
+      <c r="J5" s="101">
+        <v>5269</v>
+      </c>
+      <c r="K5" s="99">
+        <v>3838</v>
+      </c>
+      <c r="L5" s="102">
+        <v>4835</v>
+      </c>
+      <c r="M5" s="37">
+        <f>SUM(D5:L5)/40</f>
+        <v>500.9</v>
+      </c>
+      <c r="N5" s="39">
+        <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="38">
+        <f>SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <v>116.2242</v>
+      </c>
+      <c r="P5" s="75">
+        <f>SUM(G5:I5)/20</f>
+        <v>254.55</v>
+      </c>
+      <c r="Q5" s="40">
+        <f>SUM(J5:L5)/20</f>
+        <v>697.1</v>
+      </c>
+      <c r="R5" s="41" t="e">
+        <f>SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S5" s="42">
+        <f>SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="42">
+        <f>SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="43" t="e">
+        <f>SUM(R5:T5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V5" s="44" t="e">
+        <f>SUM(D5:F5)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W5" s="45">
+        <f>SUM(G5:I5)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="45">
+        <f>SUM(J5:L5)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="46" t="e">
+        <f>SUM(V5:X5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="81">
+        <v>46179</v>
+      </c>
+      <c r="B6" s="47">
+        <v>2</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="81"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="42">
+      <c r="D6" s="76"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="51">
         <v>240</v>
       </c>
-      <c r="H5" s="82">
+      <c r="H6" s="77">
         <v>240</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I6" s="50">
         <v>240</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J6" s="51">
         <v>240</v>
       </c>
-      <c r="K5" s="82">
+      <c r="K6" s="77">
         <v>240</v>
       </c>
-      <c r="L5" s="83">
+      <c r="L6" s="78">
         <v>600</v>
       </c>
-      <c r="M5" s="39">
-        <f>SUM(D5:L5)/40</f>
+      <c r="M6" s="49">
+        <f t="shared" ref="M6:M26" si="0">SUM(D6:L6)/40</f>
         <v>45</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N6" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="40">
-        <f>SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P5" s="84">
-        <f>SUM(G5:I5)/20</f>
+      <c r="O6" s="50">
+        <f t="shared" ref="O6:O25" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <v>116.2242</v>
+      </c>
+      <c r="P6" s="75">
+        <f t="shared" ref="P6" si="2">SUM(G6:I6)/20</f>
         <v>36</v>
       </c>
-      <c r="Q5" s="43">
-        <f>SUM(J5:L5)/20</f>
+      <c r="Q6" s="40">
+        <f t="shared" ref="Q6" si="3">SUM(J6:L6)/20</f>
         <v>54</v>
       </c>
-      <c r="R5" s="44" t="e">
-        <f>SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S5" s="45">
-        <f>SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
-        <v>0</v>
-      </c>
-      <c r="T5" s="45">
-        <f>SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
-        <v>0</v>
-      </c>
-      <c r="U5" s="46" t="e">
-        <f>SUM(R5:T5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V5" s="47" t="e">
-        <f>SUM(D5:F5)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W5" s="48">
-        <f>SUM(G5:I5)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X5" s="48">
-        <f>SUM(J5:L5)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="49" t="e">
-        <f>SUM(V5:X5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="93">
+      <c r="R6" s="52" t="e">
+        <f t="shared" ref="R6:R25" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S6" s="53">
+        <f t="shared" ref="S6:S25" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="53">
+        <f t="shared" ref="T6:T25" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="54" t="e">
+        <f t="shared" ref="U6:U12" si="7">SUM(R6:T6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V6" s="55" t="e">
+        <f t="shared" ref="V6" si="8">SUM(D6:F6)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W6" s="56">
+        <f t="shared" ref="W6" si="9">SUM(G6:I6)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="56">
+        <f t="shared" ref="X6" si="10">SUM(J6:L6)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="57" t="e">
+        <f t="shared" ref="Y6:Y12" si="11">SUM(V6:X6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="81">
         <v>46179</v>
       </c>
-      <c r="B6" s="50">
-        <v>2</v>
-      </c>
-      <c r="C6" s="51" t="s">
+      <c r="B7" s="47">
+        <v>3</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="54">
+      <c r="D7" s="76"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="51">
         <v>600</v>
       </c>
-      <c r="H6" s="86">
+      <c r="H7" s="77">
         <v>600</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I7" s="50">
         <v>1200</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J7" s="51">
         <v>1800</v>
       </c>
-      <c r="K6" s="86">
+      <c r="K7" s="77">
         <v>1200</v>
       </c>
-      <c r="L6" s="87">
+      <c r="L7" s="78">
         <v>1200</v>
       </c>
-      <c r="M6" s="52">
-        <f t="shared" ref="M6:M21" si="0">SUM(D6:L6)/40</f>
+      <c r="M7" s="49">
+        <f t="shared" ref="M7:M15" si="12">SUM(D7:L7)/40</f>
         <v>165</v>
       </c>
-      <c r="N6" s="41">
+      <c r="N7" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="53">
-        <f t="shared" ref="O6:O20" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P6" s="84">
-        <f t="shared" ref="P6:P12" si="2">SUM(G6:I6)/20</f>
+      <c r="O7" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P7" s="75">
+        <f t="shared" ref="P7:P15" si="13">SUM(G7:I7)/20</f>
         <v>120</v>
       </c>
-      <c r="Q6" s="43">
-        <f t="shared" ref="Q6:Q12" si="3">SUM(J6:L6)/20</f>
+      <c r="Q7" s="40">
+        <f t="shared" ref="Q7:Q15" si="14">SUM(J7:L7)/20</f>
         <v>210</v>
       </c>
-      <c r="R6" s="55" t="e">
-        <f t="shared" ref="R6:R20" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S6" s="56">
-        <f t="shared" ref="S6:S20" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="56">
-        <f t="shared" ref="T6:T20" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="57" t="e">
-        <f t="shared" ref="U6:U12" si="7">SUM(R6:T6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V6" s="58" t="e">
-        <f t="shared" ref="V6:V12" si="8">SUM(D6:F6)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W6" s="59">
-        <f t="shared" ref="W6:W12" si="9">SUM(G6:I6)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X6" s="59">
-        <f t="shared" ref="X6:X12" si="10">SUM(J6:L6)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="60" t="e">
-        <f t="shared" ref="Y6:Y12" si="11">SUM(V6:X6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="93">
-        <v>46179</v>
-      </c>
-      <c r="B7" s="50">
-        <v>3</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="85">
-        <v>1400</v>
-      </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="54">
+      <c r="R7" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S7" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V7" s="55" t="e">
+        <f t="shared" ref="V7:V15" si="15">SUM(D7:F7)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W7" s="56">
+        <f t="shared" ref="W7:W15" si="16">SUM(G7:I7)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="56">
+        <f t="shared" ref="X7:X15" si="17">SUM(J7:L7)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="81">
+        <v>46181</v>
+      </c>
+      <c r="B8" s="47">
+        <v>4</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="76">
+        <v>800</v>
+      </c>
+      <c r="E8" s="77"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="51">
+        <v>800</v>
+      </c>
+      <c r="H8" s="77">
+        <v>800</v>
+      </c>
+      <c r="I8" s="50">
+        <v>800</v>
+      </c>
+      <c r="J8" s="51">
+        <v>800</v>
+      </c>
+      <c r="K8" s="77">
+        <v>800</v>
+      </c>
+      <c r="L8" s="78">
+        <v>800</v>
+      </c>
+      <c r="M8" s="49">
+        <f t="shared" si="12"/>
+        <v>140</v>
+      </c>
+      <c r="N8" s="39">
+        <f t="shared" ref="N8:N25" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P8" s="75">
+        <f t="shared" si="13"/>
+        <v>120</v>
+      </c>
+      <c r="Q8" s="40">
+        <f t="shared" si="14"/>
+        <v>120</v>
+      </c>
+      <c r="R8" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S8" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V8" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W8" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="81">
+        <v>46181</v>
+      </c>
+      <c r="B9" s="47">
+        <v>5</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="76">
+        <v>80</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="51">
+        <v>80</v>
+      </c>
+      <c r="H9" s="77">
+        <v>80</v>
+      </c>
+      <c r="I9" s="50">
+        <v>80</v>
+      </c>
+      <c r="J9" s="51">
+        <v>80</v>
+      </c>
+      <c r="K9" s="77">
+        <v>80</v>
+      </c>
+      <c r="L9" s="78">
+        <v>80</v>
+      </c>
+      <c r="M9" s="49">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="N9" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P9" s="75">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="Q9" s="40">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="R9" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S9" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V9" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W9" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="81">
+        <v>46182</v>
+      </c>
+      <c r="B10" s="47">
+        <v>6</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="76">
+        <v>0</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="51">
+        <v>280</v>
+      </c>
+      <c r="H10" s="77">
+        <v>0</v>
+      </c>
+      <c r="I10" s="50">
+        <v>320</v>
+      </c>
+      <c r="J10" s="51">
+        <v>600</v>
+      </c>
+      <c r="K10" s="77">
+        <v>600</v>
+      </c>
+      <c r="L10" s="78">
+        <v>2200</v>
+      </c>
+      <c r="M10" s="49">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+      <c r="N10" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P10" s="75">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="Q10" s="40">
+        <f t="shared" si="14"/>
+        <v>170</v>
+      </c>
+      <c r="R10" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S10" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V10" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W10" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="81">
+        <v>46182</v>
+      </c>
+      <c r="B11" s="47">
+        <v>7</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="76">
+        <v>200</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="51">
+        <v>200</v>
+      </c>
+      <c r="H11" s="77">
+        <v>200</v>
+      </c>
+      <c r="I11" s="50">
+        <v>200</v>
+      </c>
+      <c r="J11" s="51">
+        <v>200</v>
+      </c>
+      <c r="K11" s="77">
+        <v>200</v>
+      </c>
+      <c r="L11" s="78">
+        <v>200</v>
+      </c>
+      <c r="M11" s="49">
+        <f t="shared" si="12"/>
+        <v>35</v>
+      </c>
+      <c r="N11" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P11" s="75">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="Q11" s="40">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="R11" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S11" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V11" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W11" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="81">
+        <v>46182</v>
+      </c>
+      <c r="B12" s="47">
+        <v>8</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="76"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="51">
+        <v>560</v>
+      </c>
+      <c r="K12" s="77">
+        <v>560</v>
+      </c>
+      <c r="L12" s="78">
+        <v>880</v>
+      </c>
+      <c r="M12" s="49">
+        <f t="shared" si="12"/>
+        <v>50</v>
+      </c>
+      <c r="N12" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P12" s="75">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="40">
+        <f t="shared" si="14"/>
+        <v>100</v>
+      </c>
+      <c r="R12" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S12" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="54" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V12" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W12" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="57" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="81">
+        <v>46183</v>
+      </c>
+      <c r="B13" s="47">
+        <v>9</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="76"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="51">
+        <v>1200</v>
+      </c>
+      <c r="H13" s="77">
+        <v>1200</v>
+      </c>
+      <c r="I13" s="50">
+        <v>1800</v>
+      </c>
+      <c r="J13" s="51">
+        <v>2400</v>
+      </c>
+      <c r="K13" s="77">
+        <v>1800</v>
+      </c>
+      <c r="L13" s="78">
+        <v>1800</v>
+      </c>
+      <c r="M13" s="49">
+        <f t="shared" si="12"/>
+        <v>255</v>
+      </c>
+      <c r="N13" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P13" s="75">
+        <f t="shared" si="13"/>
+        <v>210</v>
+      </c>
+      <c r="Q13" s="40">
+        <f t="shared" si="14"/>
+        <v>300</v>
+      </c>
+      <c r="R13" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S13" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="54" t="e">
+        <f t="shared" ref="U13:U25" si="19">SUM(R13:T13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V13" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W13" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="57" t="e">
+        <f t="shared" ref="Y13:Y25" si="20">SUM(V13:X13)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="81">
+        <v>46183</v>
+      </c>
+      <c r="B14" s="47">
+        <v>10</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="76"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="77">
+        <v>40</v>
+      </c>
+      <c r="I14" s="50">
+        <v>40</v>
+      </c>
+      <c r="J14" s="51">
+        <v>40</v>
+      </c>
+      <c r="K14" s="77">
+        <v>40</v>
+      </c>
+      <c r="L14" s="78">
+        <v>40</v>
+      </c>
+      <c r="M14" s="49">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="N14" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P14" s="75">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="Q14" s="40">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="R14" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S14" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="54" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V14" s="55" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W14" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="57" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="81">
+        <v>46183</v>
+      </c>
+      <c r="B15" s="47">
+        <v>11</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="76"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="51">
         <v>400</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H15" s="77">
+        <v>200</v>
+      </c>
+      <c r="I15" s="50">
         <v>400</v>
       </c>
-      <c r="I7" s="53">
-        <v>0</v>
-      </c>
-      <c r="J7" s="54">
+      <c r="J15" s="51">
         <v>400</v>
       </c>
-      <c r="K7" s="86">
+      <c r="K15" s="77">
+        <v>200</v>
+      </c>
+      <c r="L15" s="78">
         <v>400</v>
       </c>
-      <c r="L7" s="87">
-        <v>600</v>
-      </c>
-      <c r="M7" s="52">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="N7" s="41">
-        <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="53">
+      <c r="M15" s="49">
+        <f t="shared" si="12"/>
+        <v>50</v>
+      </c>
+      <c r="N15" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="50">
         <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P7" s="84">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="Q7" s="43">
-        <f t="shared" si="3"/>
-        <v>70</v>
-      </c>
-      <c r="R7" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S7" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V7" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W7" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X7" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="93">
-        <v>46181</v>
-      </c>
-      <c r="B8" s="50">
-        <v>4</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="85">
-        <v>800</v>
-      </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="54">
-        <v>800</v>
-      </c>
-      <c r="H8" s="86">
-        <v>800</v>
-      </c>
-      <c r="I8" s="53">
-        <v>800</v>
-      </c>
-      <c r="J8" s="54">
-        <v>800</v>
-      </c>
-      <c r="K8" s="86">
-        <v>800</v>
-      </c>
-      <c r="L8" s="87">
-        <v>800</v>
-      </c>
-      <c r="M8" s="52">
-        <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="N8" s="41">
-        <f t="shared" ref="N8:N20" si="12">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P8" s="84">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="Q8" s="43">
-        <f t="shared" si="3"/>
-        <v>120</v>
-      </c>
-      <c r="R8" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S8" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U8" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V8" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W8" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X8" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="93">
-        <v>46181</v>
-      </c>
-      <c r="B9" s="50">
-        <v>5</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="85">
-        <v>80</v>
-      </c>
-      <c r="E9" s="86"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="54">
-        <v>80</v>
-      </c>
-      <c r="H9" s="86">
-        <v>80</v>
-      </c>
-      <c r="I9" s="53">
-        <v>80</v>
-      </c>
-      <c r="J9" s="54">
-        <v>80</v>
-      </c>
-      <c r="K9" s="86">
-        <v>80</v>
-      </c>
-      <c r="L9" s="87">
-        <v>80</v>
-      </c>
-      <c r="M9" s="52">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="N9" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P9" s="84">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="Q9" s="43">
-        <f t="shared" si="3"/>
-        <v>12</v>
-      </c>
-      <c r="R9" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S9" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V9" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W9" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X9" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="93">
-        <v>46182</v>
-      </c>
-      <c r="B10" s="50">
-        <v>6</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="85">
-        <v>0</v>
-      </c>
-      <c r="E10" s="86"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="54">
-        <v>280</v>
-      </c>
-      <c r="H10" s="86">
-        <v>0</v>
-      </c>
-      <c r="I10" s="53">
-        <v>320</v>
-      </c>
-      <c r="J10" s="54">
-        <v>600</v>
-      </c>
-      <c r="K10" s="86">
-        <v>600</v>
-      </c>
-      <c r="L10" s="87">
-        <v>2200</v>
-      </c>
-      <c r="M10" s="52">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-      <c r="N10" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P10" s="84">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="Q10" s="43">
-        <f t="shared" si="3"/>
-        <v>170</v>
-      </c>
-      <c r="R10" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S10" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V10" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W10" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="93">
-        <v>46182</v>
-      </c>
-      <c r="B11" s="50">
-        <v>7</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="85">
-        <v>200</v>
-      </c>
-      <c r="E11" s="86"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="54">
-        <v>200</v>
-      </c>
-      <c r="H11" s="86">
-        <v>200</v>
-      </c>
-      <c r="I11" s="53">
-        <v>200</v>
-      </c>
-      <c r="J11" s="54">
-        <v>200</v>
-      </c>
-      <c r="K11" s="86">
-        <v>200</v>
-      </c>
-      <c r="L11" s="87">
-        <v>200</v>
-      </c>
-      <c r="M11" s="52">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="N11" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P11" s="84">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="Q11" s="43">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="R11" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S11" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V11" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W11" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="93">
-        <v>46182</v>
-      </c>
-      <c r="B12" s="50">
-        <v>8</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="54">
-        <v>560</v>
-      </c>
-      <c r="K12" s="86">
-        <v>560</v>
-      </c>
-      <c r="L12" s="87">
-        <v>880</v>
-      </c>
-      <c r="M12" s="52">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="N12" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P12" s="84">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="43">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="R12" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S12" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V12" s="58" t="e">
-        <f t="shared" si="8"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W12" s="59">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="59">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="60" t="e">
-        <f t="shared" si="11"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="93">
-        <v>46183</v>
-      </c>
-      <c r="B13" s="50">
-        <v>9</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="54">
-        <v>1200</v>
-      </c>
-      <c r="H13" s="86">
-        <v>1200</v>
-      </c>
-      <c r="I13" s="53">
-        <v>1800</v>
-      </c>
-      <c r="J13" s="54">
-        <v>2400</v>
-      </c>
-      <c r="K13" s="86">
-        <v>1800</v>
-      </c>
-      <c r="L13" s="87">
-        <v>1800</v>
-      </c>
-      <c r="M13" s="52">
-        <f t="shared" ref="M13:M19" si="13">SUM(D13:L13)/40</f>
-        <v>255</v>
-      </c>
-      <c r="N13" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P13" s="84">
-        <f t="shared" ref="P13:P20" si="14">SUM(G13:I13)/20</f>
-        <v>210</v>
-      </c>
-      <c r="Q13" s="43">
-        <f t="shared" ref="Q13:Q20" si="15">SUM(J13:L13)/20</f>
-        <v>300</v>
-      </c>
-      <c r="R13" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S13" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="57" t="e">
-        <f t="shared" ref="U13:U20" si="16">SUM(R13:T13)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V13" s="58" t="e">
-        <f t="shared" ref="V13:V20" si="17">SUM(D13:F13)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W13" s="59">
-        <f t="shared" ref="W13:W20" si="18">SUM(G13:I13)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X13" s="59">
-        <f t="shared" ref="X13:X20" si="19">SUM(J13:L13)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="60" t="e">
-        <f t="shared" ref="Y13:Y20" si="20">SUM(V13:X13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="93">
-        <v>46183</v>
-      </c>
-      <c r="B14" s="50">
-        <v>10</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="86">
-        <v>40</v>
-      </c>
-      <c r="I14" s="53">
-        <v>40</v>
-      </c>
-      <c r="J14" s="54">
-        <v>40</v>
-      </c>
-      <c r="K14" s="86">
-        <v>40</v>
-      </c>
-      <c r="L14" s="87">
-        <v>40</v>
-      </c>
-      <c r="M14" s="52">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="N14" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P14" s="84">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="Q14" s="43">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="R14" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S14" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V14" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W14" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="60" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="93">
-        <v>46183</v>
-      </c>
-      <c r="B15" s="50">
-        <v>11</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="54">
-        <v>400</v>
-      </c>
-      <c r="H15" s="86">
-        <v>200</v>
-      </c>
-      <c r="I15" s="53">
-        <v>400</v>
-      </c>
-      <c r="J15" s="54">
-        <v>400</v>
-      </c>
-      <c r="K15" s="86">
-        <v>200</v>
-      </c>
-      <c r="L15" s="87">
-        <v>400</v>
-      </c>
-      <c r="M15" s="52">
+        <v>116.2242</v>
+      </c>
+      <c r="P15" s="75">
         <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="N15" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P15" s="84">
+      <c r="Q15" s="40">
         <f t="shared" si="14"/>
         <v>50</v>
       </c>
-      <c r="Q15" s="43">
+      <c r="R15" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S15" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="54" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V15" s="55" t="e">
         <f t="shared" si="15"/>
-        <v>50</v>
-      </c>
-      <c r="R15" s="55" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W15" s="56">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="56">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="57" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="81">
+        <v>46184</v>
+      </c>
+      <c r="B16" s="47">
+        <v>12</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="51">
+        <v>40</v>
+      </c>
+      <c r="H16" s="77">
+        <v>40</v>
+      </c>
+      <c r="I16" s="50">
+        <v>40</v>
+      </c>
+      <c r="J16" s="51">
+        <v>40</v>
+      </c>
+      <c r="K16" s="77">
+        <v>40</v>
+      </c>
+      <c r="L16" s="78">
+        <v>40</v>
+      </c>
+      <c r="M16" s="49">
+        <f t="shared" ref="M16:M17" si="21">SUM(D16:L16)/40</f>
+        <v>6</v>
+      </c>
+      <c r="N16" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P16" s="75">
+        <f t="shared" ref="P16:P17" si="22">SUM(G16:I16)/20</f>
+        <v>6</v>
+      </c>
+      <c r="Q16" s="40">
+        <f t="shared" ref="Q16:Q17" si="23">SUM(J16:L16)/20</f>
+        <v>6</v>
+      </c>
+      <c r="R16" s="52" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S15" s="56">
+      <c r="S16" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T15" s="56">
+      <c r="T16" s="53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U15" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V15" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W15" s="59">
+      <c r="U16" s="54" t="e">
+        <f t="shared" ref="U16:U17" si="24">SUM(R16:T16)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V16" s="55" t="e">
+        <f t="shared" ref="V16:V17" si="25">SUM(D16:F16)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W16" s="56">
+        <f t="shared" ref="W16:W17" si="26">SUM(G16:I16)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X16" s="56">
+        <f t="shared" ref="X16:X17" si="27">SUM(J16:L16)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="57" t="e">
+        <f t="shared" ref="Y16:Y17" si="28">SUM(V16:X16)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="81">
+        <v>46184</v>
+      </c>
+      <c r="B17" s="47">
+        <v>13</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="76"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="51">
+        <v>1280</v>
+      </c>
+      <c r="H17" s="77">
+        <v>3400</v>
+      </c>
+      <c r="I17" s="50">
+        <v>1840</v>
+      </c>
+      <c r="J17" s="51"/>
+      <c r="K17" s="77">
+        <v>5040</v>
+      </c>
+      <c r="L17" s="78">
+        <v>1760</v>
+      </c>
+      <c r="M17" s="49">
+        <f t="shared" si="21"/>
+        <v>333</v>
+      </c>
+      <c r="N17" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="X15" s="59">
+      <c r="O17" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P17" s="75">
+        <f t="shared" si="22"/>
+        <v>326</v>
+      </c>
+      <c r="Q17" s="40">
+        <f t="shared" si="23"/>
+        <v>340</v>
+      </c>
+      <c r="R17" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S17" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="54" t="e">
+        <f t="shared" si="24"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V17" s="55" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W17" s="56">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="56">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="57" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18" s="81"/>
+      <c r="B18" s="47">
+        <v>14</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="76"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="50">
+        <v>80</v>
+      </c>
+      <c r="J18" s="51">
+        <v>80</v>
+      </c>
+      <c r="K18" s="77">
+        <v>80</v>
+      </c>
+      <c r="L18" s="78">
+        <v>80</v>
+      </c>
+      <c r="M18" s="49">
+        <f t="shared" ref="M18:M21" si="29">SUM(D18:L18)/40</f>
+        <v>8</v>
+      </c>
+      <c r="N18" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P18" s="75">
+        <f t="shared" ref="P18:P21" si="30">SUM(G18:I18)/20</f>
+        <v>4</v>
+      </c>
+      <c r="Q18" s="40">
+        <f t="shared" ref="Q18:Q21" si="31">SUM(J18:L18)/20</f>
+        <v>12</v>
+      </c>
+      <c r="R18" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S18" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="54" t="e">
+        <f t="shared" ref="U18:U21" si="32">SUM(R18:T18)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V18" s="55" t="e">
+        <f t="shared" ref="V18:V21" si="33">SUM(D18:F18)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W18" s="56">
+        <f t="shared" ref="W18:W21" si="34">SUM(G18:I18)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X18" s="56">
+        <f t="shared" ref="X18:X21" si="35">SUM(J18:L18)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="57" t="e">
+        <f t="shared" ref="Y18:Y21" si="36">SUM(V18:X18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19" s="81"/>
+      <c r="B19" s="47">
+        <v>15</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="76"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="51">
+        <v>80</v>
+      </c>
+      <c r="H19" s="77">
+        <v>80</v>
+      </c>
+      <c r="I19" s="50">
+        <v>120</v>
+      </c>
+      <c r="J19" s="51">
+        <v>80</v>
+      </c>
+      <c r="K19" s="77">
+        <v>40</v>
+      </c>
+      <c r="L19" s="78">
+        <v>80</v>
+      </c>
+      <c r="M19" s="49">
+        <f t="shared" si="29"/>
+        <v>12</v>
+      </c>
+      <c r="N19" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P19" s="75">
+        <f t="shared" si="30"/>
+        <v>14</v>
+      </c>
+      <c r="Q19" s="40">
+        <f t="shared" si="31"/>
+        <v>10</v>
+      </c>
+      <c r="R19" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S19" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="54" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V19" s="55" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W19" s="56">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="56">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="57" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20" s="81"/>
+      <c r="B20" s="47">
+        <v>16</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="76">
+        <v>40</v>
+      </c>
+      <c r="E20" s="77"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="51">
+        <v>40</v>
+      </c>
+      <c r="H20" s="77"/>
+      <c r="I20" s="50">
+        <v>40</v>
+      </c>
+      <c r="J20" s="51"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="78">
+        <v>80</v>
+      </c>
+      <c r="M20" s="49">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="N20" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P20" s="75">
+        <f t="shared" si="30"/>
+        <v>4</v>
+      </c>
+      <c r="Q20" s="40">
+        <f t="shared" si="31"/>
+        <v>4</v>
+      </c>
+      <c r="R20" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S20" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="54" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V20" s="55" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W20" s="56">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="56">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="57" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21" s="81">
+        <v>46184</v>
+      </c>
+      <c r="B21" s="47">
+        <v>17</v>
+      </c>
+      <c r="C21" s="58"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="49">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P21" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="40">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S21" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="54" t="e">
+        <f t="shared" si="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V21" s="55" t="e">
+        <f t="shared" si="33"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W21" s="56">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="56">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="57" t="e">
+        <f t="shared" si="36"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22" s="81"/>
+      <c r="B22" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="131"/>
+      <c r="D22" s="91">
+        <f>SUM(D6:D21)</f>
+        <v>1120</v>
+      </c>
+      <c r="E22" s="91">
+        <f t="shared" ref="E22:L22" si="37">SUM(E6:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="91">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="91">
+        <f t="shared" si="37"/>
+        <v>5240</v>
+      </c>
+      <c r="H22" s="91">
+        <f t="shared" si="37"/>
+        <v>6880</v>
+      </c>
+      <c r="I22" s="91">
+        <f t="shared" si="37"/>
+        <v>7200</v>
+      </c>
+      <c r="J22" s="91">
+        <f t="shared" si="37"/>
+        <v>7320</v>
+      </c>
+      <c r="K22" s="91">
+        <f t="shared" si="37"/>
+        <v>10920</v>
+      </c>
+      <c r="L22" s="91">
+        <f t="shared" si="37"/>
+        <v>10240</v>
+      </c>
+      <c r="M22" s="49">
+        <f t="shared" ref="M22:M24" si="38">SUM(D22:L22)/40</f>
+        <v>1223</v>
+      </c>
+      <c r="N22" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P22" s="75">
+        <f t="shared" ref="P22:P25" si="39">SUM(G22:I22)/20</f>
+        <v>966</v>
+      </c>
+      <c r="Q22" s="40">
+        <f t="shared" ref="Q22:Q25" si="40">SUM(J22:L22)/20</f>
+        <v>1424</v>
+      </c>
+      <c r="R22" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S22" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="54" t="e">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="60" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="V22" s="55" t="e">
+        <f t="shared" ref="V22:V25" si="41">SUM(D22:F22)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W22" s="56">
+        <f t="shared" ref="W22:W25" si="42">SUM(G22:I22)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X22" s="56">
+        <f t="shared" ref="X22:X25" si="43">SUM(J22:L22)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="57" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="93"/>
-      <c r="B16" s="50">
-        <v>12</v>
-      </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="52">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="53">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23" s="81"/>
+      <c r="B23" s="47">
+        <v>0</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="76">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="77"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="51">
+        <v>400</v>
+      </c>
+      <c r="H23" s="77">
+        <v>400</v>
+      </c>
+      <c r="I23" s="50">
+        <v>0</v>
+      </c>
+      <c r="J23" s="51">
+        <v>400</v>
+      </c>
+      <c r="K23" s="77">
+        <v>400</v>
+      </c>
+      <c r="L23" s="78">
+        <v>600</v>
+      </c>
+      <c r="M23" s="49">
+        <f t="shared" si="38"/>
+        <v>90</v>
+      </c>
+      <c r="N23" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="50">
         <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P16" s="84">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="43">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="55" t="e">
+        <v>116.2242</v>
+      </c>
+      <c r="P23" s="75">
+        <f t="shared" si="39"/>
+        <v>40</v>
+      </c>
+      <c r="Q23" s="40">
+        <f t="shared" si="40"/>
+        <v>70</v>
+      </c>
+      <c r="R23" s="52" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S16" s="56">
+      <c r="S23" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T16" s="56">
+      <c r="T23" s="53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U16" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V16" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W16" s="59">
+      <c r="U23" s="54" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V23" s="55" t="e">
+        <f t="shared" si="41"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W23" s="56">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="56">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="57" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B24" s="47">
+        <v>0</v>
+      </c>
+      <c r="C24" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="76">
+        <v>0</v>
+      </c>
+      <c r="E24" s="77"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="51">
+        <v>280</v>
+      </c>
+      <c r="H24" s="77">
+        <v>0</v>
+      </c>
+      <c r="I24" s="50">
+        <v>320</v>
+      </c>
+      <c r="J24" s="51">
+        <v>600</v>
+      </c>
+      <c r="K24" s="77">
+        <v>600</v>
+      </c>
+      <c r="L24" s="78">
+        <v>2200</v>
+      </c>
+      <c r="M24" s="49">
+        <f t="shared" si="38"/>
+        <v>100</v>
+      </c>
+      <c r="N24" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="X16" s="59">
+      <c r="O24" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P24" s="75">
+        <f t="shared" si="39"/>
+        <v>30</v>
+      </c>
+      <c r="Q24" s="40">
+        <f t="shared" si="40"/>
+        <v>170</v>
+      </c>
+      <c r="R24" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S24" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="54" t="e">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="60" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="V24" s="55" t="e">
+        <f t="shared" si="41"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W24" s="56">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="56">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="57" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="93"/>
-      <c r="B17" s="50">
-        <v>13</v>
-      </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="52">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="53">
+    <row r="25" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="118" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="90">
+        <f>SUM(D23:D24)</f>
+        <v>1400</v>
+      </c>
+      <c r="E25" s="90">
+        <f t="shared" ref="E25:L25" si="44">SUM(E23:E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="90">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="90">
+        <f t="shared" si="44"/>
+        <v>680</v>
+      </c>
+      <c r="H25" s="90">
+        <f t="shared" si="44"/>
+        <v>400</v>
+      </c>
+      <c r="I25" s="90">
+        <f t="shared" si="44"/>
+        <v>320</v>
+      </c>
+      <c r="J25" s="90">
+        <f t="shared" si="44"/>
+        <v>1000</v>
+      </c>
+      <c r="K25" s="90">
+        <f t="shared" si="44"/>
+        <v>1000</v>
+      </c>
+      <c r="L25" s="90">
+        <f t="shared" si="44"/>
+        <v>2800</v>
+      </c>
+      <c r="M25" s="60">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="N25" s="61">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="59">
         <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P17" s="84">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="43">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="55" t="e">
+        <v>116.2242</v>
+      </c>
+      <c r="P25" s="75">
+        <f t="shared" si="39"/>
+        <v>70</v>
+      </c>
+      <c r="Q25" s="40">
+        <f t="shared" si="40"/>
+        <v>240</v>
+      </c>
+      <c r="R25" s="52" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S17" s="56">
+      <c r="S25" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T17" s="56">
+      <c r="T25" s="53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U17" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V17" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W17" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="59">
+      <c r="U25" s="54" t="e">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="60" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="V25" s="55" t="e">
+        <f t="shared" si="41"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W25" s="56">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="56">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="57" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="93"/>
-      <c r="B18" s="50">
-        <v>14</v>
-      </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="54"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="52">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P18" s="84">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="43">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S18" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V18" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W18" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="60" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B19" s="50">
-        <v>15</v>
-      </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="54"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="52">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="41">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="53">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P19" s="84">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="43">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S19" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V19" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W19" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="60" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="50">
-        <v>16</v>
-      </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="64">
+    <row r="26" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="108"/>
+      <c r="D26" s="92">
+        <f>SUM(D22,D25)</f>
+        <v>2520</v>
+      </c>
+      <c r="E26" s="92">
+        <f t="shared" ref="E26:L26" si="45">SUM(E22,E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="92">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="92">
+        <f t="shared" si="45"/>
+        <v>5920</v>
+      </c>
+      <c r="H26" s="92">
+        <f t="shared" si="45"/>
+        <v>7280</v>
+      </c>
+      <c r="I26" s="92">
+        <f t="shared" si="45"/>
+        <v>7520</v>
+      </c>
+      <c r="J26" s="92">
+        <f t="shared" si="45"/>
+        <v>8320</v>
+      </c>
+      <c r="K26" s="92">
+        <f t="shared" si="45"/>
+        <v>11920</v>
+      </c>
+      <c r="L26" s="92">
+        <f t="shared" si="45"/>
+        <v>13040</v>
+      </c>
+      <c r="M26" s="62">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="65">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="63">
-        <f t="shared" si="1"/>
-        <v>430.99799999999999</v>
-      </c>
-      <c r="P20" s="84">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="43">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S20" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="57" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V20" s="58" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W20" s="59">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="59">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="60" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="113" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="114"/>
-      <c r="D21" s="67">
-        <f>SUM(D5:D20)</f>
-        <v>2480</v>
-      </c>
-      <c r="E21" s="68">
-        <f t="shared" ref="E21:L21" si="21">SUM(E5:E20)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="69">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="70">
-        <f t="shared" si="21"/>
-        <v>4200</v>
-      </c>
-      <c r="H21" s="68">
-        <f t="shared" si="21"/>
-        <v>3760</v>
-      </c>
-      <c r="I21" s="69">
-        <f t="shared" si="21"/>
-        <v>5080</v>
-      </c>
-      <c r="J21" s="70">
-        <f t="shared" si="21"/>
-        <v>7520</v>
-      </c>
-      <c r="K21" s="68">
-        <f t="shared" si="21"/>
-        <v>6120</v>
-      </c>
-      <c r="L21" s="69">
-        <f t="shared" si="21"/>
-        <v>8800</v>
-      </c>
-      <c r="M21" s="67">
-        <f t="shared" si="0"/>
-        <v>949</v>
-      </c>
-      <c r="N21" s="71">
-        <f>SUM(N5:N20)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="69">
-        <f t="shared" ref="O21:Y21" si="22">SUM(O5:O20)</f>
-        <v>6895.9679999999971</v>
-      </c>
-      <c r="P21" s="70">
-        <f t="shared" si="22"/>
-        <v>652</v>
-      </c>
-      <c r="Q21" s="72">
-        <f t="shared" si="22"/>
-        <v>1122</v>
-      </c>
-      <c r="R21" s="73" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S21" s="74">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="74">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="75" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V21" s="76" t="e">
-        <f t="shared" si="22"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W21" s="77">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="77">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="78" t="e">
-        <f t="shared" si="22"/>
+        <v>1413</v>
+      </c>
+      <c r="N26" s="65">
+        <f>SUM(N5:N25)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="63">
+        <f t="shared" ref="O26:Y26" si="46">SUM(O5:O25)</f>
+        <v>2440.7082000000014</v>
+      </c>
+      <c r="P26" s="64">
+        <f t="shared" si="46"/>
+        <v>2326.5500000000002</v>
+      </c>
+      <c r="Q26" s="66">
+        <f t="shared" si="46"/>
+        <v>4025.1</v>
+      </c>
+      <c r="R26" s="67" t="e">
+        <f t="shared" si="46"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S26" s="68">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="68">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="69" t="e">
+        <f t="shared" si="46"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V26" s="70" t="e">
+        <f t="shared" si="46"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W26" s="71">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="71">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="72" t="e">
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:A4"/>
+  <mergeCells count="11">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3292,205 +3897,252 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C3:M12"/>
+  <dimension ref="C3:N13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.36328125" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" customWidth="1"/>
-    <col min="10" max="10" width="38.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.36328125" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="11" max="11" width="38.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="124" t="s">
+    <row r="3" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="K3" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-    </row>
-    <row r="4" spans="3:13" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="95"/>
-      <c r="D4" s="95" t="s">
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+    </row>
+    <row r="4" spans="3:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="83"/>
+      <c r="D4" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="83" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="83" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:13" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="97" t="s">
+    <row r="5" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="85" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="94">
-        <v>227.95</v>
-      </c>
-      <c r="E5" s="94">
-        <v>949</v>
-      </c>
-      <c r="F5" s="98">
-        <f>SUM(D5:E5)</f>
-        <v>1176.95</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="D5" s="96">
+        <v>248.22</v>
+      </c>
+      <c r="E5" s="82">
+        <v>1222</v>
+      </c>
+      <c r="F5" s="82">
+        <v>190</v>
+      </c>
+      <c r="G5" s="95">
+        <f>SUM(D5:F5)</f>
+        <v>1660.22</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="7">
         <v>70</v>
       </c>
-      <c r="L5" s="5">
+      <c r="M5" s="5">
         <v>7794</v>
       </c>
-      <c r="M5" s="6">
-        <f t="shared" ref="M5:M11" si="0">L5/40</f>
+      <c r="N5" s="6">
+        <f t="shared" ref="N5:N11" si="0">M5/40</f>
         <v>194.85</v>
       </c>
     </row>
-    <row r="6" spans="3:13" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="97" t="s">
+    <row r="6" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="96">
         <f>D5*40</f>
-        <v>9118</v>
-      </c>
-      <c r="E6" s="94">
+        <v>9928.7999999999993</v>
+      </c>
+      <c r="E6" s="82">
         <f>E5*40</f>
-        <v>37960</v>
-      </c>
-      <c r="F6" s="98">
-        <f>SUM(D6:E6)</f>
-        <v>47078</v>
-      </c>
-      <c r="J6" s="1" t="s">
+        <v>48880</v>
+      </c>
+      <c r="F6" s="82">
+        <f>F5*40</f>
+        <v>7600</v>
+      </c>
+      <c r="G6" s="95">
+        <f>SUM(D6:F6)</f>
+        <v>66408.800000000003</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>70</v>
       </c>
-      <c r="L6" s="5">
+      <c r="M6" s="5">
         <v>8638</v>
       </c>
-      <c r="M6" s="6">
+      <c r="N6" s="6">
         <f t="shared" si="0"/>
         <v>215.95</v>
       </c>
     </row>
-    <row r="7" spans="3:13" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="J7" s="1" t="s">
+    <row r="7" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" s="94"/>
+      <c r="K7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>70</v>
       </c>
-      <c r="L7" s="5">
+      <c r="M7" s="5">
         <v>153</v>
       </c>
-      <c r="M7" s="6">
+      <c r="N7" s="6">
         <f t="shared" si="0"/>
         <v>3.8250000000000002</v>
       </c>
     </row>
-    <row r="8" spans="3:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="J8" s="1" t="s">
+    <row r="8" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>120</v>
       </c>
-      <c r="L8" s="5">
+      <c r="M8" s="5">
         <v>805</v>
       </c>
-      <c r="M8" s="6">
+      <c r="N8" s="6">
         <f t="shared" si="0"/>
         <v>20.125</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="J9" s="1" t="s">
+    <row r="9" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9">
+        <f>D8-D5</f>
+        <v>-248.22</v>
+      </c>
+      <c r="E9">
+        <f>E8-E5</f>
+        <v>-1222</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>120</v>
       </c>
-      <c r="L9" s="5">
+      <c r="M9" s="5">
         <v>1874</v>
       </c>
-      <c r="M9" s="6">
+      <c r="N9" s="6">
         <f t="shared" si="0"/>
         <v>46.85</v>
       </c>
     </row>
-    <row r="10" spans="3:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="J10" s="1" t="s">
+    <row r="10" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>120</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5">
+      <c r="M10" s="5"/>
+      <c r="N10" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="J11" s="1" t="s">
+    <row r="11" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="133"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="L11" s="5">
+      <c r="M11" s="5">
         <v>72000</v>
       </c>
-      <c r="M11" s="5">
+      <c r="N11" s="5">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
     </row>
-    <row r="12" spans="3:13" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="J12" s="8" t="s">
+    <row r="12" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" s="104" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="95">
+        <v>500.9</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="9">
-        <f>SUM(L5:L11)</f>
+      <c r="L12" s="2"/>
+      <c r="M12" s="8">
+        <f>SUM(M5:M11)</f>
         <v>91264</v>
       </c>
-      <c r="M12" s="10">
-        <f>SUM(M5:M11)</f>
+      <c r="N12" s="9">
+        <f>SUM(N5:N11)</f>
         <v>2281.6</v>
       </c>
     </row>
+    <row r="13" spans="3:14" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="D13" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="106">
+        <v>20036</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="C3:F3"/>
+  <mergeCells count="3">
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3510,13 +4162,13 @@
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="84" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3623,16 +4275,16 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="99"/>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="102"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="89"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3641,7 +4293,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
-            <xm:f>Sheet1!$B$10:$B$18</xm:f>
+            <xm:f>Sheet1!$B$10:$B$22</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B20</xm:sqref>
         </x14:dataValidation>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834887AF-6771-44B1-B42A-213B1EE58C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CF6FD9-2E65-4599-959E-A3E8AF6E555A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -251,6 +251,24 @@
   </si>
   <si>
     <t xml:space="preserve">Last Month Sale </t>
+  </si>
+  <si>
+    <t>Monthly Targets</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons </t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -262,7 +280,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,8 +357,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,8 +422,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -987,6 +1032,104 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1003,7 +1146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1267,6 +1410,98 @@
     <xf numFmtId="1" fontId="7" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1306,46 +1541,25 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1656,7 +1870,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B7:D22"/>
+  <dimension ref="B7:F22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.453125" bestFit="1" customWidth="1"/>
@@ -1669,9 +1883,13 @@
     <col min="10" max="10" width="8.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="80" t="s">
         <v>33</v>
       </c>
@@ -1681,8 +1899,11 @@
       <c r="D9" s="80" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F9" s="107" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1692,15 +1913,18 @@
       <c r="D10" s="79">
         <v>3520247902365</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
@@ -1711,7 +1935,7 @@
         <v>300426949714</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1722,7 +1946,7 @@
         <v>3277876126916</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1733,7 +1957,7 @@
         <v>3520255124113</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1744,7 +1968,7 @@
         <v>3520255124113</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1806,20 +2030,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="120">
+      <c r="B1" s="129">
         <v>46174</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -1841,10 +2065,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="130" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -1877,13 +2101,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="109"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="112" t="s">
+      <c r="M2" s="143"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="113"/>
+      <c r="Q2" s="147"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -1902,8 +2126,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="117"/>
-      <c r="B3" s="122"/>
+      <c r="A3" s="151"/>
+      <c r="B3" s="131"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -1934,29 +2158,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="114" t="s">
+      <c r="M3" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="115"/>
-      <c r="O3" s="116"/>
+      <c r="N3" s="149"/>
+      <c r="O3" s="150"/>
       <c r="P3" s="73"/>
       <c r="Q3" s="74"/>
-      <c r="R3" s="124" t="s">
+      <c r="R3" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="125"/>
-      <c r="T3" s="125"/>
-      <c r="U3" s="126"/>
-      <c r="V3" s="127" t="s">
+      <c r="S3" s="134"/>
+      <c r="T3" s="134"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="128"/>
-      <c r="X3" s="128"/>
-      <c r="Y3" s="129"/>
+      <c r="W3" s="137"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="138"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="117"/>
-      <c r="B4" s="123"/>
+      <c r="A4" s="151"/>
+      <c r="B4" s="132"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2123,7 +2347,9 @@
       <c r="C6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="76"/>
+      <c r="D6" s="76" t="s">
+        <v>81</v>
+      </c>
       <c r="E6" s="77"/>
       <c r="F6" s="78"/>
       <c r="G6" s="51">
@@ -2145,7 +2371,7 @@
         <v>600</v>
       </c>
       <c r="M6" s="49">
-        <f t="shared" ref="M6:M26" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M28" si="0">SUM(D6:L6)/40</f>
         <v>45</v>
       </c>
       <c r="N6" s="39">
@@ -2153,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="50">
-        <f t="shared" ref="O6:O25" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O27" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>116.2242</v>
       </c>
       <c r="P6" s="75">
@@ -2165,15 +2391,15 @@
         <v>54</v>
       </c>
       <c r="R6" s="52" t="e">
-        <f t="shared" ref="R6:R25" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R27" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="53">
-        <f t="shared" ref="S6:S25" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S27" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="53">
-        <f t="shared" ref="T6:T25" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T27" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="54" t="e">
@@ -2204,33 +2430,19 @@
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>39</v>
-      </c>
+      <c r="C7" s="58"/>
       <c r="D7" s="76"/>
       <c r="E7" s="77"/>
       <c r="F7" s="78"/>
-      <c r="G7" s="51">
-        <v>600</v>
-      </c>
-      <c r="H7" s="77">
-        <v>600</v>
-      </c>
-      <c r="I7" s="50">
-        <v>1200</v>
-      </c>
-      <c r="J7" s="51">
-        <v>1800</v>
-      </c>
-      <c r="K7" s="77">
-        <v>1200</v>
-      </c>
-      <c r="L7" s="78">
-        <v>1200</v>
-      </c>
+      <c r="G7" s="51"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="78"/>
       <c r="M7" s="49">
         <f t="shared" ref="M7:M15" si="12">SUM(D7:L7)/40</f>
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="N7" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
@@ -2242,11 +2454,11 @@
       </c>
       <c r="P7" s="75">
         <f t="shared" ref="P7:P15" si="13">SUM(G7:I7)/20</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="40">
         <f t="shared" ref="Q7:Q15" si="14">SUM(J7:L7)/20</f>
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="R7" s="52" t="e">
         <f t="shared" si="4"/>
@@ -2319,7 +2531,7 @@
         <v>140</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N25" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N27" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="50">
@@ -2767,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="54" t="e">
-        <f t="shared" ref="U13:U25" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U27" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="55" t="e">
@@ -2783,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="57" t="e">
-        <f t="shared" ref="Y13:Y25" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y27" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3120,7 +3332,9 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="81"/>
+      <c r="A18" s="81">
+        <v>46184</v>
+      </c>
       <c r="B18" s="47">
         <v>14</v>
       </c>
@@ -3145,7 +3359,7 @@
         <v>80</v>
       </c>
       <c r="M18" s="49">
-        <f t="shared" ref="M18:M21" si="29">SUM(D18:L18)/40</f>
+        <f t="shared" ref="M18:M20" si="29">SUM(D18:L18)/40</f>
         <v>8</v>
       </c>
       <c r="N18" s="39">
@@ -3157,11 +3371,11 @@
         <v>116.2242</v>
       </c>
       <c r="P18" s="75">
-        <f t="shared" ref="P18:P21" si="30">SUM(G18:I18)/20</f>
+        <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
         <v>4</v>
       </c>
       <c r="Q18" s="40">
-        <f t="shared" ref="Q18:Q21" si="31">SUM(J18:L18)/20</f>
+        <f t="shared" ref="Q18:Q20" si="31">SUM(J18:L18)/20</f>
         <v>12</v>
       </c>
       <c r="R18" s="52" t="e">
@@ -3177,28 +3391,30 @@
         <v>0</v>
       </c>
       <c r="U18" s="54" t="e">
-        <f t="shared" ref="U18:U21" si="32">SUM(R18:T18)</f>
+        <f t="shared" ref="U18:U20" si="32">SUM(R18:T18)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V18" s="55" t="e">
-        <f t="shared" ref="V18:V21" si="33">SUM(D18:F18)*$V$3</f>
+        <f t="shared" ref="V18:V20" si="33">SUM(D18:F18)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W18" s="56">
-        <f t="shared" ref="W18:W21" si="34">SUM(G18:I18)*$W$3</f>
+        <f t="shared" ref="W18:W20" si="34">SUM(G18:I18)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X18" s="56">
-        <f t="shared" ref="X18:X21" si="35">SUM(J18:L18)*$X$3</f>
+        <f t="shared" ref="X18:X20" si="35">SUM(J18:L18)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y18" s="57" t="e">
-        <f t="shared" ref="Y18:Y21" si="36">SUM(V18:X18)</f>
+        <f t="shared" ref="Y18:Y20" si="36">SUM(V18:X18)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="81"/>
+      <c r="A19" s="81">
+        <v>46184</v>
+      </c>
       <c r="B19" s="47">
         <v>15</v>
       </c>
@@ -3280,7 +3496,9 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="81"/>
+      <c r="A20" s="81">
+        <v>46184</v>
+      </c>
       <c r="B20" s="47">
         <v>16</v>
       </c>
@@ -3359,24 +3577,38 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="81">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="78"/>
+      <c r="C21" s="108" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="109"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="112">
+        <v>600</v>
+      </c>
+      <c r="H21" s="110">
+        <v>600</v>
+      </c>
+      <c r="I21" s="113">
+        <v>1200</v>
+      </c>
+      <c r="J21" s="112">
+        <v>1800</v>
+      </c>
+      <c r="K21" s="110">
+        <v>1200</v>
+      </c>
+      <c r="L21" s="111">
+        <v>1200</v>
+      </c>
       <c r="M21" s="49">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
+        <v>165</v>
       </c>
       <c r="N21" s="39">
         <f t="shared" si="18"/>
@@ -3387,12 +3619,12 @@
         <v>116.2242</v>
       </c>
       <c r="P21" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
+        <v>120</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
+        <v>210</v>
       </c>
       <c r="R21" s="52" t="e">
         <f t="shared" si="4"/>
@@ -3407,71 +3639,56 @@
         <v>0</v>
       </c>
       <c r="U21" s="54" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="U21:U23" si="40">SUM(R21:T21)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V21" s="55" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="V21:V23" si="41">SUM(D21:F21)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W21" s="56">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="W21:W23" si="42">SUM(G21:I21)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X21" s="56">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="X21:X23" si="43">SUM(J21:L21)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y21" s="57" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="Y21:Y23" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="81"/>
-      <c r="B22" s="130" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="131"/>
-      <c r="D22" s="91">
-        <f>SUM(D6:D21)</f>
-        <v>1120</v>
-      </c>
-      <c r="E22" s="91">
-        <f t="shared" ref="E22:L22" si="37">SUM(E6:E21)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="91">
+      <c r="A22" s="81">
+        <v>46185</v>
+      </c>
+      <c r="B22" s="47">
+        <v>18</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="76"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="50">
+        <v>40</v>
+      </c>
+      <c r="J22" s="51">
+        <v>40</v>
+      </c>
+      <c r="K22" s="77">
+        <v>40</v>
+      </c>
+      <c r="L22" s="78">
+        <v>40</v>
+      </c>
+      <c r="M22" s="49">
         <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="91">
-        <f t="shared" si="37"/>
-        <v>5240</v>
-      </c>
-      <c r="H22" s="91">
-        <f t="shared" si="37"/>
-        <v>6880</v>
-      </c>
-      <c r="I22" s="91">
-        <f t="shared" si="37"/>
-        <v>7200</v>
-      </c>
-      <c r="J22" s="91">
-        <f t="shared" si="37"/>
-        <v>7320</v>
-      </c>
-      <c r="K22" s="91">
-        <f t="shared" si="37"/>
-        <v>10920</v>
-      </c>
-      <c r="L22" s="91">
-        <f t="shared" si="37"/>
-        <v>10240</v>
-      </c>
-      <c r="M22" s="49">
-        <f t="shared" ref="M22:M24" si="38">SUM(D22:L22)/40</f>
-        <v>1223</v>
+        <v>4</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
@@ -3482,12 +3699,12 @@
         <v>116.2242</v>
       </c>
       <c r="P22" s="75">
-        <f t="shared" ref="P22:P25" si="39">SUM(G22:I22)/20</f>
-        <v>966</v>
+        <f t="shared" si="38"/>
+        <v>2</v>
       </c>
       <c r="Q22" s="40">
-        <f t="shared" ref="Q22:Q25" si="40">SUM(J22:L22)/20</f>
-        <v>1424</v>
+        <f t="shared" si="39"/>
+        <v>6</v>
       </c>
       <c r="R22" s="52" t="e">
         <f t="shared" si="4"/>
@@ -3502,60 +3719,46 @@
         <v>0</v>
       </c>
       <c r="U22" s="54" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>#VALUE!</v>
       </c>
       <c r="V22" s="55" t="e">
-        <f t="shared" ref="V22:V25" si="41">SUM(D22:F22)*$V$3</f>
+        <f t="shared" si="41"/>
         <v>#VALUE!</v>
       </c>
       <c r="W22" s="56">
-        <f t="shared" ref="W22:W25" si="42">SUM(G22:I22)*$W$3</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="X22" s="56">
-        <f t="shared" ref="X22:X25" si="43">SUM(J22:L22)*$X$3</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Y22" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="81"/>
+      <c r="A23" s="81">
+        <v>46185</v>
+      </c>
       <c r="B23" s="47">
-        <v>0</v>
-      </c>
-      <c r="C23" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="76">
-        <v>1400</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C23" s="58"/>
+      <c r="D23" s="76"/>
       <c r="E23" s="77"/>
       <c r="F23" s="78"/>
-      <c r="G23" s="51">
-        <v>400</v>
-      </c>
-      <c r="H23" s="77">
-        <v>400</v>
-      </c>
-      <c r="I23" s="50">
-        <v>0</v>
-      </c>
-      <c r="J23" s="51">
-        <v>400</v>
-      </c>
-      <c r="K23" s="77">
-        <v>400</v>
-      </c>
-      <c r="L23" s="78">
-        <v>600</v>
-      </c>
+      <c r="G23" s="51"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="78"/>
       <c r="M23" s="49">
-        <f t="shared" si="38"/>
-        <v>90</v>
+        <f t="shared" si="37"/>
+        <v>0</v>
       </c>
       <c r="N23" s="39">
         <f t="shared" si="18"/>
@@ -3566,12 +3769,12 @@
         <v>116.2242</v>
       </c>
       <c r="P23" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="40">
         <f t="shared" si="39"/>
-        <v>40</v>
-      </c>
-      <c r="Q23" s="40">
-        <f t="shared" si="40"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R23" s="52" t="e">
         <f t="shared" si="4"/>
@@ -3586,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="54" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="40"/>
         <v>#VALUE!</v>
       </c>
       <c r="V23" s="55" t="e">
@@ -3602,43 +3805,55 @@
         <v>0</v>
       </c>
       <c r="Y23" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B24" s="47">
-        <v>0</v>
-      </c>
-      <c r="C24" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="76">
-        <v>0</v>
-      </c>
-      <c r="E24" s="77"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="51">
-        <v>280</v>
-      </c>
-      <c r="H24" s="77">
-        <v>0</v>
-      </c>
-      <c r="I24" s="50">
-        <v>320</v>
-      </c>
-      <c r="J24" s="51">
-        <v>600</v>
-      </c>
-      <c r="K24" s="77">
-        <v>600</v>
-      </c>
-      <c r="L24" s="78">
-        <v>2200</v>
+      <c r="A24" s="81"/>
+      <c r="B24" s="139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="140"/>
+      <c r="D24" s="91">
+        <f>SUM(D6:D23)</f>
+        <v>1120</v>
+      </c>
+      <c r="E24" s="91">
+        <f t="shared" ref="E24:L24" si="45">SUM(E6:E23)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="91">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="91">
+        <f t="shared" si="45"/>
+        <v>5240</v>
+      </c>
+      <c r="H24" s="91">
+        <f t="shared" si="45"/>
+        <v>6880</v>
+      </c>
+      <c r="I24" s="91">
+        <f t="shared" si="45"/>
+        <v>7240</v>
+      </c>
+      <c r="J24" s="91">
+        <f t="shared" si="45"/>
+        <v>7360</v>
+      </c>
+      <c r="K24" s="91">
+        <f t="shared" si="45"/>
+        <v>10960</v>
+      </c>
+      <c r="L24" s="91">
+        <f t="shared" si="45"/>
+        <v>10280</v>
       </c>
       <c r="M24" s="49">
-        <f t="shared" si="38"/>
-        <v>100</v>
+        <f t="shared" ref="M24:M26" si="46">SUM(D24:L24)/40</f>
+        <v>1227</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
@@ -3649,12 +3864,12 @@
         <v>116.2242</v>
       </c>
       <c r="P24" s="75">
-        <f t="shared" si="39"/>
-        <v>30</v>
+        <f t="shared" ref="P24:P27" si="47">SUM(G24:I24)/20</f>
+        <v>968</v>
       </c>
       <c r="Q24" s="40">
-        <f t="shared" si="40"/>
-        <v>170</v>
+        <f t="shared" ref="Q24:Q27" si="48">SUM(J24:L24)/20</f>
+        <v>1430</v>
       </c>
       <c r="R24" s="52" t="e">
         <f t="shared" si="4"/>
@@ -3673,15 +3888,15 @@
         <v>#VALUE!</v>
       </c>
       <c r="V24" s="55" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="V24:V27" si="49">SUM(D24:F24)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W24" s="56">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="W24:W27" si="50">SUM(G24:I24)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X24" s="56">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="X24:X27" si="51">SUM(J24:L24)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y24" s="57" t="e">
@@ -3689,207 +3904,374 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="118" t="s">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A25" s="81"/>
+      <c r="B25" s="47">
+        <v>0</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="76">
+        <v>1400</v>
+      </c>
+      <c r="E25" s="77"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="51">
+        <v>400</v>
+      </c>
+      <c r="H25" s="77">
+        <v>400</v>
+      </c>
+      <c r="I25" s="50">
+        <v>0</v>
+      </c>
+      <c r="J25" s="51">
+        <v>400</v>
+      </c>
+      <c r="K25" s="77">
+        <v>400</v>
+      </c>
+      <c r="L25" s="78">
+        <v>600</v>
+      </c>
+      <c r="M25" s="49">
+        <f t="shared" si="46"/>
+        <v>90</v>
+      </c>
+      <c r="N25" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P25" s="75">
+        <f t="shared" si="47"/>
+        <v>40</v>
+      </c>
+      <c r="Q25" s="40">
+        <f t="shared" si="48"/>
+        <v>70</v>
+      </c>
+      <c r="R25" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S25" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="54" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V25" s="55" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W25" s="56">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="56">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="57" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B26" s="47">
+        <v>0</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="76">
+        <v>0</v>
+      </c>
+      <c r="E26" s="77"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="51">
+        <v>280</v>
+      </c>
+      <c r="H26" s="77">
+        <v>0</v>
+      </c>
+      <c r="I26" s="50">
+        <v>320</v>
+      </c>
+      <c r="J26" s="51">
+        <v>600</v>
+      </c>
+      <c r="K26" s="77">
+        <v>600</v>
+      </c>
+      <c r="L26" s="78">
+        <v>2200</v>
+      </c>
+      <c r="M26" s="49">
+        <f t="shared" si="46"/>
+        <v>100</v>
+      </c>
+      <c r="N26" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="50">
+        <f t="shared" si="1"/>
+        <v>116.2242</v>
+      </c>
+      <c r="P26" s="75">
+        <f t="shared" si="47"/>
+        <v>30</v>
+      </c>
+      <c r="Q26" s="40">
+        <f t="shared" si="48"/>
+        <v>170</v>
+      </c>
+      <c r="R26" s="52" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S26" s="53">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="53">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="54" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V26" s="55" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W26" s="56">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="56">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="57" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="152" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="90">
-        <f>SUM(D23:D24)</f>
+      <c r="C27" s="153"/>
+      <c r="D27" s="90">
+        <f>SUM(D25:D26)</f>
         <v>1400</v>
       </c>
-      <c r="E25" s="90">
-        <f t="shared" ref="E25:L25" si="44">SUM(E23:E24)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="90">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="90">
-        <f t="shared" si="44"/>
+      <c r="E27" s="90">
+        <f t="shared" ref="E27:L27" si="52">SUM(E25:E26)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="90">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="90">
+        <f t="shared" si="52"/>
         <v>680</v>
       </c>
-      <c r="H25" s="90">
-        <f t="shared" si="44"/>
+      <c r="H27" s="90">
+        <f t="shared" si="52"/>
         <v>400</v>
       </c>
-      <c r="I25" s="90">
-        <f t="shared" si="44"/>
+      <c r="I27" s="90">
+        <f t="shared" si="52"/>
         <v>320</v>
       </c>
-      <c r="J25" s="90">
-        <f t="shared" si="44"/>
+      <c r="J27" s="90">
+        <f t="shared" si="52"/>
         <v>1000</v>
       </c>
-      <c r="K25" s="90">
-        <f t="shared" si="44"/>
+      <c r="K27" s="90">
+        <f t="shared" si="52"/>
         <v>1000</v>
       </c>
-      <c r="L25" s="90">
-        <f t="shared" si="44"/>
+      <c r="L27" s="90">
+        <f t="shared" si="52"/>
         <v>2800</v>
       </c>
-      <c r="M25" s="60">
+      <c r="M27" s="60">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="N25" s="61">
+      <c r="N27" s="61">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O25" s="59">
+      <c r="O27" s="59">
         <f t="shared" si="1"/>
         <v>116.2242</v>
       </c>
-      <c r="P25" s="75">
-        <f t="shared" si="39"/>
+      <c r="P27" s="75">
+        <f t="shared" si="47"/>
         <v>70</v>
       </c>
-      <c r="Q25" s="40">
-        <f t="shared" si="40"/>
+      <c r="Q27" s="40">
+        <f t="shared" si="48"/>
         <v>240</v>
       </c>
-      <c r="R25" s="52" t="e">
+      <c r="R27" s="52" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S25" s="53">
+      <c r="S27" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T25" s="53">
+      <c r="T27" s="53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U25" s="54" t="e">
+      <c r="U27" s="54" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V25" s="55" t="e">
-        <f t="shared" si="41"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W25" s="56">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="56">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="57" t="e">
+      <c r="V27" s="55" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W27" s="56">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="56">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="57" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="107" t="s">
+    <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="108"/>
-      <c r="D26" s="92">
-        <f>SUM(D22,D25)</f>
+      <c r="C28" s="142"/>
+      <c r="D28" s="92">
+        <f>SUM(D24,D27)</f>
         <v>2520</v>
       </c>
-      <c r="E26" s="92">
-        <f t="shared" ref="E26:L26" si="45">SUM(E22,E25)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="92">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="92">
-        <f t="shared" si="45"/>
+      <c r="E28" s="92">
+        <f t="shared" ref="E28:L28" si="53">SUM(E24,E27)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="92">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="92">
+        <f t="shared" si="53"/>
         <v>5920</v>
       </c>
-      <c r="H26" s="92">
-        <f t="shared" si="45"/>
+      <c r="H28" s="92">
+        <f t="shared" si="53"/>
         <v>7280</v>
       </c>
-      <c r="I26" s="92">
-        <f t="shared" si="45"/>
-        <v>7520</v>
-      </c>
-      <c r="J26" s="92">
-        <f t="shared" si="45"/>
-        <v>8320</v>
-      </c>
-      <c r="K26" s="92">
-        <f t="shared" si="45"/>
-        <v>11920</v>
-      </c>
-      <c r="L26" s="92">
-        <f t="shared" si="45"/>
-        <v>13040</v>
-      </c>
-      <c r="M26" s="62">
+      <c r="I28" s="92">
+        <f t="shared" si="53"/>
+        <v>7560</v>
+      </c>
+      <c r="J28" s="92">
+        <f t="shared" si="53"/>
+        <v>8360</v>
+      </c>
+      <c r="K28" s="92">
+        <f t="shared" si="53"/>
+        <v>11960</v>
+      </c>
+      <c r="L28" s="92">
+        <f t="shared" si="53"/>
+        <v>13080</v>
+      </c>
+      <c r="M28" s="62">
         <f t="shared" si="0"/>
-        <v>1413</v>
-      </c>
-      <c r="N26" s="65">
-        <f>SUM(N5:N25)</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="63">
-        <f t="shared" ref="O26:Y26" si="46">SUM(O5:O25)</f>
-        <v>2440.7082000000014</v>
-      </c>
-      <c r="P26" s="64">
-        <f t="shared" si="46"/>
-        <v>2326.5500000000002</v>
-      </c>
-      <c r="Q26" s="66">
-        <f t="shared" si="46"/>
-        <v>4025.1</v>
-      </c>
-      <c r="R26" s="67" t="e">
-        <f t="shared" si="46"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S26" s="68">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="68">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="69" t="e">
-        <f t="shared" si="46"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V26" s="70" t="e">
-        <f t="shared" si="46"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W26" s="71">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="71">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="72" t="e">
-        <f t="shared" si="46"/>
+        <v>1417</v>
+      </c>
+      <c r="N28" s="65">
+        <f>SUM(N5:N27)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="63">
+        <f t="shared" ref="O28:Y28" si="54">SUM(O5:O27)</f>
+        <v>2673.1566000000016</v>
+      </c>
+      <c r="P28" s="64">
+        <f t="shared" si="54"/>
+        <v>2330.5500000000002</v>
+      </c>
+      <c r="Q28" s="66">
+        <f t="shared" si="54"/>
+        <v>4037.1</v>
+      </c>
+      <c r="R28" s="67" t="e">
+        <f t="shared" si="54"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S28" s="68">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="68">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="69" t="e">
+        <f t="shared" si="54"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V28" s="70" t="e">
+        <f t="shared" si="54"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W28" s="71">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="71">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="72" t="e">
+        <f t="shared" si="54"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3897,35 +4279,44 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C3:N13"/>
+  <dimension ref="C2:N13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
     <col min="5" max="6" width="12.36328125" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="38.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="132" t="s">
+      <c r="C3" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="132"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="K3" s="132" t="s">
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="159" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="160"/>
+      <c r="K3" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
     </row>
     <row r="4" spans="3:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="83"/>
+      <c r="C4" s="120"/>
       <c r="D4" s="83" t="s">
         <v>53</v>
       </c>
@@ -3935,8 +4326,14 @@
       <c r="F4" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="83" t="s">
+      <c r="G4" s="121" t="s">
         <v>56</v>
+      </c>
+      <c r="H4" s="114" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="115" t="s">
+        <v>80</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -3952,7 +4349,7 @@
       </c>
     </row>
     <row r="5" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="122" t="s">
         <v>58</v>
       </c>
       <c r="D5" s="96">
@@ -3964,9 +4361,16 @@
       <c r="F5" s="82">
         <v>190</v>
       </c>
-      <c r="G5" s="95">
+      <c r="G5" s="123">
         <f>SUM(D5:F5)</f>
         <v>1660.22</v>
+      </c>
+      <c r="H5" s="116">
+        <v>10000</v>
+      </c>
+      <c r="I5" s="117">
+        <f>G5-H5</f>
+        <v>-8339.7800000000007</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -3982,25 +4386,33 @@
         <v>194.85</v>
       </c>
     </row>
-    <row r="6" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="85" t="s">
+    <row r="6" spans="3:14" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C6" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="96">
+      <c r="D6" s="125">
         <f>D5*40</f>
         <v>9928.7999999999993</v>
       </c>
-      <c r="E6" s="82">
+      <c r="E6" s="126">
         <f>E5*40</f>
         <v>48880</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="126">
         <f>F5*40</f>
         <v>7600</v>
       </c>
-      <c r="G6" s="95">
+      <c r="G6" s="127">
         <f>SUM(D6:F6)</f>
         <v>66408.800000000003</v>
+      </c>
+      <c r="H6" s="118">
+        <f>H5*40</f>
+        <v>400000</v>
+      </c>
+      <c r="I6" s="119">
+        <f>G6-H6</f>
+        <v>-333591.2</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -4054,11 +4466,11 @@
       <c r="C9" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="128">
         <f>D8-D5</f>
         <v>-248.22</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="128">
         <f>E8-E5</f>
         <v>-1222</v>
       </c>
@@ -4090,12 +4502,11 @@
       </c>
     </row>
     <row r="11" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D11" s="133" t="s">
+      <c r="C11" s="158" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="133"/>
+      <c r="D11" s="158"/>
       <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -4111,10 +4522,10 @@
       </c>
     </row>
     <row r="12" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D12" s="104" t="s">
+      <c r="C12" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="95">
+      <c r="D12" s="95">
         <v>500.9</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -4131,18 +4542,19 @@
       </c>
     </row>
     <row r="13" spans="3:14" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="D13" s="105" t="s">
+      <c r="C13" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="106">
+      <c r="D13" s="106">
         <v>20036</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="C3:G3"/>
-    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CF6FD9-2E65-4599-959E-A3E8AF6E555A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA740B03-790D-4723-888F-67E12AA686D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -205,9 +205,6 @@
     <t>PACK'S</t>
   </si>
   <si>
-    <t>Primary Report MTD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Client Name </t>
   </si>
   <si>
@@ -268,7 +265,19 @@
     <t>Remaining</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">Gourmet Food </t>
+  </si>
+  <si>
+    <t>3218709-2</t>
+  </si>
+  <si>
+    <t>Stock In Hand (Primary)</t>
+  </si>
+  <si>
+    <t>Expired Pcs</t>
+  </si>
+  <si>
+    <t>Sale End to End</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1271,7 +1280,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1398,9 +1406,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1413,16 +1418,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1466,6 +1461,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1541,9 +1537,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1560,6 +1553,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1870,7 +1866,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B7:F22"/>
+  <dimension ref="B7:F23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.453125" bestFit="1" customWidth="1"/>
@@ -1886,21 +1882,21 @@
     <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="79" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="105" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="80" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="107" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
@@ -1910,7 +1906,7 @@
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="78">
         <v>3520247902365</v>
       </c>
       <c r="F10">
@@ -1931,7 +1927,7 @@
       <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="78">
         <v>300426949714</v>
       </c>
     </row>
@@ -1942,7 +1938,7 @@
       <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="78">
         <v>3277876126916</v>
       </c>
     </row>
@@ -1953,7 +1949,7 @@
       <c r="C14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="79">
+      <c r="D14" s="78">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1964,7 +1960,7 @@
       <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="78">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1975,7 +1971,7 @@
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="78">
         <v>3520268948847</v>
       </c>
     </row>
@@ -1995,31 +1991,42 @@
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="81" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="93" t="s">
+    <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="92" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
         <v>65</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="92" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="93" t="s">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="92" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="93" t="s">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="92" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="93" t="s">
-        <v>69</v>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="92" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="121">
+        <v>3277876231301</v>
       </c>
     </row>
   </sheetData>
@@ -2030,20 +2037,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="129">
+      <c r="B1" s="122">
         <v>46174</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2065,10 +2072,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="123" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2101,13 +2108,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="143"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="146" t="s">
+      <c r="M2" s="136"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="147"/>
+      <c r="Q2" s="140"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2126,8 +2133,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="151"/>
-      <c r="B3" s="131"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="124"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2158,29 +2165,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="148" t="s">
+      <c r="M3" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="149"/>
-      <c r="O3" s="150"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="133" t="s">
+      <c r="N3" s="142"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="134"/>
-      <c r="T3" s="134"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="136" t="s">
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="137"/>
-      <c r="X3" s="137"/>
-      <c r="Y3" s="138"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="130"/>
+      <c r="Y3" s="131"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="151"/>
-      <c r="B4" s="132"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="125"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2252,36 +2259,36 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="81">
+      <c r="A5" s="80">
         <v>46179</v>
       </c>
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="97" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="98">
+      <c r="C5" s="96" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="97">
         <v>1003</v>
       </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="101">
+      <c r="E5" s="98"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="100">
         <v>1613</v>
       </c>
-      <c r="H5" s="99">
+      <c r="H5" s="98">
         <v>2442</v>
       </c>
-      <c r="I5" s="100">
+      <c r="I5" s="99">
         <v>1036</v>
       </c>
-      <c r="J5" s="101">
+      <c r="J5" s="100">
         <v>5269</v>
       </c>
-      <c r="K5" s="99">
+      <c r="K5" s="98">
         <v>3838</v>
       </c>
-      <c r="L5" s="102">
+      <c r="L5" s="101">
         <v>4835</v>
       </c>
       <c r="M5" s="37">
@@ -2294,9 +2301,9 @@
       </c>
       <c r="O5" s="38">
         <f>SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>116.2242</v>
-      </c>
-      <c r="P5" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P5" s="74">
         <f>SUM(G5:I5)/20</f>
         <v>254.55</v>
       </c>
@@ -2338,531 +2345,539 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="81">
+      <c r="A6" s="80">
         <v>46179</v>
       </c>
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="51">
-        <v>240</v>
-      </c>
-      <c r="H6" s="77">
-        <v>240</v>
-      </c>
-      <c r="I6" s="50">
-        <v>240</v>
-      </c>
-      <c r="J6" s="51">
-        <v>240</v>
-      </c>
-      <c r="K6" s="77">
-        <v>240</v>
-      </c>
-      <c r="L6" s="78">
-        <v>600</v>
-      </c>
-      <c r="M6" s="49">
+      <c r="C6" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="75">
+        <v>800</v>
+      </c>
+      <c r="E6" s="76"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="50">
+        <v>800</v>
+      </c>
+      <c r="H6" s="76">
+        <v>800</v>
+      </c>
+      <c r="I6" s="49">
+        <v>800</v>
+      </c>
+      <c r="J6" s="50">
+        <v>800</v>
+      </c>
+      <c r="K6" s="76">
+        <v>800</v>
+      </c>
+      <c r="L6" s="77">
+        <v>800</v>
+      </c>
+      <c r="M6" s="48">
         <f t="shared" ref="M6:M28" si="0">SUM(D6:L6)/40</f>
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="N6" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="50">
+      <c r="O6" s="49">
         <f t="shared" ref="O6:O27" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
-        <v>116.2242</v>
-      </c>
-      <c r="P6" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P6" s="74">
         <f t="shared" ref="P6" si="2">SUM(G6:I6)/20</f>
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="Q6" s="40">
         <f t="shared" ref="Q6" si="3">SUM(J6:L6)/20</f>
-        <v>54</v>
-      </c>
-      <c r="R6" s="52" t="e">
+        <v>120</v>
+      </c>
+      <c r="R6" s="51" t="e">
         <f t="shared" ref="R6:R27" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="52">
         <f t="shared" ref="S6:S27" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
-      <c r="T6" s="53">
+      <c r="T6" s="52">
         <f t="shared" ref="T6:T27" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
-      <c r="U6" s="54" t="e">
+      <c r="U6" s="53" t="e">
         <f t="shared" ref="U6:U12" si="7">SUM(R6:T6)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V6" s="55" t="e">
+      <c r="V6" s="54" t="e">
         <f t="shared" ref="V6" si="8">SUM(D6:F6)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W6" s="56">
+      <c r="W6" s="55">
         <f t="shared" ref="W6" si="9">SUM(G6:I6)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X6" s="56">
+      <c r="X6" s="55">
         <f t="shared" ref="X6" si="10">SUM(J6:L6)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y6" s="57" t="e">
+      <c r="Y6" s="56" t="e">
         <f t="shared" ref="Y6:Y12" si="11">SUM(V6:X6)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="81">
+      <c r="A7" s="80">
         <v>46179</v>
       </c>
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="49">
+      <c r="C7" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="75">
+        <v>80</v>
+      </c>
+      <c r="E7" s="76"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="50">
+        <v>80</v>
+      </c>
+      <c r="H7" s="76">
+        <v>80</v>
+      </c>
+      <c r="I7" s="49">
+        <v>80</v>
+      </c>
+      <c r="J7" s="50">
+        <v>80</v>
+      </c>
+      <c r="K7" s="76">
+        <v>80</v>
+      </c>
+      <c r="L7" s="77">
+        <v>80</v>
+      </c>
+      <c r="M7" s="48">
         <f t="shared" ref="M7:M15" si="12">SUM(D7:L7)/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N7" s="39">
         <f>SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="50">
+      <c r="O7" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P7" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P7" s="74">
         <f t="shared" ref="P7:P15" si="13">SUM(G7:I7)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q7" s="40">
         <f t="shared" ref="Q7:Q15" si="14">SUM(J7:L7)/20</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="52" t="e">
+        <v>12</v>
+      </c>
+      <c r="R7" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S7" s="53">
+      <c r="S7" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T7" s="53">
+      <c r="T7" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U7" s="54" t="e">
+      <c r="U7" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V7" s="55" t="e">
+      <c r="V7" s="54" t="e">
         <f t="shared" ref="V7:V15" si="15">SUM(D7:F7)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W7" s="56">
+      <c r="W7" s="55">
         <f t="shared" ref="W7:W15" si="16">SUM(G7:I7)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X7" s="56">
+      <c r="X7" s="55">
         <f t="shared" ref="X7:X15" si="17">SUM(J7:L7)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="57" t="e">
+      <c r="Y7" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="81">
+      <c r="A8" s="80">
         <v>46181</v>
       </c>
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="76">
-        <v>800</v>
-      </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="51">
-        <v>800</v>
-      </c>
-      <c r="H8" s="77">
-        <v>800</v>
-      </c>
-      <c r="I8" s="50">
-        <v>800</v>
-      </c>
-      <c r="J8" s="51">
-        <v>800</v>
-      </c>
-      <c r="K8" s="77">
-        <v>800</v>
-      </c>
-      <c r="L8" s="78">
-        <v>800</v>
-      </c>
-      <c r="M8" s="49">
+      <c r="C8" s="57" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="75">
+        <v>200</v>
+      </c>
+      <c r="E8" s="76"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="50">
+        <v>200</v>
+      </c>
+      <c r="H8" s="76">
+        <v>200</v>
+      </c>
+      <c r="I8" s="49">
+        <v>200</v>
+      </c>
+      <c r="J8" s="50">
+        <v>200</v>
+      </c>
+      <c r="K8" s="76">
+        <v>200</v>
+      </c>
+      <c r="L8" s="77">
+        <v>200</v>
+      </c>
+      <c r="M8" s="48">
         <f t="shared" si="12"/>
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="N8" s="39">
         <f t="shared" ref="N8:N27" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="50">
+      <c r="O8" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P8" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P8" s="74">
         <f t="shared" si="13"/>
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" si="14"/>
-        <v>120</v>
-      </c>
-      <c r="R8" s="52" t="e">
+        <v>30</v>
+      </c>
+      <c r="R8" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S8" s="53">
+      <c r="S8" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U8" s="54" t="e">
+      <c r="U8" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V8" s="55" t="e">
+      <c r="V8" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W8" s="56">
+      <c r="W8" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X8" s="56">
+      <c r="X8" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y8" s="57" t="e">
+      <c r="Y8" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="81">
+      <c r="A9" s="80">
         <v>46181</v>
       </c>
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="76">
-        <v>80</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="51">
-        <v>80</v>
-      </c>
-      <c r="H9" s="77">
-        <v>80</v>
-      </c>
-      <c r="I9" s="50">
-        <v>80</v>
-      </c>
-      <c r="J9" s="51">
-        <v>80</v>
-      </c>
-      <c r="K9" s="77">
-        <v>80</v>
-      </c>
-      <c r="L9" s="78">
-        <v>80</v>
-      </c>
-      <c r="M9" s="49">
+      <c r="C9" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="75"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50">
+        <v>560</v>
+      </c>
+      <c r="K9" s="76">
+        <v>560</v>
+      </c>
+      <c r="L9" s="77">
+        <v>880</v>
+      </c>
+      <c r="M9" s="48">
         <f t="shared" si="12"/>
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="N9" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O9" s="50">
+      <c r="O9" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P9" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P9" s="74">
         <f t="shared" si="13"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="14"/>
-        <v>12</v>
-      </c>
-      <c r="R9" s="52" t="e">
+        <v>100</v>
+      </c>
+      <c r="R9" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S9" s="53">
+      <c r="S9" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T9" s="53">
+      <c r="T9" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U9" s="54" t="e">
+      <c r="U9" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V9" s="55" t="e">
+      <c r="V9" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W9" s="56">
+      <c r="W9" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X9" s="56">
+      <c r="X9" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y9" s="57" t="e">
+      <c r="Y9" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="81">
+      <c r="A10" s="80">
         <v>46182</v>
       </c>
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="76">
-        <v>0</v>
-      </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="51">
-        <v>280</v>
-      </c>
-      <c r="H10" s="77">
-        <v>0</v>
-      </c>
-      <c r="I10" s="50">
-        <v>320</v>
-      </c>
-      <c r="J10" s="51">
-        <v>600</v>
-      </c>
-      <c r="K10" s="77">
-        <v>600</v>
-      </c>
-      <c r="L10" s="78">
-        <v>2200</v>
-      </c>
-      <c r="M10" s="49">
+      <c r="C10" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="75"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="50">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="76">
+        <v>1200</v>
+      </c>
+      <c r="I10" s="49">
+        <v>1800</v>
+      </c>
+      <c r="J10" s="50">
+        <v>2400</v>
+      </c>
+      <c r="K10" s="76">
+        <v>1800</v>
+      </c>
+      <c r="L10" s="77">
+        <v>1800</v>
+      </c>
+      <c r="M10" s="48">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="N10" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O10" s="50">
+      <c r="O10" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P10" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P10" s="74">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="14"/>
-        <v>170</v>
-      </c>
-      <c r="R10" s="52" t="e">
+        <v>300</v>
+      </c>
+      <c r="R10" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S10" s="53">
+      <c r="S10" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T10" s="53">
+      <c r="T10" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U10" s="54" t="e">
+      <c r="U10" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V10" s="55" t="e">
+      <c r="V10" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W10" s="56">
+      <c r="W10" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X10" s="56">
+      <c r="X10" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="57" t="e">
+      <c r="Y10" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="81">
+      <c r="A11" s="80">
         <v>46182</v>
       </c>
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="76">
-        <v>200</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="51">
-        <v>200</v>
-      </c>
-      <c r="H11" s="77">
-        <v>200</v>
-      </c>
-      <c r="I11" s="50">
-        <v>200</v>
-      </c>
-      <c r="J11" s="51">
-        <v>200</v>
-      </c>
-      <c r="K11" s="77">
-        <v>200</v>
-      </c>
-      <c r="L11" s="78">
-        <v>200</v>
-      </c>
-      <c r="M11" s="49">
+      <c r="C11" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="75"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="76">
+        <v>40</v>
+      </c>
+      <c r="I11" s="49">
+        <v>40</v>
+      </c>
+      <c r="J11" s="50">
+        <v>40</v>
+      </c>
+      <c r="K11" s="76">
+        <v>40</v>
+      </c>
+      <c r="L11" s="77">
+        <v>40</v>
+      </c>
+      <c r="M11" s="48">
         <f t="shared" si="12"/>
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="N11" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O11" s="50">
+      <c r="O11" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P11" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P11" s="74">
         <f t="shared" si="13"/>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="14"/>
-        <v>30</v>
-      </c>
-      <c r="R11" s="52" t="e">
+        <v>6</v>
+      </c>
+      <c r="R11" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S11" s="53">
+      <c r="S11" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T11" s="53">
+      <c r="T11" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U11" s="54" t="e">
+      <c r="U11" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V11" s="55" t="e">
+      <c r="V11" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W11" s="56">
+      <c r="W11" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X11" s="56">
+      <c r="X11" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y11" s="57" t="e">
+      <c r="Y11" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="81">
+      <c r="A12" s="80">
         <v>46182</v>
       </c>
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="76"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="51">
-        <v>560</v>
-      </c>
-      <c r="K12" s="77">
-        <v>560</v>
-      </c>
-      <c r="L12" s="78">
-        <v>880</v>
-      </c>
-      <c r="M12" s="49">
+      <c r="C12" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="50">
+        <v>400</v>
+      </c>
+      <c r="H12" s="76">
+        <v>200</v>
+      </c>
+      <c r="I12" s="49">
+        <v>400</v>
+      </c>
+      <c r="J12" s="50">
+        <v>400</v>
+      </c>
+      <c r="K12" s="76">
+        <v>200</v>
+      </c>
+      <c r="L12" s="77">
+        <v>400</v>
+      </c>
+      <c r="M12" s="48">
         <f t="shared" si="12"/>
         <v>50</v>
       </c>
@@ -2870,893 +2885,883 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O12" s="50">
+      <c r="O12" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P12" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P12" s="74">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="14"/>
-        <v>100</v>
-      </c>
-      <c r="R12" s="52" t="e">
+        <v>50</v>
+      </c>
+      <c r="R12" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S12" s="53">
+      <c r="S12" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T12" s="53">
+      <c r="T12" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U12" s="54" t="e">
+      <c r="U12" s="53" t="e">
         <f t="shared" si="7"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V12" s="55" t="e">
+      <c r="V12" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W12" s="56">
+      <c r="W12" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X12" s="56">
+      <c r="X12" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="57" t="e">
+      <c r="Y12" s="56" t="e">
         <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="81">
+      <c r="A13" s="80">
         <v>46183</v>
       </c>
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="76"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="51">
-        <v>1200</v>
-      </c>
-      <c r="H13" s="77">
-        <v>1200</v>
-      </c>
-      <c r="I13" s="50">
-        <v>1800</v>
-      </c>
-      <c r="J13" s="51">
-        <v>2400</v>
-      </c>
-      <c r="K13" s="77">
-        <v>1800</v>
-      </c>
-      <c r="L13" s="78">
-        <v>1800</v>
-      </c>
-      <c r="M13" s="49">
+      <c r="C13" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="75"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="50">
+        <v>40</v>
+      </c>
+      <c r="H13" s="76">
+        <v>40</v>
+      </c>
+      <c r="I13" s="49">
+        <v>40</v>
+      </c>
+      <c r="J13" s="50">
+        <v>40</v>
+      </c>
+      <c r="K13" s="76">
+        <v>40</v>
+      </c>
+      <c r="L13" s="77">
+        <v>40</v>
+      </c>
+      <c r="M13" s="48">
         <f t="shared" si="12"/>
-        <v>255</v>
+        <v>6</v>
       </c>
       <c r="N13" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O13" s="50">
+      <c r="O13" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P13" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P13" s="74">
         <f t="shared" si="13"/>
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="14"/>
-        <v>300</v>
-      </c>
-      <c r="R13" s="52" t="e">
+        <v>6</v>
+      </c>
+      <c r="R13" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S13" s="53">
+      <c r="S13" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T13" s="53">
+      <c r="T13" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U13" s="54" t="e">
+      <c r="U13" s="53" t="e">
         <f t="shared" ref="U13:U27" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V13" s="55" t="e">
+      <c r="V13" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W13" s="56">
+      <c r="W13" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X13" s="56">
+      <c r="X13" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y13" s="57" t="e">
+      <c r="Y13" s="56" t="e">
         <f t="shared" ref="Y13:Y27" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="81">
+      <c r="A14" s="80">
         <v>46183</v>
       </c>
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="77">
-        <v>40</v>
-      </c>
-      <c r="I14" s="50">
-        <v>40</v>
-      </c>
-      <c r="J14" s="51">
-        <v>40</v>
-      </c>
-      <c r="K14" s="77">
-        <v>40</v>
-      </c>
-      <c r="L14" s="78">
-        <v>40</v>
-      </c>
-      <c r="M14" s="49">
+      <c r="C14" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="75"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="50">
+        <v>240</v>
+      </c>
+      <c r="H14" s="76">
+        <v>240</v>
+      </c>
+      <c r="I14" s="49">
+        <v>240</v>
+      </c>
+      <c r="J14" s="50">
+        <v>240</v>
+      </c>
+      <c r="K14" s="76">
+        <v>240</v>
+      </c>
+      <c r="L14" s="77">
+        <v>600</v>
+      </c>
+      <c r="M14" s="48">
         <f t="shared" si="12"/>
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N14" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O14" s="50">
+      <c r="O14" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P14" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P14" s="74">
+        <f t="shared" si="13"/>
+        <v>36</v>
+      </c>
+      <c r="Q14" s="40">
+        <f t="shared" si="14"/>
+        <v>54</v>
+      </c>
+      <c r="R14" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S14" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V14" s="54" t="e">
+        <f t="shared" si="15"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W14" s="55">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X14" s="55">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="80">
+        <v>46183</v>
+      </c>
+      <c r="B15" s="47">
+        <v>11</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="49">
+        <v>80</v>
+      </c>
+      <c r="J15" s="50">
+        <v>80</v>
+      </c>
+      <c r="K15" s="76">
+        <v>80</v>
+      </c>
+      <c r="L15" s="77">
+        <v>80</v>
+      </c>
+      <c r="M15" s="48">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="N15" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P15" s="74">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="Q14" s="40">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="R14" s="52" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S14" s="53">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="53">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="54" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V14" s="55" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W14" s="56">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="56">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="57" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="81">
-        <v>46183</v>
-      </c>
-      <c r="B15" s="47">
-        <v>11</v>
-      </c>
-      <c r="C15" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="76"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="51">
-        <v>400</v>
-      </c>
-      <c r="H15" s="77">
-        <v>200</v>
-      </c>
-      <c r="I15" s="50">
-        <v>400</v>
-      </c>
-      <c r="J15" s="51">
-        <v>400</v>
-      </c>
-      <c r="K15" s="77">
-        <v>200</v>
-      </c>
-      <c r="L15" s="78">
-        <v>400</v>
-      </c>
-      <c r="M15" s="49">
-        <f t="shared" si="12"/>
-        <v>50</v>
-      </c>
-      <c r="N15" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="50">
-        <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P15" s="75">
-        <f t="shared" si="13"/>
-        <v>50</v>
-      </c>
       <c r="Q15" s="40">
         <f t="shared" si="14"/>
-        <v>50</v>
-      </c>
-      <c r="R15" s="52" t="e">
+        <v>12</v>
+      </c>
+      <c r="R15" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S15" s="53">
+      <c r="S15" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T15" s="53">
+      <c r="T15" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U15" s="54" t="e">
+      <c r="U15" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V15" s="55" t="e">
+      <c r="V15" s="54" t="e">
         <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W15" s="56">
+      <c r="W15" s="55">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X15" s="56">
+      <c r="X15" s="55">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Y15" s="57" t="e">
+      <c r="Y15" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="81">
+      <c r="A16" s="80">
         <v>46184</v>
       </c>
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="51">
+      <c r="C16" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="75"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="50">
+        <v>80</v>
+      </c>
+      <c r="H16" s="76">
+        <v>80</v>
+      </c>
+      <c r="I16" s="49">
+        <v>120</v>
+      </c>
+      <c r="J16" s="50">
+        <v>80</v>
+      </c>
+      <c r="K16" s="76">
         <v>40</v>
       </c>
-      <c r="H16" s="77">
-        <v>40</v>
-      </c>
-      <c r="I16" s="50">
-        <v>40</v>
-      </c>
-      <c r="J16" s="51">
-        <v>40</v>
-      </c>
-      <c r="K16" s="77">
-        <v>40</v>
-      </c>
-      <c r="L16" s="78">
-        <v>40</v>
-      </c>
-      <c r="M16" s="49">
+      <c r="L16" s="77">
+        <v>80</v>
+      </c>
+      <c r="M16" s="48">
         <f t="shared" ref="M16:M17" si="21">SUM(D16:L16)/40</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N16" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O16" s="50">
+      <c r="O16" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P16" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P16" s="74">
         <f t="shared" ref="P16:P17" si="22">SUM(G16:I16)/20</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" ref="Q16:Q17" si="23">SUM(J16:L16)/20</f>
-        <v>6</v>
-      </c>
-      <c r="R16" s="52" t="e">
+        <v>10</v>
+      </c>
+      <c r="R16" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S16" s="53">
+      <c r="S16" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T16" s="53">
+      <c r="T16" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U16" s="54" t="e">
+      <c r="U16" s="53" t="e">
         <f t="shared" ref="U16:U17" si="24">SUM(R16:T16)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V16" s="55" t="e">
+      <c r="V16" s="54" t="e">
         <f t="shared" ref="V16:V17" si="25">SUM(D16:F16)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W16" s="56">
+      <c r="W16" s="55">
         <f t="shared" ref="W16:W17" si="26">SUM(G16:I16)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X16" s="56">
+      <c r="X16" s="55">
         <f t="shared" ref="X16:X17" si="27">SUM(J16:L16)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="57" t="e">
+      <c r="Y16" s="56" t="e">
         <f t="shared" ref="Y16:Y17" si="28">SUM(V16:X16)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="81">
+      <c r="A17" s="80">
         <v>46184</v>
       </c>
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="51">
-        <v>1280</v>
-      </c>
-      <c r="H17" s="77">
-        <v>3400</v>
-      </c>
-      <c r="I17" s="50">
-        <v>1840</v>
-      </c>
-      <c r="J17" s="51"/>
-      <c r="K17" s="77">
-        <v>5040</v>
-      </c>
-      <c r="L17" s="78">
-        <v>1760</v>
-      </c>
-      <c r="M17" s="49">
+      <c r="C17" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="75">
+        <v>40</v>
+      </c>
+      <c r="E17" s="76"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="50">
+        <v>40</v>
+      </c>
+      <c r="H17" s="76"/>
+      <c r="I17" s="49">
+        <v>40</v>
+      </c>
+      <c r="J17" s="50"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="77">
+        <v>80</v>
+      </c>
+      <c r="M17" s="48">
         <f t="shared" si="21"/>
-        <v>333</v>
+        <v>5</v>
       </c>
       <c r="N17" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O17" s="50">
+      <c r="O17" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P17" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P17" s="74">
         <f t="shared" si="22"/>
-        <v>326</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="23"/>
-        <v>340</v>
-      </c>
-      <c r="R17" s="52" t="e">
+        <v>4</v>
+      </c>
+      <c r="R17" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S17" s="53">
+      <c r="S17" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T17" s="53">
+      <c r="T17" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U17" s="54" t="e">
+      <c r="U17" s="53" t="e">
         <f t="shared" si="24"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V17" s="55" t="e">
+      <c r="V17" s="54" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W17" s="56">
+      <c r="W17" s="55">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="X17" s="56">
+      <c r="X17" s="55">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="57" t="e">
+      <c r="Y17" s="56" t="e">
         <f t="shared" si="28"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="81">
+      <c r="A18" s="80">
         <v>46184</v>
       </c>
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="58" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="76"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="50">
-        <v>80</v>
-      </c>
-      <c r="J18" s="51">
-        <v>80</v>
-      </c>
-      <c r="K18" s="77">
-        <v>80</v>
-      </c>
-      <c r="L18" s="78">
-        <v>80</v>
-      </c>
-      <c r="M18" s="49">
+      <c r="C18" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="75"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="50">
+        <v>600</v>
+      </c>
+      <c r="H18" s="76">
+        <v>597</v>
+      </c>
+      <c r="I18" s="49">
+        <v>797</v>
+      </c>
+      <c r="J18" s="50">
+        <v>1597</v>
+      </c>
+      <c r="K18" s="76">
+        <v>1184</v>
+      </c>
+      <c r="L18" s="77">
+        <v>1199</v>
+      </c>
+      <c r="M18" s="48">
         <f t="shared" ref="M18:M20" si="29">SUM(D18:L18)/40</f>
-        <v>8</v>
+        <v>149.35</v>
       </c>
       <c r="N18" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O18" s="50">
+      <c r="O18" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P18" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P18" s="74">
         <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
-        <v>4</v>
+        <v>99.7</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" ref="Q18:Q20" si="31">SUM(J18:L18)/20</f>
-        <v>12</v>
-      </c>
-      <c r="R18" s="52" t="e">
+        <v>199</v>
+      </c>
+      <c r="R18" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S18" s="53">
+      <c r="S18" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T18" s="53">
+      <c r="T18" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U18" s="54" t="e">
+      <c r="U18" s="53" t="e">
         <f t="shared" ref="U18:U20" si="32">SUM(R18:T18)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V18" s="55" t="e">
+      <c r="V18" s="54" t="e">
         <f t="shared" ref="V18:V20" si="33">SUM(D18:F18)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W18" s="56">
+      <c r="W18" s="55">
         <f t="shared" ref="W18:W20" si="34">SUM(G18:I18)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X18" s="56">
+      <c r="X18" s="55">
         <f t="shared" ref="X18:X20" si="35">SUM(J18:L18)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="57" t="e">
+      <c r="Y18" s="56" t="e">
         <f t="shared" ref="Y18:Y20" si="36">SUM(V18:X18)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="81">
+      <c r="A19" s="80">
         <v>46184</v>
       </c>
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="76"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="51">
-        <v>80</v>
-      </c>
-      <c r="H19" s="77">
-        <v>80</v>
-      </c>
-      <c r="I19" s="50">
-        <v>120</v>
-      </c>
-      <c r="J19" s="51">
-        <v>80</v>
-      </c>
-      <c r="K19" s="77">
+      <c r="C19" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="75"/>
+      <c r="E19" s="76"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="49">
         <v>40</v>
       </c>
-      <c r="L19" s="78">
-        <v>80</v>
-      </c>
-      <c r="M19" s="49">
+      <c r="J19" s="50">
+        <v>40</v>
+      </c>
+      <c r="K19" s="76">
+        <v>40</v>
+      </c>
+      <c r="L19" s="77">
+        <v>40</v>
+      </c>
+      <c r="M19" s="48">
         <f t="shared" si="29"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N19" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O19" s="50">
+      <c r="O19" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P19" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P19" s="74">
         <f t="shared" si="30"/>
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="31"/>
-        <v>10</v>
-      </c>
-      <c r="R19" s="52" t="e">
+        <v>6</v>
+      </c>
+      <c r="R19" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S19" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T19" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U19" s="54" t="e">
+      <c r="U19" s="53" t="e">
         <f t="shared" si="32"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V19" s="55" t="e">
+      <c r="V19" s="54" t="e">
         <f t="shared" si="33"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W19" s="56">
+      <c r="W19" s="55">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="X19" s="56">
+      <c r="X19" s="55">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="57" t="e">
+      <c r="Y19" s="56" t="e">
         <f t="shared" si="36"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="81">
+      <c r="A20" s="80">
         <v>46184</v>
       </c>
       <c r="B20" s="47">
         <v>16</v>
       </c>
-      <c r="C20" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="76">
+      <c r="C20" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="75"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="50">
         <v>40</v>
       </c>
-      <c r="E20" s="77"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="51">
+      <c r="H20" s="76">
         <v>40</v>
       </c>
-      <c r="H20" s="77"/>
-      <c r="I20" s="50">
+      <c r="I20" s="49">
         <v>40</v>
       </c>
-      <c r="J20" s="51"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78">
-        <v>80</v>
-      </c>
-      <c r="M20" s="49">
+      <c r="J20" s="50">
+        <v>40</v>
+      </c>
+      <c r="K20" s="76">
+        <v>40</v>
+      </c>
+      <c r="L20" s="77">
+        <v>40</v>
+      </c>
+      <c r="M20" s="48">
         <f t="shared" si="29"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N20" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O20" s="50">
+      <c r="O20" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P20" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P20" s="74">
         <f t="shared" si="30"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="31"/>
-        <v>4</v>
-      </c>
-      <c r="R20" s="52" t="e">
+        <v>6</v>
+      </c>
+      <c r="R20" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S20" s="53">
+      <c r="S20" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T20" s="53">
+      <c r="T20" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U20" s="54" t="e">
+      <c r="U20" s="53" t="e">
         <f t="shared" si="32"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V20" s="55" t="e">
+      <c r="V20" s="54" t="e">
         <f t="shared" si="33"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W20" s="56">
+      <c r="W20" s="55">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="X20" s="56">
+      <c r="X20" s="55">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="57" t="e">
+      <c r="Y20" s="56" t="e">
         <f t="shared" si="36"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="81">
+      <c r="A21" s="80">
         <v>46185</v>
       </c>
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="108" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="109"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="112">
-        <v>600</v>
-      </c>
-      <c r="H21" s="110">
-        <v>600</v>
-      </c>
-      <c r="I21" s="113">
-        <v>1200</v>
-      </c>
-      <c r="J21" s="112">
-        <v>1800</v>
-      </c>
-      <c r="K21" s="110">
-        <v>1200</v>
-      </c>
-      <c r="L21" s="111">
-        <v>1200</v>
-      </c>
-      <c r="M21" s="49">
+      <c r="C21" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="75"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="50">
+        <v>120</v>
+      </c>
+      <c r="H21" s="76">
+        <v>120</v>
+      </c>
+      <c r="I21" s="49">
+        <v>120</v>
+      </c>
+      <c r="J21" s="50">
+        <v>120</v>
+      </c>
+      <c r="K21" s="76">
+        <v>120</v>
+      </c>
+      <c r="L21" s="77">
+        <v>120</v>
+      </c>
+      <c r="M21" s="48">
         <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
-        <v>165</v>
+        <v>18</v>
       </c>
       <c r="N21" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O21" s="50">
+      <c r="O21" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P21" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P21" s="74">
         <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
-        <v>210</v>
-      </c>
-      <c r="R21" s="52" t="e">
+        <v>18</v>
+      </c>
+      <c r="R21" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S21" s="53">
+      <c r="S21" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T21" s="53">
+      <c r="T21" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U21" s="54" t="e">
+      <c r="U21" s="53" t="e">
         <f t="shared" ref="U21:U23" si="40">SUM(R21:T21)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="V21" s="55" t="e">
+      <c r="V21" s="54" t="e">
         <f t="shared" ref="V21:V23" si="41">SUM(D21:F21)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W21" s="56">
+      <c r="W21" s="55">
         <f t="shared" ref="W21:W23" si="42">SUM(G21:I21)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X21" s="56">
+      <c r="X21" s="55">
         <f t="shared" ref="X21:X23" si="43">SUM(J21:L21)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="57" t="e">
+      <c r="Y21" s="56" t="e">
         <f t="shared" ref="Y21:Y23" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="81">
+      <c r="A22" s="80">
         <v>46185</v>
       </c>
       <c r="B22" s="47">
         <v>18</v>
       </c>
-      <c r="C22" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="76"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="50">
-        <v>40</v>
-      </c>
-      <c r="J22" s="51">
-        <v>40</v>
-      </c>
-      <c r="K22" s="77">
-        <v>40</v>
-      </c>
-      <c r="L22" s="78">
-        <v>40</v>
-      </c>
-      <c r="M22" s="49">
+      <c r="C22" s="57"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="48">
         <f t="shared" si="37"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O22" s="50">
+      <c r="O22" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P22" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P22" s="74">
         <f t="shared" si="38"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="39"/>
-        <v>6</v>
-      </c>
-      <c r="R22" s="52" t="e">
+        <v>0</v>
+      </c>
+      <c r="R22" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S22" s="53">
+      <c r="S22" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T22" s="53">
+      <c r="T22" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U22" s="54" t="e">
+      <c r="U22" s="53" t="e">
         <f t="shared" si="40"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V22" s="55" t="e">
+      <c r="V22" s="54" t="e">
         <f t="shared" si="41"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W22" s="56">
+      <c r="W22" s="55">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="X22" s="56">
+      <c r="X22" s="55">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="Y22" s="57" t="e">
+      <c r="Y22" s="56" t="e">
         <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="81">
+      <c r="A23" s="80">
         <v>46185</v>
       </c>
       <c r="B23" s="47">
         <v>19</v>
       </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="49">
+      <c r="C23" s="57"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="48">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
@@ -3764,11 +3769,11 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O23" s="50">
+      <c r="O23" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P23" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P23" s="74">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
@@ -3776,355 +3781,353 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="R23" s="52" t="e">
+      <c r="R23" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S23" s="53">
+      <c r="S23" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T23" s="53">
+      <c r="T23" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U23" s="54" t="e">
+      <c r="U23" s="53" t="e">
         <f t="shared" si="40"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V23" s="55" t="e">
+      <c r="V23" s="54" t="e">
         <f t="shared" si="41"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W23" s="56">
+      <c r="W23" s="55">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="X23" s="56">
+      <c r="X23" s="55">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="57" t="e">
+      <c r="Y23" s="56" t="e">
         <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="81"/>
-      <c r="B24" s="139" t="s">
+      <c r="A24" s="80"/>
+      <c r="B24" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="140"/>
-      <c r="D24" s="91">
+      <c r="C24" s="133"/>
+      <c r="D24" s="90">
         <f>SUM(D6:D23)</f>
         <v>1120</v>
       </c>
-      <c r="E24" s="91">
+      <c r="E24" s="90">
         <f t="shared" ref="E24:L24" si="45">SUM(E6:E23)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="91">
+      <c r="F24" s="90">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="G24" s="91">
+      <c r="G24" s="90">
         <f t="shared" si="45"/>
-        <v>5240</v>
-      </c>
-      <c r="H24" s="91">
+        <v>3840</v>
+      </c>
+      <c r="H24" s="90">
         <f t="shared" si="45"/>
-        <v>6880</v>
-      </c>
-      <c r="I24" s="91">
+        <v>3637</v>
+      </c>
+      <c r="I24" s="90">
         <f t="shared" si="45"/>
-        <v>7240</v>
-      </c>
-      <c r="J24" s="91">
+        <v>4837</v>
+      </c>
+      <c r="J24" s="90">
         <f t="shared" si="45"/>
-        <v>7360</v>
-      </c>
-      <c r="K24" s="91">
+        <v>6717</v>
+      </c>
+      <c r="K24" s="90">
         <f t="shared" si="45"/>
-        <v>10960</v>
-      </c>
-      <c r="L24" s="91">
+        <v>5464</v>
+      </c>
+      <c r="L24" s="90">
         <f t="shared" si="45"/>
-        <v>10280</v>
-      </c>
-      <c r="M24" s="49">
+        <v>6479</v>
+      </c>
+      <c r="M24" s="48">
         <f t="shared" ref="M24:M26" si="46">SUM(D24:L24)/40</f>
-        <v>1227</v>
+        <v>802.35</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O24" s="50">
+      <c r="O24" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P24" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P24" s="74">
         <f t="shared" ref="P24:P27" si="47">SUM(G24:I24)/20</f>
-        <v>968</v>
+        <v>615.70000000000005</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" ref="Q24:Q27" si="48">SUM(J24:L24)/20</f>
-        <v>1430</v>
-      </c>
-      <c r="R24" s="52" t="e">
+        <v>933</v>
+      </c>
+      <c r="R24" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S24" s="53">
+      <c r="S24" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T24" s="53">
+      <c r="T24" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U24" s="54" t="e">
+      <c r="U24" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V24" s="55" t="e">
+      <c r="V24" s="54" t="e">
         <f t="shared" ref="V24:V27" si="49">SUM(D24:F24)*$V$3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W24" s="56">
+      <c r="W24" s="55">
         <f t="shared" ref="W24:W27" si="50">SUM(G24:I24)*$W$3</f>
         <v>0</v>
       </c>
-      <c r="X24" s="56">
+      <c r="X24" s="55">
         <f t="shared" ref="X24:X27" si="51">SUM(J24:L24)*$X$3</f>
         <v>0</v>
       </c>
-      <c r="Y24" s="57" t="e">
+      <c r="Y24" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="81"/>
+      <c r="A25" s="80"/>
       <c r="B25" s="47">
         <v>0</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="75"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="50">
+        <v>280</v>
+      </c>
+      <c r="H25" s="76">
+        <v>0</v>
+      </c>
+      <c r="I25" s="49">
+        <v>320</v>
+      </c>
+      <c r="J25" s="50">
+        <v>600</v>
+      </c>
+      <c r="K25" s="76">
+        <v>600</v>
+      </c>
+      <c r="L25" s="77">
+        <v>2200</v>
+      </c>
+      <c r="M25" s="48">
+        <f t="shared" si="46"/>
+        <v>100</v>
+      </c>
+      <c r="N25" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P25" s="74">
+        <f t="shared" si="47"/>
+        <v>30</v>
+      </c>
+      <c r="Q25" s="40">
+        <f t="shared" si="48"/>
+        <v>170</v>
+      </c>
+      <c r="R25" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S25" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V25" s="54" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W25" s="55">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="55">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B26" s="47">
+        <v>1</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="76">
+      <c r="D26" s="75">
         <v>1400</v>
       </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="51">
+      <c r="E26" s="76"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="50">
         <v>400</v>
       </c>
-      <c r="H25" s="77">
+      <c r="H26" s="76">
         <v>400</v>
       </c>
-      <c r="I25" s="50">
-        <v>0</v>
-      </c>
-      <c r="J25" s="51">
+      <c r="I26" s="49">
+        <v>0</v>
+      </c>
+      <c r="J26" s="50">
         <v>400</v>
       </c>
-      <c r="K25" s="77">
+      <c r="K26" s="76">
         <v>400</v>
       </c>
-      <c r="L25" s="78">
+      <c r="L26" s="77">
         <v>600</v>
       </c>
-      <c r="M25" s="49">
+      <c r="M26" s="48">
         <f t="shared" si="46"/>
         <v>90</v>
       </c>
-      <c r="N25" s="39">
+      <c r="N26" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O25" s="50">
+      <c r="O26" s="49">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P25" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P26" s="74">
         <f t="shared" si="47"/>
         <v>40</v>
       </c>
-      <c r="Q25" s="40">
+      <c r="Q26" s="40">
         <f t="shared" si="48"/>
         <v>70</v>
       </c>
-      <c r="R25" s="52" t="e">
+      <c r="R26" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S25" s="53">
+      <c r="S26" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T25" s="53">
+      <c r="T26" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U25" s="54" t="e">
+      <c r="U26" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V25" s="55" t="e">
+      <c r="V26" s="54" t="e">
         <f t="shared" si="49"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W25" s="56">
+      <c r="W26" s="55">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="X25" s="56">
+      <c r="X26" s="55">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="Y25" s="57" t="e">
+      <c r="Y26" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B26" s="47">
-        <v>0</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="76">
-        <v>0</v>
-      </c>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="51">
-        <v>280</v>
-      </c>
-      <c r="H26" s="77">
-        <v>0</v>
-      </c>
-      <c r="I26" s="50">
-        <v>320</v>
-      </c>
-      <c r="J26" s="51">
-        <v>600</v>
-      </c>
-      <c r="K26" s="77">
-        <v>600</v>
-      </c>
-      <c r="L26" s="78">
-        <v>2200</v>
-      </c>
-      <c r="M26" s="49">
-        <f t="shared" si="46"/>
-        <v>100</v>
-      </c>
-      <c r="N26" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="50">
-        <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P26" s="75">
-        <f t="shared" si="47"/>
-        <v>30</v>
-      </c>
-      <c r="Q26" s="40">
-        <f t="shared" si="48"/>
-        <v>170</v>
-      </c>
-      <c r="R26" s="52" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S26" s="53">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="53">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="54" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V26" s="55" t="e">
-        <f t="shared" si="49"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W26" s="56">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="56">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="57" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
     <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="152" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="153"/>
-      <c r="D27" s="90">
+      <c r="B27" s="145" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="146"/>
+      <c r="D27" s="89">
         <f>SUM(D25:D26)</f>
         <v>1400</v>
       </c>
-      <c r="E27" s="90">
+      <c r="E27" s="89">
         <f t="shared" ref="E27:L27" si="52">SUM(E25:E26)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="89">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="G27" s="90">
+      <c r="G27" s="89">
         <f t="shared" si="52"/>
         <v>680</v>
       </c>
-      <c r="H27" s="90">
+      <c r="H27" s="89">
         <f t="shared" si="52"/>
         <v>400</v>
       </c>
-      <c r="I27" s="90">
+      <c r="I27" s="89">
         <f t="shared" si="52"/>
         <v>320</v>
       </c>
-      <c r="J27" s="90">
+      <c r="J27" s="89">
         <f t="shared" si="52"/>
         <v>1000</v>
       </c>
-      <c r="K27" s="90">
+      <c r="K27" s="89">
         <f t="shared" si="52"/>
         <v>1000</v>
       </c>
-      <c r="L27" s="90">
+      <c r="L27" s="89">
         <f t="shared" si="52"/>
         <v>2800</v>
       </c>
-      <c r="M27" s="60">
+      <c r="M27" s="59">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="N27" s="61">
+      <c r="N27" s="60">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O27" s="59">
+      <c r="O27" s="58">
         <f t="shared" si="1"/>
-        <v>116.2242</v>
-      </c>
-      <c r="P27" s="75">
+        <v>331.63</v>
+      </c>
+      <c r="P27" s="74">
         <f t="shared" si="47"/>
         <v>70</v>
       </c>
@@ -4132,131 +4135,180 @@
         <f t="shared" si="48"/>
         <v>240</v>
       </c>
-      <c r="R27" s="52" t="e">
+      <c r="R27" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S27" s="53">
+      <c r="S27" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T27" s="53">
+      <c r="T27" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U27" s="54" t="e">
+      <c r="U27" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V27" s="55" t="e">
+      <c r="V27" s="54" t="e">
         <f t="shared" si="49"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W27" s="56">
+      <c r="W27" s="55">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="X27" s="56">
+      <c r="X27" s="55">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="57" t="e">
+      <c r="Y27" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="141" t="s">
+      <c r="B28" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="142"/>
-      <c r="D28" s="92">
+      <c r="C28" s="135"/>
+      <c r="D28" s="91">
         <f>SUM(D24,D27)</f>
         <v>2520</v>
       </c>
-      <c r="E28" s="92">
+      <c r="E28" s="91">
         <f t="shared" ref="E28:L28" si="53">SUM(E24,E27)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="92">
+      <c r="F28" s="91">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="G28" s="92">
+      <c r="G28" s="91">
         <f t="shared" si="53"/>
-        <v>5920</v>
-      </c>
-      <c r="H28" s="92">
+        <v>4520</v>
+      </c>
+      <c r="H28" s="91">
         <f t="shared" si="53"/>
-        <v>7280</v>
-      </c>
-      <c r="I28" s="92">
+        <v>4037</v>
+      </c>
+      <c r="I28" s="91">
         <f t="shared" si="53"/>
-        <v>7560</v>
-      </c>
-      <c r="J28" s="92">
+        <v>5157</v>
+      </c>
+      <c r="J28" s="91">
         <f t="shared" si="53"/>
-        <v>8360</v>
-      </c>
-      <c r="K28" s="92">
+        <v>7717</v>
+      </c>
+      <c r="K28" s="91">
         <f t="shared" si="53"/>
-        <v>11960</v>
-      </c>
-      <c r="L28" s="92">
+        <v>6464</v>
+      </c>
+      <c r="L28" s="91">
         <f t="shared" si="53"/>
-        <v>13080</v>
-      </c>
-      <c r="M28" s="62">
+        <v>9279</v>
+      </c>
+      <c r="M28" s="61">
         <f t="shared" si="0"/>
-        <v>1417</v>
-      </c>
-      <c r="N28" s="65">
+        <v>992.35</v>
+      </c>
+      <c r="N28" s="64">
         <f>SUM(N5:N27)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="63">
+      <c r="O28" s="62">
         <f t="shared" ref="O28:Y28" si="54">SUM(O5:O27)</f>
-        <v>2673.1566000000016</v>
-      </c>
-      <c r="P28" s="64">
+        <v>7627.4900000000016</v>
+      </c>
+      <c r="P28" s="63">
         <f t="shared" si="54"/>
-        <v>2330.5500000000002</v>
-      </c>
-      <c r="Q28" s="66">
+        <v>1625.95</v>
+      </c>
+      <c r="Q28" s="65">
         <f t="shared" si="54"/>
-        <v>4037.1</v>
-      </c>
-      <c r="R28" s="67" t="e">
+        <v>3043.1</v>
+      </c>
+      <c r="R28" s="66" t="e">
         <f t="shared" si="54"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S28" s="68">
+      <c r="S28" s="67">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="T28" s="68">
+      <c r="T28" s="67">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="U28" s="69" t="e">
+      <c r="U28" s="68" t="e">
         <f t="shared" si="54"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V28" s="70" t="e">
+      <c r="V28" s="69" t="e">
         <f t="shared" si="54"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W28" s="71">
+      <c r="W28" s="70">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="X28" s="71">
+      <c r="X28" s="70">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="72" t="e">
+      <c r="Y28" s="71" t="e">
         <f t="shared" si="54"/>
         <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29">
+        <v>280</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>320</v>
+      </c>
+      <c r="J29">
+        <v>600</v>
+      </c>
+      <c r="K29">
+        <v>600</v>
+      </c>
+      <c r="L29">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30">
+        <v>1400</v>
+      </c>
+      <c r="G30">
+        <v>400</v>
+      </c>
+      <c r="H30">
+        <v>400</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>400</v>
+      </c>
+      <c r="K30">
+        <v>400</v>
+      </c>
+      <c r="L30">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -4279,7 +4331,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:N13"/>
+  <dimension ref="C2:O13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -4292,48 +4344,51 @@
     <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="38.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.08984375" customWidth="1"/>
     <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="155" t="s">
+    <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C3" s="147" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="159" t="s">
+      <c r="D3" s="148"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="151" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="152"/>
+      <c r="K3" s="153" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="153"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="153"/>
+      <c r="O3" s="153"/>
+    </row>
+    <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="112"/>
+      <c r="D4" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="107" t="s">
         <v>79</v>
-      </c>
-      <c r="I3" s="160"/>
-      <c r="K3" s="154" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
-    </row>
-    <row r="4" spans="3:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="120"/>
-      <c r="D4" s="83" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="121" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="115" t="s">
-        <v>80</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -4347,30 +4402,33 @@
       <c r="N4" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="122" t="s">
+      <c r="O4" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="96">
-        <v>248.22</v>
-      </c>
-      <c r="E5" s="82">
-        <v>1222</v>
-      </c>
-      <c r="F5" s="82">
+      <c r="D5" s="95">
+        <v>320.92</v>
+      </c>
+      <c r="E5" s="81">
+        <v>802.35</v>
+      </c>
+      <c r="F5" s="81">
         <v>190</v>
       </c>
-      <c r="G5" s="123">
+      <c r="G5" s="115">
         <f>SUM(D5:F5)</f>
-        <v>1660.22</v>
-      </c>
-      <c r="H5" s="116">
+        <v>1313.27</v>
+      </c>
+      <c r="H5" s="108">
         <v>10000</v>
       </c>
-      <c r="I5" s="117">
+      <c r="I5" s="109">
         <f>G5-H5</f>
-        <v>-8339.7800000000007</v>
+        <v>-8686.73</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -4379,40 +4437,43 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>7794</v>
+        <v>20391</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>194.85</v>
-      </c>
-    </row>
-    <row r="6" spans="3:14" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C6" s="124" t="s">
+        <v>509.77499999999998</v>
+      </c>
+      <c r="O5" s="83">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C6" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="125">
+      <c r="D6" s="117">
         <f>D5*40</f>
-        <v>9928.7999999999993</v>
-      </c>
-      <c r="E6" s="126">
+        <v>12836.800000000001</v>
+      </c>
+      <c r="E6" s="118">
         <f>E5*40</f>
-        <v>48880</v>
-      </c>
-      <c r="F6" s="126">
+        <v>32094</v>
+      </c>
+      <c r="F6" s="118">
         <f>F5*40</f>
         <v>7600</v>
       </c>
-      <c r="G6" s="127">
+      <c r="G6" s="119">
         <f>SUM(D6:F6)</f>
-        <v>66408.800000000003</v>
-      </c>
-      <c r="H6" s="118">
+        <v>52530.8</v>
+      </c>
+      <c r="H6" s="110">
         <f>H5*40</f>
         <v>400000</v>
       </c>
-      <c r="I6" s="119">
+      <c r="I6" s="111">
         <f>G6-H6</f>
-        <v>-333591.2</v>
+        <v>-347469.2</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -4421,15 +4482,18 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>8638</v>
+        <v>21114</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>215.95</v>
-      </c>
-    </row>
-    <row r="7" spans="3:14" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="94"/>
+        <v>527.85</v>
+      </c>
+      <c r="O6" s="83">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" s="93"/>
       <c r="K7" s="1" t="s">
         <v>3</v>
       </c>
@@ -4437,16 +4501,22 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>153</v>
+        <v>10976</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>3.8250000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" s="85" t="s">
-        <v>62</v>
+        <v>274.39999999999998</v>
+      </c>
+      <c r="O7" s="83">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" s="84" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8">
+        <v>765</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>4</v>
@@ -4455,24 +4525,27 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>805</v>
+        <v>22714</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>20.125</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" s="85" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="128">
+        <v>567.85</v>
+      </c>
+      <c r="O8" s="83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="120">
         <f>D8-D5</f>
-        <v>-248.22</v>
-      </c>
-      <c r="E9" s="128">
+        <v>-320.92</v>
+      </c>
+      <c r="E9" s="120">
         <f>E8-E5</f>
-        <v>-1222</v>
+        <v>-37.350000000000023</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -4481,32 +4554,43 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>1874</v>
+        <v>24231</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>46.85</v>
-      </c>
-    </row>
-    <row r="10" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>605.77499999999998</v>
+      </c>
+      <c r="O9" s="83">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L10" s="7">
         <v>120</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5">
+      <c r="M10" s="5">
+        <v>14849</v>
+      </c>
+      <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="158" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="158"/>
-      <c r="F11" s="103"/>
+        <v>371.22500000000002</v>
+      </c>
+      <c r="O10" s="83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C11" s="150" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="150"/>
+      <c r="F11" s="150" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="150"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -4514,19 +4598,29 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>72000</v>
-      </c>
-      <c r="N11" s="5">
+        <v>58621</v>
+      </c>
+      <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="12" spans="3:14" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" s="104" t="s">
+        <v>1465.5250000000001</v>
+      </c>
+      <c r="O11" s="83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C12" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="95">
+      <c r="D12" s="94">
         <v>500.9</v>
+      </c>
+      <c r="F12" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="104">
+        <f>D12+G5</f>
+        <v>1814.17</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -4534,27 +4628,40 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>91264</v>
+        <v>172896</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>2281.6</v>
-      </c>
-    </row>
-    <row r="13" spans="3:14" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C13" s="105" t="s">
+        <v>4322.3999999999996</v>
+      </c>
+      <c r="O12" s="9">
+        <f>SUM(O5:O11)</f>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="C13" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="106">
+      <c r="D13" s="104">
+        <f>D12*40</f>
         <v>20036</v>
       </c>
+      <c r="F13" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="104">
+        <f>G12*40</f>
+        <v>72566.8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="K3:N3"/>
+  <mergeCells count="5">
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="H3:I3"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4574,13 +4681,13 @@
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="84" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="84" t="s">
+      <c r="B1" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="83" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4687,16 +4794,16 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="86"/>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="87"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA740B03-790D-4723-888F-67E12AA686D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49F2E4F-B829-498D-B081-5B0194A436DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -2037,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
@@ -3681,19 +3681,33 @@
       <c r="B22" s="47">
         <v>18</v>
       </c>
-      <c r="C22" s="57"/>
+      <c r="C22" s="57" t="s">
+        <v>80</v>
+      </c>
       <c r="D22" s="75"/>
       <c r="E22" s="76"/>
       <c r="F22" s="77"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="77"/>
+      <c r="G22" s="50">
+        <v>300</v>
+      </c>
+      <c r="H22" s="76">
+        <v>300</v>
+      </c>
+      <c r="I22" s="49">
+        <v>300</v>
+      </c>
+      <c r="J22" s="50">
+        <v>300</v>
+      </c>
+      <c r="K22" s="76">
+        <v>300</v>
+      </c>
+      <c r="L22" s="77">
+        <v>300</v>
+      </c>
       <c r="M22" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
@@ -3705,11 +3719,11 @@
       </c>
       <c r="P22" s="74">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R22" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3834,31 +3848,31 @@
       </c>
       <c r="G24" s="90">
         <f t="shared" si="45"/>
-        <v>3840</v>
+        <v>4140</v>
       </c>
       <c r="H24" s="90">
         <f t="shared" si="45"/>
-        <v>3637</v>
+        <v>3937</v>
       </c>
       <c r="I24" s="90">
         <f t="shared" si="45"/>
-        <v>4837</v>
+        <v>5137</v>
       </c>
       <c r="J24" s="90">
         <f t="shared" si="45"/>
-        <v>6717</v>
+        <v>7017</v>
       </c>
       <c r="K24" s="90">
         <f t="shared" si="45"/>
-        <v>5464</v>
+        <v>5764</v>
       </c>
       <c r="L24" s="90">
         <f t="shared" si="45"/>
-        <v>6479</v>
+        <v>6779</v>
       </c>
       <c r="M24" s="48">
         <f t="shared" ref="M24:M26" si="46">SUM(D24:L24)/40</f>
-        <v>802.35</v>
+        <v>847.35</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
@@ -3870,11 +3884,11 @@
       </c>
       <c r="P24" s="74">
         <f t="shared" ref="P24:P27" si="47">SUM(G24:I24)/20</f>
-        <v>615.70000000000005</v>
+        <v>660.7</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" ref="Q24:Q27" si="48">SUM(J24:L24)/20</f>
-        <v>933</v>
+        <v>978</v>
       </c>
       <c r="R24" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3921,26 +3935,32 @@
       <c r="E25" s="76"/>
       <c r="F25" s="77"/>
       <c r="G25" s="50">
-        <v>280</v>
+        <f>280+1600</f>
+        <v>1880</v>
       </c>
       <c r="H25" s="76">
-        <v>0</v>
+        <f>0+600</f>
+        <v>600</v>
       </c>
       <c r="I25" s="49">
-        <v>320</v>
+        <f>320+1800</f>
+        <v>2120</v>
       </c>
       <c r="J25" s="50">
-        <v>600</v>
+        <f>600+2800</f>
+        <v>3400</v>
       </c>
       <c r="K25" s="76">
-        <v>600</v>
+        <f>600+2400</f>
+        <v>3000</v>
       </c>
       <c r="L25" s="77">
-        <v>2200</v>
+        <f>2200+2800</f>
+        <v>5000</v>
       </c>
       <c r="M25" s="48">
         <f t="shared" si="46"/>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="18"/>
@@ -3952,11 +3972,11 @@
       </c>
       <c r="P25" s="74">
         <f t="shared" si="47"/>
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="48"/>
-        <v>170</v>
+        <v>570</v>
       </c>
       <c r="R25" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4093,31 +4113,31 @@
       </c>
       <c r="G27" s="89">
         <f t="shared" si="52"/>
-        <v>680</v>
+        <v>2280</v>
       </c>
       <c r="H27" s="89">
         <f t="shared" si="52"/>
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="I27" s="89">
         <f t="shared" si="52"/>
-        <v>320</v>
+        <v>2120</v>
       </c>
       <c r="J27" s="89">
         <f t="shared" si="52"/>
-        <v>1000</v>
+        <v>3800</v>
       </c>
       <c r="K27" s="89">
         <f t="shared" si="52"/>
-        <v>1000</v>
+        <v>3400</v>
       </c>
       <c r="L27" s="89">
         <f t="shared" si="52"/>
-        <v>2800</v>
+        <v>5600</v>
       </c>
       <c r="M27" s="59">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>490</v>
       </c>
       <c r="N27" s="60">
         <f t="shared" si="18"/>
@@ -4129,11 +4149,11 @@
       </c>
       <c r="P27" s="74">
         <f t="shared" si="47"/>
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="48"/>
-        <v>240</v>
+        <v>640</v>
       </c>
       <c r="R27" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4187,31 +4207,31 @@
       </c>
       <c r="G28" s="91">
         <f t="shared" si="53"/>
-        <v>4520</v>
+        <v>6420</v>
       </c>
       <c r="H28" s="91">
         <f t="shared" si="53"/>
-        <v>4037</v>
+        <v>4937</v>
       </c>
       <c r="I28" s="91">
         <f t="shared" si="53"/>
-        <v>5157</v>
+        <v>7257</v>
       </c>
       <c r="J28" s="91">
         <f t="shared" si="53"/>
-        <v>7717</v>
+        <v>10817</v>
       </c>
       <c r="K28" s="91">
         <f t="shared" si="53"/>
-        <v>6464</v>
+        <v>9164</v>
       </c>
       <c r="L28" s="91">
         <f t="shared" si="53"/>
-        <v>9279</v>
+        <v>12379</v>
       </c>
       <c r="M28" s="61">
         <f t="shared" si="0"/>
-        <v>992.35</v>
+        <v>1337.35</v>
       </c>
       <c r="N28" s="64">
         <f>SUM(N5:N27)</f>
@@ -4223,11 +4243,11 @@
       </c>
       <c r="P28" s="63">
         <f t="shared" si="54"/>
-        <v>1625.95</v>
+        <v>2115.9499999999998</v>
       </c>
       <c r="Q28" s="65">
         <f t="shared" si="54"/>
-        <v>3043.1</v>
+        <v>3933.1</v>
       </c>
       <c r="R28" s="66" t="e">
         <f t="shared" si="54"/>
@@ -4260,55 +4280,6 @@
       <c r="Y28" s="71" t="e">
         <f t="shared" si="54"/>
         <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29">
-        <v>280</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>320</v>
-      </c>
-      <c r="J29">
-        <v>600</v>
-      </c>
-      <c r="K29">
-        <v>600</v>
-      </c>
-      <c r="L29">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30">
-        <v>1400</v>
-      </c>
-      <c r="G30">
-        <v>400</v>
-      </c>
-      <c r="H30">
-        <v>400</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>400</v>
-      </c>
-      <c r="K30">
-        <v>400</v>
-      </c>
-      <c r="L30">
-        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -4411,24 +4382,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="95">
-        <v>320.92</v>
+        <v>341.7</v>
       </c>
       <c r="E5" s="81">
-        <v>802.35</v>
+        <v>847.35</v>
       </c>
       <c r="F5" s="81">
-        <v>190</v>
+        <v>490</v>
       </c>
       <c r="G5" s="115">
         <f>SUM(D5:F5)</f>
-        <v>1313.27</v>
+        <v>1679.05</v>
       </c>
       <c r="H5" s="108">
         <v>10000</v>
       </c>
       <c r="I5" s="109">
         <f>G5-H5</f>
-        <v>-8686.73</v>
+        <v>-8320.9500000000007</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -4453,19 +4424,19 @@
       </c>
       <c r="D6" s="117">
         <f>D5*40</f>
-        <v>12836.800000000001</v>
+        <v>13668</v>
       </c>
       <c r="E6" s="118">
         <f>E5*40</f>
-        <v>32094</v>
+        <v>33894</v>
       </c>
       <c r="F6" s="118">
         <f>F5*40</f>
-        <v>7600</v>
+        <v>19600</v>
       </c>
       <c r="G6" s="119">
         <f>SUM(D6:F6)</f>
-        <v>52530.8</v>
+        <v>67162</v>
       </c>
       <c r="H6" s="110">
         <f>H5*40</f>
@@ -4473,7 +4444,7 @@
       </c>
       <c r="I6" s="111">
         <f>G6-H6</f>
-        <v>-347469.2</v>
+        <v>-332838</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -4515,9 +4486,6 @@
       <c r="C8" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="E8">
-        <v>765</v>
-      </c>
       <c r="K8" s="1" t="s">
         <v>4</v>
       </c>
@@ -4541,11 +4509,11 @@
       </c>
       <c r="D9" s="120">
         <f>D8-D5</f>
-        <v>-320.92</v>
+        <v>-341.7</v>
       </c>
       <c r="E9" s="120">
         <f>E8-E5</f>
-        <v>-37.350000000000023</v>
+        <v>-847.35</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -4620,7 +4588,7 @@
       </c>
       <c r="G12" s="104">
         <f>D12+G5</f>
-        <v>1814.17</v>
+        <v>2179.9499999999998</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -4652,7 +4620,7 @@
       </c>
       <c r="G13" s="104">
         <f>G12*40</f>
-        <v>72566.8</v>
+        <v>87198</v>
       </c>
     </row>
   </sheetData>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49F2E4F-B829-498D-B081-5B0194A436DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1219ACEF-617D-4B2E-8D3A-005A4F0459AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1462,42 +1462,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1535,6 +1499,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2044,13 +2044,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="122">
-        <v>46174</v>
-      </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
+      <c r="B1" s="135">
+        <v>46186</v>
+      </c>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2072,10 +2072,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="136" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2108,13 +2108,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="136"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="139" t="s">
+      <c r="M2" s="124"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="126"/>
+      <c r="P2" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="140"/>
+      <c r="Q2" s="128"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2133,8 +2133,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="144"/>
-      <c r="B3" s="124"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="137"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2165,29 +2165,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="141" t="s">
+      <c r="M3" s="129" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="142"/>
-      <c r="O3" s="143"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="131"/>
       <c r="P3" s="72"/>
       <c r="Q3" s="73"/>
-      <c r="R3" s="126" t="s">
+      <c r="R3" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="128"/>
-      <c r="V3" s="129" t="s">
+      <c r="S3" s="140"/>
+      <c r="T3" s="140"/>
+      <c r="U3" s="141"/>
+      <c r="V3" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="130"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="131"/>
+      <c r="W3" s="143"/>
+      <c r="X3" s="143"/>
+      <c r="Y3" s="144"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="144"/>
-      <c r="B4" s="125"/>
+      <c r="A4" s="132"/>
+      <c r="B4" s="138"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3759,9 +3759,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="80">
-        <v>46185</v>
-      </c>
+      <c r="A23" s="80"/>
       <c r="B23" s="47">
         <v>19</v>
       </c>
@@ -3830,10 +3828,10 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="80"/>
-      <c r="B24" s="132" t="s">
+      <c r="B24" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="133"/>
+      <c r="C24" s="146"/>
       <c r="D24" s="90">
         <f>SUM(D6:D23)</f>
         <v>1120</v>
@@ -4095,10 +4093,10 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="146"/>
+      <c r="C27" s="134"/>
       <c r="D27" s="89">
         <f>SUM(D25:D26)</f>
         <v>1400</v>
@@ -4189,10 +4187,10 @@
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="134" t="s">
+      <c r="B28" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="135"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="91">
         <f>SUM(D24,D27)</f>
         <v>2520</v>
@@ -4284,17 +4282,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1219ACEF-617D-4B2E-8D3A-005A4F0459AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910BE895-D8F0-46AF-A289-2E66D359EB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1462,6 +1462,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1499,42 +1535,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2044,13 +2044,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="135">
+      <c r="B1" s="122">
         <v>46186</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2072,10 +2072,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="136" t="s">
+      <c r="B2" s="123" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2108,13 +2108,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="124"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="126"/>
-      <c r="P2" s="127" t="s">
+      <c r="M2" s="136"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="128"/>
+      <c r="Q2" s="140"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2133,8 +2133,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="132"/>
-      <c r="B3" s="137"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="124"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2165,29 +2165,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="129" t="s">
+      <c r="M3" s="141" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="130"/>
-      <c r="O3" s="131"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="143"/>
       <c r="P3" s="72"/>
       <c r="Q3" s="73"/>
-      <c r="R3" s="139" t="s">
+      <c r="R3" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="140"/>
-      <c r="T3" s="140"/>
-      <c r="U3" s="141"/>
-      <c r="V3" s="142" t="s">
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="144"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="130"/>
+      <c r="Y3" s="131"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="132"/>
-      <c r="B4" s="138"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="125"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" s="80"/>
-      <c r="B24" s="145" t="s">
+      <c r="B24" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="146"/>
+      <c r="C24" s="133"/>
       <c r="D24" s="90">
         <f>SUM(D6:D23)</f>
         <v>1120</v>
@@ -4093,10 +4093,10 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="133" t="s">
+      <c r="B27" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="134"/>
+      <c r="C27" s="146"/>
       <c r="D27" s="89">
         <f>SUM(D25:D26)</f>
         <v>1400</v>
@@ -4187,10 +4187,10 @@
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="123"/>
+      <c r="C28" s="135"/>
       <c r="D28" s="91">
         <f>SUM(D24,D27)</f>
         <v>2520</v>
@@ -4282,17 +4282,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910BE895-D8F0-46AF-A289-2E66D359EB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595DF46A-3930-4912-85F5-8DF06E9CDB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -278,6 +278,24 @@
   </si>
   <si>
     <t>Sale End to End</t>
+  </si>
+  <si>
+    <t>Gourmet Food johar towm</t>
+  </si>
+  <si>
+    <t>Gourmet Food 12 G</t>
+  </si>
+  <si>
+    <t>Gourmet Food Fizaya</t>
+  </si>
+  <si>
+    <t>Gourmet Food Calvery</t>
+  </si>
+  <si>
+    <t>Galaxy Super Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake City Mart </t>
   </si>
 </sst>
 </file>
@@ -2037,10 +2055,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2378,7 +2396,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M28" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M33" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2386,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O27" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O32" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="74">
@@ -2398,15 +2416,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R27" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R32" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S27" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S32" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T27" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T32" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2554,7 +2572,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N27" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N32" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -2994,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U27" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U32" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3010,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y27" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y32" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3622,7 +3640,7 @@
         <v>120</v>
       </c>
       <c r="M21" s="48">
-        <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
+        <f t="shared" ref="M21:M28" si="37">SUM(D21:L21)/40</f>
         <v>18</v>
       </c>
       <c r="N21" s="39">
@@ -3634,11 +3652,11 @@
         <v>331.63</v>
       </c>
       <c r="P21" s="74">
-        <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
+        <f t="shared" ref="P21:P28" si="38">SUM(G21:I21)/20</f>
         <v>18</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
+        <f t="shared" ref="Q21:Q28" si="39">SUM(J21:L21)/20</f>
         <v>18</v>
       </c>
       <c r="R21" s="51" t="e">
@@ -3654,23 +3672,23 @@
         <v>0</v>
       </c>
       <c r="U21" s="53" t="e">
-        <f t="shared" ref="U21:U23" si="40">SUM(R21:T21)</f>
+        <f t="shared" ref="U21:U28" si="40">SUM(R21:T21)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V21" s="54" t="e">
-        <f t="shared" ref="V21:V23" si="41">SUM(D21:F21)*$V$3</f>
+        <f t="shared" ref="V21:V28" si="41">SUM(D21:F21)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W21" s="55">
-        <f t="shared" ref="W21:W23" si="42">SUM(G21:I21)*$W$3</f>
+        <f t="shared" ref="W21:W28" si="42">SUM(G21:I21)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X21" s="55">
-        <f t="shared" ref="X21:X23" si="43">SUM(J21:L21)*$X$3</f>
+        <f t="shared" ref="X21:X28" si="43">SUM(J21:L21)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y23" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y29" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3759,23 +3777,39 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="80"/>
+      <c r="A23" s="80">
+        <v>46189</v>
+      </c>
       <c r="B23" s="47">
         <v>19</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="57" t="s">
+        <v>85</v>
+      </c>
       <c r="D23" s="75"/>
       <c r="E23" s="76"/>
       <c r="F23" s="77"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="77"/>
+      <c r="G23" s="50">
+        <v>80</v>
+      </c>
+      <c r="H23" s="76">
+        <v>80</v>
+      </c>
+      <c r="I23" s="49">
+        <v>80</v>
+      </c>
+      <c r="J23" s="50">
+        <v>80</v>
+      </c>
+      <c r="K23" s="76">
+        <v>80</v>
+      </c>
+      <c r="L23" s="77">
+        <v>80</v>
+      </c>
       <c r="M23" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N23" s="39">
         <f t="shared" si="18"/>
@@ -3787,11 +3821,11 @@
       </c>
       <c r="P23" s="74">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R23" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3806,11 +3840,11 @@
         <v>0</v>
       </c>
       <c r="U23" s="53" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="U23:U27" si="45">SUM(R23:T23)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V23" s="54" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="V23:V27" si="46">SUM(D23:F23)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W23" s="55">
@@ -3827,50 +3861,39 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="80"/>
-      <c r="B24" s="132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="133"/>
-      <c r="D24" s="90">
-        <f>SUM(D6:D23)</f>
-        <v>1120</v>
-      </c>
-      <c r="E24" s="90">
-        <f t="shared" ref="E24:L24" si="45">SUM(E6:E23)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="90">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="90">
-        <f t="shared" si="45"/>
-        <v>4140</v>
-      </c>
-      <c r="H24" s="90">
-        <f t="shared" si="45"/>
-        <v>3937</v>
-      </c>
-      <c r="I24" s="90">
-        <f t="shared" si="45"/>
-        <v>5137</v>
-      </c>
-      <c r="J24" s="90">
-        <f t="shared" si="45"/>
-        <v>7017</v>
-      </c>
-      <c r="K24" s="90">
-        <f t="shared" si="45"/>
-        <v>5764</v>
-      </c>
-      <c r="L24" s="90">
-        <f t="shared" si="45"/>
-        <v>6779</v>
+      <c r="A24" s="80">
+        <v>46189</v>
+      </c>
+      <c r="B24" s="47">
+        <v>20</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="75"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="50">
+        <v>80</v>
+      </c>
+      <c r="H24" s="76">
+        <v>80</v>
+      </c>
+      <c r="I24" s="49">
+        <v>80</v>
+      </c>
+      <c r="J24" s="50">
+        <v>80</v>
+      </c>
+      <c r="K24" s="76">
+        <v>80</v>
+      </c>
+      <c r="L24" s="77">
+        <v>80</v>
       </c>
       <c r="M24" s="48">
-        <f t="shared" ref="M24:M26" si="46">SUM(D24:L24)/40</f>
-        <v>847.35</v>
+        <f t="shared" ref="M24:M27" si="47">SUM(D24:L24)/40</f>
+        <v>12</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
@@ -3881,12 +3904,12 @@
         <v>331.63</v>
       </c>
       <c r="P24" s="74">
-        <f t="shared" ref="P24:P27" si="47">SUM(G24:I24)/20</f>
-        <v>660.7</v>
+        <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
+        <v>12</v>
       </c>
       <c r="Q24" s="40">
-        <f t="shared" ref="Q24:Q27" si="48">SUM(J24:L24)/20</f>
-        <v>978</v>
+        <f t="shared" ref="Q24:Q27" si="49">SUM(J24:L24)/20</f>
+        <v>12</v>
       </c>
       <c r="R24" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3901,11 +3924,11 @@
         <v>0</v>
       </c>
       <c r="U24" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
       <c r="V24" s="54" t="e">
-        <f t="shared" ref="V24:V27" si="49">SUM(D24:F24)*$V$3</f>
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
       <c r="W24" s="55">
@@ -3917,48 +3940,44 @@
         <v>0</v>
       </c>
       <c r="Y24" s="56" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="80"/>
+      <c r="A25" s="80">
+        <v>46189</v>
+      </c>
       <c r="B25" s="47">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="D25" s="75"/>
       <c r="E25" s="76"/>
       <c r="F25" s="77"/>
       <c r="G25" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
+        <v>80</v>
       </c>
       <c r="H25" s="76">
-        <f>0+600</f>
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="I25" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
+        <v>80</v>
       </c>
       <c r="J25" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
+        <v>80</v>
       </c>
       <c r="K25" s="76">
-        <f>600+2400</f>
-        <v>3000</v>
+        <v>80</v>
       </c>
       <c r="L25" s="77">
-        <f>2200+2800</f>
-        <v>5000</v>
+        <v>80</v>
       </c>
       <c r="M25" s="48">
-        <f t="shared" si="46"/>
-        <v>400</v>
+        <f t="shared" si="47"/>
+        <v>12</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="18"/>
@@ -3969,12 +3988,12 @@
         <v>331.63</v>
       </c>
       <c r="P25" s="74">
-        <f t="shared" si="47"/>
-        <v>230</v>
+        <f t="shared" si="48"/>
+        <v>12</v>
       </c>
       <c r="Q25" s="40">
-        <f t="shared" si="48"/>
-        <v>570</v>
+        <f t="shared" si="49"/>
+        <v>12</v>
       </c>
       <c r="R25" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3989,11 +4008,11 @@
         <v>0</v>
       </c>
       <c r="U25" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
       <c r="V25" s="54" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
       <c r="W25" s="55">
@@ -4005,43 +4024,44 @@
         <v>0</v>
       </c>
       <c r="Y25" s="56" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A26" s="80">
+        <v>46189</v>
+      </c>
       <c r="B26" s="47">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="75">
-        <v>1400</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D26" s="75"/>
       <c r="E26" s="76"/>
       <c r="F26" s="77"/>
       <c r="G26" s="50">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="H26" s="76">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="I26" s="49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J26" s="50">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="K26" s="76">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="L26" s="77">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="M26" s="48">
-        <f t="shared" si="46"/>
-        <v>90</v>
+        <f t="shared" si="47"/>
+        <v>6</v>
       </c>
       <c r="N26" s="39">
         <f t="shared" si="18"/>
@@ -4052,12 +4072,12 @@
         <v>331.63</v>
       </c>
       <c r="P26" s="74">
-        <f t="shared" si="47"/>
-        <v>40</v>
+        <f t="shared" si="48"/>
+        <v>6</v>
       </c>
       <c r="Q26" s="40">
-        <f t="shared" si="48"/>
-        <v>70</v>
+        <f t="shared" si="49"/>
+        <v>6</v>
       </c>
       <c r="R26" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4072,11 +4092,11 @@
         <v>0</v>
       </c>
       <c r="U26" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="45"/>
         <v>#VALUE!</v>
       </c>
       <c r="V26" s="54" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="46"/>
         <v>#VALUE!</v>
       </c>
       <c r="W26" s="55">
@@ -4088,211 +4108,649 @@
         <v>0</v>
       </c>
       <c r="Y26" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A27" s="80">
+        <v>46189</v>
+      </c>
+      <c r="B27" s="47">
+        <v>23</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="75">
+        <v>80</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="50">
+        <v>80</v>
+      </c>
+      <c r="H27" s="76">
+        <v>80</v>
+      </c>
+      <c r="I27" s="49">
+        <v>80</v>
+      </c>
+      <c r="J27" s="50">
+        <v>80</v>
+      </c>
+      <c r="K27" s="76">
+        <v>80</v>
+      </c>
+      <c r="L27" s="77">
+        <v>80</v>
+      </c>
+      <c r="M27" s="48">
+        <f t="shared" si="47"/>
+        <v>14</v>
+      </c>
+      <c r="N27" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P27" s="74">
+        <f t="shared" si="48"/>
+        <v>12</v>
+      </c>
+      <c r="Q27" s="40">
+        <f t="shared" si="49"/>
+        <v>12</v>
+      </c>
+      <c r="R27" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S27" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="53" t="e">
+        <f t="shared" si="45"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V27" s="54" t="e">
+        <f t="shared" si="46"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W27" s="55">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="55">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A28" s="80">
+        <v>46189</v>
+      </c>
+      <c r="B28" s="47">
+        <v>24</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="75">
+        <v>120</v>
+      </c>
+      <c r="E28" s="76"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="50">
+        <v>120</v>
+      </c>
+      <c r="H28" s="76">
+        <v>120</v>
+      </c>
+      <c r="I28" s="49">
+        <v>120</v>
+      </c>
+      <c r="J28" s="50">
+        <v>120</v>
+      </c>
+      <c r="K28" s="76">
+        <v>120</v>
+      </c>
+      <c r="L28" s="77">
+        <v>120</v>
+      </c>
+      <c r="M28" s="48">
+        <f t="shared" si="37"/>
+        <v>21</v>
+      </c>
+      <c r="N28" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P28" s="74">
+        <f t="shared" si="38"/>
+        <v>18</v>
+      </c>
+      <c r="Q28" s="40">
+        <f t="shared" si="39"/>
+        <v>18</v>
+      </c>
+      <c r="R28" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S28" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="53" t="e">
+        <f t="shared" si="40"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V28" s="54" t="e">
+        <f t="shared" si="41"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W28" s="55">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="55">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A29" s="80"/>
+      <c r="B29" s="132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="133"/>
+      <c r="D29" s="90">
+        <f>SUM(D6:D28)</f>
+        <v>1320</v>
+      </c>
+      <c r="E29" s="90">
+        <f t="shared" ref="E29:L29" si="52">SUM(E6:E28)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="90">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="90">
+        <f t="shared" si="52"/>
+        <v>4620</v>
+      </c>
+      <c r="H29" s="90">
+        <f t="shared" si="52"/>
+        <v>4417</v>
+      </c>
+      <c r="I29" s="90">
+        <f t="shared" si="52"/>
+        <v>5617</v>
+      </c>
+      <c r="J29" s="90">
+        <f t="shared" si="52"/>
+        <v>7497</v>
+      </c>
+      <c r="K29" s="90">
+        <f t="shared" si="52"/>
+        <v>6244</v>
+      </c>
+      <c r="L29" s="90">
+        <f t="shared" si="52"/>
+        <v>7259</v>
+      </c>
+      <c r="M29" s="48">
+        <f t="shared" ref="M29:M31" si="53">SUM(D29:L29)/40</f>
+        <v>924.35</v>
+      </c>
+      <c r="N29" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O29" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P29" s="74">
+        <f t="shared" ref="P29:P32" si="54">SUM(G29:I29)/20</f>
+        <v>732.7</v>
+      </c>
+      <c r="Q29" s="40">
+        <f t="shared" ref="Q29:Q32" si="55">SUM(J29:L29)/20</f>
+        <v>1050</v>
+      </c>
+      <c r="R29" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S29" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V29" s="54" t="e">
+        <f t="shared" ref="V29:V32" si="56">SUM(D29:F29)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W29" s="55">
+        <f t="shared" ref="W29:W32" si="57">SUM(G29:I29)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X29" s="55">
+        <f t="shared" ref="X29:X32" si="58">SUM(J29:L29)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A30" s="80"/>
+      <c r="B30" s="47">
+        <v>0</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="75"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H30" s="76">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I30" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J30" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K30" s="76">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L30" s="77">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M30" s="48">
+        <f t="shared" si="53"/>
+        <v>400</v>
+      </c>
+      <c r="N30" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P30" s="74">
+        <f t="shared" si="54"/>
+        <v>230</v>
+      </c>
+      <c r="Q30" s="40">
+        <f t="shared" si="55"/>
+        <v>570</v>
+      </c>
+      <c r="R30" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S30" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V30" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W30" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="145" t="s">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B31" s="47">
+        <v>1</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="75">
+        <v>1400</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="50">
+        <v>400</v>
+      </c>
+      <c r="H31" s="76">
+        <v>400</v>
+      </c>
+      <c r="I31" s="49">
+        <v>0</v>
+      </c>
+      <c r="J31" s="50">
+        <v>400</v>
+      </c>
+      <c r="K31" s="76">
+        <v>400</v>
+      </c>
+      <c r="L31" s="77">
+        <v>600</v>
+      </c>
+      <c r="M31" s="48">
+        <f t="shared" si="53"/>
+        <v>90</v>
+      </c>
+      <c r="N31" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O31" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P31" s="74">
+        <f t="shared" si="54"/>
+        <v>40</v>
+      </c>
+      <c r="Q31" s="40">
+        <f t="shared" si="55"/>
+        <v>70</v>
+      </c>
+      <c r="R31" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S31" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V31" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W31" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="146"/>
-      <c r="D27" s="89">
-        <f>SUM(D25:D26)</f>
+      <c r="C32" s="146"/>
+      <c r="D32" s="89">
+        <f>SUM(D30:D31)</f>
         <v>1400</v>
       </c>
-      <c r="E27" s="89">
-        <f t="shared" ref="E27:L27" si="52">SUM(E25:E26)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="89">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="89">
-        <f t="shared" si="52"/>
+      <c r="E32" s="89">
+        <f t="shared" ref="E32:L32" si="59">SUM(E30:E31)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="89">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="89">
+        <f t="shared" si="59"/>
         <v>2280</v>
       </c>
-      <c r="H27" s="89">
-        <f t="shared" si="52"/>
+      <c r="H32" s="89">
+        <f t="shared" si="59"/>
         <v>1000</v>
       </c>
-      <c r="I27" s="89">
-        <f t="shared" si="52"/>
+      <c r="I32" s="89">
+        <f t="shared" si="59"/>
         <v>2120</v>
       </c>
-      <c r="J27" s="89">
-        <f t="shared" si="52"/>
+      <c r="J32" s="89">
+        <f t="shared" si="59"/>
         <v>3800</v>
       </c>
-      <c r="K27" s="89">
-        <f t="shared" si="52"/>
+      <c r="K32" s="89">
+        <f t="shared" si="59"/>
         <v>3400</v>
       </c>
-      <c r="L27" s="89">
-        <f t="shared" si="52"/>
+      <c r="L32" s="89">
+        <f t="shared" si="59"/>
         <v>5600</v>
       </c>
-      <c r="M27" s="59">
+      <c r="M32" s="59">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
-      <c r="N27" s="60">
+      <c r="N32" s="60">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O27" s="58">
+      <c r="O32" s="58">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P27" s="74">
-        <f t="shared" si="47"/>
+      <c r="P32" s="74">
+        <f t="shared" si="54"/>
         <v>270</v>
       </c>
-      <c r="Q27" s="40">
-        <f t="shared" si="48"/>
+      <c r="Q32" s="40">
+        <f t="shared" si="55"/>
         <v>640</v>
       </c>
-      <c r="R27" s="51" t="e">
+      <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S27" s="52">
+      <c r="S32" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T27" s="52">
+      <c r="T32" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U27" s="53" t="e">
+      <c r="U32" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V27" s="54" t="e">
-        <f t="shared" si="49"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W27" s="55">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="55">
-        <f t="shared" si="51"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="56" t="e">
+      <c r="V32" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W32" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="134" t="s">
+    <row r="33" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="135"/>
-      <c r="D28" s="91">
-        <f>SUM(D24,D27)</f>
-        <v>2520</v>
-      </c>
-      <c r="E28" s="91">
-        <f t="shared" ref="E28:L28" si="53">SUM(E24,E27)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="91">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="91">
-        <f t="shared" si="53"/>
-        <v>6420</v>
-      </c>
-      <c r="H28" s="91">
-        <f t="shared" si="53"/>
-        <v>4937</v>
-      </c>
-      <c r="I28" s="91">
-        <f t="shared" si="53"/>
-        <v>7257</v>
-      </c>
-      <c r="J28" s="91">
-        <f t="shared" si="53"/>
-        <v>10817</v>
-      </c>
-      <c r="K28" s="91">
-        <f t="shared" si="53"/>
-        <v>9164</v>
-      </c>
-      <c r="L28" s="91">
-        <f t="shared" si="53"/>
-        <v>12379</v>
-      </c>
-      <c r="M28" s="61">
+      <c r="C33" s="135"/>
+      <c r="D33" s="91">
+        <f>SUM(D29,D32)</f>
+        <v>2720</v>
+      </c>
+      <c r="E33" s="91">
+        <f t="shared" ref="E33:L33" si="60">SUM(E29,E32)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="91">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="91">
+        <f t="shared" si="60"/>
+        <v>6900</v>
+      </c>
+      <c r="H33" s="91">
+        <f t="shared" si="60"/>
+        <v>5417</v>
+      </c>
+      <c r="I33" s="91">
+        <f t="shared" si="60"/>
+        <v>7737</v>
+      </c>
+      <c r="J33" s="91">
+        <f t="shared" si="60"/>
+        <v>11297</v>
+      </c>
+      <c r="K33" s="91">
+        <f t="shared" si="60"/>
+        <v>9644</v>
+      </c>
+      <c r="L33" s="91">
+        <f t="shared" si="60"/>
+        <v>12859</v>
+      </c>
+      <c r="M33" s="61">
         <f t="shared" si="0"/>
-        <v>1337.35</v>
-      </c>
-      <c r="N28" s="64">
-        <f>SUM(N5:N27)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="62">
-        <f t="shared" ref="O28:Y28" si="54">SUM(O5:O27)</f>
-        <v>7627.4900000000016</v>
-      </c>
-      <c r="P28" s="63">
-        <f t="shared" si="54"/>
-        <v>2115.9499999999998</v>
-      </c>
-      <c r="Q28" s="65">
-        <f t="shared" si="54"/>
-        <v>3933.1</v>
-      </c>
-      <c r="R28" s="66" t="e">
-        <f t="shared" si="54"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S28" s="67">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="67">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="68" t="e">
-        <f t="shared" si="54"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V28" s="69" t="e">
-        <f t="shared" si="54"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W28" s="70">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="70">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="71" t="e">
-        <f t="shared" si="54"/>
+        <v>1414.35</v>
+      </c>
+      <c r="N33" s="64">
+        <f>SUM(N5:N32)</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="62">
+        <f t="shared" ref="O33:Y33" si="61">SUM(O5:O32)</f>
+        <v>9285.64</v>
+      </c>
+      <c r="P33" s="63">
+        <f t="shared" si="61"/>
+        <v>2259.9499999999998</v>
+      </c>
+      <c r="Q33" s="65">
+        <f t="shared" si="61"/>
+        <v>4077.1</v>
+      </c>
+      <c r="R33" s="66" t="e">
+        <f t="shared" si="61"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S33" s="67">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="67">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="68" t="e">
+        <f t="shared" si="61"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V33" s="69" t="e">
+        <f t="shared" si="61"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W33" s="70">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="70">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="71" t="e">
+        <f t="shared" si="61"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4380,24 +4838,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="95">
-        <v>341.7</v>
+        <v>353</v>
       </c>
       <c r="E5" s="81">
-        <v>847.35</v>
+        <v>924.35</v>
       </c>
       <c r="F5" s="81">
         <v>490</v>
       </c>
       <c r="G5" s="115">
         <f>SUM(D5:F5)</f>
-        <v>1679.05</v>
+        <v>1767.35</v>
       </c>
       <c r="H5" s="108">
         <v>10000</v>
       </c>
       <c r="I5" s="109">
         <f>G5-H5</f>
-        <v>-8320.9500000000007</v>
+        <v>-8232.65</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -4422,11 +4880,11 @@
       </c>
       <c r="D6" s="117">
         <f>D5*40</f>
-        <v>13668</v>
+        <v>14120</v>
       </c>
       <c r="E6" s="118">
         <f>E5*40</f>
-        <v>33894</v>
+        <v>36974</v>
       </c>
       <c r="F6" s="118">
         <f>F5*40</f>
@@ -4434,7 +4892,7 @@
       </c>
       <c r="G6" s="119">
         <f>SUM(D6:F6)</f>
-        <v>67162</v>
+        <v>70694</v>
       </c>
       <c r="H6" s="110">
         <f>H5*40</f>
@@ -4442,7 +4900,7 @@
       </c>
       <c r="I6" s="111">
         <f>G6-H6</f>
-        <v>-332838</v>
+        <v>-329306</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -4507,11 +4965,11 @@
       </c>
       <c r="D9" s="120">
         <f>D8-D5</f>
-        <v>-341.7</v>
+        <v>-353</v>
       </c>
       <c r="E9" s="120">
         <f>E8-E5</f>
-        <v>-847.35</v>
+        <v>-924.35</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -4586,7 +5044,7 @@
       </c>
       <c r="G12" s="104">
         <f>D12+G5</f>
-        <v>2179.9499999999998</v>
+        <v>2268.25</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -4618,7 +5076,7 @@
       </c>
       <c r="G13" s="104">
         <f>G12*40</f>
-        <v>87198</v>
+        <v>90730</v>
       </c>
     </row>
   </sheetData>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595DF46A-3930-4912-85F5-8DF06E9CDB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2146169-D6EA-4DE3-A48F-4C302D6D0163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="112">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -214,9 +214,6 @@
     <t>Diff</t>
   </si>
   <si>
-    <t xml:space="preserve">SD Total </t>
-  </si>
-  <si>
     <t xml:space="preserve">24/7 Mart </t>
   </si>
   <si>
@@ -296,6 +293,72 @@
   </si>
   <si>
     <t xml:space="preserve">Lake City Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown </t>
+  </si>
+  <si>
+    <t>Sohail Traders</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SB5:C38D Total </t>
+  </si>
+  <si>
+    <t>Risan Askari 11</t>
+  </si>
+  <si>
+    <t>Gourmet Shalamar Link</t>
+  </si>
+  <si>
+    <t>Gourmet Shadbagh</t>
+  </si>
+  <si>
+    <t>Gourmet Bata Pur</t>
+  </si>
+  <si>
+    <t>Gourmet Salamat Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Daroghawala</t>
+  </si>
+  <si>
+    <t>Gourmet Railway Palaza</t>
+  </si>
+  <si>
+    <t>Gourmet Taj Bagh</t>
+  </si>
+  <si>
+    <t>Gourmet Taj Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Baghban Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Sultan Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Shadi Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Manawa GT Road</t>
+  </si>
+  <si>
+    <t>MB Traders</t>
+  </si>
+  <si>
+    <t>Total In PC's</t>
+  </si>
+  <si>
+    <t>Total In CTN's</t>
+  </si>
+  <si>
+    <t>In Hand</t>
+  </si>
+  <si>
+    <t>Products</t>
   </si>
 </sst>
 </file>
@@ -400,7 +463,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,8 +524,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -1168,12 +1237,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1327,9 +1407,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1480,6 +1557,106 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1514,45 +1691,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1900,21 +2038,21 @@
     <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="104" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="79" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="79" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="79" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="105" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
@@ -1924,7 +2062,7 @@
       <c r="C10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="77">
         <v>3520247902365</v>
       </c>
       <c r="F10">
@@ -1945,7 +2083,7 @@
       <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="77">
         <v>300426949714</v>
       </c>
     </row>
@@ -1956,7 +2094,7 @@
       <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="77">
         <v>3277876126916</v>
       </c>
     </row>
@@ -1967,7 +2105,7 @@
       <c r="C14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="78">
+      <c r="D14" s="77">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1978,7 +2116,7 @@
       <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="77">
         <v>3520255124113</v>
       </c>
     </row>
@@ -1989,7 +2127,7 @@
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="77">
         <v>3520268948847</v>
       </c>
     </row>
@@ -2009,41 +2147,41 @@
       <c r="C18" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="81" t="s">
+      <c r="D18" s="80" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="92" t="s">
+      <c r="B19" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="91" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="92" t="s">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="91" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="92" t="s">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="91" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="92" t="s">
-        <v>68</v>
-      </c>
-    </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="92" t="s">
-        <v>80</v>
+      <c r="B23" s="91" t="s">
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="121">
+        <v>80</v>
+      </c>
+      <c r="D23" s="120">
         <v>3277876231301</v>
       </c>
     </row>
@@ -2055,20 +2193,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="122">
+      <c r="B1" s="165">
         <v>46186</v>
       </c>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2090,10 +2228,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="162" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="123" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2126,13 +2264,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="136"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="138"/>
-      <c r="P2" s="139" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="140"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2151,8 +2289,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="144"/>
-      <c r="B3" s="124"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2183,29 +2321,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="141" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="142"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="126" t="s">
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="128"/>
-      <c r="V3" s="129" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="130"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="131"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="144"/>
-      <c r="B4" s="125"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2277,36 +2415,36 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="80">
+      <c r="A5" s="79">
         <v>46179</v>
       </c>
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="97">
+      <c r="C5" s="95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="96">
         <v>1003</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="100">
+      <c r="E5" s="97"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="99">
         <v>1613</v>
       </c>
-      <c r="H5" s="98">
+      <c r="H5" s="97">
         <v>2442</v>
       </c>
-      <c r="I5" s="99">
+      <c r="I5" s="98">
         <v>1036</v>
       </c>
-      <c r="J5" s="100">
+      <c r="J5" s="99">
         <v>5269</v>
       </c>
-      <c r="K5" s="98">
+      <c r="K5" s="97">
         <v>3838</v>
       </c>
-      <c r="L5" s="101">
+      <c r="L5" s="100">
         <v>4835</v>
       </c>
       <c r="M5" s="37">
@@ -2321,7 +2459,7 @@
         <f>SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
-      <c r="P5" s="74">
+      <c r="P5" s="73">
         <f>SUM(G5:I5)/20</f>
         <v>254.55</v>
       </c>
@@ -2363,7 +2501,7 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="80">
+      <c r="A6" s="79">
         <v>46179</v>
       </c>
       <c r="B6" s="47">
@@ -2372,15 +2510,15 @@
       <c r="C6" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="74">
         <v>800</v>
       </c>
-      <c r="E6" s="76"/>
-      <c r="F6" s="77"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="76"/>
       <c r="G6" s="50">
         <v>800</v>
       </c>
-      <c r="H6" s="76">
+      <c r="H6" s="75">
         <v>800</v>
       </c>
       <c r="I6" s="49">
@@ -2389,14 +2527,14 @@
       <c r="J6" s="50">
         <v>800</v>
       </c>
-      <c r="K6" s="76">
+      <c r="K6" s="75">
         <v>800</v>
       </c>
-      <c r="L6" s="77">
+      <c r="L6" s="76">
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M33" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M52" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2404,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O32" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O51" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
-      <c r="P6" s="74">
+      <c r="P6" s="73">
         <f t="shared" ref="P6" si="2">SUM(G6:I6)/20</f>
         <v>120</v>
       </c>
@@ -2416,15 +2554,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R32" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R51" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S32" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S51" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T32" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T51" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2449,7 +2587,7 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="80">
+      <c r="A7" s="79">
         <v>46179</v>
       </c>
       <c r="B7" s="47">
@@ -2458,15 +2596,15 @@
       <c r="C7" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="75">
-        <v>80</v>
-      </c>
-      <c r="E7" s="76"/>
-      <c r="F7" s="77"/>
+      <c r="D7" s="74">
+        <v>80</v>
+      </c>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
       <c r="G7" s="50">
         <v>80</v>
       </c>
-      <c r="H7" s="76">
+      <c r="H7" s="75">
         <v>80</v>
       </c>
       <c r="I7" s="49">
@@ -2475,10 +2613,10 @@
       <c r="J7" s="50">
         <v>80</v>
       </c>
-      <c r="K7" s="76">
-        <v>80</v>
-      </c>
-      <c r="L7" s="77">
+      <c r="K7" s="75">
+        <v>80</v>
+      </c>
+      <c r="L7" s="76">
         <v>80</v>
       </c>
       <c r="M7" s="48">
@@ -2493,7 +2631,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="73">
         <f t="shared" ref="P7:P15" si="13">SUM(G7:I7)/20</f>
         <v>12</v>
       </c>
@@ -2535,7 +2673,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="80">
+      <c r="A8" s="79">
         <v>46181</v>
       </c>
       <c r="B8" s="47">
@@ -2544,15 +2682,15 @@
       <c r="C8" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="74">
         <v>200</v>
       </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="77"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
       <c r="G8" s="50">
         <v>200</v>
       </c>
-      <c r="H8" s="76">
+      <c r="H8" s="75">
         <v>200</v>
       </c>
       <c r="I8" s="49">
@@ -2561,10 +2699,10 @@
       <c r="J8" s="50">
         <v>200</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="75">
         <v>200</v>
       </c>
-      <c r="L8" s="77">
+      <c r="L8" s="76">
         <v>200</v>
       </c>
       <c r="M8" s="48">
@@ -2572,14 +2710,14 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N32" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N51" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P8" s="74">
+      <c r="P8" s="73">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
@@ -2621,31 +2759,31 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="80">
+      <c r="A9" s="79">
         <v>46181</v>
       </c>
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50">
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="129"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="131">
         <v>560</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="129">
         <v>560</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="130">
         <v>880</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="132">
         <f t="shared" si="12"/>
         <v>50</v>
       </c>
@@ -2657,7 +2795,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P9" s="74">
+      <c r="P9" s="73">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -2699,7 +2837,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="80">
+      <c r="A10" s="79">
         <v>46182</v>
       </c>
       <c r="B10" s="47">
@@ -2708,13 +2846,13 @@
       <c r="C10" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="75"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="77"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="76"/>
       <c r="G10" s="50">
         <v>1200</v>
       </c>
-      <c r="H10" s="76">
+      <c r="H10" s="75">
         <v>1200</v>
       </c>
       <c r="I10" s="49">
@@ -2723,10 +2861,10 @@
       <c r="J10" s="50">
         <v>2400</v>
       </c>
-      <c r="K10" s="76">
+      <c r="K10" s="75">
         <v>1800</v>
       </c>
-      <c r="L10" s="77">
+      <c r="L10" s="76">
         <v>1800</v>
       </c>
       <c r="M10" s="48">
@@ -2741,7 +2879,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P10" s="74">
+      <c r="P10" s="73">
         <f t="shared" si="13"/>
         <v>210</v>
       </c>
@@ -2783,7 +2921,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="80">
+      <c r="A11" s="79">
         <v>46182</v>
       </c>
       <c r="B11" s="47">
@@ -2792,11 +2930,11 @@
       <c r="C11" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="75"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="77"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="76"/>
       <c r="G11" s="50"/>
-      <c r="H11" s="76">
+      <c r="H11" s="75">
         <v>40</v>
       </c>
       <c r="I11" s="49">
@@ -2805,10 +2943,10 @@
       <c r="J11" s="50">
         <v>40</v>
       </c>
-      <c r="K11" s="76">
-        <v>40</v>
-      </c>
-      <c r="L11" s="77">
+      <c r="K11" s="75">
+        <v>40</v>
+      </c>
+      <c r="L11" s="76">
         <v>40</v>
       </c>
       <c r="M11" s="48">
@@ -2823,7 +2961,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P11" s="74">
+      <c r="P11" s="73">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
@@ -2865,7 +3003,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="80">
+      <c r="A12" s="79">
         <v>46182</v>
       </c>
       <c r="B12" s="47">
@@ -2874,13 +3012,13 @@
       <c r="C12" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
       <c r="G12" s="50">
         <v>400</v>
       </c>
-      <c r="H12" s="76">
+      <c r="H12" s="75">
         <v>200</v>
       </c>
       <c r="I12" s="49">
@@ -2889,10 +3027,10 @@
       <c r="J12" s="50">
         <v>400</v>
       </c>
-      <c r="K12" s="76">
+      <c r="K12" s="75">
         <v>200</v>
       </c>
-      <c r="L12" s="77">
+      <c r="L12" s="76">
         <v>400</v>
       </c>
       <c r="M12" s="48">
@@ -2907,7 +3045,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P12" s="74">
+      <c r="P12" s="73">
         <f t="shared" si="13"/>
         <v>50</v>
       </c>
@@ -2949,22 +3087,22 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="80">
+      <c r="A13" s="79">
         <v>46183</v>
       </c>
       <c r="B13" s="47">
         <v>9</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="75"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="77"/>
+        <v>63</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="76"/>
       <c r="G13" s="50">
         <v>40</v>
       </c>
-      <c r="H13" s="76">
+      <c r="H13" s="75">
         <v>40</v>
       </c>
       <c r="I13" s="49">
@@ -2973,10 +3111,10 @@
       <c r="J13" s="50">
         <v>40</v>
       </c>
-      <c r="K13" s="76">
-        <v>40</v>
-      </c>
-      <c r="L13" s="77">
+      <c r="K13" s="75">
+        <v>40</v>
+      </c>
+      <c r="L13" s="76">
         <v>40</v>
       </c>
       <c r="M13" s="48">
@@ -2991,7 +3129,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P13" s="74">
+      <c r="P13" s="73">
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
@@ -3012,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U32" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U51" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3028,12 +3166,12 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y32" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y51" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="80">
+      <c r="A14" s="79">
         <v>46183</v>
       </c>
       <c r="B14" s="47">
@@ -3042,13 +3180,13 @@
       <c r="C14" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="75"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="77"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="76"/>
       <c r="G14" s="50">
         <v>240</v>
       </c>
-      <c r="H14" s="76">
+      <c r="H14" s="75">
         <v>240</v>
       </c>
       <c r="I14" s="49">
@@ -3057,10 +3195,10 @@
       <c r="J14" s="50">
         <v>240</v>
       </c>
-      <c r="K14" s="76">
+      <c r="K14" s="75">
         <v>240</v>
       </c>
-      <c r="L14" s="77">
+      <c r="L14" s="76">
         <v>600</v>
       </c>
       <c r="M14" s="48">
@@ -3075,7 +3213,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P14" s="74">
+      <c r="P14" s="73">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
@@ -3117,30 +3255,30 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="80">
+      <c r="A15" s="79">
         <v>46183</v>
       </c>
       <c r="B15" s="47">
         <v>11</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="77"/>
+        <v>68</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
       <c r="G15" s="50"/>
-      <c r="H15" s="76"/>
+      <c r="H15" s="75"/>
       <c r="I15" s="49">
         <v>80</v>
       </c>
       <c r="J15" s="50">
         <v>80</v>
       </c>
-      <c r="K15" s="76">
-        <v>80</v>
-      </c>
-      <c r="L15" s="77">
+      <c r="K15" s="75">
+        <v>80</v>
+      </c>
+      <c r="L15" s="76">
         <v>80</v>
       </c>
       <c r="M15" s="48">
@@ -3155,7 +3293,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P15" s="74">
+      <c r="P15" s="73">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
@@ -3197,22 +3335,22 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="80">
+      <c r="A16" s="79">
         <v>46184</v>
       </c>
       <c r="B16" s="47">
         <v>12</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="77"/>
+        <v>69</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="76"/>
       <c r="G16" s="50">
         <v>80</v>
       </c>
-      <c r="H16" s="76">
+      <c r="H16" s="75">
         <v>80</v>
       </c>
       <c r="I16" s="49">
@@ -3221,10 +3359,10 @@
       <c r="J16" s="50">
         <v>80</v>
       </c>
-      <c r="K16" s="76">
-        <v>40</v>
-      </c>
-      <c r="L16" s="77">
+      <c r="K16" s="75">
+        <v>40</v>
+      </c>
+      <c r="L16" s="76">
         <v>80</v>
       </c>
       <c r="M16" s="48">
@@ -3239,7 +3377,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P16" s="74">
+      <c r="P16" s="73">
         <f t="shared" ref="P16:P17" si="22">SUM(G16:I16)/20</f>
         <v>14</v>
       </c>
@@ -3281,30 +3419,30 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="80">
+      <c r="A17" s="79">
         <v>46184</v>
       </c>
       <c r="B17" s="47">
         <v>13</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="75">
-        <v>40</v>
-      </c>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
+        <v>70</v>
+      </c>
+      <c r="D17" s="74">
+        <v>40</v>
+      </c>
+      <c r="E17" s="75"/>
+      <c r="F17" s="76"/>
       <c r="G17" s="50">
         <v>40</v>
       </c>
-      <c r="H17" s="76"/>
+      <c r="H17" s="75"/>
       <c r="I17" s="49">
         <v>40</v>
       </c>
       <c r="J17" s="50"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="77">
+      <c r="K17" s="75"/>
+      <c r="L17" s="76">
         <v>80</v>
       </c>
       <c r="M17" s="48">
@@ -3319,7 +3457,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P17" s="74">
+      <c r="P17" s="73">
         <f t="shared" si="22"/>
         <v>4</v>
       </c>
@@ -3361,7 +3499,7 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="80">
+      <c r="A18" s="79">
         <v>46184</v>
       </c>
       <c r="B18" s="47">
@@ -3370,13 +3508,13 @@
       <c r="C18" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="75"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="77"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="76"/>
       <c r="G18" s="50">
         <v>600</v>
       </c>
-      <c r="H18" s="76">
+      <c r="H18" s="75">
         <v>597</v>
       </c>
       <c r="I18" s="49">
@@ -3385,10 +3523,10 @@
       <c r="J18" s="50">
         <v>1597</v>
       </c>
-      <c r="K18" s="76">
+      <c r="K18" s="75">
         <v>1184</v>
       </c>
-      <c r="L18" s="77">
+      <c r="L18" s="76">
         <v>1199</v>
       </c>
       <c r="M18" s="48">
@@ -3403,7 +3541,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P18" s="74">
+      <c r="P18" s="73">
         <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
         <v>99.7</v>
       </c>
@@ -3445,30 +3583,30 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="80">
+      <c r="A19" s="79">
         <v>46184</v>
       </c>
       <c r="B19" s="47">
         <v>15</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="75"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="77"/>
+        <v>76</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="76"/>
       <c r="G19" s="50"/>
-      <c r="H19" s="76"/>
+      <c r="H19" s="75"/>
       <c r="I19" s="49">
         <v>40</v>
       </c>
       <c r="J19" s="50">
         <v>40</v>
       </c>
-      <c r="K19" s="76">
-        <v>40</v>
-      </c>
-      <c r="L19" s="77">
+      <c r="K19" s="75">
+        <v>40</v>
+      </c>
+      <c r="L19" s="76">
         <v>40</v>
       </c>
       <c r="M19" s="48">
@@ -3483,7 +3621,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P19" s="74">
+      <c r="P19" s="73">
         <f t="shared" si="30"/>
         <v>2</v>
       </c>
@@ -3525,22 +3663,22 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="80">
+      <c r="A20" s="79">
         <v>46184</v>
       </c>
       <c r="B20" s="47">
         <v>16</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="75"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
+        <v>63</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
       <c r="G20" s="50">
         <v>40</v>
       </c>
-      <c r="H20" s="76">
+      <c r="H20" s="75">
         <v>40</v>
       </c>
       <c r="I20" s="49">
@@ -3549,10 +3687,10 @@
       <c r="J20" s="50">
         <v>40</v>
       </c>
-      <c r="K20" s="76">
-        <v>40</v>
-      </c>
-      <c r="L20" s="77">
+      <c r="K20" s="75">
+        <v>40</v>
+      </c>
+      <c r="L20" s="76">
         <v>40</v>
       </c>
       <c r="M20" s="48">
@@ -3567,7 +3705,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P20" s="74">
+      <c r="P20" s="73">
         <f t="shared" si="30"/>
         <v>6</v>
       </c>
@@ -3609,22 +3747,22 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="80">
+      <c r="A21" s="79">
         <v>46185</v>
       </c>
       <c r="B21" s="47">
         <v>17</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="75"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="77"/>
+        <v>79</v>
+      </c>
+      <c r="D21" s="74"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="76"/>
       <c r="G21" s="50">
         <v>120</v>
       </c>
-      <c r="H21" s="76">
+      <c r="H21" s="75">
         <v>120</v>
       </c>
       <c r="I21" s="49">
@@ -3633,14 +3771,14 @@
       <c r="J21" s="50">
         <v>120</v>
       </c>
-      <c r="K21" s="76">
+      <c r="K21" s="75">
         <v>120</v>
       </c>
-      <c r="L21" s="77">
+      <c r="L21" s="76">
         <v>120</v>
       </c>
       <c r="M21" s="48">
-        <f t="shared" ref="M21:M28" si="37">SUM(D21:L21)/40</f>
+        <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
         <v>18</v>
       </c>
       <c r="N21" s="39">
@@ -3651,12 +3789,12 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P21" s="74">
-        <f t="shared" ref="P21:P28" si="38">SUM(G21:I21)/20</f>
+      <c r="P21" s="73">
+        <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
         <v>18</v>
       </c>
       <c r="Q21" s="40">
-        <f t="shared" ref="Q21:Q28" si="39">SUM(J21:L21)/20</f>
+        <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
         <v>18</v>
       </c>
       <c r="R21" s="51" t="e">
@@ -3672,58 +3810,58 @@
         <v>0</v>
       </c>
       <c r="U21" s="53" t="e">
-        <f t="shared" ref="U21:U28" si="40">SUM(R21:T21)</f>
+        <f t="shared" ref="U21:U22" si="40">SUM(R21:T21)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V21" s="54" t="e">
-        <f t="shared" ref="V21:V28" si="41">SUM(D21:F21)*$V$3</f>
+        <f t="shared" ref="V21:V22" si="41">SUM(D21:F21)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W21" s="55">
-        <f t="shared" ref="W21:W28" si="42">SUM(G21:I21)*$W$3</f>
+        <f t="shared" ref="W21:W23" si="42">SUM(G21:I21)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X21" s="55">
-        <f t="shared" ref="X21:X28" si="43">SUM(J21:L21)*$X$3</f>
+        <f t="shared" ref="X21:X23" si="43">SUM(J21:L21)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y29" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y47" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="80">
+      <c r="A22" s="79">
         <v>46185</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="133">
         <v>18</v>
       </c>
-      <c r="C22" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="50">
+      <c r="C22" s="127" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="134"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="131">
         <v>300</v>
       </c>
-      <c r="H22" s="76">
+      <c r="H22" s="129">
         <v>300</v>
       </c>
-      <c r="I22" s="49">
+      <c r="I22" s="56">
         <v>300</v>
       </c>
-      <c r="J22" s="50">
+      <c r="J22" s="131">
         <v>300</v>
       </c>
-      <c r="K22" s="76">
+      <c r="K22" s="129">
         <v>300</v>
       </c>
-      <c r="L22" s="77">
+      <c r="L22" s="130">
         <v>300</v>
       </c>
-      <c r="M22" s="48">
+      <c r="M22" s="132">
         <f t="shared" si="37"/>
         <v>45</v>
       </c>
@@ -3735,7 +3873,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P22" s="74">
+      <c r="P22" s="73">
         <f t="shared" si="38"/>
         <v>45</v>
       </c>
@@ -3777,34 +3915,34 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="80">
+      <c r="A23" s="79">
         <v>46189</v>
       </c>
       <c r="B23" s="47">
         <v>19</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="75"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="50">
-        <v>80</v>
-      </c>
-      <c r="H23" s="76">
-        <v>80</v>
-      </c>
-      <c r="I23" s="49">
-        <v>80</v>
-      </c>
-      <c r="J23" s="50">
-        <v>80</v>
-      </c>
-      <c r="K23" s="76">
-        <v>80</v>
-      </c>
-      <c r="L23" s="77">
+        <v>84</v>
+      </c>
+      <c r="D23" s="74"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="137">
+        <v>80</v>
+      </c>
+      <c r="H23" s="138">
+        <v>80</v>
+      </c>
+      <c r="I23" s="139">
+        <v>80</v>
+      </c>
+      <c r="J23" s="137">
+        <v>80</v>
+      </c>
+      <c r="K23" s="138">
+        <v>80</v>
+      </c>
+      <c r="L23" s="140">
         <v>80</v>
       </c>
       <c r="M23" s="48">
@@ -3819,7 +3957,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P23" s="74">
+      <c r="P23" s="73">
         <f t="shared" si="38"/>
         <v>12</v>
       </c>
@@ -3861,34 +3999,34 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="80">
+      <c r="A24" s="79">
         <v>46189</v>
       </c>
       <c r="B24" s="47">
         <v>20</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="75"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="50">
-        <v>80</v>
-      </c>
-      <c r="H24" s="76">
-        <v>80</v>
-      </c>
-      <c r="I24" s="49">
-        <v>80</v>
-      </c>
-      <c r="J24" s="50">
-        <v>80</v>
-      </c>
-      <c r="K24" s="76">
-        <v>80</v>
-      </c>
-      <c r="L24" s="77">
+        <v>85</v>
+      </c>
+      <c r="D24" s="74"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="137">
+        <v>80</v>
+      </c>
+      <c r="H24" s="138">
+        <v>80</v>
+      </c>
+      <c r="I24" s="139">
+        <v>80</v>
+      </c>
+      <c r="J24" s="137">
+        <v>80</v>
+      </c>
+      <c r="K24" s="138">
+        <v>80</v>
+      </c>
+      <c r="L24" s="140">
         <v>80</v>
       </c>
       <c r="M24" s="48">
@@ -3903,7 +4041,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P24" s="74">
+      <c r="P24" s="73">
         <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
         <v>12</v>
       </c>
@@ -3945,34 +4083,34 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="80">
+      <c r="A25" s="79">
         <v>46189</v>
       </c>
       <c r="B25" s="47">
         <v>21</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="75"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="50">
-        <v>80</v>
-      </c>
-      <c r="H25" s="76">
-        <v>80</v>
-      </c>
-      <c r="I25" s="49">
-        <v>80</v>
-      </c>
-      <c r="J25" s="50">
-        <v>80</v>
-      </c>
-      <c r="K25" s="76">
-        <v>80</v>
-      </c>
-      <c r="L25" s="77">
+        <v>86</v>
+      </c>
+      <c r="D25" s="74"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="137">
+        <v>80</v>
+      </c>
+      <c r="H25" s="138">
+        <v>80</v>
+      </c>
+      <c r="I25" s="139">
+        <v>80</v>
+      </c>
+      <c r="J25" s="137">
+        <v>80</v>
+      </c>
+      <c r="K25" s="138">
+        <v>80</v>
+      </c>
+      <c r="L25" s="140">
         <v>80</v>
       </c>
       <c r="M25" s="48">
@@ -3987,7 +4125,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P25" s="74">
+      <c r="P25" s="73">
         <f t="shared" si="48"/>
         <v>12</v>
       </c>
@@ -4029,34 +4167,34 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="80">
+      <c r="A26" s="79">
         <v>46189</v>
       </c>
       <c r="B26" s="47">
         <v>22</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="75"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="50">
-        <v>40</v>
-      </c>
-      <c r="H26" s="76">
-        <v>40</v>
-      </c>
-      <c r="I26" s="49">
-        <v>40</v>
-      </c>
-      <c r="J26" s="50">
-        <v>40</v>
-      </c>
-      <c r="K26" s="76">
-        <v>40</v>
-      </c>
-      <c r="L26" s="77">
+        <v>87</v>
+      </c>
+      <c r="D26" s="74"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="137">
+        <v>40</v>
+      </c>
+      <c r="H26" s="138">
+        <v>40</v>
+      </c>
+      <c r="I26" s="139">
+        <v>40</v>
+      </c>
+      <c r="J26" s="137">
+        <v>40</v>
+      </c>
+      <c r="K26" s="138">
+        <v>40</v>
+      </c>
+      <c r="L26" s="140">
         <v>40</v>
       </c>
       <c r="M26" s="48">
@@ -4071,7 +4209,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P26" s="74">
+      <c r="P26" s="73">
         <f t="shared" si="48"/>
         <v>6</v>
       </c>
@@ -4113,36 +4251,36 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="80">
+      <c r="A27" s="79">
         <v>46189</v>
       </c>
       <c r="B27" s="47">
         <v>23</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="75">
-        <v>80</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="50">
-        <v>80</v>
-      </c>
-      <c r="H27" s="76">
-        <v>80</v>
-      </c>
-      <c r="I27" s="49">
-        <v>80</v>
-      </c>
-      <c r="J27" s="50">
-        <v>80</v>
-      </c>
-      <c r="K27" s="76">
-        <v>80</v>
-      </c>
-      <c r="L27" s="77">
+        <v>88</v>
+      </c>
+      <c r="D27" s="74">
+        <v>80</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="137">
+        <v>80</v>
+      </c>
+      <c r="H27" s="138">
+        <v>80</v>
+      </c>
+      <c r="I27" s="139">
+        <v>80</v>
+      </c>
+      <c r="J27" s="137">
+        <v>80</v>
+      </c>
+      <c r="K27" s="138">
+        <v>80</v>
+      </c>
+      <c r="L27" s="140">
         <v>80</v>
       </c>
       <c r="M27" s="48">
@@ -4157,7 +4295,7 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P27" s="74">
+      <c r="P27" s="73">
         <f t="shared" si="48"/>
         <v>12</v>
       </c>
@@ -4199,40 +4337,40 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="80">
+      <c r="A28" s="79">
         <v>46189</v>
       </c>
       <c r="B28" s="47">
         <v>24</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="75">
+        <v>89</v>
+      </c>
+      <c r="D28" s="74">
         <v>120</v>
       </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="50">
+      <c r="E28" s="75"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="137">
         <v>120</v>
       </c>
-      <c r="H28" s="76">
+      <c r="H28" s="138">
         <v>120</v>
       </c>
-      <c r="I28" s="49">
+      <c r="I28" s="139">
         <v>120</v>
       </c>
-      <c r="J28" s="50">
+      <c r="J28" s="137">
         <v>120</v>
       </c>
-      <c r="K28" s="76">
+      <c r="K28" s="138">
         <v>120</v>
       </c>
-      <c r="L28" s="77">
+      <c r="L28" s="140">
         <v>120</v>
       </c>
       <c r="M28" s="48">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="M28:M46" si="52">SUM(D28:L28)/40</f>
         <v>21</v>
       </c>
       <c r="N28" s="39">
@@ -4243,12 +4381,12 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P28" s="74">
-        <f t="shared" si="38"/>
+      <c r="P28" s="73">
+        <f t="shared" ref="P28:P46" si="53">SUM(G28:I28)/20</f>
         <v>18</v>
       </c>
       <c r="Q28" s="40">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="Q28:Q46" si="54">SUM(J28:L28)/20</f>
         <v>18</v>
       </c>
       <c r="R28" s="51" t="e">
@@ -4264,71 +4402,58 @@
         <v>0</v>
       </c>
       <c r="U28" s="53" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="U28:U46" si="55">SUM(R28:T28)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V28" s="54" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="V28:V46" si="56">SUM(D28:F28)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W28" s="55">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="W28:W46" si="57">SUM(G28:I28)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X28" s="55">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="X28:X46" si="58">SUM(J28:L28)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y28" s="56" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Y28:Y46" si="59">SUM(V28:X28)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="80"/>
-      <c r="B29" s="132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="133"/>
-      <c r="D29" s="90">
-        <f>SUM(D6:D28)</f>
-        <v>1320</v>
-      </c>
-      <c r="E29" s="90">
-        <f t="shared" ref="E29:L29" si="52">SUM(E6:E28)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="90">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="90">
-        <f t="shared" si="52"/>
-        <v>4620</v>
-      </c>
-      <c r="H29" s="90">
-        <f t="shared" si="52"/>
-        <v>4417</v>
-      </c>
-      <c r="I29" s="90">
-        <f t="shared" si="52"/>
-        <v>5617</v>
-      </c>
-      <c r="J29" s="90">
-        <f t="shared" si="52"/>
-        <v>7497</v>
-      </c>
-      <c r="K29" s="90">
-        <f t="shared" si="52"/>
-        <v>6244</v>
-      </c>
-      <c r="L29" s="90">
-        <f t="shared" si="52"/>
-        <v>7259</v>
+      <c r="A29" s="79">
+        <v>46189</v>
+      </c>
+      <c r="B29" s="47">
+        <v>25</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="137">
+        <v>40</v>
+      </c>
+      <c r="H29" s="138">
+        <v>40</v>
+      </c>
+      <c r="I29" s="139">
+        <v>80</v>
+      </c>
+      <c r="J29" s="137">
+        <v>40</v>
+      </c>
+      <c r="K29" s="138"/>
+      <c r="L29" s="140">
+        <v>80</v>
       </c>
       <c r="M29" s="48">
-        <f t="shared" ref="M29:M31" si="53">SUM(D29:L29)/40</f>
-        <v>924.35</v>
+        <f t="shared" ref="M29" si="60">SUM(D29:L29)/40</f>
+        <v>7</v>
       </c>
       <c r="N29" s="39">
         <f t="shared" si="18"/>
@@ -4338,13 +4463,13 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P29" s="74">
-        <f t="shared" ref="P29:P32" si="54">SUM(G29:I29)/20</f>
-        <v>732.7</v>
+      <c r="P29" s="73">
+        <f t="shared" ref="P29" si="61">SUM(G29:I29)/20</f>
+        <v>8</v>
       </c>
       <c r="Q29" s="40">
-        <f t="shared" ref="Q29:Q32" si="55">SUM(J29:L29)/20</f>
-        <v>1050</v>
+        <f t="shared" ref="Q29" si="62">SUM(J29:L29)/20</f>
+        <v>6</v>
       </c>
       <c r="R29" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4359,64 +4484,60 @@
         <v>0</v>
       </c>
       <c r="U29" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="U29" si="63">SUM(R29:T29)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V29" s="54" t="e">
-        <f t="shared" ref="V29:V32" si="56">SUM(D29:F29)*$V$3</f>
+        <f t="shared" ref="V29" si="64">SUM(D29:F29)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W29" s="55">
-        <f t="shared" ref="W29:W32" si="57">SUM(G29:I29)*$W$3</f>
+        <f t="shared" ref="W29" si="65">SUM(G29:I29)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X29" s="55">
-        <f t="shared" ref="X29:X32" si="58">SUM(J29:L29)*$X$3</f>
+        <f t="shared" ref="X29" si="66">SUM(J29:L29)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y29" s="56" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Y29" si="67">SUM(V29:X29)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="80"/>
+      <c r="A30" s="79">
+        <v>46190</v>
+      </c>
       <c r="B30" s="47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="75"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77"/>
+        <v>44</v>
+      </c>
+      <c r="D30" s="74"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76"/>
       <c r="G30" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
-      </c>
-      <c r="H30" s="76">
-        <f>0+600</f>
-        <v>600</v>
+        <v>80</v>
+      </c>
+      <c r="H30" s="75">
+        <v>80</v>
       </c>
       <c r="I30" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
+        <v>200</v>
       </c>
       <c r="J30" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
-      </c>
-      <c r="K30" s="76">
-        <f>600+2400</f>
-        <v>3000</v>
-      </c>
-      <c r="L30" s="77">
-        <f>2200+2800</f>
-        <v>5000</v>
+        <v>80</v>
+      </c>
+      <c r="K30" s="75">
+        <v>80</v>
+      </c>
+      <c r="L30" s="76">
+        <v>200</v>
       </c>
       <c r="M30" s="48">
-        <f t="shared" si="53"/>
-        <v>400</v>
+        <f t="shared" si="52"/>
+        <v>18</v>
       </c>
       <c r="N30" s="39">
         <f t="shared" si="18"/>
@@ -4426,13 +4547,13 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P30" s="74">
+      <c r="P30" s="73">
+        <f t="shared" si="53"/>
+        <v>18</v>
+      </c>
+      <c r="Q30" s="40">
         <f t="shared" si="54"/>
-        <v>230</v>
-      </c>
-      <c r="Q30" s="40">
-        <f t="shared" si="55"/>
-        <v>570</v>
+        <v>18</v>
       </c>
       <c r="R30" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4447,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>#VALUE!</v>
       </c>
       <c r="V30" s="54" t="e">
@@ -4463,43 +4584,44 @@
         <v>0</v>
       </c>
       <c r="Y30" s="56" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="59"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A31" s="79">
+        <v>46190</v>
+      </c>
       <c r="B31" s="47">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="75">
-        <v>1400</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77"/>
+        <v>90</v>
+      </c>
+      <c r="D31" s="74"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
       <c r="G31" s="50">
-        <v>400</v>
-      </c>
-      <c r="H31" s="76">
-        <v>400</v>
+        <v>80</v>
+      </c>
+      <c r="H31" s="75">
+        <v>80</v>
       </c>
       <c r="I31" s="49">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J31" s="50">
-        <v>400</v>
-      </c>
-      <c r="K31" s="76">
-        <v>400</v>
-      </c>
-      <c r="L31" s="77">
-        <v>600</v>
+        <v>80</v>
+      </c>
+      <c r="K31" s="75">
+        <v>80</v>
+      </c>
+      <c r="L31" s="76">
+        <v>80</v>
       </c>
       <c r="M31" s="48">
-        <f t="shared" si="53"/>
-        <v>90</v>
+        <f t="shared" si="52"/>
+        <v>12</v>
       </c>
       <c r="N31" s="39">
         <f t="shared" si="18"/>
@@ -4509,13 +4631,13 @@
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P31" s="74">
+      <c r="P31" s="73">
+        <f t="shared" si="53"/>
+        <v>12</v>
+      </c>
+      <c r="Q31" s="40">
         <f t="shared" si="54"/>
-        <v>40</v>
-      </c>
-      <c r="Q31" s="40">
-        <f t="shared" si="55"/>
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="R31" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4530,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>#VALUE!</v>
       </c>
       <c r="V31" s="54" t="e">
@@ -4546,70 +4668,60 @@
         <v>0</v>
       </c>
       <c r="Y31" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="145" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="146"/>
-      <c r="D32" s="89">
-        <f>SUM(D30:D31)</f>
-        <v>1400</v>
-      </c>
-      <c r="E32" s="89">
-        <f t="shared" ref="E32:L32" si="59">SUM(E30:E31)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="89">
         <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="89">
-        <f t="shared" si="59"/>
-        <v>2280</v>
-      </c>
-      <c r="H32" s="89">
-        <f t="shared" si="59"/>
-        <v>1000</v>
-      </c>
-      <c r="I32" s="89">
-        <f t="shared" si="59"/>
-        <v>2120</v>
-      </c>
-      <c r="J32" s="89">
-        <f t="shared" si="59"/>
-        <v>3800</v>
-      </c>
-      <c r="K32" s="89">
-        <f t="shared" si="59"/>
-        <v>3400</v>
-      </c>
-      <c r="L32" s="89">
-        <f t="shared" si="59"/>
-        <v>5600</v>
-      </c>
-      <c r="M32" s="59">
-        <f t="shared" si="0"/>
-        <v>490</v>
-      </c>
-      <c r="N32" s="60">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A32" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B32" s="47">
+        <v>28</v>
+      </c>
+      <c r="C32" s="127" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="128"/>
+      <c r="E32" s="129"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="131">
+        <v>40</v>
+      </c>
+      <c r="H32" s="129">
+        <v>40</v>
+      </c>
+      <c r="I32" s="56">
+        <v>80</v>
+      </c>
+      <c r="J32" s="131">
+        <v>80</v>
+      </c>
+      <c r="K32" s="129">
+        <v>120</v>
+      </c>
+      <c r="L32" s="130">
+        <v>40</v>
+      </c>
+      <c r="M32" s="132">
+        <f t="shared" si="52"/>
+        <v>10</v>
+      </c>
+      <c r="N32" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O32" s="58">
+      <c r="O32" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P32" s="74">
+      <c r="P32" s="73">
+        <f t="shared" si="53"/>
+        <v>8</v>
+      </c>
+      <c r="Q32" s="40">
         <f t="shared" si="54"/>
-        <v>270</v>
-      </c>
-      <c r="Q32" s="40">
-        <f t="shared" si="55"/>
-        <v>640</v>
+        <v>12</v>
       </c>
       <c r="R32" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4624,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>#VALUE!</v>
       </c>
       <c r="V32" s="54" t="e">
@@ -4640,117 +4752,1665 @@
         <v>0</v>
       </c>
       <c r="Y32" s="56" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A33" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B33" s="47">
+        <v>29</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="74"/>
+      <c r="E33" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="76"/>
+      <c r="G33" s="50">
+        <v>40</v>
+      </c>
+      <c r="H33" s="75">
+        <v>40</v>
+      </c>
+      <c r="I33" s="49">
+        <v>40</v>
+      </c>
+      <c r="J33" s="50">
+        <v>40</v>
+      </c>
+      <c r="K33" s="75">
+        <v>40</v>
+      </c>
+      <c r="L33" s="76">
+        <v>40</v>
+      </c>
+      <c r="M33" s="48">
+        <f t="shared" si="52"/>
+        <v>6</v>
+      </c>
+      <c r="N33" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O33" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P33" s="73">
+        <f t="shared" si="53"/>
+        <v>6</v>
+      </c>
+      <c r="Q33" s="40">
+        <f t="shared" si="54"/>
+        <v>6</v>
+      </c>
+      <c r="R33" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S33" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="53" t="e">
+        <f t="shared" si="55"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V33" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W33" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="56" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A34" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B34" s="47">
+        <v>30</v>
+      </c>
+      <c r="C34" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="74"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="50">
+        <v>40</v>
+      </c>
+      <c r="H34" s="75">
+        <v>40</v>
+      </c>
+      <c r="I34" s="49">
+        <v>40</v>
+      </c>
+      <c r="J34" s="50">
+        <v>40</v>
+      </c>
+      <c r="K34" s="75">
+        <v>40</v>
+      </c>
+      <c r="L34" s="76">
+        <v>40</v>
+      </c>
+      <c r="M34" s="48">
+        <f t="shared" ref="M34:M45" si="68">SUM(D34:L34)/40</f>
+        <v>6</v>
+      </c>
+      <c r="N34" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O34" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P34" s="73">
+        <f t="shared" ref="P34:P45" si="69">SUM(G34:I34)/20</f>
+        <v>6</v>
+      </c>
+      <c r="Q34" s="40">
+        <f t="shared" ref="Q34:Q45" si="70">SUM(J34:L34)/20</f>
+        <v>6</v>
+      </c>
+      <c r="R34" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S34" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="53" t="e">
+        <f t="shared" ref="U34:U45" si="71">SUM(R34:T34)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V34" s="54" t="e">
+        <f t="shared" ref="V34:V45" si="72">SUM(D34:F34)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W34" s="55">
+        <f t="shared" ref="W34:W45" si="73">SUM(G34:I34)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X34" s="55">
+        <f t="shared" ref="X34:X45" si="74">SUM(J34:L34)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="56" t="e">
+        <f t="shared" ref="Y34:Y45" si="75">SUM(V34:X34)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A35" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B35" s="47">
+        <v>31</v>
+      </c>
+      <c r="C35" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="74"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="50">
+        <v>40</v>
+      </c>
+      <c r="H35" s="75">
+        <v>40</v>
+      </c>
+      <c r="I35" s="49">
+        <v>40</v>
+      </c>
+      <c r="J35" s="50">
+        <v>40</v>
+      </c>
+      <c r="K35" s="75">
+        <v>40</v>
+      </c>
+      <c r="L35" s="76">
+        <v>40</v>
+      </c>
+      <c r="M35" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N35" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P35" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q35" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R35" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S35" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V35" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W35" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A36" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B36" s="47">
+        <v>32</v>
+      </c>
+      <c r="C36" s="57" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="74"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="50">
+        <v>40</v>
+      </c>
+      <c r="H36" s="75">
+        <v>40</v>
+      </c>
+      <c r="I36" s="49">
+        <v>40</v>
+      </c>
+      <c r="J36" s="50">
+        <v>40</v>
+      </c>
+      <c r="K36" s="75">
+        <v>40</v>
+      </c>
+      <c r="L36" s="76">
+        <v>40</v>
+      </c>
+      <c r="M36" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N36" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P36" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q36" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R36" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S36" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V36" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W36" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A37" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B37" s="47">
+        <v>33</v>
+      </c>
+      <c r="C37" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="74"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="50">
+        <v>80</v>
+      </c>
+      <c r="H37" s="75">
+        <v>80</v>
+      </c>
+      <c r="I37" s="49">
+        <v>80</v>
+      </c>
+      <c r="J37" s="50">
+        <v>80</v>
+      </c>
+      <c r="K37" s="75">
+        <v>80</v>
+      </c>
+      <c r="L37" s="76">
+        <v>80</v>
+      </c>
+      <c r="M37" s="48">
+        <f t="shared" si="68"/>
+        <v>12</v>
+      </c>
+      <c r="N37" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P37" s="73">
+        <f t="shared" si="69"/>
+        <v>12</v>
+      </c>
+      <c r="Q37" s="40">
+        <f t="shared" si="70"/>
+        <v>12</v>
+      </c>
+      <c r="R37" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S37" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V37" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W37" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A38" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B38" s="47">
+        <v>34</v>
+      </c>
+      <c r="C38" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="74"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="50">
+        <v>40</v>
+      </c>
+      <c r="H38" s="75">
+        <v>40</v>
+      </c>
+      <c r="I38" s="49">
+        <v>40</v>
+      </c>
+      <c r="J38" s="50">
+        <v>40</v>
+      </c>
+      <c r="K38" s="75">
+        <v>40</v>
+      </c>
+      <c r="L38" s="76">
+        <v>40</v>
+      </c>
+      <c r="M38" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N38" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P38" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q38" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R38" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S38" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V38" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W38" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A39" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B39" s="47">
+        <v>35</v>
+      </c>
+      <c r="C39" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="74"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="50">
+        <v>80</v>
+      </c>
+      <c r="H39" s="75">
+        <v>80</v>
+      </c>
+      <c r="I39" s="49">
+        <v>80</v>
+      </c>
+      <c r="J39" s="50">
+        <v>80</v>
+      </c>
+      <c r="K39" s="75">
+        <v>80</v>
+      </c>
+      <c r="L39" s="76">
+        <v>80</v>
+      </c>
+      <c r="M39" s="48">
+        <f t="shared" si="68"/>
+        <v>12</v>
+      </c>
+      <c r="N39" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O39" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P39" s="73">
+        <f t="shared" si="69"/>
+        <v>12</v>
+      </c>
+      <c r="Q39" s="40">
+        <f t="shared" si="70"/>
+        <v>12</v>
+      </c>
+      <c r="R39" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S39" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V39" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W39" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X39" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A40" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B40" s="47">
+        <v>36</v>
+      </c>
+      <c r="C40" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="74"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="50">
+        <v>80</v>
+      </c>
+      <c r="H40" s="75">
+        <v>80</v>
+      </c>
+      <c r="I40" s="49">
+        <v>80</v>
+      </c>
+      <c r="J40" s="50">
+        <v>80</v>
+      </c>
+      <c r="K40" s="75">
+        <v>80</v>
+      </c>
+      <c r="L40" s="76">
+        <v>80</v>
+      </c>
+      <c r="M40" s="48">
+        <f t="shared" si="68"/>
+        <v>12</v>
+      </c>
+      <c r="N40" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O40" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P40" s="73">
+        <f t="shared" si="69"/>
+        <v>12</v>
+      </c>
+      <c r="Q40" s="40">
+        <f t="shared" si="70"/>
+        <v>12</v>
+      </c>
+      <c r="R40" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S40" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V40" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W40" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A41" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B41" s="47">
+        <v>37</v>
+      </c>
+      <c r="C41" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="74"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="50">
+        <v>40</v>
+      </c>
+      <c r="H41" s="75">
+        <v>40</v>
+      </c>
+      <c r="I41" s="49">
+        <v>40</v>
+      </c>
+      <c r="J41" s="50">
+        <v>40</v>
+      </c>
+      <c r="K41" s="75">
+        <v>40</v>
+      </c>
+      <c r="L41" s="76">
+        <v>40</v>
+      </c>
+      <c r="M41" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N41" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P41" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q41" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R41" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S41" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V41" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W41" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A42" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B42" s="47">
+        <v>38</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="74"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="50">
+        <v>40</v>
+      </c>
+      <c r="H42" s="75">
+        <v>40</v>
+      </c>
+      <c r="I42" s="49">
+        <v>40</v>
+      </c>
+      <c r="J42" s="50">
+        <v>40</v>
+      </c>
+      <c r="K42" s="75">
+        <v>40</v>
+      </c>
+      <c r="L42" s="76">
+        <v>40</v>
+      </c>
+      <c r="M42" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N42" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P42" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q42" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R42" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S42" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V42" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W42" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A43" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B43" s="47">
+        <v>39</v>
+      </c>
+      <c r="C43" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="74"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="50">
+        <v>40</v>
+      </c>
+      <c r="H43" s="75">
+        <v>40</v>
+      </c>
+      <c r="I43" s="49">
+        <v>40</v>
+      </c>
+      <c r="J43" s="50">
+        <v>40</v>
+      </c>
+      <c r="K43" s="75">
+        <v>40</v>
+      </c>
+      <c r="L43" s="76">
+        <v>40</v>
+      </c>
+      <c r="M43" s="48">
+        <f t="shared" si="68"/>
+        <v>6</v>
+      </c>
+      <c r="N43" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P43" s="73">
+        <f t="shared" si="69"/>
+        <v>6</v>
+      </c>
+      <c r="Q43" s="40">
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R43" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S43" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V43" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W43" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A44" s="79">
+        <v>46190</v>
+      </c>
+      <c r="B44" s="47">
+        <v>40</v>
+      </c>
+      <c r="C44" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="74"/>
+      <c r="E44" s="75"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="50">
+        <v>80</v>
+      </c>
+      <c r="H44" s="75">
+        <v>80</v>
+      </c>
+      <c r="I44" s="49">
+        <v>80</v>
+      </c>
+      <c r="J44" s="50">
+        <v>80</v>
+      </c>
+      <c r="K44" s="75">
+        <v>80</v>
+      </c>
+      <c r="L44" s="76">
+        <v>80</v>
+      </c>
+      <c r="M44" s="48">
+        <f t="shared" si="68"/>
+        <v>12</v>
+      </c>
+      <c r="N44" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P44" s="73">
+        <f t="shared" si="69"/>
+        <v>12</v>
+      </c>
+      <c r="Q44" s="40">
+        <f t="shared" si="70"/>
+        <v>12</v>
+      </c>
+      <c r="R44" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S44" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V44" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W44" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A45" s="79"/>
+      <c r="B45" s="47">
+        <v>41</v>
+      </c>
+      <c r="C45" s="57"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="75"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="75"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="48">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="N45" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P45" s="73">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="40">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="R45" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S45" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U45" s="53" t="e">
+        <f t="shared" si="71"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V45" s="54" t="e">
+        <f t="shared" si="72"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W45" s="55">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="X45" s="55">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="56" t="e">
+        <f t="shared" si="75"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A46" s="79"/>
+      <c r="B46" s="47">
+        <v>41</v>
+      </c>
+      <c r="C46" s="57"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="75"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="75"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="48">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="N46" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P46" s="73">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="40">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S46" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="53" t="e">
+        <f t="shared" si="55"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V46" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W46" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="56" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A47" s="79"/>
+      <c r="B47" s="175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="176"/>
+      <c r="D47" s="89">
+        <f>SUM(D6:D46)</f>
+        <v>1320</v>
+      </c>
+      <c r="E47" s="89">
+        <f t="shared" ref="E47:L47" si="76">SUM(E6:E46)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="89">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="89">
+        <f t="shared" si="76"/>
+        <v>5500</v>
+      </c>
+      <c r="H47" s="89">
+        <f t="shared" si="76"/>
+        <v>5297</v>
+      </c>
+      <c r="I47" s="89">
+        <f t="shared" si="76"/>
+        <v>6697</v>
+      </c>
+      <c r="J47" s="89">
+        <f t="shared" si="76"/>
+        <v>8417</v>
+      </c>
+      <c r="K47" s="89">
+        <f t="shared" si="76"/>
+        <v>7164</v>
+      </c>
+      <c r="L47" s="89">
+        <f t="shared" si="76"/>
+        <v>8299</v>
+      </c>
+      <c r="M47" s="48">
+        <f t="shared" ref="M47:M50" si="77">SUM(D47:L47)/40</f>
+        <v>1067.3499999999999</v>
+      </c>
+      <c r="N47" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O47" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P47" s="73">
+        <f t="shared" ref="P47:P51" si="78">SUM(G47:I47)/20</f>
+        <v>874.7</v>
+      </c>
+      <c r="Q47" s="40">
+        <f t="shared" ref="Q47:Q51" si="79">SUM(J47:L47)/20</f>
+        <v>1194</v>
+      </c>
+      <c r="R47" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S47" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V47" s="54" t="e">
+        <f t="shared" ref="V47:V51" si="80">SUM(D47:F47)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W47" s="55">
+        <f t="shared" ref="W47:W51" si="81">SUM(G47:I47)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X47" s="55">
+        <f t="shared" ref="X47:X51" si="82">SUM(J47:L47)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A48" s="79"/>
+      <c r="B48" s="121">
+        <v>0</v>
+      </c>
+      <c r="C48" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D48" s="122">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="123"/>
+      <c r="F48" s="124"/>
+      <c r="G48" s="123"/>
+      <c r="H48" s="123"/>
+      <c r="I48" s="124"/>
+      <c r="J48" s="123">
+        <v>520</v>
+      </c>
+      <c r="K48" s="123">
+        <v>920</v>
+      </c>
+      <c r="L48" s="124">
+        <v>960</v>
+      </c>
+      <c r="M48" s="125">
+        <f>SUM(D48:L48)</f>
+        <v>4000</v>
+      </c>
+      <c r="N48" s="39"/>
+      <c r="O48" s="49"/>
+      <c r="P48" s="73"/>
+      <c r="Q48" s="40"/>
+      <c r="R48" s="51"/>
+      <c r="S48" s="52"/>
+      <c r="T48" s="52"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="54"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="56"/>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A49" s="79"/>
+      <c r="B49" s="47">
+        <v>1</v>
+      </c>
+      <c r="C49" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="74"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H49" s="75">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I49" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J49" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K49" s="75">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L49" s="76">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M49" s="48">
+        <f t="shared" si="77"/>
+        <v>400</v>
+      </c>
+      <c r="N49" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O49" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P49" s="73">
+        <f t="shared" si="78"/>
+        <v>230</v>
+      </c>
+      <c r="Q49" s="40">
+        <f t="shared" si="79"/>
+        <v>570</v>
+      </c>
+      <c r="R49" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S49" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V49" s="54" t="e">
+        <f t="shared" si="80"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W49" s="55">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="X49" s="55">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="134" t="s">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B50" s="47">
+        <v>2</v>
+      </c>
+      <c r="C50" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="74">
+        <v>1400</v>
+      </c>
+      <c r="E50" s="75"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="50">
+        <v>400</v>
+      </c>
+      <c r="H50" s="75">
+        <v>400</v>
+      </c>
+      <c r="I50" s="49">
+        <v>0</v>
+      </c>
+      <c r="J50" s="50">
+        <v>400</v>
+      </c>
+      <c r="K50" s="75">
+        <v>400</v>
+      </c>
+      <c r="L50" s="76">
+        <v>600</v>
+      </c>
+      <c r="M50" s="48">
+        <f t="shared" si="77"/>
+        <v>90</v>
+      </c>
+      <c r="N50" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P50" s="73">
+        <f t="shared" si="78"/>
+        <v>40</v>
+      </c>
+      <c r="Q50" s="40">
+        <f t="shared" si="79"/>
+        <v>70</v>
+      </c>
+      <c r="R50" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S50" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V50" s="54" t="e">
+        <f t="shared" si="80"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W50" s="55">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="55">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="163" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="164"/>
+      <c r="D51" s="88">
+        <f>SUM(D49:D50)</f>
+        <v>1400</v>
+      </c>
+      <c r="E51" s="88">
+        <f t="shared" ref="E51:L51" si="83">SUM(E49:E50)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="88">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="88">
+        <f t="shared" si="83"/>
+        <v>2280</v>
+      </c>
+      <c r="H51" s="88">
+        <f t="shared" si="83"/>
+        <v>1000</v>
+      </c>
+      <c r="I51" s="88">
+        <f t="shared" si="83"/>
+        <v>2120</v>
+      </c>
+      <c r="J51" s="88">
+        <f t="shared" si="83"/>
+        <v>3800</v>
+      </c>
+      <c r="K51" s="88">
+        <f t="shared" si="83"/>
+        <v>3400</v>
+      </c>
+      <c r="L51" s="88">
+        <f t="shared" si="83"/>
+        <v>5600</v>
+      </c>
+      <c r="M51" s="126">
+        <f>SUM(M48:M50)</f>
+        <v>4490</v>
+      </c>
+      <c r="N51" s="59">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O51" s="58">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P51" s="73">
+        <f t="shared" si="78"/>
+        <v>270</v>
+      </c>
+      <c r="Q51" s="40">
+        <f t="shared" si="79"/>
+        <v>640</v>
+      </c>
+      <c r="R51" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S51" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V51" s="54" t="e">
+        <f t="shared" si="80"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W51" s="55">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="55">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="135"/>
-      <c r="D33" s="91">
-        <f>SUM(D29,D32)</f>
+      <c r="C52" s="153"/>
+      <c r="D52" s="90">
+        <f>SUM(D47,D51)</f>
         <v>2720</v>
       </c>
-      <c r="E33" s="91">
-        <f t="shared" ref="E33:L33" si="60">SUM(E29,E32)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="91">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="91">
-        <f t="shared" si="60"/>
-        <v>6900</v>
-      </c>
-      <c r="H33" s="91">
-        <f t="shared" si="60"/>
-        <v>5417</v>
-      </c>
-      <c r="I33" s="91">
-        <f t="shared" si="60"/>
-        <v>7737</v>
-      </c>
-      <c r="J33" s="91">
-        <f t="shared" si="60"/>
-        <v>11297</v>
-      </c>
-      <c r="K33" s="91">
-        <f t="shared" si="60"/>
-        <v>9644</v>
-      </c>
-      <c r="L33" s="91">
-        <f t="shared" si="60"/>
-        <v>12859</v>
-      </c>
-      <c r="M33" s="61">
+      <c r="E52" s="90">
+        <f t="shared" ref="E52:L52" si="84">SUM(E47,E51)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="90">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="G52" s="90">
+        <f t="shared" si="84"/>
+        <v>7780</v>
+      </c>
+      <c r="H52" s="90">
+        <f t="shared" si="84"/>
+        <v>6297</v>
+      </c>
+      <c r="I52" s="90">
+        <f t="shared" si="84"/>
+        <v>8817</v>
+      </c>
+      <c r="J52" s="90">
+        <f t="shared" si="84"/>
+        <v>12217</v>
+      </c>
+      <c r="K52" s="90">
+        <f t="shared" si="84"/>
+        <v>10564</v>
+      </c>
+      <c r="L52" s="90">
+        <f t="shared" si="84"/>
+        <v>13899</v>
+      </c>
+      <c r="M52" s="60">
         <f t="shared" si="0"/>
-        <v>1414.35</v>
-      </c>
-      <c r="N33" s="64">
-        <f>SUM(N5:N32)</f>
-        <v>0</v>
-      </c>
-      <c r="O33" s="62">
-        <f t="shared" ref="O33:Y33" si="61">SUM(O5:O32)</f>
-        <v>9285.64</v>
-      </c>
-      <c r="P33" s="63">
-        <f t="shared" si="61"/>
-        <v>2259.9499999999998</v>
-      </c>
-      <c r="Q33" s="65">
-        <f t="shared" si="61"/>
-        <v>4077.1</v>
-      </c>
-      <c r="R33" s="66" t="e">
-        <f t="shared" si="61"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S33" s="67">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="67">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="68" t="e">
-        <f t="shared" si="61"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V33" s="69" t="e">
-        <f t="shared" si="61"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W33" s="70">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="70">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="71" t="e">
-        <f t="shared" si="61"/>
+        <v>1557.35</v>
+      </c>
+      <c r="N52" s="63">
+        <f>SUM(N5:N51)</f>
+        <v>0</v>
+      </c>
+      <c r="O52" s="61">
+        <f t="shared" ref="O52:Y52" si="85">SUM(O5:O51)</f>
+        <v>15254.979999999985</v>
+      </c>
+      <c r="P52" s="62">
+        <f t="shared" si="85"/>
+        <v>2543.9499999999998</v>
+      </c>
+      <c r="Q52" s="64">
+        <f t="shared" si="85"/>
+        <v>4365.1000000000004</v>
+      </c>
+      <c r="R52" s="65" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S52" s="66">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="66">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="67" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V52" s="68" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W52" s="69">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="X52" s="69">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="70" t="e">
+        <f t="shared" si="85"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4758,7 +6418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:O13"/>
+  <dimension ref="C2:O25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -4771,51 +6431,50 @@
     <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="38.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.08984375" customWidth="1"/>
-    <col min="14" max="14" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="147" t="s">
+      <c r="C3" s="177" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="148"/>
-      <c r="E3" s="148"/>
-      <c r="F3" s="148"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="151" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="181" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="182"/>
+      <c r="K3" s="183" t="s">
+        <v>81</v>
+      </c>
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="183"/>
+    </row>
+    <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="111"/>
+      <c r="D4" s="81" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="112" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="106" t="s">
         <v>78</v>
-      </c>
-      <c r="I3" s="152"/>
-      <c r="K3" s="153" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="153"/>
-      <c r="M3" s="153"/>
-      <c r="N3" s="153"/>
-      <c r="O3" s="153"/>
-    </row>
-    <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="112"/>
-      <c r="D4" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="82" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="107" t="s">
-        <v>79</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -4830,32 +6489,32 @@
         <v>10</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="95">
-        <v>353</v>
-      </c>
-      <c r="E5" s="81">
-        <v>924.35</v>
-      </c>
-      <c r="F5" s="81">
-        <v>490</v>
-      </c>
-      <c r="G5" s="115">
+      <c r="D5" s="94">
+        <v>435.95</v>
+      </c>
+      <c r="E5" s="80">
+        <v>1067.3499999999999</v>
+      </c>
+      <c r="F5" s="80">
+        <v>550</v>
+      </c>
+      <c r="G5" s="114">
         <f>SUM(D5:F5)</f>
-        <v>1767.35</v>
-      </c>
-      <c r="H5" s="108">
+        <v>2053.3000000000002</v>
+      </c>
+      <c r="H5" s="107">
         <v>10000</v>
       </c>
-      <c r="I5" s="109">
+      <c r="I5" s="108">
         <f>G5-H5</f>
-        <v>-8232.65</v>
+        <v>-7946.7</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -4864,43 +6523,43 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>20391</v>
+        <v>16359</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>509.77499999999998</v>
-      </c>
-      <c r="O5" s="83">
-        <v>99</v>
+        <v>408.97500000000002</v>
+      </c>
+      <c r="O5" s="82">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="117">
+      <c r="D6" s="116">
         <f>D5*40</f>
-        <v>14120</v>
-      </c>
-      <c r="E6" s="118">
+        <v>17438</v>
+      </c>
+      <c r="E6" s="117">
         <f>E5*40</f>
-        <v>36974</v>
-      </c>
-      <c r="F6" s="118">
+        <v>42694</v>
+      </c>
+      <c r="F6" s="117">
         <f>F5*40</f>
-        <v>19600</v>
-      </c>
-      <c r="G6" s="119">
+        <v>22000</v>
+      </c>
+      <c r="G6" s="118">
         <f>SUM(D6:F6)</f>
-        <v>70694</v>
-      </c>
-      <c r="H6" s="110">
+        <v>82132</v>
+      </c>
+      <c r="H6" s="109">
         <f>H5*40</f>
         <v>400000</v>
       </c>
-      <c r="I6" s="111">
+      <c r="I6" s="110">
         <f>G6-H6</f>
-        <v>-329306</v>
+        <v>-317868</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -4909,18 +6568,18 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>21114</v>
+        <v>17947</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>527.85</v>
-      </c>
-      <c r="O6" s="83">
-        <v>54</v>
+        <v>448.67500000000001</v>
+      </c>
+      <c r="O6" s="82">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="93"/>
+      <c r="C7" s="92"/>
       <c r="K7" s="1" t="s">
         <v>3</v>
       </c>
@@ -4928,18 +6587,18 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>10976</v>
+        <v>6390</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>274.39999999999998</v>
-      </c>
-      <c r="O7" s="83">
-        <v>17</v>
+        <v>159.75</v>
+      </c>
+      <c r="O7" s="82">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="83" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -4949,27 +6608,27 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>22714</v>
+        <v>17573</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>567.85</v>
-      </c>
-      <c r="O8" s="83">
-        <v>4</v>
+        <v>439.32499999999999</v>
+      </c>
+      <c r="O8" s="82">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="120">
+      <c r="D9" s="119">
         <f>D8-D5</f>
-        <v>-353</v>
-      </c>
-      <c r="E9" s="120">
+        <v>-435.95</v>
+      </c>
+      <c r="E9" s="119">
         <f>E8-E5</f>
-        <v>-924.35</v>
+        <v>-1067.3499999999999</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -4978,14 +6637,14 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>24231</v>
+        <v>11088</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>605.77499999999998</v>
-      </c>
-      <c r="O9" s="83">
-        <v>18</v>
+        <v>277.2</v>
+      </c>
+      <c r="O9" s="82">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -4996,25 +6655,25 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>14849</v>
+        <v>16398</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>371.22500000000002</v>
-      </c>
-      <c r="O10" s="83">
-        <v>2</v>
+        <v>409.95</v>
+      </c>
+      <c r="O10" s="82">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="150" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="150"/>
-      <c r="F11" s="150" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="150"/>
+      <c r="C11" s="180" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="180"/>
+      <c r="F11" s="180" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="180"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -5022,29 +6681,29 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>58621</v>
+        <v>58249</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1465.5250000000001</v>
-      </c>
-      <c r="O11" s="83">
-        <v>5</v>
+        <v>1456.2249999999999</v>
+      </c>
+      <c r="O11" s="82">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="94">
+      <c r="D12" s="93">
         <v>500.9</v>
       </c>
-      <c r="F12" s="102" t="s">
+      <c r="F12" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="104">
+      <c r="G12" s="103">
         <f>D12+G5</f>
-        <v>2268.25</v>
+        <v>2554.2000000000003</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -5052,32 +6711,182 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>172896</v>
+        <v>144004</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>4322.3999999999996</v>
+        <v>3600.1</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="104">
+      <c r="D13" s="103">
         <f>D12*40</f>
         <v>20036</v>
       </c>
-      <c r="F13" s="103" t="s">
+      <c r="F13" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="104">
+      <c r="G13" s="103">
         <f>G12*40</f>
-        <v>90730</v>
-      </c>
+        <v>102168.00000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="K16" s="148" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="148" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="148" t="s">
+        <v>75</v>
+      </c>
+      <c r="N16" s="148" t="s">
+        <v>110</v>
+      </c>
+      <c r="O16" s="141"/>
+    </row>
+    <row r="17" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K17" s="144" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="146">
+        <v>70</v>
+      </c>
+      <c r="M17" s="145">
+        <v>9659</v>
+      </c>
+      <c r="N17" s="145">
+        <v>16359</v>
+      </c>
+      <c r="O17" s="142"/>
+    </row>
+    <row r="18" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L18" s="147">
+        <v>70</v>
+      </c>
+      <c r="M18" s="5">
+        <v>8160</v>
+      </c>
+      <c r="N18" s="5">
+        <v>17947</v>
+      </c>
+      <c r="O18" s="142"/>
+    </row>
+    <row r="19" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L19" s="147">
+        <v>70</v>
+      </c>
+      <c r="M19" s="5">
+        <v>10451</v>
+      </c>
+      <c r="N19" s="5">
+        <v>6390</v>
+      </c>
+      <c r="O19" s="142"/>
+    </row>
+    <row r="20" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="147">
+        <v>120</v>
+      </c>
+      <c r="M20" s="5">
+        <v>15901</v>
+      </c>
+      <c r="N20" s="5">
+        <v>17573</v>
+      </c>
+      <c r="O20" s="142"/>
+    </row>
+    <row r="21" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="147">
+        <v>120</v>
+      </c>
+      <c r="M21" s="5">
+        <v>14283</v>
+      </c>
+      <c r="N21" s="5">
+        <v>11088</v>
+      </c>
+      <c r="O21" s="142"/>
+    </row>
+    <row r="22" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L22" s="147">
+        <v>120</v>
+      </c>
+      <c r="M22" s="5">
+        <v>18153</v>
+      </c>
+      <c r="N22" s="5">
+        <v>16398</v>
+      </c>
+      <c r="O22" s="142"/>
+    </row>
+    <row r="23" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="147">
+        <v>60</v>
+      </c>
+      <c r="M23" s="5">
+        <v>5525</v>
+      </c>
+      <c r="N23" s="5">
+        <v>58249</v>
+      </c>
+      <c r="O23" s="142"/>
+    </row>
+    <row r="24" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K24" s="149" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="150"/>
+      <c r="M24" s="151">
+        <f>SUM(M17:M23)</f>
+        <v>82132</v>
+      </c>
+      <c r="N24" s="151">
+        <f>SUM(N17:N23)</f>
+        <v>144004</v>
+      </c>
+      <c r="O24" s="143"/>
+    </row>
+    <row r="25" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="K25" s="149" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="150"/>
+      <c r="M25" s="151">
+        <f>M24/40</f>
+        <v>2053.3000000000002</v>
+      </c>
+      <c r="N25" s="151">
+        <f>N24/40</f>
+        <v>3600.1</v>
+      </c>
+      <c r="O25" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5105,13 +6914,13 @@
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="82" t="s">
         <v>9</v>
       </c>
     </row>
@@ -5218,16 +7027,16 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="85"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="88"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="87"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2146169-D6EA-4DE3-A48F-4C302D6D0163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF4850B-BDA4-4F6E-B53D-1C5F35728833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="160">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -359,6 +359,150 @@
   </si>
   <si>
     <t>Products</t>
+  </si>
+  <si>
+    <t>Rambo 5 Orders</t>
+  </si>
+  <si>
+    <t>DIFF</t>
+  </si>
+  <si>
+    <t>Gourmet Food Shama Cenema</t>
+  </si>
+  <si>
+    <t>Gourmet Food Temple Road</t>
+  </si>
+  <si>
+    <t>Gourmet Food Shadman</t>
+  </si>
+  <si>
+    <t>Gourmet Food Nisbat Road</t>
+  </si>
+  <si>
+    <t>Gourmet Food Sultanpura</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Nilam Cinema</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Lal pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Jhora Pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Zarar Shaheed Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Sadar Kachari</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Dharampura</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Shadbagh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food About Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Ghalib Market</t>
+  </si>
+  <si>
+    <t>Al -fatah</t>
+  </si>
+  <si>
+    <t>20-06-26</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Gourmet Food</t>
+  </si>
+  <si>
+    <t>Aslam Super mart</t>
+  </si>
+  <si>
+    <t>4 Seasons</t>
+  </si>
+  <si>
+    <t>Raheem wapda</t>
+  </si>
+  <si>
+    <t>Raheem iqbal</t>
+  </si>
+  <si>
+    <t>On The Way</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Al Raheem Iqbal Town</t>
+  </si>
+  <si>
+    <t>Al Raheem Wapda Town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air Line Society </t>
+  </si>
+  <si>
+    <t>Barkat Market</t>
+  </si>
+  <si>
+    <t>College Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EME Society </t>
+  </si>
+  <si>
+    <t>Miletry Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moter Way </t>
+  </si>
+  <si>
+    <t>Peco Road</t>
+  </si>
+  <si>
+    <t>Punjab Housing Socity</t>
+  </si>
+  <si>
+    <t>Rehber DHA</t>
+  </si>
+  <si>
+    <t>Riwand Road</t>
+  </si>
+  <si>
+    <t>Umer Chowk</t>
+  </si>
+  <si>
+    <t>Velencia Town</t>
+  </si>
+  <si>
+    <t>Wapda Town</t>
+  </si>
+  <si>
+    <t>Chung</t>
+  </si>
+  <si>
+    <t>Behria Town</t>
+  </si>
+  <si>
+    <t>TownShip Lahore</t>
+  </si>
+  <si>
+    <t>PerSntage</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
 </sst>
 </file>
@@ -463,7 +607,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -530,6 +674,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="58">
     <border>
@@ -1253,7 +1403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1591,15 +1741,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1618,6 +1759,83 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1655,42 +1873,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1719,7 +1901,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2193,20 +2386,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="164">
         <v>46186</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2228,10 +2422,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="186" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="165" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2264,13 +2458,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="178"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="182"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2289,8 +2483,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="186"/>
+      <c r="B3" s="166"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2321,29 +2515,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="184"/>
+      <c r="O3" s="185"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="169"/>
+      <c r="T3" s="169"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="173"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="186"/>
+      <c r="B4" s="167"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2534,7 +2728,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M52" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M85" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2542,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O51" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O84" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2554,15 +2748,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R51" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R84" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S51" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S84" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T51" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T84" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2710,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N51" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N84" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3150,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U51" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U84" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3166,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y51" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y84" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3826,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y47" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y80" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4370,7 +4564,7 @@
         <v>120</v>
       </c>
       <c r="M28" s="48">
-        <f t="shared" ref="M28:M46" si="52">SUM(D28:L28)/40</f>
+        <f t="shared" ref="M28:M60" si="52">SUM(D28:L28)/40</f>
         <v>21</v>
       </c>
       <c r="N28" s="39">
@@ -4382,11 +4576,11 @@
         <v>331.63</v>
       </c>
       <c r="P28" s="73">
-        <f t="shared" ref="P28:P46" si="53">SUM(G28:I28)/20</f>
+        <f t="shared" ref="P28:P60" si="53">SUM(G28:I28)/20</f>
         <v>18</v>
       </c>
       <c r="Q28" s="40">
-        <f t="shared" ref="Q28:Q46" si="54">SUM(J28:L28)/20</f>
+        <f t="shared" ref="Q28:Q60" si="54">SUM(J28:L28)/20</f>
         <v>18</v>
       </c>
       <c r="R28" s="51" t="e">
@@ -4402,23 +4596,23 @@
         <v>0</v>
       </c>
       <c r="U28" s="53" t="e">
-        <f t="shared" ref="U28:U46" si="55">SUM(R28:T28)</f>
+        <f t="shared" ref="U28:U60" si="55">SUM(R28:T28)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V28" s="54" t="e">
-        <f t="shared" ref="V28:V46" si="56">SUM(D28:F28)*$V$3</f>
+        <f t="shared" ref="V28:V60" si="56">SUM(D28:F28)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W28" s="55">
-        <f t="shared" ref="W28:W46" si="57">SUM(G28:I28)*$W$3</f>
+        <f t="shared" ref="W28:W60" si="57">SUM(G28:I28)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X28" s="55">
-        <f t="shared" ref="X28:X46" si="58">SUM(J28:L28)*$X$3</f>
+        <f t="shared" ref="X28:X60" si="58">SUM(J28:L28)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y28" s="56" t="e">
-        <f t="shared" ref="Y28:Y46" si="59">SUM(V28:X28)</f>
+        <f t="shared" ref="Y28:Y60" si="59">SUM(V28:X28)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4874,7 +5068,7 @@
         <v>40</v>
       </c>
       <c r="M34" s="48">
-        <f t="shared" ref="M34:M45" si="68">SUM(D34:L34)/40</f>
+        <f t="shared" ref="M34:M46" si="68">SUM(D34:L34)/40</f>
         <v>6</v>
       </c>
       <c r="N34" s="39">
@@ -4886,11 +5080,11 @@
         <v>331.63</v>
       </c>
       <c r="P34" s="73">
-        <f t="shared" ref="P34:P45" si="69">SUM(G34:I34)/20</f>
+        <f t="shared" ref="P34:P46" si="69">SUM(G34:I34)/20</f>
         <v>6</v>
       </c>
       <c r="Q34" s="40">
-        <f t="shared" ref="Q34:Q45" si="70">SUM(J34:L34)/20</f>
+        <f t="shared" ref="Q34:Q46" si="70">SUM(J34:L34)/20</f>
         <v>6</v>
       </c>
       <c r="R34" s="51" t="e">
@@ -4914,11 +5108,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="W34" s="55">
-        <f t="shared" ref="W34:W45" si="73">SUM(G34:I34)*$W$3</f>
+        <f t="shared" ref="W34:W46" si="73">SUM(G34:I34)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X34" s="55">
-        <f t="shared" ref="X34:X45" si="74">SUM(J34:L34)*$X$3</f>
+        <f t="shared" ref="X34:X46" si="74">SUM(J34:L34)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y34" s="56" t="e">
@@ -5767,23 +5961,39 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="79">
+        <v>46191</v>
+      </c>
       <c r="B45" s="47">
         <v>41</v>
       </c>
-      <c r="C45" s="57"/>
+      <c r="C45" s="57" t="s">
+        <v>112</v>
+      </c>
       <c r="D45" s="74"/>
       <c r="E45" s="75"/>
       <c r="F45" s="76"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="76"/>
+      <c r="G45" s="50">
+        <v>280</v>
+      </c>
+      <c r="H45" s="75">
+        <v>600</v>
+      </c>
+      <c r="I45" s="49">
+        <v>600</v>
+      </c>
+      <c r="J45" s="50">
+        <v>520</v>
+      </c>
+      <c r="K45" s="75">
+        <v>760</v>
+      </c>
+      <c r="L45" s="76">
+        <v>760</v>
+      </c>
       <c r="M45" s="48">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="N45" s="39">
         <f t="shared" si="18"/>
@@ -5795,11 +6005,11 @@
       </c>
       <c r="P45" s="73">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q45" s="40">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="R45" s="51" t="e">
         <f t="shared" si="4"/>
@@ -5835,23 +6045,39 @@
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="79">
+        <v>46191</v>
+      </c>
       <c r="B46" s="47">
-        <v>41</v>
-      </c>
-      <c r="C46" s="57"/>
+        <v>42</v>
+      </c>
+      <c r="C46" s="57" t="s">
+        <v>114</v>
+      </c>
       <c r="D46" s="74"/>
       <c r="E46" s="75"/>
       <c r="F46" s="76"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="50"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="76"/>
+      <c r="G46" s="50">
+        <v>40</v>
+      </c>
+      <c r="H46" s="75">
+        <v>40</v>
+      </c>
+      <c r="I46" s="49">
+        <v>40</v>
+      </c>
+      <c r="J46" s="50">
+        <v>40</v>
+      </c>
+      <c r="K46" s="75">
+        <v>40</v>
+      </c>
+      <c r="L46" s="76">
+        <v>40</v>
+      </c>
       <c r="M46" s="48">
-        <f t="shared" si="52"/>
-        <v>0</v>
+        <f t="shared" si="68"/>
+        <v>6</v>
       </c>
       <c r="N46" s="39">
         <f t="shared" si="18"/>
@@ -5862,91 +6088,62 @@
         <v>331.63</v>
       </c>
       <c r="P46" s="73">
-        <f t="shared" si="53"/>
-        <v>0</v>
+        <f t="shared" si="69"/>
+        <v>6</v>
       </c>
       <c r="Q46" s="40">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="R46" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S46" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T46" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U46" s="53" t="e">
-        <f t="shared" si="55"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V46" s="54" t="e">
-        <f t="shared" si="56"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="70"/>
+        <v>6</v>
+      </c>
+      <c r="R46" s="51"/>
+      <c r="S46" s="52"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="53"/>
+      <c r="V46" s="54"/>
       <c r="W46" s="55">
-        <f t="shared" si="57"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="X46" s="55">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="56" t="e">
-        <f t="shared" si="59"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="56"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
-      <c r="B47" s="175" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="176"/>
-      <c r="D47" s="89">
-        <f>SUM(D6:D46)</f>
-        <v>1320</v>
-      </c>
-      <c r="E47" s="89">
-        <f t="shared" ref="E47:L47" si="76">SUM(E6:E46)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="89">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="G47" s="89">
-        <f t="shared" si="76"/>
-        <v>5500</v>
-      </c>
-      <c r="H47" s="89">
-        <f t="shared" si="76"/>
-        <v>5297</v>
-      </c>
-      <c r="I47" s="89">
-        <f t="shared" si="76"/>
-        <v>6697</v>
-      </c>
-      <c r="J47" s="89">
-        <f t="shared" si="76"/>
-        <v>8417</v>
-      </c>
-      <c r="K47" s="89">
-        <f t="shared" si="76"/>
-        <v>7164</v>
-      </c>
-      <c r="L47" s="89">
-        <f t="shared" si="76"/>
-        <v>8299</v>
+      <c r="A47" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B47" s="47">
+        <v>43</v>
+      </c>
+      <c r="C47" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="74"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="50">
+        <v>40</v>
+      </c>
+      <c r="H47" s="75">
+        <v>40</v>
+      </c>
+      <c r="I47" s="49">
+        <v>40</v>
+      </c>
+      <c r="J47" s="50">
+        <v>40</v>
+      </c>
+      <c r="K47" s="75">
+        <v>40</v>
+      </c>
+      <c r="L47" s="76">
+        <v>40</v>
       </c>
       <c r="M47" s="48">
-        <f t="shared" ref="M47:M50" si="77">SUM(D47:L47)/40</f>
-        <v>1067.3499999999999</v>
+        <f t="shared" ref="M47:M59" si="76">SUM(D47:L47)/40</f>
+        <v>6</v>
       </c>
       <c r="N47" s="39">
         <f t="shared" si="18"/>
@@ -5957,126 +6154,128 @@
         <v>331.63</v>
       </c>
       <c r="P47" s="73">
-        <f t="shared" ref="P47:P51" si="78">SUM(G47:I47)/20</f>
-        <v>874.7</v>
+        <f t="shared" ref="P47:P59" si="77">SUM(G47:I47)/20</f>
+        <v>6</v>
       </c>
       <c r="Q47" s="40">
-        <f t="shared" ref="Q47:Q51" si="79">SUM(J47:L47)/20</f>
-        <v>1194</v>
-      </c>
-      <c r="R47" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S47" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T47" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U47" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V47" s="54" t="e">
-        <f t="shared" ref="V47:V51" si="80">SUM(D47:F47)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" ref="Q47:Q59" si="78">SUM(J47:L47)/20</f>
+        <v>6</v>
+      </c>
+      <c r="R47" s="51"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="53"/>
+      <c r="V47" s="54"/>
       <c r="W47" s="55">
-        <f t="shared" ref="W47:W51" si="81">SUM(G47:I47)*$W$3</f>
+        <f t="shared" ref="W47:W59" si="79">SUM(G47:I47)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X47" s="55">
-        <f t="shared" ref="X47:X51" si="82">SUM(J47:L47)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="56" t="e">
-        <f t="shared" si="44"/>
-        <v>#VALUE!</v>
-      </c>
+        <f t="shared" ref="X47:X59" si="80">SUM(J47:L47)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="56"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
-      <c r="B48" s="121">
-        <v>0</v>
+      <c r="A48" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B48" s="47">
+        <v>44</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="122">
-        <v>1600</v>
-      </c>
-      <c r="E48" s="123"/>
-      <c r="F48" s="124"/>
-      <c r="G48" s="123"/>
-      <c r="H48" s="123"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="123">
-        <v>520</v>
-      </c>
-      <c r="K48" s="123">
-        <v>920</v>
-      </c>
-      <c r="L48" s="124">
-        <v>960</v>
-      </c>
-      <c r="M48" s="125">
-        <f>SUM(D48:L48)</f>
-        <v>4000</v>
-      </c>
-      <c r="N48" s="39"/>
-      <c r="O48" s="49"/>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="40"/>
+        <v>116</v>
+      </c>
+      <c r="D48" s="74"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="50">
+        <v>40</v>
+      </c>
+      <c r="H48" s="75">
+        <v>40</v>
+      </c>
+      <c r="I48" s="49">
+        <v>40</v>
+      </c>
+      <c r="J48" s="50">
+        <v>40</v>
+      </c>
+      <c r="K48" s="75">
+        <v>40</v>
+      </c>
+      <c r="L48" s="76">
+        <v>40</v>
+      </c>
+      <c r="M48" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N48" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O48" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P48" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q48" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
       <c r="R48" s="51"/>
       <c r="S48" s="52"/>
       <c r="T48" s="52"/>
       <c r="U48" s="53"/>
       <c r="V48" s="54"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="55"/>
+      <c r="W48" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X48" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="79"/>
+      <c r="A49" s="79">
+        <v>46191</v>
+      </c>
       <c r="B49" s="47">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="D49" s="74"/>
       <c r="E49" s="75"/>
       <c r="F49" s="76"/>
       <c r="G49" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
+        <v>40</v>
       </c>
       <c r="H49" s="75">
-        <f>0+600</f>
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="I49" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
+        <v>40</v>
       </c>
       <c r="J49" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
+        <v>40</v>
       </c>
       <c r="K49" s="75">
-        <f>600+2400</f>
-        <v>3000</v>
+        <v>40</v>
       </c>
       <c r="L49" s="76">
-        <f>2200+2800</f>
-        <v>5000</v>
+        <v>40</v>
       </c>
       <c r="M49" s="48">
-        <f t="shared" si="77"/>
-        <v>400</v>
+        <f t="shared" si="76"/>
+        <v>6</v>
       </c>
       <c r="N49" s="39">
         <f t="shared" si="18"/>
@@ -6087,79 +6286,62 @@
         <v>331.63</v>
       </c>
       <c r="P49" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q49" s="40">
         <f t="shared" si="78"/>
-        <v>230</v>
-      </c>
-      <c r="Q49" s="40">
+        <v>6</v>
+      </c>
+      <c r="R49" s="51"/>
+      <c r="S49" s="52"/>
+      <c r="T49" s="52"/>
+      <c r="U49" s="53"/>
+      <c r="V49" s="54"/>
+      <c r="W49" s="55">
         <f t="shared" si="79"/>
-        <v>570</v>
-      </c>
-      <c r="R49" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S49" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T49" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U49" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V49" s="54" t="e">
+        <v>0</v>
+      </c>
+      <c r="X49" s="55">
         <f t="shared" si="80"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W49" s="55">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="X49" s="55">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A50" s="79">
+        <v>46191</v>
+      </c>
       <c r="B50" s="47">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="74">
-        <v>1400</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="D50" s="74"/>
       <c r="E50" s="75"/>
       <c r="F50" s="76"/>
       <c r="G50" s="50">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="H50" s="75">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="I50" s="49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J50" s="50">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="K50" s="75">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="L50" s="76">
-        <v>600</v>
+        <v>40</v>
       </c>
       <c r="M50" s="48">
-        <f t="shared" si="77"/>
-        <v>90</v>
+        <f t="shared" si="76"/>
+        <v>6</v>
       </c>
       <c r="N50" s="39">
         <f t="shared" si="18"/>
@@ -6170,248 +6352,2799 @@
         <v>331.63</v>
       </c>
       <c r="P50" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q50" s="40">
         <f t="shared" si="78"/>
-        <v>40</v>
-      </c>
-      <c r="Q50" s="40">
+        <v>6</v>
+      </c>
+      <c r="R50" s="51"/>
+      <c r="S50" s="52"/>
+      <c r="T50" s="52"/>
+      <c r="U50" s="53"/>
+      <c r="V50" s="54"/>
+      <c r="W50" s="55">
         <f t="shared" si="79"/>
-        <v>70</v>
-      </c>
-      <c r="R50" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S50" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T50" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U50" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V50" s="54" t="e">
+        <v>0</v>
+      </c>
+      <c r="X50" s="55">
         <f t="shared" si="80"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W50" s="55">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="X50" s="55">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="163" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="164"/>
-      <c r="D51" s="88">
-        <f>SUM(D49:D50)</f>
-        <v>1400</v>
-      </c>
-      <c r="E51" s="88">
-        <f t="shared" ref="E51:L51" si="83">SUM(E49:E50)</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="88">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="G51" s="88">
-        <f t="shared" si="83"/>
-        <v>2280</v>
-      </c>
-      <c r="H51" s="88">
-        <f t="shared" si="83"/>
-        <v>1000</v>
-      </c>
-      <c r="I51" s="88">
-        <f t="shared" si="83"/>
-        <v>2120</v>
-      </c>
-      <c r="J51" s="88">
-        <f t="shared" si="83"/>
-        <v>3800</v>
-      </c>
-      <c r="K51" s="88">
-        <f t="shared" si="83"/>
-        <v>3400</v>
-      </c>
-      <c r="L51" s="88">
-        <f t="shared" si="83"/>
-        <v>5600</v>
-      </c>
-      <c r="M51" s="126">
-        <f>SUM(M48:M50)</f>
-        <v>4490</v>
-      </c>
-      <c r="N51" s="59">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="56"/>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A51" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B51" s="47">
+        <v>47</v>
+      </c>
+      <c r="C51" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="50">
+        <v>40</v>
+      </c>
+      <c r="H51" s="75">
+        <v>40</v>
+      </c>
+      <c r="I51" s="49">
+        <v>40</v>
+      </c>
+      <c r="J51" s="50">
+        <v>40</v>
+      </c>
+      <c r="K51" s="75">
+        <v>40</v>
+      </c>
+      <c r="L51" s="76">
+        <v>40</v>
+      </c>
+      <c r="M51" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N51" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O51" s="58">
+      <c r="O51" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
       <c r="P51" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q51" s="40">
         <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R51" s="51"/>
+      <c r="S51" s="52"/>
+      <c r="T51" s="52"/>
+      <c r="U51" s="53"/>
+      <c r="V51" s="54"/>
+      <c r="W51" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="56"/>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A52" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B52" s="47">
+        <v>48</v>
+      </c>
+      <c r="C52" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="74"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="50">
+        <v>40</v>
+      </c>
+      <c r="H52" s="75">
+        <v>40</v>
+      </c>
+      <c r="I52" s="49">
+        <v>40</v>
+      </c>
+      <c r="J52" s="50">
+        <v>40</v>
+      </c>
+      <c r="K52" s="75">
+        <v>40</v>
+      </c>
+      <c r="L52" s="76">
+        <v>40</v>
+      </c>
+      <c r="M52" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N52" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O52" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P52" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q52" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R52" s="51"/>
+      <c r="S52" s="52"/>
+      <c r="T52" s="52"/>
+      <c r="U52" s="53"/>
+      <c r="V52" s="54"/>
+      <c r="W52" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X52" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="56"/>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A53" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B53" s="47">
+        <v>49</v>
+      </c>
+      <c r="C53" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="74"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="50">
+        <v>40</v>
+      </c>
+      <c r="H53" s="75">
+        <v>40</v>
+      </c>
+      <c r="I53" s="49">
+        <v>40</v>
+      </c>
+      <c r="J53" s="50">
+        <v>40</v>
+      </c>
+      <c r="K53" s="75">
+        <v>40</v>
+      </c>
+      <c r="L53" s="76">
+        <v>40</v>
+      </c>
+      <c r="M53" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N53" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P53" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q53" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R53" s="51"/>
+      <c r="S53" s="52"/>
+      <c r="T53" s="52"/>
+      <c r="U53" s="53"/>
+      <c r="V53" s="54"/>
+      <c r="W53" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X53" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y53" s="56"/>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A54" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B54" s="47">
+        <v>50</v>
+      </c>
+      <c r="C54" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="74"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="50">
+        <v>40</v>
+      </c>
+      <c r="H54" s="75">
+        <v>40</v>
+      </c>
+      <c r="I54" s="49">
+        <v>40</v>
+      </c>
+      <c r="J54" s="50">
+        <v>40</v>
+      </c>
+      <c r="K54" s="75">
+        <v>40</v>
+      </c>
+      <c r="L54" s="76">
+        <v>40</v>
+      </c>
+      <c r="M54" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N54" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P54" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q54" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R54" s="51"/>
+      <c r="S54" s="52"/>
+      <c r="T54" s="52"/>
+      <c r="U54" s="53"/>
+      <c r="V54" s="54"/>
+      <c r="W54" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="56"/>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A55" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B55" s="47">
+        <v>51</v>
+      </c>
+      <c r="C55" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" s="74"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="50">
+        <v>40</v>
+      </c>
+      <c r="H55" s="75">
+        <v>40</v>
+      </c>
+      <c r="I55" s="49">
+        <v>40</v>
+      </c>
+      <c r="J55" s="50">
+        <v>40</v>
+      </c>
+      <c r="K55" s="75">
+        <v>40</v>
+      </c>
+      <c r="L55" s="76">
+        <v>40</v>
+      </c>
+      <c r="M55" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N55" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P55" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q55" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R55" s="51"/>
+      <c r="S55" s="52"/>
+      <c r="T55" s="52"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="54"/>
+      <c r="W55" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X55" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y55" s="56"/>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A56" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B56" s="47">
+        <v>52</v>
+      </c>
+      <c r="C56" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="D56" s="74"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="50">
+        <v>40</v>
+      </c>
+      <c r="H56" s="75">
+        <v>40</v>
+      </c>
+      <c r="I56" s="49">
+        <v>40</v>
+      </c>
+      <c r="J56" s="50">
+        <v>40</v>
+      </c>
+      <c r="K56" s="75">
+        <v>40</v>
+      </c>
+      <c r="L56" s="76">
+        <v>40</v>
+      </c>
+      <c r="M56" s="48">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N56" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O56" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P56" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q56" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R56" s="51"/>
+      <c r="S56" s="52"/>
+      <c r="T56" s="52"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="54"/>
+      <c r="W56" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y56" s="56"/>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A57" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B57" s="47">
+        <v>53</v>
+      </c>
+      <c r="C57" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75">
+        <v>40</v>
+      </c>
+      <c r="H57" s="75">
+        <v>40</v>
+      </c>
+      <c r="I57" s="157">
+        <v>40</v>
+      </c>
+      <c r="J57" s="75">
+        <v>40</v>
+      </c>
+      <c r="K57" s="75">
+        <v>40</v>
+      </c>
+      <c r="L57" s="75">
+        <v>40</v>
+      </c>
+      <c r="M57" s="156">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N57" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P57" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q57" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R57" s="51"/>
+      <c r="S57" s="52"/>
+      <c r="T57" s="52"/>
+      <c r="U57" s="53"/>
+      <c r="V57" s="54"/>
+      <c r="W57" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X57" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="56"/>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A58" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B58" s="47">
+        <v>54</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75">
+        <v>40</v>
+      </c>
+      <c r="H58" s="75">
+        <v>40</v>
+      </c>
+      <c r="I58" s="157">
+        <v>40</v>
+      </c>
+      <c r="J58" s="75">
+        <v>40</v>
+      </c>
+      <c r="K58" s="75">
+        <v>40</v>
+      </c>
+      <c r="L58" s="75">
+        <v>40</v>
+      </c>
+      <c r="M58" s="156">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N58" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P58" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q58" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R58" s="51"/>
+      <c r="S58" s="52"/>
+      <c r="T58" s="52"/>
+      <c r="U58" s="53"/>
+      <c r="V58" s="54"/>
+      <c r="W58" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X58" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y58" s="56"/>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A59" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B59" s="47">
+        <v>55</v>
+      </c>
+      <c r="C59" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75">
+        <v>40</v>
+      </c>
+      <c r="H59" s="75">
+        <v>40</v>
+      </c>
+      <c r="I59" s="157">
+        <v>40</v>
+      </c>
+      <c r="J59" s="75">
+        <v>40</v>
+      </c>
+      <c r="K59" s="75">
+        <v>40</v>
+      </c>
+      <c r="L59" s="75">
+        <v>40</v>
+      </c>
+      <c r="M59" s="156">
+        <f t="shared" si="76"/>
+        <v>6</v>
+      </c>
+      <c r="N59" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O59" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P59" s="73">
+        <f t="shared" si="77"/>
+        <v>6</v>
+      </c>
+      <c r="Q59" s="40">
+        <f t="shared" si="78"/>
+        <v>6</v>
+      </c>
+      <c r="R59" s="51"/>
+      <c r="S59" s="52"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="53"/>
+      <c r="V59" s="54"/>
+      <c r="W59" s="55">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="X59" s="55">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="56"/>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A60" s="79">
+        <v>46191</v>
+      </c>
+      <c r="B60" s="47">
+        <v>56</v>
+      </c>
+      <c r="C60" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75">
+        <v>800</v>
+      </c>
+      <c r="H60" s="75">
+        <v>1200</v>
+      </c>
+      <c r="I60" s="157">
+        <v>2800</v>
+      </c>
+      <c r="J60" s="75">
+        <v>1800</v>
+      </c>
+      <c r="K60" s="75">
+        <v>1200</v>
+      </c>
+      <c r="L60" s="75">
+        <v>3600</v>
+      </c>
+      <c r="M60" s="156">
+        <f t="shared" si="52"/>
+        <v>285</v>
+      </c>
+      <c r="N60" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P60" s="73">
+        <f t="shared" si="53"/>
+        <v>240</v>
+      </c>
+      <c r="Q60" s="40">
+        <f t="shared" si="54"/>
+        <v>330</v>
+      </c>
+      <c r="R60" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S60" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U60" s="53" t="e">
+        <f t="shared" si="55"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V60" s="54" t="e">
+        <f t="shared" si="56"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W60" s="55">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="X60" s="55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="56" t="e">
+        <f t="shared" si="59"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A61" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B61" s="47">
+        <v>57</v>
+      </c>
+      <c r="C61" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="149"/>
+      <c r="E61" s="149"/>
+      <c r="F61" s="149"/>
+      <c r="G61" s="149">
+        <v>80</v>
+      </c>
+      <c r="H61" s="149">
+        <v>0</v>
+      </c>
+      <c r="I61" s="158">
+        <v>200</v>
+      </c>
+      <c r="J61" s="149">
+        <v>200</v>
+      </c>
+      <c r="K61" s="149">
+        <v>0</v>
+      </c>
+      <c r="L61" s="149">
+        <v>400</v>
+      </c>
+      <c r="M61" s="156">
+        <f t="shared" ref="M61:M79" si="81">SUM(D61:L61)/40</f>
+        <v>22</v>
+      </c>
+      <c r="N61" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P61" s="73">
+        <f t="shared" ref="P61:P79" si="82">SUM(G61:I61)/20</f>
+        <v>14</v>
+      </c>
+      <c r="Q61" s="40">
+        <f t="shared" ref="Q61:Q79" si="83">SUM(J61:L61)/20</f>
+        <v>30</v>
+      </c>
+      <c r="R61" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S61" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T61" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U61" s="53" t="e">
+        <f t="shared" ref="U61:U79" si="84">SUM(R61:T61)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V61" s="54" t="e">
+        <f t="shared" ref="V61:V79" si="85">SUM(D61:F61)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W61" s="55">
+        <f t="shared" ref="W61:W79" si="86">SUM(G61:I61)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X61" s="55">
+        <f t="shared" ref="X61:X79" si="87">SUM(J61:L61)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="56" t="e">
+        <f t="shared" ref="Y61:Y79" si="88">SUM(V61:X61)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A62" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B62" s="47">
+        <v>58</v>
+      </c>
+      <c r="C62" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
+      <c r="F62" s="149"/>
+      <c r="G62" s="149">
+        <v>80</v>
+      </c>
+      <c r="H62" s="149">
+        <v>80</v>
+      </c>
+      <c r="I62" s="158">
+        <v>200</v>
+      </c>
+      <c r="J62" s="149">
+        <v>120</v>
+      </c>
+      <c r="K62" s="149">
+        <v>120</v>
+      </c>
+      <c r="L62" s="149">
+        <v>200</v>
+      </c>
+      <c r="M62" s="156">
+        <f t="shared" si="81"/>
+        <v>20</v>
+      </c>
+      <c r="N62" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O62" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P62" s="73">
+        <f t="shared" si="82"/>
+        <v>18</v>
+      </c>
+      <c r="Q62" s="40">
+        <f t="shared" si="83"/>
+        <v>22</v>
+      </c>
+      <c r="R62" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S62" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T62" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U62" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V62" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W62" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X62" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y62" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A63" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B63" s="47">
+        <v>59</v>
+      </c>
+      <c r="C63" s="154" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" s="149"/>
+      <c r="E63" s="149"/>
+      <c r="F63" s="149"/>
+      <c r="G63" s="149">
+        <v>40</v>
+      </c>
+      <c r="H63" s="149">
+        <v>40</v>
+      </c>
+      <c r="I63" s="158">
+        <v>40</v>
+      </c>
+      <c r="J63" s="149">
+        <v>40</v>
+      </c>
+      <c r="K63" s="149">
+        <v>40</v>
+      </c>
+      <c r="L63" s="149">
+        <v>40</v>
+      </c>
+      <c r="M63" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N63" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O63" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P63" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q63" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R63" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S63" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T63" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U63" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V63" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W63" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X63" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y63" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A64" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B64" s="47">
+        <v>60</v>
+      </c>
+      <c r="C64" s="154" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="149"/>
+      <c r="E64" s="149"/>
+      <c r="F64" s="149"/>
+      <c r="G64" s="149">
+        <v>40</v>
+      </c>
+      <c r="H64" s="149">
+        <v>40</v>
+      </c>
+      <c r="I64" s="158">
+        <v>40</v>
+      </c>
+      <c r="J64" s="149">
+        <v>40</v>
+      </c>
+      <c r="K64" s="149">
+        <v>40</v>
+      </c>
+      <c r="L64" s="149">
+        <v>40</v>
+      </c>
+      <c r="M64" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N64" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O64" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P64" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q64" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R64" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S64" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T64" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U64" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V64" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W64" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X64" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y64" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A65" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B65" s="47">
+        <v>61</v>
+      </c>
+      <c r="C65" s="154" t="s">
+        <v>144</v>
+      </c>
+      <c r="D65" s="149"/>
+      <c r="E65" s="149"/>
+      <c r="F65" s="149"/>
+      <c r="G65" s="149">
+        <v>40</v>
+      </c>
+      <c r="H65" s="149">
+        <v>40</v>
+      </c>
+      <c r="I65" s="158">
+        <v>40</v>
+      </c>
+      <c r="J65" s="149">
+        <v>40</v>
+      </c>
+      <c r="K65" s="149">
+        <v>40</v>
+      </c>
+      <c r="L65" s="149">
+        <v>40</v>
+      </c>
+      <c r="M65" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N65" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O65" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P65" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q65" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R65" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S65" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T65" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U65" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V65" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W65" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X65" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y65" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A66" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B66" s="47">
+        <v>62</v>
+      </c>
+      <c r="C66" s="154" t="s">
+        <v>145</v>
+      </c>
+      <c r="D66" s="149"/>
+      <c r="E66" s="149"/>
+      <c r="F66" s="149"/>
+      <c r="G66" s="149">
+        <v>80</v>
+      </c>
+      <c r="H66" s="149">
+        <v>80</v>
+      </c>
+      <c r="I66" s="158">
+        <v>80</v>
+      </c>
+      <c r="J66" s="149">
+        <v>80</v>
+      </c>
+      <c r="K66" s="149">
+        <v>80</v>
+      </c>
+      <c r="L66" s="149">
+        <v>80</v>
+      </c>
+      <c r="M66" s="156">
+        <f t="shared" si="81"/>
+        <v>12</v>
+      </c>
+      <c r="N66" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O66" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P66" s="73">
+        <f t="shared" si="82"/>
+        <v>12</v>
+      </c>
+      <c r="Q66" s="40">
+        <f t="shared" si="83"/>
+        <v>12</v>
+      </c>
+      <c r="R66" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S66" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T66" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U66" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V66" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W66" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X66" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y66" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A67" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B67" s="47">
+        <v>63</v>
+      </c>
+      <c r="C67" s="154" t="s">
+        <v>146</v>
+      </c>
+      <c r="D67" s="149"/>
+      <c r="E67" s="149"/>
+      <c r="F67" s="149"/>
+      <c r="G67" s="149">
+        <v>40</v>
+      </c>
+      <c r="H67" s="149">
+        <v>40</v>
+      </c>
+      <c r="I67" s="158">
+        <v>40</v>
+      </c>
+      <c r="J67" s="149">
+        <v>40</v>
+      </c>
+      <c r="K67" s="149">
+        <v>40</v>
+      </c>
+      <c r="L67" s="149">
+        <v>40</v>
+      </c>
+      <c r="M67" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N67" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P67" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q67" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R67" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S67" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U67" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V67" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W67" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X67" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y67" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A68" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B68" s="47">
+        <v>64</v>
+      </c>
+      <c r="C68" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="149"/>
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="149">
+        <v>40</v>
+      </c>
+      <c r="H68" s="149">
+        <v>40</v>
+      </c>
+      <c r="I68" s="158">
+        <v>40</v>
+      </c>
+      <c r="J68" s="149">
+        <v>40</v>
+      </c>
+      <c r="K68" s="149">
+        <v>40</v>
+      </c>
+      <c r="L68" s="149">
+        <v>40</v>
+      </c>
+      <c r="M68" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N68" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P68" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q68" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R68" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S68" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T68" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V68" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W68" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X68" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y68" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A69" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B69" s="47">
+        <v>65</v>
+      </c>
+      <c r="C69" s="154" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="149">
+        <v>80</v>
+      </c>
+      <c r="H69" s="149">
+        <v>80</v>
+      </c>
+      <c r="I69" s="158">
+        <v>80</v>
+      </c>
+      <c r="J69" s="149">
+        <v>80</v>
+      </c>
+      <c r="K69" s="149">
+        <v>80</v>
+      </c>
+      <c r="L69" s="149">
+        <v>80</v>
+      </c>
+      <c r="M69" s="156">
+        <f t="shared" si="81"/>
+        <v>12</v>
+      </c>
+      <c r="N69" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P69" s="73">
+        <f t="shared" si="82"/>
+        <v>12</v>
+      </c>
+      <c r="Q69" s="40">
+        <f t="shared" si="83"/>
+        <v>12</v>
+      </c>
+      <c r="R69" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S69" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T69" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U69" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V69" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W69" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X69" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y69" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A70" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B70" s="47">
+        <v>66</v>
+      </c>
+      <c r="C70" s="154" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" s="149"/>
+      <c r="E70" s="149"/>
+      <c r="F70" s="149"/>
+      <c r="G70" s="149">
+        <v>40</v>
+      </c>
+      <c r="H70" s="149">
+        <v>40</v>
+      </c>
+      <c r="I70" s="158">
+        <v>40</v>
+      </c>
+      <c r="J70" s="149">
+        <v>40</v>
+      </c>
+      <c r="K70" s="149">
+        <v>40</v>
+      </c>
+      <c r="L70" s="149">
+        <v>40</v>
+      </c>
+      <c r="M70" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N70" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P70" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q70" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R70" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S70" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T70" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U70" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V70" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W70" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X70" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y70" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A71" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B71" s="47">
+        <v>67</v>
+      </c>
+      <c r="C71" s="162" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71" s="129"/>
+      <c r="E71" s="129"/>
+      <c r="F71" s="129"/>
+      <c r="G71" s="129">
+        <v>0</v>
+      </c>
+      <c r="H71" s="129">
+        <v>0</v>
+      </c>
+      <c r="I71" s="163">
+        <v>0</v>
+      </c>
+      <c r="J71" s="129">
+        <v>0</v>
+      </c>
+      <c r="K71" s="129">
+        <v>0</v>
+      </c>
+      <c r="L71" s="129">
+        <v>0</v>
+      </c>
+      <c r="M71" s="156">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N71" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O71" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P71" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R71" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S71" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T71" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U71" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V71" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W71" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X71" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y71" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A72" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B72" s="47">
+        <v>68</v>
+      </c>
+      <c r="C72" s="154" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="149"/>
+      <c r="E72" s="149"/>
+      <c r="F72" s="149"/>
+      <c r="G72" s="149">
+        <v>40</v>
+      </c>
+      <c r="H72" s="149">
+        <v>40</v>
+      </c>
+      <c r="I72" s="158">
+        <v>40</v>
+      </c>
+      <c r="J72" s="149">
+        <v>40</v>
+      </c>
+      <c r="K72" s="149">
+        <v>40</v>
+      </c>
+      <c r="L72" s="149">
+        <v>40</v>
+      </c>
+      <c r="M72" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N72" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O72" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P72" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q72" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R72" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S72" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T72" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U72" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V72" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W72" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X72" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y72" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A73" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B73" s="47">
+        <v>69</v>
+      </c>
+      <c r="C73" s="154" t="s">
+        <v>152</v>
+      </c>
+      <c r="D73" s="149"/>
+      <c r="E73" s="149"/>
+      <c r="F73" s="149"/>
+      <c r="G73" s="149">
+        <v>40</v>
+      </c>
+      <c r="H73" s="149">
+        <v>40</v>
+      </c>
+      <c r="I73" s="158">
+        <v>40</v>
+      </c>
+      <c r="J73" s="149">
+        <v>40</v>
+      </c>
+      <c r="K73" s="149">
+        <v>40</v>
+      </c>
+      <c r="L73" s="149">
+        <v>40</v>
+      </c>
+      <c r="M73" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N73" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O73" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P73" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q73" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R73" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S73" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T73" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V73" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W73" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X73" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y73" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A74" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B74" s="47">
+        <v>70</v>
+      </c>
+      <c r="C74" s="159" t="s">
+        <v>153</v>
+      </c>
+      <c r="D74" s="149"/>
+      <c r="E74" s="149"/>
+      <c r="F74" s="150"/>
+      <c r="G74" s="149">
+        <v>40</v>
+      </c>
+      <c r="H74" s="149">
+        <v>40</v>
+      </c>
+      <c r="I74" s="158">
+        <v>40</v>
+      </c>
+      <c r="J74" s="149">
+        <v>40</v>
+      </c>
+      <c r="K74" s="149">
+        <v>40</v>
+      </c>
+      <c r="L74" s="149">
+        <v>40</v>
+      </c>
+      <c r="M74" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N74" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O74" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P74" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q74" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R74" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S74" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T74" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U74" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V74" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W74" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X74" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y74" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A75" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B75" s="47">
+        <v>71</v>
+      </c>
+      <c r="C75" s="159" t="s">
+        <v>154</v>
+      </c>
+      <c r="D75" s="149"/>
+      <c r="E75" s="150"/>
+      <c r="F75" s="150"/>
+      <c r="G75" s="149">
+        <v>40</v>
+      </c>
+      <c r="H75" s="149">
+        <v>40</v>
+      </c>
+      <c r="I75" s="158">
+        <v>40</v>
+      </c>
+      <c r="J75" s="149">
+        <v>40</v>
+      </c>
+      <c r="K75" s="149">
+        <v>40</v>
+      </c>
+      <c r="L75" s="149">
+        <v>40</v>
+      </c>
+      <c r="M75" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N75" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O75" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P75" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q75" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R75" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S75" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T75" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U75" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V75" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W75" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X75" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y75" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A76" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B76" s="47">
+        <v>72</v>
+      </c>
+      <c r="C76" s="159" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76" s="149"/>
+      <c r="E76" s="150"/>
+      <c r="F76" s="150"/>
+      <c r="G76" s="149">
+        <v>40</v>
+      </c>
+      <c r="H76" s="149">
+        <v>40</v>
+      </c>
+      <c r="I76" s="158">
+        <v>40</v>
+      </c>
+      <c r="J76" s="149">
+        <v>40</v>
+      </c>
+      <c r="K76" s="149">
+        <v>40</v>
+      </c>
+      <c r="L76" s="149">
+        <v>40</v>
+      </c>
+      <c r="M76" s="156">
+        <f t="shared" si="81"/>
+        <v>6</v>
+      </c>
+      <c r="N76" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O76" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P76" s="73">
+        <f t="shared" si="82"/>
+        <v>6</v>
+      </c>
+      <c r="Q76" s="40">
+        <f t="shared" si="83"/>
+        <v>6</v>
+      </c>
+      <c r="R76" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S76" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T76" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U76" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V76" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W76" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X76" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A77" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B77" s="47">
+        <v>73</v>
+      </c>
+      <c r="C77" s="160" t="s">
+        <v>156</v>
+      </c>
+      <c r="D77" s="129"/>
+      <c r="E77" s="131"/>
+      <c r="F77" s="131"/>
+      <c r="G77" s="131">
+        <v>0</v>
+      </c>
+      <c r="H77" s="131">
+        <v>0</v>
+      </c>
+      <c r="I77" s="161">
+        <v>0</v>
+      </c>
+      <c r="J77" s="131">
+        <v>0</v>
+      </c>
+      <c r="K77" s="131">
+        <v>0</v>
+      </c>
+      <c r="L77" s="131">
+        <v>0</v>
+      </c>
+      <c r="M77" s="156">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O77" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P77" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S77" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V77" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W77" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X77" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A78" s="79">
+        <v>46192</v>
+      </c>
+      <c r="B78" s="47">
+        <v>74</v>
+      </c>
+      <c r="C78" s="160" t="s">
+        <v>157</v>
+      </c>
+      <c r="D78" s="129"/>
+      <c r="E78" s="131"/>
+      <c r="F78" s="131"/>
+      <c r="G78" s="131">
+        <v>0</v>
+      </c>
+      <c r="H78" s="131">
+        <v>0</v>
+      </c>
+      <c r="I78" s="161">
+        <v>0</v>
+      </c>
+      <c r="J78" s="131">
+        <v>0</v>
+      </c>
+      <c r="K78" s="131">
+        <v>0</v>
+      </c>
+      <c r="L78" s="131">
+        <v>0</v>
+      </c>
+      <c r="M78" s="156">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N78" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O78" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P78" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q78" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R78" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S78" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T78" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U78" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V78" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W78" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X78" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y78" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A79" s="79"/>
+      <c r="B79" s="47">
+        <v>75</v>
+      </c>
+      <c r="C79" s="155"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="156"/>
+      <c r="J79" s="50"/>
+      <c r="K79" s="50"/>
+      <c r="L79" s="50"/>
+      <c r="M79" s="156">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N79" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O79" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P79" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R79" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S79" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T79" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U79" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V79" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W79" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X79" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y79" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A80" s="79"/>
+      <c r="B80" s="174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="175"/>
+      <c r="D80" s="89">
+        <f t="shared" ref="D80:L80" si="89">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E80" s="89">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="89">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="89">
+        <f t="shared" si="89"/>
+        <v>7140</v>
+      </c>
+      <c r="H80" s="89">
+        <f t="shared" si="89"/>
+        <v>7657</v>
+      </c>
+      <c r="I80" s="89">
+        <f t="shared" si="89"/>
+        <v>10657</v>
+      </c>
+      <c r="J80" s="89">
+        <f t="shared" si="89"/>
+        <v>11297</v>
+      </c>
+      <c r="K80" s="89">
+        <f t="shared" si="89"/>
+        <v>9684</v>
+      </c>
+      <c r="L80" s="89">
+        <f t="shared" si="89"/>
+        <v>13219</v>
+      </c>
+      <c r="M80" s="48">
+        <f t="shared" ref="M80:M83" si="90">SUM(D80:L80)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N80" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O80" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P80" s="73">
+        <f t="shared" ref="P80:P84" si="91">SUM(G80:I80)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q80" s="40">
+        <f t="shared" ref="Q80:Q84" si="92">SUM(J80:L80)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R80" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S80" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T80" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V80" s="54" t="e">
+        <f t="shared" ref="V80:V84" si="93">SUM(D80:F80)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W80" s="55">
+        <f t="shared" ref="W80:W84" si="94">SUM(G80:I80)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X80" s="55">
+        <f t="shared" ref="X80:X84" si="95">SUM(J80:L80)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y80" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A81" s="79"/>
+      <c r="B81" s="121">
+        <v>0</v>
+      </c>
+      <c r="C81" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="122">
+        <v>1600</v>
+      </c>
+      <c r="E81" s="123"/>
+      <c r="F81" s="124"/>
+      <c r="G81" s="123"/>
+      <c r="H81" s="123"/>
+      <c r="I81" s="124"/>
+      <c r="J81" s="123">
+        <v>520</v>
+      </c>
+      <c r="K81" s="123">
+        <v>920</v>
+      </c>
+      <c r="L81" s="124">
+        <v>960</v>
+      </c>
+      <c r="M81" s="125">
+        <f>SUM(D81:L81)</f>
+        <v>4000</v>
+      </c>
+      <c r="N81" s="39"/>
+      <c r="O81" s="49"/>
+      <c r="P81" s="73"/>
+      <c r="Q81" s="40"/>
+      <c r="R81" s="51"/>
+      <c r="S81" s="52"/>
+      <c r="T81" s="52"/>
+      <c r="U81" s="53"/>
+      <c r="V81" s="54"/>
+      <c r="W81" s="55"/>
+      <c r="X81" s="55"/>
+      <c r="Y81" s="56"/>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A82" s="79"/>
+      <c r="B82" s="47">
+        <v>1</v>
+      </c>
+      <c r="C82" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="74"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="76"/>
+      <c r="G82" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H82" s="75">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I82" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J82" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K82" s="75">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L82" s="76">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M82" s="48">
+        <f t="shared" si="90"/>
+        <v>400</v>
+      </c>
+      <c r="N82" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O82" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P82" s="73">
+        <f t="shared" si="91"/>
+        <v>230</v>
+      </c>
+      <c r="Q82" s="40">
+        <f t="shared" si="92"/>
+        <v>570</v>
+      </c>
+      <c r="R82" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S82" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T82" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U82" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V82" s="54" t="e">
+        <f t="shared" si="93"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W82" s="55">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="X82" s="55">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="Y82" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B83" s="47">
+        <v>2</v>
+      </c>
+      <c r="C83" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="74">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="75"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="50">
+        <v>400</v>
+      </c>
+      <c r="H83" s="75">
+        <v>400</v>
+      </c>
+      <c r="I83" s="49">
+        <v>0</v>
+      </c>
+      <c r="J83" s="50">
+        <v>400</v>
+      </c>
+      <c r="K83" s="75">
+        <v>400</v>
+      </c>
+      <c r="L83" s="76">
+        <v>600</v>
+      </c>
+      <c r="M83" s="48">
+        <f t="shared" si="90"/>
+        <v>90</v>
+      </c>
+      <c r="N83" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O83" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P83" s="73">
+        <f t="shared" si="91"/>
+        <v>40</v>
+      </c>
+      <c r="Q83" s="40">
+        <f t="shared" si="92"/>
+        <v>70</v>
+      </c>
+      <c r="R83" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S83" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T83" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U83" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V83" s="54" t="e">
+        <f t="shared" si="93"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W83" s="55">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="X83" s="55">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="Y83" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B84" s="187" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="188"/>
+      <c r="D84" s="88">
+        <f>SUM(D82:D83)</f>
+        <v>1400</v>
+      </c>
+      <c r="E84" s="88">
+        <f t="shared" ref="E84:L84" si="96">SUM(E82:E83)</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="G84" s="88">
+        <f t="shared" si="96"/>
+        <v>2280</v>
+      </c>
+      <c r="H84" s="88">
+        <f t="shared" si="96"/>
+        <v>1000</v>
+      </c>
+      <c r="I84" s="88">
+        <f t="shared" si="96"/>
+        <v>2120</v>
+      </c>
+      <c r="J84" s="88">
+        <f t="shared" si="96"/>
+        <v>3800</v>
+      </c>
+      <c r="K84" s="88">
+        <f t="shared" si="96"/>
+        <v>3400</v>
+      </c>
+      <c r="L84" s="88">
+        <f t="shared" si="96"/>
+        <v>5600</v>
+      </c>
+      <c r="M84" s="126">
+        <f>SUM(M81:M83)</f>
+        <v>4490</v>
+      </c>
+      <c r="N84" s="59">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O84" s="58">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P84" s="73">
+        <f t="shared" si="91"/>
         <v>270</v>
       </c>
-      <c r="Q51" s="40">
-        <f t="shared" si="79"/>
+      <c r="Q84" s="40">
+        <f t="shared" si="92"/>
         <v>640</v>
       </c>
-      <c r="R51" s="51" t="e">
+      <c r="R84" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S51" s="52">
+      <c r="S84" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T51" s="52">
+      <c r="T84" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U51" s="53" t="e">
+      <c r="U84" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V51" s="54" t="e">
-        <f t="shared" si="80"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W51" s="55">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="X51" s="55">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="56" t="e">
+      <c r="V84" s="54" t="e">
+        <f t="shared" si="93"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W84" s="55">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="X84" s="55">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="152" t="s">
+    <row r="85" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B85" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="153"/>
-      <c r="D52" s="90">
-        <f>SUM(D47,D51)</f>
+      <c r="C85" s="177"/>
+      <c r="D85" s="90">
+        <f>SUM(D80,D84)</f>
         <v>2720</v>
       </c>
-      <c r="E52" s="90">
-        <f t="shared" ref="E52:L52" si="84">SUM(E47,E51)</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="90">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="90">
-        <f t="shared" si="84"/>
-        <v>7780</v>
-      </c>
-      <c r="H52" s="90">
-        <f t="shared" si="84"/>
-        <v>6297</v>
-      </c>
-      <c r="I52" s="90">
-        <f t="shared" si="84"/>
-        <v>8817</v>
-      </c>
-      <c r="J52" s="90">
-        <f t="shared" si="84"/>
-        <v>12217</v>
-      </c>
-      <c r="K52" s="90">
-        <f t="shared" si="84"/>
-        <v>10564</v>
-      </c>
-      <c r="L52" s="90">
-        <f t="shared" si="84"/>
-        <v>13899</v>
-      </c>
-      <c r="M52" s="60">
+      <c r="E85" s="90">
+        <f t="shared" ref="E85:L85" si="97">SUM(E80,E84)</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="90">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="90">
+        <f t="shared" si="97"/>
+        <v>9420</v>
+      </c>
+      <c r="H85" s="90">
+        <f t="shared" si="97"/>
+        <v>8657</v>
+      </c>
+      <c r="I85" s="90">
+        <f t="shared" si="97"/>
+        <v>12777</v>
+      </c>
+      <c r="J85" s="90">
+        <f t="shared" si="97"/>
+        <v>15097</v>
+      </c>
+      <c r="K85" s="90">
+        <f t="shared" si="97"/>
+        <v>13084</v>
+      </c>
+      <c r="L85" s="90">
+        <f t="shared" si="97"/>
+        <v>18819</v>
+      </c>
+      <c r="M85" s="60">
         <f t="shared" si="0"/>
-        <v>1557.35</v>
-      </c>
-      <c r="N52" s="63">
-        <f>SUM(N5:N51)</f>
-        <v>0</v>
-      </c>
-      <c r="O52" s="61">
-        <f t="shared" ref="O52:Y52" si="85">SUM(O5:O51)</f>
-        <v>15254.979999999985</v>
-      </c>
-      <c r="P52" s="62">
-        <f t="shared" si="85"/>
-        <v>2543.9499999999998</v>
-      </c>
-      <c r="Q52" s="64">
-        <f t="shared" si="85"/>
-        <v>4365.1000000000004</v>
-      </c>
-      <c r="R52" s="65" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S52" s="66">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="T52" s="66">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="U52" s="67" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V52" s="68" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W52" s="69">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="X52" s="69">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="70" t="e">
-        <f t="shared" si="85"/>
+        <v>2014.35</v>
+      </c>
+      <c r="N85" s="63">
+        <f>SUM(N5:N84)</f>
+        <v>0</v>
+      </c>
+      <c r="O85" s="61">
+        <f t="shared" ref="O85:Y85" si="98">SUM(O5:O84)</f>
+        <v>26198.770000000011</v>
+      </c>
+      <c r="P85" s="62">
+        <f t="shared" si="98"/>
+        <v>3461.95</v>
+      </c>
+      <c r="Q85" s="64">
+        <f t="shared" si="98"/>
+        <v>5539.1</v>
+      </c>
+      <c r="R85" s="65" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S85" s="66">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="T85" s="66">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="67" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V85" s="68" t="e">
+        <f t="shared" si="98"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W85" s="69">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="X85" s="69">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="70" t="e">
+        <f t="shared" si="98"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B84:C84"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B80:C80"/>
   </mergeCells>
+  <conditionalFormatting sqref="C45:C59">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6437,24 +9170,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="189" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="181" t="s">
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="182"/>
-      <c r="K3" s="183" t="s">
+      <c r="I3" s="194"/>
+      <c r="K3" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="183"/>
-      <c r="O3" s="183"/>
+      <c r="L3" s="195"/>
+      <c r="M3" s="195"/>
+      <c r="N3" s="195"/>
+      <c r="O3" s="195"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="111"/>
@@ -6497,24 +9230,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="94">
-        <v>435.95</v>
+        <v>548</v>
       </c>
       <c r="E5" s="80">
-        <v>1067.3499999999999</v>
+        <v>1656</v>
       </c>
       <c r="F5" s="80">
-        <v>550</v>
+        <v>590</v>
       </c>
       <c r="G5" s="114">
         <f>SUM(D5:F5)</f>
-        <v>2053.3000000000002</v>
+        <v>2794</v>
       </c>
       <c r="H5" s="107">
         <v>10000</v>
       </c>
       <c r="I5" s="108">
         <f>G5-H5</f>
-        <v>-7946.7</v>
+        <v>-7206</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -6523,14 +9256,14 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>16359</v>
+        <v>13608</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>408.97500000000002</v>
+        <v>340.2</v>
       </c>
       <c r="O5" s="82">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6539,19 +9272,19 @@
       </c>
       <c r="D6" s="116">
         <f>D5*40</f>
-        <v>17438</v>
+        <v>21920</v>
       </c>
       <c r="E6" s="117">
         <f>E5*40</f>
-        <v>42694</v>
+        <v>66240</v>
       </c>
       <c r="F6" s="117">
         <f>F5*40</f>
-        <v>22000</v>
+        <v>23600</v>
       </c>
       <c r="G6" s="118">
         <f>SUM(D6:F6)</f>
-        <v>82132</v>
+        <v>111760</v>
       </c>
       <c r="H6" s="109">
         <f>H5*40</f>
@@ -6559,7 +9292,7 @@
       </c>
       <c r="I6" s="110">
         <f>G6-H6</f>
-        <v>-317868</v>
+        <v>-288240</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -6568,11 +9301,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>17947</v>
+        <v>14695</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>448.67500000000001</v>
+        <v>367.375</v>
       </c>
       <c r="O6" s="82">
         <v>56</v>
@@ -6587,14 +9320,14 @@
         <v>70</v>
       </c>
       <c r="M7" s="5">
-        <v>6390</v>
+        <v>1335</v>
       </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>159.75</v>
+        <v>33.375</v>
       </c>
       <c r="O7" s="82">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -6608,14 +9341,14 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>17573</v>
+        <v>12655</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>439.32499999999999</v>
+        <v>316.375</v>
       </c>
       <c r="O8" s="82">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -6624,11 +9357,11 @@
       </c>
       <c r="D9" s="119">
         <f>D8-D5</f>
-        <v>-435.95</v>
+        <v>-548</v>
       </c>
       <c r="E9" s="119">
         <f>E8-E5</f>
-        <v>-1067.3499999999999</v>
+        <v>-1656</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -6637,11 +9370,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>11088</v>
+        <v>7217</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>277.2</v>
+        <v>180.42500000000001</v>
       </c>
       <c r="O9" s="82">
         <v>33</v>
@@ -6655,25 +9388,32 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>16398</v>
+        <v>9472</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>409.95</v>
+        <v>236.8</v>
       </c>
       <c r="O10" s="82">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="180"/>
-      <c r="F11" s="180" t="s">
+      <c r="D11" s="192"/>
+      <c r="F11" s="192" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="180"/>
+      <c r="G11" s="192"/>
+      <c r="H11" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11">
+        <f>D5/20</f>
+        <v>27.4</v>
+      </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -6681,11 +9421,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>58249</v>
+        <v>57979</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1456.2249999999999</v>
+        <v>1449.4749999999999</v>
       </c>
       <c r="O11" s="82">
         <v>20</v>
@@ -6703,7 +9443,7 @@
       </c>
       <c r="G12" s="103">
         <f>D12+G5</f>
-        <v>2554.2000000000003</v>
+        <v>3294.9</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -6711,15 +9451,15 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>144004</v>
+        <v>116961</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>3600.1</v>
+        <v>2924.0249999999996</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
@@ -6735,158 +9475,187 @@
       </c>
       <c r="G13" s="103">
         <f>G12*40</f>
-        <v>102168.00000000001</v>
+        <v>131796</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="K16" s="148" t="s">
+      <c r="K16" s="145" t="s">
         <v>111</v>
       </c>
-      <c r="L16" s="148" t="s">
+      <c r="L16" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="148" t="s">
+      <c r="M16" s="145" t="s">
         <v>75</v>
       </c>
-      <c r="N16" s="148" t="s">
+      <c r="N16" s="145" t="s">
         <v>110</v>
       </c>
-      <c r="O16" s="141"/>
+      <c r="O16" s="145" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="17" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="K17" s="144" t="s">
+      <c r="K17" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="146">
+      <c r="L17" s="143">
         <v>70</v>
       </c>
-      <c r="M17" s="145">
-        <v>9659</v>
-      </c>
-      <c r="N17" s="145">
-        <v>16359</v>
-      </c>
-      <c r="O17" s="142"/>
+      <c r="M17" s="142">
+        <v>11562</v>
+      </c>
+      <c r="N17" s="151">
+        <v>13270</v>
+      </c>
+      <c r="O17" s="152">
+        <f>N17-M5</f>
+        <v>-338</v>
+      </c>
     </row>
     <row r="18" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="147">
+      <c r="L18" s="144">
         <v>70</v>
       </c>
       <c r="M18" s="5">
-        <v>8160</v>
+        <v>10770</v>
       </c>
       <c r="N18" s="5">
-        <v>17947</v>
-      </c>
-      <c r="O18" s="142"/>
+        <v>14352</v>
+      </c>
+      <c r="O18" s="152">
+        <f>N18-M6</f>
+        <v>-343</v>
+      </c>
     </row>
     <row r="19" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L19" s="147">
+      <c r="L19" s="144">
         <v>70</v>
       </c>
       <c r="M19" s="5">
-        <v>10451</v>
+        <v>14619</v>
       </c>
       <c r="N19" s="5">
-        <v>6390</v>
-      </c>
-      <c r="O19" s="142"/>
+        <v>1010</v>
+      </c>
+      <c r="O19" s="152">
+        <f t="shared" ref="O19:O23" si="1">N19-M7</f>
+        <v>-325</v>
+      </c>
     </row>
     <row r="20" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="147">
+      <c r="L20" s="144">
         <v>120</v>
       </c>
       <c r="M20" s="5">
-        <v>15901</v>
+        <v>19143</v>
       </c>
       <c r="N20" s="5">
-        <v>17573</v>
-      </c>
-      <c r="O20" s="142"/>
+        <v>12294</v>
+      </c>
+      <c r="O20" s="152">
+        <f t="shared" si="1"/>
+        <v>-361</v>
+      </c>
     </row>
     <row r="21" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="147">
+      <c r="L21" s="144">
         <v>120</v>
       </c>
       <c r="M21" s="5">
-        <v>14283</v>
+        <v>17100</v>
       </c>
       <c r="N21" s="5">
-        <v>11088</v>
-      </c>
-      <c r="O21" s="142"/>
+        <v>6522</v>
+      </c>
+      <c r="O21" s="152">
+        <f t="shared" si="1"/>
+        <v>-695</v>
+      </c>
     </row>
     <row r="22" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="147">
+      <c r="L22" s="144">
         <v>120</v>
       </c>
       <c r="M22" s="5">
-        <v>18153</v>
+        <v>23404</v>
       </c>
       <c r="N22" s="5">
-        <v>16398</v>
-      </c>
-      <c r="O22" s="142"/>
+        <v>9539</v>
+      </c>
+      <c r="O22" s="152">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
     </row>
     <row r="23" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="147">
+      <c r="L23" s="144">
         <v>60</v>
       </c>
       <c r="M23" s="5">
-        <v>5525</v>
+        <v>7379</v>
       </c>
       <c r="N23" s="5">
-        <v>58249</v>
-      </c>
-      <c r="O23" s="142"/>
-    </row>
-    <row r="24" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="K24" s="149" t="s">
+        <v>57991</v>
+      </c>
+      <c r="O23" s="152">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="K24" s="146" t="s">
         <v>108</v>
       </c>
-      <c r="L24" s="150"/>
-      <c r="M24" s="151">
+      <c r="L24" s="147"/>
+      <c r="M24" s="148">
         <f>SUM(M17:M23)</f>
-        <v>82132</v>
-      </c>
-      <c r="N24" s="151">
+        <v>103977</v>
+      </c>
+      <c r="N24" s="148">
         <f>SUM(N17:N23)</f>
-        <v>144004</v>
-      </c>
-      <c r="O24" s="143"/>
-    </row>
-    <row r="25" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="K25" s="149" t="s">
+        <v>114978</v>
+      </c>
+      <c r="O24" s="145">
+        <f>SUM(O17:O23)</f>
+        <v>-1983</v>
+      </c>
+    </row>
+    <row r="25" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="K25" s="146" t="s">
         <v>109</v>
       </c>
-      <c r="L25" s="150"/>
-      <c r="M25" s="151">
+      <c r="L25" s="147"/>
+      <c r="M25" s="148">
         <f>M24/40</f>
-        <v>2053.3000000000002</v>
-      </c>
-      <c r="N25" s="151">
+        <v>2599.4250000000002</v>
+      </c>
+      <c r="N25" s="148">
         <f>N24/40</f>
-        <v>3600.1</v>
-      </c>
-      <c r="O25" s="143"/>
+        <v>2874.45</v>
+      </c>
+      <c r="O25" s="145">
+        <f>O24/40</f>
+        <v>-49.575000000000003</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6902,15 +9671,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7265625" customWidth="1"/>
     <col min="4" max="4" width="5.6328125" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.81640625" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -6923,120 +9697,233 @@
       <c r="D1" s="82" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
+      <c r="I1" s="153" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="153" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" s="153" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I2" s="82" t="s">
+        <v>136</v>
+      </c>
+      <c r="J2" s="82">
+        <v>20</v>
+      </c>
+      <c r="K2" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I3" s="82" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="82">
+        <v>22</v>
+      </c>
+      <c r="K3" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I4" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="82">
+        <v>114</v>
+      </c>
+      <c r="K4" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I5" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="82">
+        <v>60</v>
+      </c>
+      <c r="K5" s="82" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I6" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="J6" s="82">
+        <v>15</v>
+      </c>
+      <c r="K6" s="82" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I7" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="J7" s="82">
+        <v>72</v>
+      </c>
+      <c r="K7" s="82" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="84"/>
       <c r="B19" s="84"/>
       <c r="C19" s="84"/>
       <c r="D19" s="84"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="85"/>
       <c r="B20" s="86"/>
       <c r="C20" s="86"/>
       <c r="D20" s="87"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="82"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF4850B-BDA4-4F6E-B53D-1C5F35728833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDA7A9B-0B26-4F19-A5DF-C3A9C7118B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="165">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -503,6 +503,21 @@
   </si>
   <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>4 Season</t>
+  </si>
+  <si>
+    <t>8074586-2</t>
+  </si>
+  <si>
+    <t>Allowed</t>
+  </si>
+  <si>
+    <t>Sana C &amp; C</t>
+  </si>
+  <si>
+    <t>Rambo BT</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1605,7 +1620,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1631,7 +1645,6 @@
     <xf numFmtId="1" fontId="6" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1706,7 +1719,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1800,6 +1812,57 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1834,45 +1897,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2215,12 +2239,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B7:F23"/>
+  <dimension ref="B7:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" customWidth="1"/>
     <col min="6" max="6" width="39.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.6328125" bestFit="1" customWidth="1"/>
@@ -2235,147 +2260,183 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="104" t="s">
+      <c r="E9" s="161" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="102" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="92">
         <v>3520247902365</v>
       </c>
+      <c r="E10" s="162"/>
       <c r="F10">
         <v>10000</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="162"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="77">
+      <c r="C12" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="92">
         <v>300426949714</v>
       </c>
+      <c r="E12" s="162"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="92">
         <v>3277876126916</v>
       </c>
+      <c r="E13" s="162"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="92">
         <v>3520255124113</v>
       </c>
+      <c r="E14" s="162"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="92">
         <v>3520255124113</v>
       </c>
+      <c r="E15" s="162"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="92">
         <v>3520268948847</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
+      <c r="E16" s="162"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="79" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="2" t="s">
+      <c r="D17" s="79"/>
+      <c r="E17" s="162"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D18" s="79" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="91" t="s">
+      <c r="E18" s="162"/>
+    </row>
+    <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="163" t="s">
         <v>63</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="162" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="91" t="s">
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="163" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="91" t="s">
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="163" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="91" t="s">
+      <c r="C21" s="162"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="163" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="91" t="s">
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" s="163" t="s">
         <v>79</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="162" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="120">
+      <c r="D23" s="164">
         <v>3277876231301</v>
+      </c>
+      <c r="E23" s="162"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="163" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="162" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2394,13 +2455,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="164">
+      <c r="B1" s="178">
         <v>46186</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2422,10 +2483,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="175" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="179" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2458,13 +2519,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="178"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="181" t="s">
+      <c r="M2" s="167"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="182"/>
+      <c r="Q2" s="171"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2483,8 +2544,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="186"/>
-      <c r="B3" s="166"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="180"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2515,29 +2576,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="183" t="s">
+      <c r="M3" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="184"/>
-      <c r="O3" s="185"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="174"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="168" t="s">
+      <c r="R3" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="169"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="171" t="s">
+      <c r="S3" s="183"/>
+      <c r="T3" s="183"/>
+      <c r="U3" s="184"/>
+      <c r="V3" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="173"/>
+      <c r="W3" s="186"/>
+      <c r="X3" s="186"/>
+      <c r="Y3" s="187"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="186"/>
-      <c r="B4" s="167"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="181"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2609,36 +2670,36 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="79">
+      <c r="A5" s="78">
         <v>46179</v>
       </c>
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="95" t="s">
+      <c r="C5" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="96">
+      <c r="D5" s="94">
         <v>1003</v>
       </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99">
+      <c r="E5" s="95"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="97">
         <v>1613</v>
       </c>
-      <c r="H5" s="97">
+      <c r="H5" s="95">
         <v>2442</v>
       </c>
-      <c r="I5" s="98">
+      <c r="I5" s="96">
         <v>1036</v>
       </c>
-      <c r="J5" s="99">
+      <c r="J5" s="97">
         <v>5269</v>
       </c>
-      <c r="K5" s="97">
+      <c r="K5" s="95">
         <v>3838</v>
       </c>
-      <c r="L5" s="100">
+      <c r="L5" s="98">
         <v>4835</v>
       </c>
       <c r="M5" s="37">
@@ -2695,7 +2756,7 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="79">
+      <c r="A6" s="78">
         <v>46179</v>
       </c>
       <c r="B6" s="47">
@@ -2781,7 +2842,7 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="79">
+      <c r="A7" s="78">
         <v>46179</v>
       </c>
       <c r="B7" s="47">
@@ -2867,7 +2928,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="79">
+      <c r="A8" s="78">
         <v>46181</v>
       </c>
       <c r="B8" s="47">
@@ -2953,31 +3014,31 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="79">
+      <c r="A9" s="78">
         <v>46181</v>
       </c>
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="127" t="s">
+      <c r="C9" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="129"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="128"/>
+      <c r="H9" s="126"/>
       <c r="I9" s="56"/>
-      <c r="J9" s="131">
+      <c r="J9" s="128">
         <v>560</v>
       </c>
-      <c r="K9" s="129">
+      <c r="K9" s="126">
         <v>560</v>
       </c>
-      <c r="L9" s="130">
+      <c r="L9" s="127">
         <v>880</v>
       </c>
-      <c r="M9" s="132">
+      <c r="M9" s="129">
         <f t="shared" si="12"/>
         <v>50</v>
       </c>
@@ -3031,7 +3092,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="79">
+      <c r="A10" s="78">
         <v>46182</v>
       </c>
       <c r="B10" s="47">
@@ -3115,7 +3176,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="79">
+      <c r="A11" s="78">
         <v>46182</v>
       </c>
       <c r="B11" s="47">
@@ -3197,7 +3258,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="79">
+      <c r="A12" s="78">
         <v>46182</v>
       </c>
       <c r="B12" s="47">
@@ -3281,7 +3342,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="79">
+      <c r="A13" s="78">
         <v>46183</v>
       </c>
       <c r="B13" s="47">
@@ -3365,7 +3426,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="79">
+      <c r="A14" s="78">
         <v>46183</v>
       </c>
       <c r="B14" s="47">
@@ -3449,7 +3510,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="79">
+      <c r="A15" s="78">
         <v>46183</v>
       </c>
       <c r="B15" s="47">
@@ -3529,7 +3590,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="79">
+      <c r="A16" s="78">
         <v>46184</v>
       </c>
       <c r="B16" s="47">
@@ -3613,7 +3674,7 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="79">
+      <c r="A17" s="78">
         <v>46184</v>
       </c>
       <c r="B17" s="47">
@@ -3693,7 +3754,7 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="79">
+      <c r="A18" s="78">
         <v>46184</v>
       </c>
       <c r="B18" s="47">
@@ -3777,7 +3838,7 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="79">
+      <c r="A19" s="78">
         <v>46184</v>
       </c>
       <c r="B19" s="47">
@@ -3857,7 +3918,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="79">
+      <c r="A20" s="78">
         <v>46184</v>
       </c>
       <c r="B20" s="47">
@@ -3941,7 +4002,7 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="79">
+      <c r="A21" s="78">
         <v>46185</v>
       </c>
       <c r="B21" s="47">
@@ -4025,37 +4086,37 @@
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="79">
+      <c r="A22" s="78">
         <v>46185</v>
       </c>
-      <c r="B22" s="133">
+      <c r="B22" s="130">
         <v>18</v>
       </c>
-      <c r="C22" s="127" t="s">
+      <c r="C22" s="124" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="134"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="131">
+      <c r="D22" s="131"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="128">
         <v>300</v>
       </c>
-      <c r="H22" s="129">
+      <c r="H22" s="126">
         <v>300</v>
       </c>
       <c r="I22" s="56">
         <v>300</v>
       </c>
-      <c r="J22" s="131">
+      <c r="J22" s="128">
         <v>300</v>
       </c>
-      <c r="K22" s="129">
+      <c r="K22" s="126">
         <v>300</v>
       </c>
-      <c r="L22" s="130">
+      <c r="L22" s="127">
         <v>300</v>
       </c>
-      <c r="M22" s="132">
+      <c r="M22" s="129">
         <f t="shared" si="37"/>
         <v>45</v>
       </c>
@@ -4109,7 +4170,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="79">
+      <c r="A23" s="78">
         <v>46189</v>
       </c>
       <c r="B23" s="47">
@@ -4121,22 +4182,22 @@
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
       <c r="F23" s="76"/>
-      <c r="G23" s="137">
+      <c r="G23" s="134">
         <v>80</v>
       </c>
-      <c r="H23" s="138">
+      <c r="H23" s="135">
         <v>80</v>
       </c>
-      <c r="I23" s="139">
+      <c r="I23" s="136">
         <v>80</v>
       </c>
-      <c r="J23" s="137">
+      <c r="J23" s="134">
         <v>80</v>
       </c>
-      <c r="K23" s="138">
+      <c r="K23" s="135">
         <v>80</v>
       </c>
-      <c r="L23" s="140">
+      <c r="L23" s="137">
         <v>80</v>
       </c>
       <c r="M23" s="48">
@@ -4193,7 +4254,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="79">
+      <c r="A24" s="78">
         <v>46189</v>
       </c>
       <c r="B24" s="47">
@@ -4205,22 +4266,22 @@
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
       <c r="F24" s="76"/>
-      <c r="G24" s="137">
+      <c r="G24" s="134">
         <v>80</v>
       </c>
-      <c r="H24" s="138">
+      <c r="H24" s="135">
         <v>80</v>
       </c>
-      <c r="I24" s="139">
+      <c r="I24" s="136">
         <v>80</v>
       </c>
-      <c r="J24" s="137">
+      <c r="J24" s="134">
         <v>80</v>
       </c>
-      <c r="K24" s="138">
+      <c r="K24" s="135">
         <v>80</v>
       </c>
-      <c r="L24" s="140">
+      <c r="L24" s="137">
         <v>80</v>
       </c>
       <c r="M24" s="48">
@@ -4277,7 +4338,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="79">
+      <c r="A25" s="78">
         <v>46189</v>
       </c>
       <c r="B25" s="47">
@@ -4289,22 +4350,22 @@
       <c r="D25" s="74"/>
       <c r="E25" s="75"/>
       <c r="F25" s="76"/>
-      <c r="G25" s="137">
+      <c r="G25" s="134">
         <v>80</v>
       </c>
-      <c r="H25" s="138">
+      <c r="H25" s="135">
         <v>80</v>
       </c>
-      <c r="I25" s="139">
+      <c r="I25" s="136">
         <v>80</v>
       </c>
-      <c r="J25" s="137">
+      <c r="J25" s="134">
         <v>80</v>
       </c>
-      <c r="K25" s="138">
+      <c r="K25" s="135">
         <v>80</v>
       </c>
-      <c r="L25" s="140">
+      <c r="L25" s="137">
         <v>80</v>
       </c>
       <c r="M25" s="48">
@@ -4361,7 +4422,7 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="79">
+      <c r="A26" s="78">
         <v>46189</v>
       </c>
       <c r="B26" s="47">
@@ -4373,22 +4434,22 @@
       <c r="D26" s="74"/>
       <c r="E26" s="75"/>
       <c r="F26" s="76"/>
-      <c r="G26" s="137">
-        <v>40</v>
-      </c>
-      <c r="H26" s="138">
-        <v>40</v>
-      </c>
-      <c r="I26" s="139">
-        <v>40</v>
-      </c>
-      <c r="J26" s="137">
-        <v>40</v>
-      </c>
-      <c r="K26" s="138">
-        <v>40</v>
-      </c>
-      <c r="L26" s="140">
+      <c r="G26" s="134">
+        <v>40</v>
+      </c>
+      <c r="H26" s="135">
+        <v>40</v>
+      </c>
+      <c r="I26" s="136">
+        <v>40</v>
+      </c>
+      <c r="J26" s="134">
+        <v>40</v>
+      </c>
+      <c r="K26" s="135">
+        <v>40</v>
+      </c>
+      <c r="L26" s="137">
         <v>40</v>
       </c>
       <c r="M26" s="48">
@@ -4445,7 +4506,7 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="79">
+      <c r="A27" s="78">
         <v>46189</v>
       </c>
       <c r="B27" s="47">
@@ -4459,22 +4520,22 @@
       </c>
       <c r="E27" s="75"/>
       <c r="F27" s="76"/>
-      <c r="G27" s="137">
+      <c r="G27" s="134">
         <v>80</v>
       </c>
-      <c r="H27" s="138">
+      <c r="H27" s="135">
         <v>80</v>
       </c>
-      <c r="I27" s="139">
+      <c r="I27" s="136">
         <v>80</v>
       </c>
-      <c r="J27" s="137">
+      <c r="J27" s="134">
         <v>80</v>
       </c>
-      <c r="K27" s="138">
+      <c r="K27" s="135">
         <v>80</v>
       </c>
-      <c r="L27" s="140">
+      <c r="L27" s="137">
         <v>80</v>
       </c>
       <c r="M27" s="48">
@@ -4531,7 +4592,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="79">
+      <c r="A28" s="78">
         <v>46189</v>
       </c>
       <c r="B28" s="47">
@@ -4545,22 +4606,22 @@
       </c>
       <c r="E28" s="75"/>
       <c r="F28" s="76"/>
-      <c r="G28" s="137">
+      <c r="G28" s="134">
         <v>120</v>
       </c>
-      <c r="H28" s="138">
+      <c r="H28" s="135">
         <v>120</v>
       </c>
-      <c r="I28" s="139">
+      <c r="I28" s="136">
         <v>120</v>
       </c>
-      <c r="J28" s="137">
+      <c r="J28" s="134">
         <v>120</v>
       </c>
-      <c r="K28" s="138">
+      <c r="K28" s="135">
         <v>120</v>
       </c>
-      <c r="L28" s="140">
+      <c r="L28" s="137">
         <v>120</v>
       </c>
       <c r="M28" s="48">
@@ -4617,7 +4678,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="79">
+      <c r="A29" s="78">
         <v>46189</v>
       </c>
       <c r="B29" s="47">
@@ -4629,20 +4690,20 @@
       <c r="D29" s="74"/>
       <c r="E29" s="75"/>
       <c r="F29" s="76"/>
-      <c r="G29" s="137">
-        <v>40</v>
-      </c>
-      <c r="H29" s="138">
-        <v>40</v>
-      </c>
-      <c r="I29" s="139">
+      <c r="G29" s="134">
+        <v>40</v>
+      </c>
+      <c r="H29" s="135">
+        <v>40</v>
+      </c>
+      <c r="I29" s="136">
         <v>80</v>
       </c>
-      <c r="J29" s="137">
-        <v>40</v>
-      </c>
-      <c r="K29" s="138"/>
-      <c r="L29" s="140">
+      <c r="J29" s="134">
+        <v>40</v>
+      </c>
+      <c r="K29" s="135"/>
+      <c r="L29" s="137">
         <v>80</v>
       </c>
       <c r="M29" s="48">
@@ -4699,7 +4760,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="79">
+      <c r="A30" s="78">
         <v>46190</v>
       </c>
       <c r="B30" s="47">
@@ -4783,7 +4844,7 @@
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="79">
+      <c r="A31" s="78">
         <v>46190</v>
       </c>
       <c r="B31" s="47">
@@ -4867,37 +4928,37 @@
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="79">
+      <c r="A32" s="78">
         <v>46190</v>
       </c>
       <c r="B32" s="47">
         <v>28</v>
       </c>
-      <c r="C32" s="127" t="s">
+      <c r="C32" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="128"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="130"/>
-      <c r="G32" s="131">
-        <v>40</v>
-      </c>
-      <c r="H32" s="129">
+      <c r="D32" s="125"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="127"/>
+      <c r="G32" s="128">
+        <v>40</v>
+      </c>
+      <c r="H32" s="126">
         <v>40</v>
       </c>
       <c r="I32" s="56">
         <v>80</v>
       </c>
-      <c r="J32" s="131">
+      <c r="J32" s="128">
         <v>80</v>
       </c>
-      <c r="K32" s="129">
+      <c r="K32" s="126">
         <v>120</v>
       </c>
-      <c r="L32" s="130">
-        <v>40</v>
-      </c>
-      <c r="M32" s="132">
+      <c r="L32" s="127">
+        <v>40</v>
+      </c>
+      <c r="M32" s="129">
         <f t="shared" si="52"/>
         <v>10</v>
       </c>
@@ -4951,7 +5012,7 @@
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A33" s="79">
+      <c r="A33" s="78">
         <v>46190</v>
       </c>
       <c r="B33" s="47">
@@ -5037,7 +5098,7 @@
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A34" s="79">
+      <c r="A34" s="78">
         <v>46190</v>
       </c>
       <c r="B34" s="47">
@@ -5121,7 +5182,7 @@
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A35" s="79">
+      <c r="A35" s="78">
         <v>46190</v>
       </c>
       <c r="B35" s="47">
@@ -5205,7 +5266,7 @@
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="79">
+      <c r="A36" s="78">
         <v>46190</v>
       </c>
       <c r="B36" s="47">
@@ -5289,7 +5350,7 @@
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A37" s="79">
+      <c r="A37" s="78">
         <v>46190</v>
       </c>
       <c r="B37" s="47">
@@ -5373,7 +5434,7 @@
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A38" s="79">
+      <c r="A38" s="78">
         <v>46190</v>
       </c>
       <c r="B38" s="47">
@@ -5457,7 +5518,7 @@
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="79">
+      <c r="A39" s="78">
         <v>46190</v>
       </c>
       <c r="B39" s="47">
@@ -5541,7 +5602,7 @@
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A40" s="79">
+      <c r="A40" s="78">
         <v>46190</v>
       </c>
       <c r="B40" s="47">
@@ -5625,7 +5686,7 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A41" s="79">
+      <c r="A41" s="78">
         <v>46190</v>
       </c>
       <c r="B41" s="47">
@@ -5709,7 +5770,7 @@
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A42" s="79">
+      <c r="A42" s="78">
         <v>46190</v>
       </c>
       <c r="B42" s="47">
@@ -5793,7 +5854,7 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="79">
+      <c r="A43" s="78">
         <v>46190</v>
       </c>
       <c r="B43" s="47">
@@ -5877,7 +5938,7 @@
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A44" s="79">
+      <c r="A44" s="78">
         <v>46190</v>
       </c>
       <c r="B44" s="47">
@@ -5961,7 +6022,7 @@
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A45" s="79">
+      <c r="A45" s="78">
         <v>46191</v>
       </c>
       <c r="B45" s="47">
@@ -6045,7 +6106,7 @@
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A46" s="79">
+      <c r="A46" s="78">
         <v>46191</v>
       </c>
       <c r="B46" s="47">
@@ -6111,7 +6172,7 @@
       <c r="Y46" s="56"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A47" s="79">
+      <c r="A47" s="78">
         <v>46191</v>
       </c>
       <c r="B47" s="47">
@@ -6177,7 +6238,7 @@
       <c r="Y47" s="56"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A48" s="79">
+      <c r="A48" s="78">
         <v>46191</v>
       </c>
       <c r="B48" s="47">
@@ -6243,7 +6304,7 @@
       <c r="Y48" s="56"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A49" s="79">
+      <c r="A49" s="78">
         <v>46191</v>
       </c>
       <c r="B49" s="47">
@@ -6309,7 +6370,7 @@
       <c r="Y49" s="56"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A50" s="79">
+      <c r="A50" s="78">
         <v>46191</v>
       </c>
       <c r="B50" s="47">
@@ -6375,7 +6436,7 @@
       <c r="Y50" s="56"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A51" s="79">
+      <c r="A51" s="78">
         <v>46191</v>
       </c>
       <c r="B51" s="47">
@@ -6441,7 +6502,7 @@
       <c r="Y51" s="56"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A52" s="79">
+      <c r="A52" s="78">
         <v>46191</v>
       </c>
       <c r="B52" s="47">
@@ -6507,7 +6568,7 @@
       <c r="Y52" s="56"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A53" s="79">
+      <c r="A53" s="78">
         <v>46191</v>
       </c>
       <c r="B53" s="47">
@@ -6573,7 +6634,7 @@
       <c r="Y53" s="56"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A54" s="79">
+      <c r="A54" s="78">
         <v>46191</v>
       </c>
       <c r="B54" s="47">
@@ -6639,7 +6700,7 @@
       <c r="Y54" s="56"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A55" s="79">
+      <c r="A55" s="78">
         <v>46191</v>
       </c>
       <c r="B55" s="47">
@@ -6705,7 +6766,7 @@
       <c r="Y55" s="56"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A56" s="79">
+      <c r="A56" s="78">
         <v>46191</v>
       </c>
       <c r="B56" s="47">
@@ -6771,7 +6832,7 @@
       <c r="Y56" s="56"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A57" s="79">
+      <c r="A57" s="78">
         <v>46191</v>
       </c>
       <c r="B57" s="47">
@@ -6789,7 +6850,7 @@
       <c r="H57" s="75">
         <v>40</v>
       </c>
-      <c r="I57" s="157">
+      <c r="I57" s="154">
         <v>40</v>
       </c>
       <c r="J57" s="75">
@@ -6801,7 +6862,7 @@
       <c r="L57" s="75">
         <v>40</v>
       </c>
-      <c r="M57" s="156">
+      <c r="M57" s="153">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -6837,7 +6898,7 @@
       <c r="Y57" s="56"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A58" s="79">
+      <c r="A58" s="78">
         <v>46191</v>
       </c>
       <c r="B58" s="47">
@@ -6855,7 +6916,7 @@
       <c r="H58" s="75">
         <v>40</v>
       </c>
-      <c r="I58" s="157">
+      <c r="I58" s="154">
         <v>40</v>
       </c>
       <c r="J58" s="75">
@@ -6867,7 +6928,7 @@
       <c r="L58" s="75">
         <v>40</v>
       </c>
-      <c r="M58" s="156">
+      <c r="M58" s="153">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -6903,7 +6964,7 @@
       <c r="Y58" s="56"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A59" s="79">
+      <c r="A59" s="78">
         <v>46191</v>
       </c>
       <c r="B59" s="47">
@@ -6921,7 +6982,7 @@
       <c r="H59" s="75">
         <v>40</v>
       </c>
-      <c r="I59" s="157">
+      <c r="I59" s="154">
         <v>40</v>
       </c>
       <c r="J59" s="75">
@@ -6933,7 +6994,7 @@
       <c r="L59" s="75">
         <v>40</v>
       </c>
-      <c r="M59" s="156">
+      <c r="M59" s="153">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -6969,7 +7030,7 @@
       <c r="Y59" s="56"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A60" s="79">
+      <c r="A60" s="78">
         <v>46191</v>
       </c>
       <c r="B60" s="47">
@@ -6987,7 +7048,7 @@
       <c r="H60" s="75">
         <v>1200</v>
       </c>
-      <c r="I60" s="157">
+      <c r="I60" s="154">
         <v>2800</v>
       </c>
       <c r="J60" s="75">
@@ -6999,7 +7060,7 @@
       <c r="L60" s="75">
         <v>3600</v>
       </c>
-      <c r="M60" s="156">
+      <c r="M60" s="153">
         <f t="shared" si="52"/>
         <v>285</v>
       </c>
@@ -7053,37 +7114,37 @@
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A61" s="79">
+      <c r="A61" s="78">
         <v>46192</v>
       </c>
       <c r="B61" s="47">
         <v>57</v>
       </c>
-      <c r="C61" s="154" t="s">
+      <c r="C61" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="D61" s="149"/>
-      <c r="E61" s="149"/>
-      <c r="F61" s="149"/>
-      <c r="G61" s="149">
+      <c r="D61" s="146"/>
+      <c r="E61" s="146"/>
+      <c r="F61" s="146"/>
+      <c r="G61" s="146">
         <v>80</v>
       </c>
-      <c r="H61" s="149">
-        <v>0</v>
-      </c>
-      <c r="I61" s="158">
+      <c r="H61" s="146">
+        <v>0</v>
+      </c>
+      <c r="I61" s="155">
         <v>200</v>
       </c>
-      <c r="J61" s="149">
+      <c r="J61" s="146">
         <v>200</v>
       </c>
-      <c r="K61" s="149">
-        <v>0</v>
-      </c>
-      <c r="L61" s="149">
+      <c r="K61" s="146">
+        <v>0</v>
+      </c>
+      <c r="L61" s="146">
         <v>400</v>
       </c>
-      <c r="M61" s="156">
+      <c r="M61" s="153">
         <f t="shared" ref="M61:M79" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
@@ -7137,37 +7198,37 @@
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A62" s="79">
+      <c r="A62" s="78">
         <v>46192</v>
       </c>
       <c r="B62" s="47">
         <v>58</v>
       </c>
-      <c r="C62" s="154" t="s">
+      <c r="C62" s="151" t="s">
         <v>141</v>
       </c>
-      <c r="D62" s="149"/>
-      <c r="E62" s="149"/>
-      <c r="F62" s="149"/>
-      <c r="G62" s="149">
+      <c r="D62" s="146"/>
+      <c r="E62" s="146"/>
+      <c r="F62" s="146"/>
+      <c r="G62" s="146">
         <v>80</v>
       </c>
-      <c r="H62" s="149">
+      <c r="H62" s="146">
         <v>80</v>
       </c>
-      <c r="I62" s="158">
+      <c r="I62" s="155">
         <v>200</v>
       </c>
-      <c r="J62" s="149">
+      <c r="J62" s="146">
         <v>120</v>
       </c>
-      <c r="K62" s="149">
+      <c r="K62" s="146">
         <v>120</v>
       </c>
-      <c r="L62" s="149">
+      <c r="L62" s="146">
         <v>200</v>
       </c>
-      <c r="M62" s="156">
+      <c r="M62" s="153">
         <f t="shared" si="81"/>
         <v>20</v>
       </c>
@@ -7221,37 +7282,37 @@
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A63" s="79">
+      <c r="A63" s="78">
         <v>46192</v>
       </c>
       <c r="B63" s="47">
         <v>59</v>
       </c>
-      <c r="C63" s="154" t="s">
+      <c r="C63" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="149"/>
-      <c r="E63" s="149"/>
-      <c r="F63" s="149"/>
-      <c r="G63" s="149">
-        <v>40</v>
-      </c>
-      <c r="H63" s="149">
-        <v>40</v>
-      </c>
-      <c r="I63" s="158">
-        <v>40</v>
-      </c>
-      <c r="J63" s="149">
-        <v>40</v>
-      </c>
-      <c r="K63" s="149">
-        <v>40</v>
-      </c>
-      <c r="L63" s="149">
-        <v>40</v>
-      </c>
-      <c r="M63" s="156">
+      <c r="D63" s="146"/>
+      <c r="E63" s="146"/>
+      <c r="F63" s="146"/>
+      <c r="G63" s="146">
+        <v>40</v>
+      </c>
+      <c r="H63" s="146">
+        <v>40</v>
+      </c>
+      <c r="I63" s="155">
+        <v>40</v>
+      </c>
+      <c r="J63" s="146">
+        <v>40</v>
+      </c>
+      <c r="K63" s="146">
+        <v>40</v>
+      </c>
+      <c r="L63" s="146">
+        <v>40</v>
+      </c>
+      <c r="M63" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7305,37 +7366,37 @@
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A64" s="79">
+      <c r="A64" s="78">
         <v>46192</v>
       </c>
       <c r="B64" s="47">
         <v>60</v>
       </c>
-      <c r="C64" s="154" t="s">
+      <c r="C64" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="149"/>
-      <c r="E64" s="149"/>
-      <c r="F64" s="149"/>
-      <c r="G64" s="149">
-        <v>40</v>
-      </c>
-      <c r="H64" s="149">
-        <v>40</v>
-      </c>
-      <c r="I64" s="158">
-        <v>40</v>
-      </c>
-      <c r="J64" s="149">
-        <v>40</v>
-      </c>
-      <c r="K64" s="149">
-        <v>40</v>
-      </c>
-      <c r="L64" s="149">
-        <v>40</v>
-      </c>
-      <c r="M64" s="156">
+      <c r="D64" s="146"/>
+      <c r="E64" s="146"/>
+      <c r="F64" s="146"/>
+      <c r="G64" s="146">
+        <v>40</v>
+      </c>
+      <c r="H64" s="146">
+        <v>40</v>
+      </c>
+      <c r="I64" s="155">
+        <v>40</v>
+      </c>
+      <c r="J64" s="146">
+        <v>40</v>
+      </c>
+      <c r="K64" s="146">
+        <v>40</v>
+      </c>
+      <c r="L64" s="146">
+        <v>40</v>
+      </c>
+      <c r="M64" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7389,37 +7450,37 @@
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A65" s="79">
+      <c r="A65" s="78">
         <v>46192</v>
       </c>
       <c r="B65" s="47">
         <v>61</v>
       </c>
-      <c r="C65" s="154" t="s">
+      <c r="C65" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="D65" s="149"/>
-      <c r="E65" s="149"/>
-      <c r="F65" s="149"/>
-      <c r="G65" s="149">
-        <v>40</v>
-      </c>
-      <c r="H65" s="149">
-        <v>40</v>
-      </c>
-      <c r="I65" s="158">
-        <v>40</v>
-      </c>
-      <c r="J65" s="149">
-        <v>40</v>
-      </c>
-      <c r="K65" s="149">
-        <v>40</v>
-      </c>
-      <c r="L65" s="149">
-        <v>40</v>
-      </c>
-      <c r="M65" s="156">
+      <c r="D65" s="146"/>
+      <c r="E65" s="146"/>
+      <c r="F65" s="146"/>
+      <c r="G65" s="146">
+        <v>40</v>
+      </c>
+      <c r="H65" s="146">
+        <v>40</v>
+      </c>
+      <c r="I65" s="155">
+        <v>40</v>
+      </c>
+      <c r="J65" s="146">
+        <v>40</v>
+      </c>
+      <c r="K65" s="146">
+        <v>40</v>
+      </c>
+      <c r="L65" s="146">
+        <v>40</v>
+      </c>
+      <c r="M65" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7473,37 +7534,37 @@
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A66" s="79">
+      <c r="A66" s="78">
         <v>46192</v>
       </c>
       <c r="B66" s="47">
         <v>62</v>
       </c>
-      <c r="C66" s="154" t="s">
+      <c r="C66" s="151" t="s">
         <v>145</v>
       </c>
-      <c r="D66" s="149"/>
-      <c r="E66" s="149"/>
-      <c r="F66" s="149"/>
-      <c r="G66" s="149">
+      <c r="D66" s="146"/>
+      <c r="E66" s="146"/>
+      <c r="F66" s="146"/>
+      <c r="G66" s="146">
         <v>80</v>
       </c>
-      <c r="H66" s="149">
+      <c r="H66" s="146">
         <v>80</v>
       </c>
-      <c r="I66" s="158">
+      <c r="I66" s="155">
         <v>80</v>
       </c>
-      <c r="J66" s="149">
+      <c r="J66" s="146">
         <v>80</v>
       </c>
-      <c r="K66" s="149">
+      <c r="K66" s="146">
         <v>80</v>
       </c>
-      <c r="L66" s="149">
+      <c r="L66" s="146">
         <v>80</v>
       </c>
-      <c r="M66" s="156">
+      <c r="M66" s="153">
         <f t="shared" si="81"/>
         <v>12</v>
       </c>
@@ -7557,37 +7618,37 @@
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A67" s="79">
+      <c r="A67" s="78">
         <v>46192</v>
       </c>
       <c r="B67" s="47">
         <v>63</v>
       </c>
-      <c r="C67" s="154" t="s">
+      <c r="C67" s="151" t="s">
         <v>146</v>
       </c>
-      <c r="D67" s="149"/>
-      <c r="E67" s="149"/>
-      <c r="F67" s="149"/>
-      <c r="G67" s="149">
-        <v>40</v>
-      </c>
-      <c r="H67" s="149">
-        <v>40</v>
-      </c>
-      <c r="I67" s="158">
-        <v>40</v>
-      </c>
-      <c r="J67" s="149">
-        <v>40</v>
-      </c>
-      <c r="K67" s="149">
-        <v>40</v>
-      </c>
-      <c r="L67" s="149">
-        <v>40</v>
-      </c>
-      <c r="M67" s="156">
+      <c r="D67" s="146"/>
+      <c r="E67" s="146"/>
+      <c r="F67" s="146"/>
+      <c r="G67" s="146">
+        <v>40</v>
+      </c>
+      <c r="H67" s="146">
+        <v>40</v>
+      </c>
+      <c r="I67" s="155">
+        <v>40</v>
+      </c>
+      <c r="J67" s="146">
+        <v>40</v>
+      </c>
+      <c r="K67" s="146">
+        <v>40</v>
+      </c>
+      <c r="L67" s="146">
+        <v>40</v>
+      </c>
+      <c r="M67" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7641,37 +7702,37 @@
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A68" s="79">
+      <c r="A68" s="78">
         <v>46192</v>
       </c>
       <c r="B68" s="47">
         <v>64</v>
       </c>
-      <c r="C68" s="154" t="s">
+      <c r="C68" s="151" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="149"/>
-      <c r="E68" s="149"/>
-      <c r="F68" s="149"/>
-      <c r="G68" s="149">
-        <v>40</v>
-      </c>
-      <c r="H68" s="149">
-        <v>40</v>
-      </c>
-      <c r="I68" s="158">
-        <v>40</v>
-      </c>
-      <c r="J68" s="149">
-        <v>40</v>
-      </c>
-      <c r="K68" s="149">
-        <v>40</v>
-      </c>
-      <c r="L68" s="149">
-        <v>40</v>
-      </c>
-      <c r="M68" s="156">
+      <c r="D68" s="146"/>
+      <c r="E68" s="146"/>
+      <c r="F68" s="146"/>
+      <c r="G68" s="146">
+        <v>40</v>
+      </c>
+      <c r="H68" s="146">
+        <v>40</v>
+      </c>
+      <c r="I68" s="155">
+        <v>40</v>
+      </c>
+      <c r="J68" s="146">
+        <v>40</v>
+      </c>
+      <c r="K68" s="146">
+        <v>40</v>
+      </c>
+      <c r="L68" s="146">
+        <v>40</v>
+      </c>
+      <c r="M68" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7725,37 +7786,37 @@
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A69" s="79">
+      <c r="A69" s="78">
         <v>46192</v>
       </c>
       <c r="B69" s="47">
         <v>65</v>
       </c>
-      <c r="C69" s="154" t="s">
+      <c r="C69" s="151" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="149"/>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="149">
+      <c r="D69" s="146"/>
+      <c r="E69" s="146"/>
+      <c r="F69" s="146"/>
+      <c r="G69" s="146">
         <v>80</v>
       </c>
-      <c r="H69" s="149">
+      <c r="H69" s="146">
         <v>80</v>
       </c>
-      <c r="I69" s="158">
+      <c r="I69" s="155">
         <v>80</v>
       </c>
-      <c r="J69" s="149">
+      <c r="J69" s="146">
         <v>80</v>
       </c>
-      <c r="K69" s="149">
+      <c r="K69" s="146">
         <v>80</v>
       </c>
-      <c r="L69" s="149">
+      <c r="L69" s="146">
         <v>80</v>
       </c>
-      <c r="M69" s="156">
+      <c r="M69" s="153">
         <f t="shared" si="81"/>
         <v>12</v>
       </c>
@@ -7809,37 +7870,37 @@
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="79">
+      <c r="A70" s="78">
         <v>46192</v>
       </c>
       <c r="B70" s="47">
         <v>66</v>
       </c>
-      <c r="C70" s="154" t="s">
+      <c r="C70" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="D70" s="149"/>
-      <c r="E70" s="149"/>
-      <c r="F70" s="149"/>
-      <c r="G70" s="149">
-        <v>40</v>
-      </c>
-      <c r="H70" s="149">
-        <v>40</v>
-      </c>
-      <c r="I70" s="158">
-        <v>40</v>
-      </c>
-      <c r="J70" s="149">
-        <v>40</v>
-      </c>
-      <c r="K70" s="149">
-        <v>40</v>
-      </c>
-      <c r="L70" s="149">
-        <v>40</v>
-      </c>
-      <c r="M70" s="156">
+      <c r="D70" s="146"/>
+      <c r="E70" s="146"/>
+      <c r="F70" s="146"/>
+      <c r="G70" s="146">
+        <v>40</v>
+      </c>
+      <c r="H70" s="146">
+        <v>40</v>
+      </c>
+      <c r="I70" s="155">
+        <v>40</v>
+      </c>
+      <c r="J70" s="146">
+        <v>40</v>
+      </c>
+      <c r="K70" s="146">
+        <v>40</v>
+      </c>
+      <c r="L70" s="146">
+        <v>40</v>
+      </c>
+      <c r="M70" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7893,37 +7954,37 @@
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="79">
+      <c r="A71" s="78">
         <v>46192</v>
       </c>
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="162" t="s">
+      <c r="C71" s="159" t="s">
         <v>150</v>
       </c>
-      <c r="D71" s="129"/>
-      <c r="E71" s="129"/>
-      <c r="F71" s="129"/>
-      <c r="G71" s="129">
-        <v>0</v>
-      </c>
-      <c r="H71" s="129">
-        <v>0</v>
-      </c>
-      <c r="I71" s="163">
-        <v>0</v>
-      </c>
-      <c r="J71" s="129">
-        <v>0</v>
-      </c>
-      <c r="K71" s="129">
-        <v>0</v>
-      </c>
-      <c r="L71" s="129">
-        <v>0</v>
-      </c>
-      <c r="M71" s="156">
+      <c r="D71" s="126"/>
+      <c r="E71" s="126"/>
+      <c r="F71" s="126"/>
+      <c r="G71" s="126">
+        <v>0</v>
+      </c>
+      <c r="H71" s="126">
+        <v>0</v>
+      </c>
+      <c r="I71" s="160">
+        <v>0</v>
+      </c>
+      <c r="J71" s="126">
+        <v>0</v>
+      </c>
+      <c r="K71" s="126">
+        <v>0</v>
+      </c>
+      <c r="L71" s="126">
+        <v>0</v>
+      </c>
+      <c r="M71" s="153">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -7977,37 +8038,37 @@
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="79">
+      <c r="A72" s="78">
         <v>46192</v>
       </c>
       <c r="B72" s="47">
         <v>68</v>
       </c>
-      <c r="C72" s="154" t="s">
+      <c r="C72" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="149"/>
-      <c r="E72" s="149"/>
-      <c r="F72" s="149"/>
-      <c r="G72" s="149">
-        <v>40</v>
-      </c>
-      <c r="H72" s="149">
-        <v>40</v>
-      </c>
-      <c r="I72" s="158">
-        <v>40</v>
-      </c>
-      <c r="J72" s="149">
-        <v>40</v>
-      </c>
-      <c r="K72" s="149">
-        <v>40</v>
-      </c>
-      <c r="L72" s="149">
-        <v>40</v>
-      </c>
-      <c r="M72" s="156">
+      <c r="D72" s="146"/>
+      <c r="E72" s="146"/>
+      <c r="F72" s="146"/>
+      <c r="G72" s="146">
+        <v>40</v>
+      </c>
+      <c r="H72" s="146">
+        <v>40</v>
+      </c>
+      <c r="I72" s="155">
+        <v>40</v>
+      </c>
+      <c r="J72" s="146">
+        <v>40</v>
+      </c>
+      <c r="K72" s="146">
+        <v>40</v>
+      </c>
+      <c r="L72" s="146">
+        <v>40</v>
+      </c>
+      <c r="M72" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8061,37 +8122,37 @@
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="79">
+      <c r="A73" s="78">
         <v>46192</v>
       </c>
       <c r="B73" s="47">
         <v>69</v>
       </c>
-      <c r="C73" s="154" t="s">
+      <c r="C73" s="151" t="s">
         <v>152</v>
       </c>
-      <c r="D73" s="149"/>
-      <c r="E73" s="149"/>
-      <c r="F73" s="149"/>
-      <c r="G73" s="149">
-        <v>40</v>
-      </c>
-      <c r="H73" s="149">
-        <v>40</v>
-      </c>
-      <c r="I73" s="158">
-        <v>40</v>
-      </c>
-      <c r="J73" s="149">
-        <v>40</v>
-      </c>
-      <c r="K73" s="149">
-        <v>40</v>
-      </c>
-      <c r="L73" s="149">
-        <v>40</v>
-      </c>
-      <c r="M73" s="156">
+      <c r="D73" s="146"/>
+      <c r="E73" s="146"/>
+      <c r="F73" s="146"/>
+      <c r="G73" s="146">
+        <v>40</v>
+      </c>
+      <c r="H73" s="146">
+        <v>40</v>
+      </c>
+      <c r="I73" s="155">
+        <v>40</v>
+      </c>
+      <c r="J73" s="146">
+        <v>40</v>
+      </c>
+      <c r="K73" s="146">
+        <v>40</v>
+      </c>
+      <c r="L73" s="146">
+        <v>40</v>
+      </c>
+      <c r="M73" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8145,37 +8206,37 @@
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="79">
+      <c r="A74" s="78">
         <v>46192</v>
       </c>
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="159" t="s">
+      <c r="C74" s="156" t="s">
         <v>153</v>
       </c>
-      <c r="D74" s="149"/>
-      <c r="E74" s="149"/>
-      <c r="F74" s="150"/>
-      <c r="G74" s="149">
-        <v>40</v>
-      </c>
-      <c r="H74" s="149">
-        <v>40</v>
-      </c>
-      <c r="I74" s="158">
-        <v>40</v>
-      </c>
-      <c r="J74" s="149">
-        <v>40</v>
-      </c>
-      <c r="K74" s="149">
-        <v>40</v>
-      </c>
-      <c r="L74" s="149">
-        <v>40</v>
-      </c>
-      <c r="M74" s="156">
+      <c r="D74" s="146"/>
+      <c r="E74" s="146"/>
+      <c r="F74" s="147"/>
+      <c r="G74" s="146">
+        <v>40</v>
+      </c>
+      <c r="H74" s="146">
+        <v>40</v>
+      </c>
+      <c r="I74" s="155">
+        <v>40</v>
+      </c>
+      <c r="J74" s="146">
+        <v>40</v>
+      </c>
+      <c r="K74" s="146">
+        <v>40</v>
+      </c>
+      <c r="L74" s="146">
+        <v>40</v>
+      </c>
+      <c r="M74" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8229,37 +8290,37 @@
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="79">
+      <c r="A75" s="78">
         <v>46192</v>
       </c>
       <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="159" t="s">
+      <c r="C75" s="156" t="s">
         <v>154</v>
       </c>
-      <c r="D75" s="149"/>
-      <c r="E75" s="150"/>
-      <c r="F75" s="150"/>
-      <c r="G75" s="149">
-        <v>40</v>
-      </c>
-      <c r="H75" s="149">
-        <v>40</v>
-      </c>
-      <c r="I75" s="158">
-        <v>40</v>
-      </c>
-      <c r="J75" s="149">
-        <v>40</v>
-      </c>
-      <c r="K75" s="149">
-        <v>40</v>
-      </c>
-      <c r="L75" s="149">
-        <v>40</v>
-      </c>
-      <c r="M75" s="156">
+      <c r="D75" s="146"/>
+      <c r="E75" s="147"/>
+      <c r="F75" s="147"/>
+      <c r="G75" s="146">
+        <v>40</v>
+      </c>
+      <c r="H75" s="146">
+        <v>40</v>
+      </c>
+      <c r="I75" s="155">
+        <v>40</v>
+      </c>
+      <c r="J75" s="146">
+        <v>40</v>
+      </c>
+      <c r="K75" s="146">
+        <v>40</v>
+      </c>
+      <c r="L75" s="146">
+        <v>40</v>
+      </c>
+      <c r="M75" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8313,37 +8374,37 @@
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="79">
+      <c r="A76" s="78">
         <v>46192</v>
       </c>
       <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="159" t="s">
+      <c r="C76" s="156" t="s">
         <v>155</v>
       </c>
-      <c r="D76" s="149"/>
-      <c r="E76" s="150"/>
-      <c r="F76" s="150"/>
-      <c r="G76" s="149">
-        <v>40</v>
-      </c>
-      <c r="H76" s="149">
-        <v>40</v>
-      </c>
-      <c r="I76" s="158">
-        <v>40</v>
-      </c>
-      <c r="J76" s="149">
-        <v>40</v>
-      </c>
-      <c r="K76" s="149">
-        <v>40</v>
-      </c>
-      <c r="L76" s="149">
-        <v>40</v>
-      </c>
-      <c r="M76" s="156">
+      <c r="D76" s="146"/>
+      <c r="E76" s="147"/>
+      <c r="F76" s="147"/>
+      <c r="G76" s="146">
+        <v>40</v>
+      </c>
+      <c r="H76" s="146">
+        <v>40</v>
+      </c>
+      <c r="I76" s="155">
+        <v>40</v>
+      </c>
+      <c r="J76" s="146">
+        <v>40</v>
+      </c>
+      <c r="K76" s="146">
+        <v>40</v>
+      </c>
+      <c r="L76" s="146">
+        <v>40</v>
+      </c>
+      <c r="M76" s="153">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8397,37 +8458,37 @@
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="79">
+      <c r="A77" s="78">
         <v>46192</v>
       </c>
       <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="160" t="s">
+      <c r="C77" s="157" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="129"/>
-      <c r="E77" s="131"/>
-      <c r="F77" s="131"/>
-      <c r="G77" s="131">
-        <v>0</v>
-      </c>
-      <c r="H77" s="131">
-        <v>0</v>
-      </c>
-      <c r="I77" s="161">
-        <v>0</v>
-      </c>
-      <c r="J77" s="131">
-        <v>0</v>
-      </c>
-      <c r="K77" s="131">
-        <v>0</v>
-      </c>
-      <c r="L77" s="131">
-        <v>0</v>
-      </c>
-      <c r="M77" s="156">
+      <c r="D77" s="126"/>
+      <c r="E77" s="128"/>
+      <c r="F77" s="128"/>
+      <c r="G77" s="128">
+        <v>0</v>
+      </c>
+      <c r="H77" s="128">
+        <v>0</v>
+      </c>
+      <c r="I77" s="158">
+        <v>0</v>
+      </c>
+      <c r="J77" s="128">
+        <v>0</v>
+      </c>
+      <c r="K77" s="128">
+        <v>0</v>
+      </c>
+      <c r="L77" s="128">
+        <v>0</v>
+      </c>
+      <c r="M77" s="153">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8481,37 +8542,37 @@
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="79">
+      <c r="A78" s="78">
         <v>46192</v>
       </c>
       <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="160" t="s">
+      <c r="C78" s="157" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="129"/>
-      <c r="E78" s="131"/>
-      <c r="F78" s="131"/>
-      <c r="G78" s="131">
-        <v>0</v>
-      </c>
-      <c r="H78" s="131">
-        <v>0</v>
-      </c>
-      <c r="I78" s="161">
-        <v>0</v>
-      </c>
-      <c r="J78" s="131">
-        <v>0</v>
-      </c>
-      <c r="K78" s="131">
-        <v>0</v>
-      </c>
-      <c r="L78" s="131">
-        <v>0</v>
-      </c>
-      <c r="M78" s="156">
+      <c r="D78" s="126"/>
+      <c r="E78" s="128"/>
+      <c r="F78" s="128"/>
+      <c r="G78" s="128">
+        <v>0</v>
+      </c>
+      <c r="H78" s="128">
+        <v>0</v>
+      </c>
+      <c r="I78" s="158">
+        <v>0</v>
+      </c>
+      <c r="J78" s="128">
+        <v>0</v>
+      </c>
+      <c r="K78" s="128">
+        <v>0</v>
+      </c>
+      <c r="L78" s="128">
+        <v>0</v>
+      </c>
+      <c r="M78" s="153">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8565,21 +8626,21 @@
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A79" s="79"/>
+      <c r="A79" s="78"/>
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="155"/>
+      <c r="C79" s="152"/>
       <c r="D79" s="50"/>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
       <c r="G79" s="50"/>
       <c r="H79" s="50"/>
-      <c r="I79" s="156"/>
+      <c r="I79" s="153"/>
       <c r="J79" s="50"/>
       <c r="K79" s="50"/>
       <c r="L79" s="50"/>
-      <c r="M79" s="156">
+      <c r="M79" s="153">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8633,44 +8694,44 @@
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A80" s="79"/>
-      <c r="B80" s="174" t="s">
+      <c r="A80" s="78"/>
+      <c r="B80" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="C80" s="175"/>
-      <c r="D80" s="89">
+      <c r="C80" s="189"/>
+      <c r="D80" s="88">
         <f t="shared" ref="D80:L80" si="89">SUM(D6:D60)</f>
         <v>1320</v>
       </c>
-      <c r="E80" s="89">
+      <c r="E80" s="88">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="F80" s="89">
+      <c r="F80" s="88">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="G80" s="89">
+      <c r="G80" s="88">
         <f t="shared" si="89"/>
         <v>7140</v>
       </c>
-      <c r="H80" s="89">
+      <c r="H80" s="88">
         <f t="shared" si="89"/>
         <v>7657</v>
       </c>
-      <c r="I80" s="89">
+      <c r="I80" s="88">
         <f t="shared" si="89"/>
         <v>10657</v>
       </c>
-      <c r="J80" s="89">
+      <c r="J80" s="88">
         <f t="shared" si="89"/>
         <v>11297</v>
       </c>
-      <c r="K80" s="89">
+      <c r="K80" s="88">
         <f t="shared" si="89"/>
         <v>9684</v>
       </c>
-      <c r="L80" s="89">
+      <c r="L80" s="88">
         <f t="shared" si="89"/>
         <v>13219</v>
       </c>
@@ -8728,31 +8789,31 @@
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A81" s="79"/>
-      <c r="B81" s="121">
+      <c r="A81" s="78"/>
+      <c r="B81" s="118">
         <v>0</v>
       </c>
       <c r="C81" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="D81" s="122">
+      <c r="D81" s="119">
         <v>1600</v>
       </c>
-      <c r="E81" s="123"/>
-      <c r="F81" s="124"/>
-      <c r="G81" s="123"/>
-      <c r="H81" s="123"/>
-      <c r="I81" s="124"/>
-      <c r="J81" s="123">
+      <c r="E81" s="120"/>
+      <c r="F81" s="121"/>
+      <c r="G81" s="120"/>
+      <c r="H81" s="120"/>
+      <c r="I81" s="121"/>
+      <c r="J81" s="120">
         <v>520</v>
       </c>
-      <c r="K81" s="123">
+      <c r="K81" s="120">
         <v>920</v>
       </c>
-      <c r="L81" s="124">
+      <c r="L81" s="121">
         <v>960</v>
       </c>
-      <c r="M81" s="125">
+      <c r="M81" s="122">
         <f>SUM(D81:L81)</f>
         <v>4000</v>
       </c>
@@ -8770,7 +8831,7 @@
       <c r="Y81" s="56"/>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A82" s="79"/>
+      <c r="A82" s="78"/>
       <c r="B82" s="47">
         <v>1</v>
       </c>
@@ -8941,47 +9002,47 @@
       </c>
     </row>
     <row r="84" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="187" t="s">
+      <c r="B84" s="176" t="s">
         <v>93</v>
       </c>
-      <c r="C84" s="188"/>
-      <c r="D84" s="88">
+      <c r="C84" s="177"/>
+      <c r="D84" s="87">
         <f>SUM(D82:D83)</f>
         <v>1400</v>
       </c>
-      <c r="E84" s="88">
+      <c r="E84" s="87">
         <f t="shared" ref="E84:L84" si="96">SUM(E82:E83)</f>
         <v>0</v>
       </c>
-      <c r="F84" s="88">
+      <c r="F84" s="87">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
-      <c r="G84" s="88">
+      <c r="G84" s="87">
         <f t="shared" si="96"/>
         <v>2280</v>
       </c>
-      <c r="H84" s="88">
+      <c r="H84" s="87">
         <f t="shared" si="96"/>
         <v>1000</v>
       </c>
-      <c r="I84" s="88">
+      <c r="I84" s="87">
         <f t="shared" si="96"/>
         <v>2120</v>
       </c>
-      <c r="J84" s="88">
+      <c r="J84" s="87">
         <f t="shared" si="96"/>
         <v>3800</v>
       </c>
-      <c r="K84" s="88">
+      <c r="K84" s="87">
         <f t="shared" si="96"/>
         <v>3400</v>
       </c>
-      <c r="L84" s="88">
+      <c r="L84" s="87">
         <f t="shared" si="96"/>
         <v>5600</v>
       </c>
-      <c r="M84" s="126">
+      <c r="M84" s="123">
         <f>SUM(M81:M83)</f>
         <v>4490</v>
       </c>
@@ -9035,43 +9096,43 @@
       </c>
     </row>
     <row r="85" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B85" s="176" t="s">
+      <c r="B85" s="165" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="177"/>
-      <c r="D85" s="90">
+      <c r="C85" s="166"/>
+      <c r="D85" s="89">
         <f>SUM(D80,D84)</f>
         <v>2720</v>
       </c>
-      <c r="E85" s="90">
+      <c r="E85" s="89">
         <f t="shared" ref="E85:L85" si="97">SUM(E80,E84)</f>
         <v>0</v>
       </c>
-      <c r="F85" s="90">
+      <c r="F85" s="89">
         <f t="shared" si="97"/>
         <v>0</v>
       </c>
-      <c r="G85" s="90">
+      <c r="G85" s="89">
         <f t="shared" si="97"/>
         <v>9420</v>
       </c>
-      <c r="H85" s="90">
+      <c r="H85" s="89">
         <f t="shared" si="97"/>
         <v>8657</v>
       </c>
-      <c r="I85" s="90">
+      <c r="I85" s="89">
         <f t="shared" si="97"/>
         <v>12777</v>
       </c>
-      <c r="J85" s="90">
+      <c r="J85" s="89">
         <f t="shared" si="97"/>
         <v>15097</v>
       </c>
-      <c r="K85" s="90">
+      <c r="K85" s="89">
         <f t="shared" si="97"/>
         <v>13084</v>
       </c>
-      <c r="L85" s="90">
+      <c r="L85" s="89">
         <f t="shared" si="97"/>
         <v>18819</v>
       </c>
@@ -9130,17 +9191,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B80:C80"/>
     <mergeCell ref="B85:C85"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B80:C80"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -9170,43 +9231,43 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="189" t="s">
+      <c r="C3" s="190" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="193" t="s">
+      <c r="D3" s="191"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="191"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="194" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="194"/>
-      <c r="K3" s="195" t="s">
+      <c r="I3" s="195"/>
+      <c r="K3" s="196" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="195"/>
-      <c r="M3" s="195"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="195"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="196"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="111"/>
-      <c r="D4" s="81" t="s">
+      <c r="C4" s="109"/>
+      <c r="D4" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="81" t="s">
+      <c r="E4" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="81" t="s">
+      <c r="F4" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="112" t="s">
+      <c r="G4" s="110" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="105" t="s">
+      <c r="H4" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="106" t="s">
+      <c r="I4" s="104" t="s">
         <v>78</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -9226,26 +9287,26 @@
       </c>
     </row>
     <row r="5" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="113" t="s">
+      <c r="C5" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="92">
         <v>548</v>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="79">
         <v>1656</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="79">
         <v>590</v>
       </c>
-      <c r="G5" s="114">
+      <c r="G5" s="112">
         <f>SUM(D5:F5)</f>
         <v>2794</v>
       </c>
-      <c r="H5" s="107">
+      <c r="H5" s="105">
         <v>10000</v>
       </c>
-      <c r="I5" s="108">
+      <c r="I5" s="106">
         <f>G5-H5</f>
         <v>-7206</v>
       </c>
@@ -9262,35 +9323,35 @@
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
         <v>340.2</v>
       </c>
-      <c r="O5" s="82">
+      <c r="O5" s="81">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C6" s="115" t="s">
+      <c r="C6" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="116">
+      <c r="D6" s="114">
         <f>D5*40</f>
         <v>21920</v>
       </c>
-      <c r="E6" s="117">
+      <c r="E6" s="115">
         <f>E5*40</f>
         <v>66240</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="115">
         <f>F5*40</f>
         <v>23600</v>
       </c>
-      <c r="G6" s="118">
+      <c r="G6" s="116">
         <f>SUM(D6:F6)</f>
         <v>111760</v>
       </c>
-      <c r="H6" s="109">
+      <c r="H6" s="107">
         <f>H5*40</f>
         <v>400000</v>
       </c>
-      <c r="I6" s="110">
+      <c r="I6" s="108">
         <f>G6-H6</f>
         <v>-288240</v>
       </c>
@@ -9307,12 +9368,12 @@
         <f t="shared" si="0"/>
         <v>367.375</v>
       </c>
-      <c r="O6" s="82">
+      <c r="O6" s="81">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="92"/>
+      <c r="C7" s="90"/>
       <c r="K7" s="1" t="s">
         <v>3</v>
       </c>
@@ -9326,12 +9387,12 @@
         <f t="shared" si="0"/>
         <v>33.375</v>
       </c>
-      <c r="O7" s="82">
+      <c r="O7" s="81">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="82" t="s">
         <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -9347,19 +9408,19 @@
         <f t="shared" si="0"/>
         <v>316.375</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="81">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="119">
+      <c r="D9" s="117">
         <f>D8-D5</f>
         <v>-548</v>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="117">
         <f>E8-E5</f>
         <v>-1656</v>
       </c>
@@ -9376,7 +9437,7 @@
         <f t="shared" si="0"/>
         <v>180.42500000000001</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="81">
         <v>33</v>
       </c>
     </row>
@@ -9394,19 +9455,19 @@
         <f t="shared" si="0"/>
         <v>236.8</v>
       </c>
-      <c r="O10" s="82">
+      <c r="O10" s="81">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="192" t="s">
+      <c r="C11" s="193" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="192"/>
-      <c r="F11" s="192" t="s">
+      <c r="D11" s="193"/>
+      <c r="F11" s="193" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="192"/>
+      <c r="G11" s="193"/>
       <c r="H11" t="s">
         <v>158</v>
       </c>
@@ -9427,21 +9488,21 @@
         <f t="shared" si="0"/>
         <v>1449.4749999999999</v>
       </c>
-      <c r="O11" s="82">
+      <c r="O11" s="81">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="93">
+      <c r="D12" s="91">
         <v>500.9</v>
       </c>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="101">
         <f>D12+G5</f>
         <v>3294.9</v>
       </c>
@@ -9463,52 +9524,52 @@
       </c>
     </row>
     <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="103">
+      <c r="D13" s="101">
         <f>D12*40</f>
         <v>20036</v>
       </c>
-      <c r="F13" s="102" t="s">
+      <c r="F13" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="103">
+      <c r="G13" s="101">
         <f>G12*40</f>
         <v>131796</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="K16" s="145" t="s">
+      <c r="K16" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="L16" s="145" t="s">
+      <c r="L16" s="142" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="145" t="s">
+      <c r="M16" s="142" t="s">
         <v>75</v>
       </c>
-      <c r="N16" s="145" t="s">
+      <c r="N16" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="O16" s="145" t="s">
+      <c r="O16" s="142" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="17" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="K17" s="141" t="s">
+      <c r="K17" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="L17" s="143">
+      <c r="L17" s="140">
         <v>70</v>
       </c>
-      <c r="M17" s="142">
+      <c r="M17" s="139">
         <v>11562</v>
       </c>
-      <c r="N17" s="151">
+      <c r="N17" s="148">
         <v>13270</v>
       </c>
-      <c r="O17" s="152">
+      <c r="O17" s="149">
         <f>N17-M5</f>
         <v>-338</v>
       </c>
@@ -9517,7 +9578,7 @@
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L18" s="144">
+      <c r="L18" s="141">
         <v>70</v>
       </c>
       <c r="M18" s="5">
@@ -9526,7 +9587,7 @@
       <c r="N18" s="5">
         <v>14352</v>
       </c>
-      <c r="O18" s="152">
+      <c r="O18" s="149">
         <f>N18-M6</f>
         <v>-343</v>
       </c>
@@ -9535,7 +9596,7 @@
       <c r="K19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L19" s="144">
+      <c r="L19" s="141">
         <v>70</v>
       </c>
       <c r="M19" s="5">
@@ -9544,7 +9605,7 @@
       <c r="N19" s="5">
         <v>1010</v>
       </c>
-      <c r="O19" s="152">
+      <c r="O19" s="149">
         <f t="shared" ref="O19:O23" si="1">N19-M7</f>
         <v>-325</v>
       </c>
@@ -9553,7 +9614,7 @@
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="144">
+      <c r="L20" s="141">
         <v>120</v>
       </c>
       <c r="M20" s="5">
@@ -9562,7 +9623,7 @@
       <c r="N20" s="5">
         <v>12294</v>
       </c>
-      <c r="O20" s="152">
+      <c r="O20" s="149">
         <f t="shared" si="1"/>
         <v>-361</v>
       </c>
@@ -9571,7 +9632,7 @@
       <c r="K21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="144">
+      <c r="L21" s="141">
         <v>120</v>
       </c>
       <c r="M21" s="5">
@@ -9580,7 +9641,7 @@
       <c r="N21" s="5">
         <v>6522</v>
       </c>
-      <c r="O21" s="152">
+      <c r="O21" s="149">
         <f t="shared" si="1"/>
         <v>-695</v>
       </c>
@@ -9589,7 +9650,7 @@
       <c r="K22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L22" s="144">
+      <c r="L22" s="141">
         <v>120</v>
       </c>
       <c r="M22" s="5">
@@ -9598,7 +9659,7 @@
       <c r="N22" s="5">
         <v>9539</v>
       </c>
-      <c r="O22" s="152">
+      <c r="O22" s="149">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -9607,7 +9668,7 @@
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="144">
+      <c r="L23" s="141">
         <v>60</v>
       </c>
       <c r="M23" s="5">
@@ -9616,43 +9677,43 @@
       <c r="N23" s="5">
         <v>57991</v>
       </c>
-      <c r="O23" s="152">
+      <c r="O23" s="149">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="K24" s="146" t="s">
+      <c r="K24" s="143" t="s">
         <v>108</v>
       </c>
-      <c r="L24" s="147"/>
-      <c r="M24" s="148">
+      <c r="L24" s="144"/>
+      <c r="M24" s="145">
         <f>SUM(M17:M23)</f>
         <v>103977</v>
       </c>
-      <c r="N24" s="148">
+      <c r="N24" s="145">
         <f>SUM(N17:N23)</f>
         <v>114978</v>
       </c>
-      <c r="O24" s="145">
+      <c r="O24" s="142">
         <f>SUM(O17:O23)</f>
         <v>-1983</v>
       </c>
     </row>
     <row r="25" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="K25" s="146" t="s">
+      <c r="K25" s="143" t="s">
         <v>109</v>
       </c>
-      <c r="L25" s="147"/>
-      <c r="M25" s="148">
+      <c r="L25" s="144"/>
+      <c r="M25" s="145">
         <f>M24/40</f>
         <v>2599.4250000000002</v>
       </c>
-      <c r="N25" s="148">
+      <c r="N25" s="145">
         <f>N24/40</f>
         <v>2874.45</v>
       </c>
-      <c r="O25" s="145">
+      <c r="O25" s="142">
         <f>O24/40</f>
         <v>-49.575000000000003</v>
       </c>
@@ -9688,22 +9749,22 @@
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="153" t="s">
+      <c r="I1" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="153" t="s">
+      <c r="J1" s="150" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="153" t="s">
+      <c r="K1" s="150" t="s">
         <v>130</v>
       </c>
     </row>
@@ -9714,13 +9775,13 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="I2" s="82" t="s">
+      <c r="I2" s="81" t="s">
         <v>136</v>
       </c>
-      <c r="J2" s="82">
+      <c r="J2" s="81">
         <v>20</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="81" t="s">
         <v>138</v>
       </c>
       <c r="L2" t="s">
@@ -9732,13 +9793,13 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="I3" s="82" t="s">
+      <c r="I3" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="J3" s="82">
+      <c r="J3" s="81">
         <v>22</v>
       </c>
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="81" t="s">
         <v>138</v>
       </c>
       <c r="L3" t="s">
@@ -9750,13 +9811,13 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="I4" s="82" t="s">
+      <c r="I4" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="J4" s="82">
+      <c r="J4" s="81">
         <v>114</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="K4" s="81" t="s">
         <v>138</v>
       </c>
       <c r="L4" t="s">
@@ -9768,13 +9829,13 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="I5" s="82" t="s">
+      <c r="I5" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="82">
+      <c r="J5" s="81">
         <v>60</v>
       </c>
-      <c r="K5" s="82" t="s">
+      <c r="K5" s="81" t="s">
         <v>138</v>
       </c>
     </row>
@@ -9783,13 +9844,13 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="I6" s="82" t="s">
+      <c r="I6" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="82">
+      <c r="J6" s="81">
         <v>15</v>
       </c>
-      <c r="K6" s="82" t="s">
+      <c r="K6" s="81" t="s">
         <v>138</v>
       </c>
     </row>
@@ -9798,13 +9859,13 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="I7" s="82" t="s">
+      <c r="I7" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="J7" s="82">
+      <c r="J7" s="81">
         <v>72</v>
       </c>
-      <c r="K7" s="82" t="s">
+      <c r="K7" s="81" t="s">
         <v>139</v>
       </c>
     </row>
@@ -9813,117 +9874,135 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
+      <c r="I8" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="J8" s="81">
+        <v>15</v>
+      </c>
+      <c r="K8" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
+      <c r="I9" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="J9" s="81">
+        <v>14</v>
+      </c>
+      <c r="K9" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
+      <c r="I10" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="J10" s="81">
+        <v>24</v>
+      </c>
+      <c r="K10" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="84"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="85"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="87"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="86"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDA7A9B-0B26-4F19-A5DF-C3A9C7118B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7373A0C1-CA51-4D68-BC3A-453D2E96F8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="167">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -518,6 +518,12 @@
   </si>
   <si>
     <t>Rambo BT</t>
+  </si>
+  <si>
+    <t>Aslam Super Mart</t>
+  </si>
+  <si>
+    <t>4 Reason</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1771,7 +1777,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1794,24 +1799,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1824,6 +1811,48 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1861,42 +1890,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2269,7 +2262,7 @@
       <c r="D9" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="161" t="s">
+      <c r="E9" s="154" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="102" t="s">
@@ -2286,7 +2279,7 @@
       <c r="D10" s="92">
         <v>3520247902365</v>
       </c>
-      <c r="E10" s="162"/>
+      <c r="E10" s="155"/>
       <c r="F10">
         <v>10000</v>
       </c>
@@ -2297,7 +2290,7 @@
       </c>
       <c r="C11" s="79"/>
       <c r="D11" s="79"/>
-      <c r="E11" s="162"/>
+      <c r="E11" s="155"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="79" t="s">
@@ -2309,7 +2302,7 @@
       <c r="D12" s="92">
         <v>300426949714</v>
       </c>
-      <c r="E12" s="162"/>
+      <c r="E12" s="155"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="79" t="s">
@@ -2321,7 +2314,7 @@
       <c r="D13" s="92">
         <v>3277876126916</v>
       </c>
-      <c r="E13" s="162"/>
+      <c r="E13" s="155"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="79" t="s">
@@ -2333,7 +2326,7 @@
       <c r="D14" s="92">
         <v>3520255124113</v>
       </c>
-      <c r="E14" s="162"/>
+      <c r="E14" s="155"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="79" t="s">
@@ -2345,7 +2338,7 @@
       <c r="D15" s="92">
         <v>3520255124113</v>
       </c>
-      <c r="E15" s="162"/>
+      <c r="E15" s="155"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="79" t="s">
@@ -2357,7 +2350,7 @@
       <c r="D16" s="92">
         <v>3520268948847</v>
       </c>
-      <c r="E16" s="162"/>
+      <c r="E16" s="155"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="79" t="s">
@@ -2367,7 +2360,7 @@
         <v>51</v>
       </c>
       <c r="D17" s="79"/>
-      <c r="E17" s="162"/>
+      <c r="E17" s="155"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="79" t="s">
@@ -2379,63 +2372,63 @@
       <c r="D18" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="162"/>
+      <c r="E18" s="155"/>
     </row>
     <row r="19" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="163" t="s">
+      <c r="B19" s="156" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="162" t="s">
+      <c r="C19" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="162"/>
-      <c r="E19" s="162"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="163" t="s">
+      <c r="B20" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="162"/>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="163" t="s">
+      <c r="B21" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="162"/>
-      <c r="D21" s="162"/>
-      <c r="E21" s="162"/>
+      <c r="C21" s="155"/>
+      <c r="D21" s="155"/>
+      <c r="E21" s="155"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="163" t="s">
+      <c r="B22" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="162"/>
-      <c r="D22" s="162"/>
-      <c r="E22" s="162"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="163" t="s">
+      <c r="B23" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="162" t="s">
+      <c r="C23" s="155" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="164">
+      <c r="D23" s="157">
         <v>3277876231301</v>
       </c>
-      <c r="E23" s="162"/>
+      <c r="E23" s="155"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="163" t="s">
+      <c r="B24" s="156" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="162" t="s">
+      <c r="C24" s="155" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="162"/>
-      <c r="E24" s="162" t="s">
+      <c r="D24" s="155"/>
+      <c r="E24" s="155" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2447,7 +2440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y85"/>
+  <dimension ref="A1:Y90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2455,13 +2448,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="178">
+      <c r="B1" s="160">
         <v>46186</v>
       </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2483,10 +2476,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="182" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="179" t="s">
+      <c r="B2" s="161" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2519,13 +2512,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="167"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170" t="s">
+      <c r="M2" s="174"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="176"/>
+      <c r="P2" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="171"/>
+      <c r="Q2" s="178"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2544,8 +2537,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="175"/>
-      <c r="B3" s="180"/>
+      <c r="A3" s="182"/>
+      <c r="B3" s="162"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2576,29 +2569,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="172" t="s">
+      <c r="M3" s="179" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="173"/>
-      <c r="O3" s="174"/>
+      <c r="N3" s="180"/>
+      <c r="O3" s="181"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="182" t="s">
+      <c r="R3" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="183"/>
-      <c r="T3" s="183"/>
-      <c r="U3" s="184"/>
-      <c r="V3" s="185" t="s">
+      <c r="S3" s="165"/>
+      <c r="T3" s="165"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="167" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="186"/>
-      <c r="X3" s="186"/>
-      <c r="Y3" s="187"/>
+      <c r="W3" s="168"/>
+      <c r="X3" s="168"/>
+      <c r="Y3" s="169"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="175"/>
-      <c r="B4" s="181"/>
+      <c r="A4" s="182"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2789,7 +2782,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M85" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M90" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2797,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O84" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O89" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2809,15 +2802,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R84" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R89" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S84" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S89" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T84" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T89" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2965,7 +2958,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N84" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N89" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3405,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U84" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U89" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3421,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y84" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y89" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4081,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y80" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y85" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -6850,7 +6843,7 @@
       <c r="H57" s="75">
         <v>40</v>
       </c>
-      <c r="I57" s="154">
+      <c r="I57" s="153">
         <v>40</v>
       </c>
       <c r="J57" s="75">
@@ -6862,7 +6855,7 @@
       <c r="L57" s="75">
         <v>40</v>
       </c>
-      <c r="M57" s="153">
+      <c r="M57" s="152">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -6916,7 +6909,7 @@
       <c r="H58" s="75">
         <v>40</v>
       </c>
-      <c r="I58" s="154">
+      <c r="I58" s="153">
         <v>40</v>
       </c>
       <c r="J58" s="75">
@@ -6928,7 +6921,7 @@
       <c r="L58" s="75">
         <v>40</v>
       </c>
-      <c r="M58" s="153">
+      <c r="M58" s="152">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -6982,7 +6975,7 @@
       <c r="H59" s="75">
         <v>40</v>
       </c>
-      <c r="I59" s="154">
+      <c r="I59" s="153">
         <v>40</v>
       </c>
       <c r="J59" s="75">
@@ -6994,7 +6987,7 @@
       <c r="L59" s="75">
         <v>40</v>
       </c>
-      <c r="M59" s="153">
+      <c r="M59" s="152">
         <f t="shared" si="76"/>
         <v>6</v>
       </c>
@@ -7048,7 +7041,7 @@
       <c r="H60" s="75">
         <v>1200</v>
       </c>
-      <c r="I60" s="154">
+      <c r="I60" s="153">
         <v>2800</v>
       </c>
       <c r="J60" s="75">
@@ -7060,7 +7053,7 @@
       <c r="L60" s="75">
         <v>3600</v>
       </c>
-      <c r="M60" s="153">
+      <c r="M60" s="152">
         <f t="shared" si="52"/>
         <v>285</v>
       </c>
@@ -7123,29 +7116,29 @@
       <c r="C61" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="D61" s="146"/>
-      <c r="E61" s="146"/>
-      <c r="F61" s="146"/>
-      <c r="G61" s="146">
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75">
         <v>80</v>
       </c>
-      <c r="H61" s="146">
-        <v>0</v>
-      </c>
-      <c r="I61" s="155">
+      <c r="H61" s="75">
+        <v>0</v>
+      </c>
+      <c r="I61" s="153">
         <v>200</v>
       </c>
-      <c r="J61" s="146">
+      <c r="J61" s="75">
         <v>200</v>
       </c>
-      <c r="K61" s="146">
-        <v>0</v>
-      </c>
-      <c r="L61" s="146">
+      <c r="K61" s="75">
+        <v>0</v>
+      </c>
+      <c r="L61" s="75">
         <v>400</v>
       </c>
-      <c r="M61" s="153">
-        <f t="shared" ref="M61:M79" si="81">SUM(D61:L61)/40</f>
+      <c r="M61" s="152">
+        <f t="shared" ref="M61:M84" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
       <c r="N61" s="39">
@@ -7157,11 +7150,11 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P79" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" ref="P61:P84" si="82">SUM(G61:I61)/20</f>
         <v>14</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q79" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" ref="Q61:Q84" si="83">SUM(J61:L61)/20</f>
         <v>30</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -7177,23 +7170,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U79" si="84">SUM(R61:T61)</f>
+        <f t="shared" ref="U61:U84" si="84">SUM(R61:T61)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V79" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" ref="V61:V84" si="85">SUM(D61:F61)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W79" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" ref="W61:W84" si="86">SUM(G61:I61)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X79" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" ref="X61:X84" si="87">SUM(J61:L61)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y79" si="88">SUM(V61:X61)</f>
+        <f t="shared" ref="Y61:Y84" si="88">SUM(V61:X61)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7207,28 +7200,28 @@
       <c r="C62" s="151" t="s">
         <v>141</v>
       </c>
-      <c r="D62" s="146"/>
-      <c r="E62" s="146"/>
-      <c r="F62" s="146"/>
-      <c r="G62" s="146">
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75">
         <v>80</v>
       </c>
-      <c r="H62" s="146">
+      <c r="H62" s="75">
         <v>80</v>
       </c>
-      <c r="I62" s="155">
+      <c r="I62" s="153">
         <v>200</v>
       </c>
-      <c r="J62" s="146">
+      <c r="J62" s="75">
         <v>120</v>
       </c>
-      <c r="K62" s="146">
+      <c r="K62" s="75">
         <v>120</v>
       </c>
-      <c r="L62" s="146">
+      <c r="L62" s="75">
         <v>200</v>
       </c>
-      <c r="M62" s="153">
+      <c r="M62" s="152">
         <f t="shared" si="81"/>
         <v>20</v>
       </c>
@@ -7291,28 +7284,28 @@
       <c r="C63" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="146"/>
-      <c r="E63" s="146"/>
-      <c r="F63" s="146"/>
-      <c r="G63" s="146">
-        <v>40</v>
-      </c>
-      <c r="H63" s="146">
-        <v>40</v>
-      </c>
-      <c r="I63" s="155">
-        <v>40</v>
-      </c>
-      <c r="J63" s="146">
-        <v>40</v>
-      </c>
-      <c r="K63" s="146">
-        <v>40</v>
-      </c>
-      <c r="L63" s="146">
-        <v>40</v>
-      </c>
-      <c r="M63" s="153">
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75">
+        <v>40</v>
+      </c>
+      <c r="H63" s="75">
+        <v>40</v>
+      </c>
+      <c r="I63" s="153">
+        <v>40</v>
+      </c>
+      <c r="J63" s="75">
+        <v>40</v>
+      </c>
+      <c r="K63" s="75">
+        <v>40</v>
+      </c>
+      <c r="L63" s="75">
+        <v>40</v>
+      </c>
+      <c r="M63" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7375,28 +7368,28 @@
       <c r="C64" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="146"/>
-      <c r="E64" s="146"/>
-      <c r="F64" s="146"/>
-      <c r="G64" s="146">
-        <v>40</v>
-      </c>
-      <c r="H64" s="146">
-        <v>40</v>
-      </c>
-      <c r="I64" s="155">
-        <v>40</v>
-      </c>
-      <c r="J64" s="146">
-        <v>40</v>
-      </c>
-      <c r="K64" s="146">
-        <v>40</v>
-      </c>
-      <c r="L64" s="146">
-        <v>40</v>
-      </c>
-      <c r="M64" s="153">
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="75">
+        <v>40</v>
+      </c>
+      <c r="H64" s="75">
+        <v>40</v>
+      </c>
+      <c r="I64" s="153">
+        <v>40</v>
+      </c>
+      <c r="J64" s="75">
+        <v>40</v>
+      </c>
+      <c r="K64" s="75">
+        <v>40</v>
+      </c>
+      <c r="L64" s="75">
+        <v>40</v>
+      </c>
+      <c r="M64" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7459,28 +7452,28 @@
       <c r="C65" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="D65" s="146"/>
-      <c r="E65" s="146"/>
-      <c r="F65" s="146"/>
-      <c r="G65" s="146">
-        <v>40</v>
-      </c>
-      <c r="H65" s="146">
-        <v>40</v>
-      </c>
-      <c r="I65" s="155">
-        <v>40</v>
-      </c>
-      <c r="J65" s="146">
-        <v>40</v>
-      </c>
-      <c r="K65" s="146">
-        <v>40</v>
-      </c>
-      <c r="L65" s="146">
-        <v>40</v>
-      </c>
-      <c r="M65" s="153">
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75">
+        <v>40</v>
+      </c>
+      <c r="H65" s="75">
+        <v>40</v>
+      </c>
+      <c r="I65" s="153">
+        <v>40</v>
+      </c>
+      <c r="J65" s="75">
+        <v>40</v>
+      </c>
+      <c r="K65" s="75">
+        <v>40</v>
+      </c>
+      <c r="L65" s="75">
+        <v>40</v>
+      </c>
+      <c r="M65" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7543,28 +7536,28 @@
       <c r="C66" s="151" t="s">
         <v>145</v>
       </c>
-      <c r="D66" s="146"/>
-      <c r="E66" s="146"/>
-      <c r="F66" s="146"/>
-      <c r="G66" s="146">
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75">
         <v>80</v>
       </c>
-      <c r="H66" s="146">
+      <c r="H66" s="75">
         <v>80</v>
       </c>
-      <c r="I66" s="155">
+      <c r="I66" s="153">
         <v>80</v>
       </c>
-      <c r="J66" s="146">
+      <c r="J66" s="75">
         <v>80</v>
       </c>
-      <c r="K66" s="146">
+      <c r="K66" s="75">
         <v>80</v>
       </c>
-      <c r="L66" s="146">
+      <c r="L66" s="75">
         <v>80</v>
       </c>
-      <c r="M66" s="153">
+      <c r="M66" s="152">
         <f t="shared" si="81"/>
         <v>12</v>
       </c>
@@ -7627,28 +7620,28 @@
       <c r="C67" s="151" t="s">
         <v>146</v>
       </c>
-      <c r="D67" s="146"/>
-      <c r="E67" s="146"/>
-      <c r="F67" s="146"/>
-      <c r="G67" s="146">
-        <v>40</v>
-      </c>
-      <c r="H67" s="146">
-        <v>40</v>
-      </c>
-      <c r="I67" s="155">
-        <v>40</v>
-      </c>
-      <c r="J67" s="146">
-        <v>40</v>
-      </c>
-      <c r="K67" s="146">
-        <v>40</v>
-      </c>
-      <c r="L67" s="146">
-        <v>40</v>
-      </c>
-      <c r="M67" s="153">
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75">
+        <v>40</v>
+      </c>
+      <c r="H67" s="75">
+        <v>40</v>
+      </c>
+      <c r="I67" s="153">
+        <v>40</v>
+      </c>
+      <c r="J67" s="75">
+        <v>40</v>
+      </c>
+      <c r="K67" s="75">
+        <v>40</v>
+      </c>
+      <c r="L67" s="75">
+        <v>40</v>
+      </c>
+      <c r="M67" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7711,28 +7704,28 @@
       <c r="C68" s="151" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="146"/>
-      <c r="E68" s="146"/>
-      <c r="F68" s="146"/>
-      <c r="G68" s="146">
-        <v>40</v>
-      </c>
-      <c r="H68" s="146">
-        <v>40</v>
-      </c>
-      <c r="I68" s="155">
-        <v>40</v>
-      </c>
-      <c r="J68" s="146">
-        <v>40</v>
-      </c>
-      <c r="K68" s="146">
-        <v>40</v>
-      </c>
-      <c r="L68" s="146">
-        <v>40</v>
-      </c>
-      <c r="M68" s="153">
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75">
+        <v>40</v>
+      </c>
+      <c r="H68" s="75">
+        <v>40</v>
+      </c>
+      <c r="I68" s="153">
+        <v>40</v>
+      </c>
+      <c r="J68" s="75">
+        <v>40</v>
+      </c>
+      <c r="K68" s="75">
+        <v>40</v>
+      </c>
+      <c r="L68" s="75">
+        <v>40</v>
+      </c>
+      <c r="M68" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7795,28 +7788,28 @@
       <c r="C69" s="151" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="146"/>
-      <c r="E69" s="146"/>
-      <c r="F69" s="146"/>
-      <c r="G69" s="146">
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75">
         <v>80</v>
       </c>
-      <c r="H69" s="146">
+      <c r="H69" s="75">
         <v>80</v>
       </c>
-      <c r="I69" s="155">
+      <c r="I69" s="153">
         <v>80</v>
       </c>
-      <c r="J69" s="146">
+      <c r="J69" s="75">
         <v>80</v>
       </c>
-      <c r="K69" s="146">
+      <c r="K69" s="75">
         <v>80</v>
       </c>
-      <c r="L69" s="146">
+      <c r="L69" s="75">
         <v>80</v>
       </c>
-      <c r="M69" s="153">
+      <c r="M69" s="152">
         <f t="shared" si="81"/>
         <v>12</v>
       </c>
@@ -7879,28 +7872,28 @@
       <c r="C70" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="D70" s="146"/>
-      <c r="E70" s="146"/>
-      <c r="F70" s="146"/>
-      <c r="G70" s="146">
-        <v>40</v>
-      </c>
-      <c r="H70" s="146">
-        <v>40</v>
-      </c>
-      <c r="I70" s="155">
-        <v>40</v>
-      </c>
-      <c r="J70" s="146">
-        <v>40</v>
-      </c>
-      <c r="K70" s="146">
-        <v>40</v>
-      </c>
-      <c r="L70" s="146">
-        <v>40</v>
-      </c>
-      <c r="M70" s="153">
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75">
+        <v>40</v>
+      </c>
+      <c r="H70" s="75">
+        <v>40</v>
+      </c>
+      <c r="I70" s="153">
+        <v>40</v>
+      </c>
+      <c r="J70" s="75">
+        <v>40</v>
+      </c>
+      <c r="K70" s="75">
+        <v>40</v>
+      </c>
+      <c r="L70" s="75">
+        <v>40</v>
+      </c>
+      <c r="M70" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -7960,31 +7953,31 @@
       <c r="B71" s="47">
         <v>67</v>
       </c>
-      <c r="C71" s="159" t="s">
+      <c r="C71" s="151" t="s">
         <v>150</v>
       </c>
-      <c r="D71" s="126"/>
-      <c r="E71" s="126"/>
-      <c r="F71" s="126"/>
-      <c r="G71" s="126">
-        <v>0</v>
-      </c>
-      <c r="H71" s="126">
-        <v>0</v>
-      </c>
-      <c r="I71" s="160">
-        <v>0</v>
-      </c>
-      <c r="J71" s="126">
-        <v>0</v>
-      </c>
-      <c r="K71" s="126">
-        <v>0</v>
-      </c>
-      <c r="L71" s="126">
-        <v>0</v>
-      </c>
-      <c r="M71" s="153">
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75">
+        <v>0</v>
+      </c>
+      <c r="H71" s="75">
+        <v>0</v>
+      </c>
+      <c r="I71" s="153">
+        <v>0</v>
+      </c>
+      <c r="J71" s="75">
+        <v>0</v>
+      </c>
+      <c r="K71" s="75">
+        <v>0</v>
+      </c>
+      <c r="L71" s="75">
+        <v>0</v>
+      </c>
+      <c r="M71" s="152">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8047,28 +8040,28 @@
       <c r="C72" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="146"/>
-      <c r="E72" s="146"/>
-      <c r="F72" s="146"/>
-      <c r="G72" s="146">
-        <v>40</v>
-      </c>
-      <c r="H72" s="146">
-        <v>40</v>
-      </c>
-      <c r="I72" s="155">
-        <v>40</v>
-      </c>
-      <c r="J72" s="146">
-        <v>40</v>
-      </c>
-      <c r="K72" s="146">
-        <v>40</v>
-      </c>
-      <c r="L72" s="146">
-        <v>40</v>
-      </c>
-      <c r="M72" s="153">
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75">
+        <v>40</v>
+      </c>
+      <c r="H72" s="75">
+        <v>40</v>
+      </c>
+      <c r="I72" s="153">
+        <v>40</v>
+      </c>
+      <c r="J72" s="75">
+        <v>40</v>
+      </c>
+      <c r="K72" s="75">
+        <v>40</v>
+      </c>
+      <c r="L72" s="75">
+        <v>40</v>
+      </c>
+      <c r="M72" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8131,28 +8124,28 @@
       <c r="C73" s="151" t="s">
         <v>152</v>
       </c>
-      <c r="D73" s="146"/>
-      <c r="E73" s="146"/>
-      <c r="F73" s="146"/>
-      <c r="G73" s="146">
-        <v>40</v>
-      </c>
-      <c r="H73" s="146">
-        <v>40</v>
-      </c>
-      <c r="I73" s="155">
-        <v>40</v>
-      </c>
-      <c r="J73" s="146">
-        <v>40</v>
-      </c>
-      <c r="K73" s="146">
-        <v>40</v>
-      </c>
-      <c r="L73" s="146">
-        <v>40</v>
-      </c>
-      <c r="M73" s="153">
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="75">
+        <v>40</v>
+      </c>
+      <c r="H73" s="75">
+        <v>40</v>
+      </c>
+      <c r="I73" s="153">
+        <v>40</v>
+      </c>
+      <c r="J73" s="75">
+        <v>40</v>
+      </c>
+      <c r="K73" s="75">
+        <v>40</v>
+      </c>
+      <c r="L73" s="75">
+        <v>40</v>
+      </c>
+      <c r="M73" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8212,31 +8205,31 @@
       <c r="B74" s="47">
         <v>70</v>
       </c>
-      <c r="C74" s="156" t="s">
+      <c r="C74" s="158" t="s">
         <v>153</v>
       </c>
-      <c r="D74" s="146"/>
-      <c r="E74" s="146"/>
-      <c r="F74" s="147"/>
-      <c r="G74" s="146">
-        <v>40</v>
-      </c>
-      <c r="H74" s="146">
-        <v>40</v>
-      </c>
-      <c r="I74" s="155">
-        <v>40</v>
-      </c>
-      <c r="J74" s="146">
-        <v>40</v>
-      </c>
-      <c r="K74" s="146">
-        <v>40</v>
-      </c>
-      <c r="L74" s="146">
-        <v>40</v>
-      </c>
-      <c r="M74" s="153">
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="50"/>
+      <c r="G74" s="75">
+        <v>40</v>
+      </c>
+      <c r="H74" s="75">
+        <v>40</v>
+      </c>
+      <c r="I74" s="153">
+        <v>40</v>
+      </c>
+      <c r="J74" s="75">
+        <v>40</v>
+      </c>
+      <c r="K74" s="75">
+        <v>40</v>
+      </c>
+      <c r="L74" s="75">
+        <v>40</v>
+      </c>
+      <c r="M74" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8296,31 +8289,31 @@
       <c r="B75" s="47">
         <v>71</v>
       </c>
-      <c r="C75" s="156" t="s">
+      <c r="C75" s="158" t="s">
         <v>154</v>
       </c>
-      <c r="D75" s="146"/>
-      <c r="E75" s="147"/>
-      <c r="F75" s="147"/>
-      <c r="G75" s="146">
-        <v>40</v>
-      </c>
-      <c r="H75" s="146">
-        <v>40</v>
-      </c>
-      <c r="I75" s="155">
-        <v>40</v>
-      </c>
-      <c r="J75" s="146">
-        <v>40</v>
-      </c>
-      <c r="K75" s="146">
-        <v>40</v>
-      </c>
-      <c r="L75" s="146">
-        <v>40</v>
-      </c>
-      <c r="M75" s="153">
+      <c r="D75" s="75"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="75">
+        <v>40</v>
+      </c>
+      <c r="H75" s="75">
+        <v>40</v>
+      </c>
+      <c r="I75" s="153">
+        <v>40</v>
+      </c>
+      <c r="J75" s="75">
+        <v>40</v>
+      </c>
+      <c r="K75" s="75">
+        <v>40</v>
+      </c>
+      <c r="L75" s="75">
+        <v>40</v>
+      </c>
+      <c r="M75" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8380,31 +8373,31 @@
       <c r="B76" s="47">
         <v>72</v>
       </c>
-      <c r="C76" s="156" t="s">
+      <c r="C76" s="158" t="s">
         <v>155</v>
       </c>
-      <c r="D76" s="146"/>
-      <c r="E76" s="147"/>
-      <c r="F76" s="147"/>
-      <c r="G76" s="146">
-        <v>40</v>
-      </c>
-      <c r="H76" s="146">
-        <v>40</v>
-      </c>
-      <c r="I76" s="155">
-        <v>40</v>
-      </c>
-      <c r="J76" s="146">
-        <v>40</v>
-      </c>
-      <c r="K76" s="146">
-        <v>40</v>
-      </c>
-      <c r="L76" s="146">
-        <v>40</v>
-      </c>
-      <c r="M76" s="153">
+      <c r="D76" s="75"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="75">
+        <v>40</v>
+      </c>
+      <c r="H76" s="75">
+        <v>40</v>
+      </c>
+      <c r="I76" s="153">
+        <v>40</v>
+      </c>
+      <c r="J76" s="75">
+        <v>40</v>
+      </c>
+      <c r="K76" s="75">
+        <v>40</v>
+      </c>
+      <c r="L76" s="75">
+        <v>40</v>
+      </c>
+      <c r="M76" s="152">
         <f t="shared" si="81"/>
         <v>6</v>
       </c>
@@ -8464,31 +8457,31 @@
       <c r="B77" s="47">
         <v>73</v>
       </c>
-      <c r="C77" s="157" t="s">
+      <c r="C77" s="158" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="126"/>
-      <c r="E77" s="128"/>
-      <c r="F77" s="128"/>
-      <c r="G77" s="128">
-        <v>0</v>
-      </c>
-      <c r="H77" s="128">
-        <v>0</v>
-      </c>
-      <c r="I77" s="158">
-        <v>0</v>
-      </c>
-      <c r="J77" s="128">
-        <v>0</v>
-      </c>
-      <c r="K77" s="128">
-        <v>0</v>
-      </c>
-      <c r="L77" s="128">
-        <v>0</v>
-      </c>
-      <c r="M77" s="153">
+      <c r="D77" s="75"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
+      <c r="G77" s="50">
+        <v>0</v>
+      </c>
+      <c r="H77" s="50">
+        <v>0</v>
+      </c>
+      <c r="I77" s="152">
+        <v>0</v>
+      </c>
+      <c r="J77" s="50">
+        <v>0</v>
+      </c>
+      <c r="K77" s="50">
+        <v>0</v>
+      </c>
+      <c r="L77" s="50">
+        <v>0</v>
+      </c>
+      <c r="M77" s="152">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8548,31 +8541,31 @@
       <c r="B78" s="47">
         <v>74</v>
       </c>
-      <c r="C78" s="157" t="s">
+      <c r="C78" s="158" t="s">
         <v>157</v>
       </c>
-      <c r="D78" s="126"/>
-      <c r="E78" s="128"/>
-      <c r="F78" s="128"/>
-      <c r="G78" s="128">
-        <v>0</v>
-      </c>
-      <c r="H78" s="128">
-        <v>0</v>
-      </c>
-      <c r="I78" s="158">
-        <v>0</v>
-      </c>
-      <c r="J78" s="128">
-        <v>0</v>
-      </c>
-      <c r="K78" s="128">
-        <v>0</v>
-      </c>
-      <c r="L78" s="128">
-        <v>0</v>
-      </c>
-      <c r="M78" s="153">
+      <c r="D78" s="75"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50">
+        <v>0</v>
+      </c>
+      <c r="H78" s="50">
+        <v>0</v>
+      </c>
+      <c r="I78" s="152">
+        <v>0</v>
+      </c>
+      <c r="J78" s="50">
+        <v>0</v>
+      </c>
+      <c r="K78" s="50">
+        <v>0</v>
+      </c>
+      <c r="L78" s="50">
+        <v>0</v>
+      </c>
+      <c r="M78" s="152">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
@@ -8630,19 +8623,33 @@
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="152"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="153"/>
-      <c r="J79" s="50"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
-      <c r="M79" s="153">
+      <c r="C79" s="150" t="s">
+        <v>165</v>
+      </c>
+      <c r="D79" s="146"/>
+      <c r="E79" s="146"/>
+      <c r="F79" s="146"/>
+      <c r="G79" s="146">
+        <v>314</v>
+      </c>
+      <c r="H79" s="146">
+        <v>353</v>
+      </c>
+      <c r="I79" s="159">
+        <v>388</v>
+      </c>
+      <c r="J79" s="146">
+        <v>350</v>
+      </c>
+      <c r="K79" s="146">
+        <v>311</v>
+      </c>
+      <c r="L79" s="146">
+        <v>396</v>
+      </c>
+      <c r="M79" s="159">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>52.8</v>
       </c>
       <c r="N79" s="39">
         <f t="shared" si="18"/>
@@ -8653,12 +8660,12 @@
         <v>331.63</v>
       </c>
       <c r="P79" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
+        <f t="shared" ref="P79:P83" si="89">SUM(G79:I79)/20</f>
+        <v>52.75</v>
       </c>
       <c r="Q79" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
+        <f t="shared" ref="Q79:Q83" si="90">SUM(J79:L79)/20</f>
+        <v>52.85</v>
       </c>
       <c r="R79" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8673,71 +8680,60 @@
         <v>0</v>
       </c>
       <c r="U79" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" ref="U79:U83" si="91">SUM(R79:T79)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V79" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="V79:V83" si="92">SUM(D79:F79)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W79" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="W79:W83" si="93">SUM(G79:I79)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X79" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" ref="X79:X83" si="94">SUM(J79:L79)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y79" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="Y79:Y83" si="95">SUM(V79:X79)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" s="78"/>
-      <c r="B80" s="188" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="189"/>
-      <c r="D80" s="88">
-        <f t="shared" ref="D80:L80" si="89">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E80" s="88">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="F80" s="88">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="G80" s="88">
-        <f t="shared" si="89"/>
-        <v>7140</v>
-      </c>
-      <c r="H80" s="88">
-        <f t="shared" si="89"/>
-        <v>7657</v>
-      </c>
-      <c r="I80" s="88">
-        <f t="shared" si="89"/>
-        <v>10657</v>
-      </c>
-      <c r="J80" s="88">
-        <f t="shared" si="89"/>
-        <v>11297</v>
-      </c>
-      <c r="K80" s="88">
-        <f t="shared" si="89"/>
-        <v>9684</v>
-      </c>
-      <c r="L80" s="88">
-        <f t="shared" si="89"/>
-        <v>13219</v>
-      </c>
-      <c r="M80" s="48">
-        <f t="shared" ref="M80:M83" si="90">SUM(D80:L80)/40</f>
-        <v>1524.35</v>
+      <c r="B80" s="47">
+        <v>76</v>
+      </c>
+      <c r="C80" s="150" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="146">
+        <v>40</v>
+      </c>
+      <c r="E80" s="146"/>
+      <c r="F80" s="146"/>
+      <c r="G80" s="146">
+        <v>40</v>
+      </c>
+      <c r="H80" s="146">
+        <v>0</v>
+      </c>
+      <c r="I80" s="159">
+        <v>120</v>
+      </c>
+      <c r="J80" s="146">
+        <v>200</v>
+      </c>
+      <c r="K80" s="146">
+        <v>0</v>
+      </c>
+      <c r="L80" s="146">
+        <v>200</v>
+      </c>
+      <c r="M80" s="159">
+        <f t="shared" si="81"/>
+        <v>15</v>
       </c>
       <c r="N80" s="39">
         <f t="shared" si="18"/>
@@ -8748,12 +8744,12 @@
         <v>331.63</v>
       </c>
       <c r="P80" s="73">
-        <f t="shared" ref="P80:P84" si="91">SUM(G80:I80)/20</f>
-        <v>1272.7</v>
+        <f t="shared" si="89"/>
+        <v>8</v>
       </c>
       <c r="Q80" s="40">
-        <f t="shared" ref="Q80:Q84" si="92">SUM(J80:L80)/20</f>
-        <v>1710</v>
+        <f t="shared" si="90"/>
+        <v>20</v>
       </c>
       <c r="R80" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8768,107 +8764,107 @@
         <v>0</v>
       </c>
       <c r="U80" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V80" s="54" t="e">
-        <f t="shared" ref="V80:V84" si="93">SUM(D80:F80)*$V$3</f>
+        <f t="shared" si="92"/>
         <v>#VALUE!</v>
       </c>
       <c r="W80" s="55">
-        <f t="shared" ref="W80:W84" si="94">SUM(G80:I80)*$W$3</f>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="X80" s="55">
-        <f t="shared" ref="X80:X84" si="95">SUM(J80:L80)*$X$3</f>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="Y80" s="56" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="95"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" s="78"/>
-      <c r="B81" s="118">
-        <v>0</v>
-      </c>
-      <c r="C81" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E81" s="120"/>
-      <c r="F81" s="121"/>
-      <c r="G81" s="120"/>
-      <c r="H81" s="120"/>
-      <c r="I81" s="121"/>
-      <c r="J81" s="120">
-        <v>520</v>
-      </c>
-      <c r="K81" s="120">
-        <v>920</v>
-      </c>
-      <c r="L81" s="121">
-        <v>960</v>
-      </c>
-      <c r="M81" s="122">
-        <f>SUM(D81:L81)</f>
-        <v>4000</v>
-      </c>
-      <c r="N81" s="39"/>
-      <c r="O81" s="49"/>
-      <c r="P81" s="73"/>
-      <c r="Q81" s="40"/>
-      <c r="R81" s="51"/>
-      <c r="S81" s="52"/>
-      <c r="T81" s="52"/>
-      <c r="U81" s="53"/>
-      <c r="V81" s="54"/>
-      <c r="W81" s="55"/>
-      <c r="X81" s="55"/>
-      <c r="Y81" s="56"/>
+      <c r="B81" s="47">
+        <v>77</v>
+      </c>
+      <c r="C81" s="151"/>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="I81" s="152"/>
+      <c r="J81" s="50"/>
+      <c r="K81" s="50"/>
+      <c r="L81" s="50"/>
+      <c r="M81" s="152"/>
+      <c r="N81" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O81" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P81" s="73">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="Q81" s="40">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="R81" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S81" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T81" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U81" s="53" t="e">
+        <f t="shared" si="91"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V81" s="54" t="e">
+        <f t="shared" si="92"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W81" s="55">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="X81" s="55">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="Y81" s="56" t="e">
+        <f t="shared" si="95"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" s="78"/>
       <c r="B82" s="47">
-        <v>1</v>
-      </c>
-      <c r="C82" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D82" s="74"/>
-      <c r="E82" s="75"/>
-      <c r="F82" s="76"/>
-      <c r="G82" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
-      </c>
-      <c r="H82" s="75">
-        <f>0+600</f>
-        <v>600</v>
-      </c>
-      <c r="I82" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
-      </c>
-      <c r="J82" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
-      </c>
-      <c r="K82" s="75">
-        <f>600+2400</f>
-        <v>3000</v>
-      </c>
-      <c r="L82" s="76">
-        <f>2200+2800</f>
-        <v>5000</v>
-      </c>
-      <c r="M82" s="48">
-        <f t="shared" si="90"/>
-        <v>400</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C82" s="151"/>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="50"/>
+      <c r="I82" s="152"/>
+      <c r="J82" s="50"/>
+      <c r="K82" s="50"/>
+      <c r="L82" s="50"/>
+      <c r="M82" s="152"/>
       <c r="N82" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -8878,12 +8874,12 @@
         <v>331.63</v>
       </c>
       <c r="P82" s="73">
-        <f t="shared" si="91"/>
-        <v>230</v>
+        <f t="shared" si="89"/>
+        <v>0</v>
       </c>
       <c r="Q82" s="40">
-        <f t="shared" si="92"/>
-        <v>570</v>
+        <f t="shared" si="90"/>
+        <v>0</v>
       </c>
       <c r="R82" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8898,60 +8894,42 @@
         <v>0</v>
       </c>
       <c r="U82" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V82" s="54" t="e">
+        <f t="shared" si="92"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W82" s="55">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W82" s="55">
+        <v>0</v>
+      </c>
+      <c r="X82" s="55">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="X82" s="55">
+      <c r="Y82" s="56" t="e">
         <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="Y82" s="56" t="e">
-        <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A83" s="78"/>
       <c r="B83" s="47">
-        <v>2</v>
-      </c>
-      <c r="C83" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83" s="74">
-        <v>1400</v>
-      </c>
-      <c r="E83" s="75"/>
-      <c r="F83" s="76"/>
-      <c r="G83" s="50">
-        <v>400</v>
-      </c>
-      <c r="H83" s="75">
-        <v>400</v>
-      </c>
-      <c r="I83" s="49">
-        <v>0</v>
-      </c>
-      <c r="J83" s="50">
-        <v>400</v>
-      </c>
-      <c r="K83" s="75">
-        <v>400</v>
-      </c>
-      <c r="L83" s="76">
-        <v>600</v>
-      </c>
-      <c r="M83" s="48">
-        <f t="shared" si="90"/>
-        <v>90</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C83" s="151"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
+      <c r="I83" s="152"/>
+      <c r="J83" s="50"/>
+      <c r="K83" s="50"/>
+      <c r="L83" s="50"/>
+      <c r="M83" s="152"/>
       <c r="N83" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -8961,12 +8939,12 @@
         <v>331.63</v>
       </c>
       <c r="P83" s="73">
-        <f t="shared" si="91"/>
-        <v>40</v>
+        <f t="shared" si="89"/>
+        <v>0</v>
       </c>
       <c r="Q83" s="40">
-        <f t="shared" si="92"/>
-        <v>70</v>
+        <f t="shared" si="90"/>
+        <v>0</v>
       </c>
       <c r="R83" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8981,86 +8959,60 @@
         <v>0</v>
       </c>
       <c r="U83" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="91"/>
         <v>#VALUE!</v>
       </c>
       <c r="V83" s="54" t="e">
+        <f t="shared" si="92"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W83" s="55">
         <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W83" s="55">
+        <v>0</v>
+      </c>
+      <c r="X83" s="55">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="X83" s="55">
+      <c r="Y83" s="56" t="e">
         <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="Y83" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="176" t="s">
-        <v>93</v>
-      </c>
-      <c r="C84" s="177"/>
-      <c r="D84" s="87">
-        <f>SUM(D82:D83)</f>
-        <v>1400</v>
-      </c>
-      <c r="E84" s="87">
-        <f t="shared" ref="E84:L84" si="96">SUM(E82:E83)</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="87">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="G84" s="87">
-        <f t="shared" si="96"/>
-        <v>2280</v>
-      </c>
-      <c r="H84" s="87">
-        <f t="shared" si="96"/>
-        <v>1000</v>
-      </c>
-      <c r="I84" s="87">
-        <f t="shared" si="96"/>
-        <v>2120</v>
-      </c>
-      <c r="J84" s="87">
-        <f t="shared" si="96"/>
-        <v>3800</v>
-      </c>
-      <c r="K84" s="87">
-        <f t="shared" si="96"/>
-        <v>3400</v>
-      </c>
-      <c r="L84" s="87">
-        <f t="shared" si="96"/>
-        <v>5600</v>
-      </c>
-      <c r="M84" s="123">
-        <f>SUM(M81:M83)</f>
-        <v>4490</v>
-      </c>
-      <c r="N84" s="59">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A84" s="78"/>
+      <c r="B84" s="47">
+        <v>80</v>
+      </c>
+      <c r="C84" s="151"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="50"/>
+      <c r="I84" s="152"/>
+      <c r="J84" s="50"/>
+      <c r="K84" s="50"/>
+      <c r="L84" s="50"/>
+      <c r="M84" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N84" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O84" s="58">
+      <c r="O84" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
       <c r="P84" s="73">
-        <f t="shared" si="91"/>
-        <v>270</v>
+        <f t="shared" si="82"/>
+        <v>0</v>
       </c>
       <c r="Q84" s="40">
-        <f t="shared" si="92"/>
-        <v>640</v>
+        <f t="shared" si="83"/>
+        <v>0</v>
       </c>
       <c r="R84" s="51" t="e">
         <f t="shared" si="4"/>
@@ -9075,133 +9027,535 @@
         <v>0</v>
       </c>
       <c r="U84" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V84" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W84" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X84" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A85" s="78"/>
+      <c r="B85" s="170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="171"/>
+      <c r="D85" s="88">
+        <f t="shared" ref="D85:L85" si="96">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E85" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="88">
+        <f t="shared" si="96"/>
+        <v>7140</v>
+      </c>
+      <c r="H85" s="88">
+        <f t="shared" si="96"/>
+        <v>7657</v>
+      </c>
+      <c r="I85" s="88">
+        <f t="shared" si="96"/>
+        <v>10657</v>
+      </c>
+      <c r="J85" s="88">
+        <f t="shared" si="96"/>
+        <v>11297</v>
+      </c>
+      <c r="K85" s="88">
+        <f t="shared" si="96"/>
+        <v>9684</v>
+      </c>
+      <c r="L85" s="88">
+        <f t="shared" si="96"/>
+        <v>13219</v>
+      </c>
+      <c r="M85" s="48">
+        <f t="shared" ref="M85:M88" si="97">SUM(D85:L85)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N85" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O85" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P85" s="73">
+        <f t="shared" ref="P85:P89" si="98">SUM(G85:I85)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q85" s="40">
+        <f t="shared" ref="Q85:Q89" si="99">SUM(J85:L85)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R85" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S85" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T85" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V84" s="54" t="e">
-        <f t="shared" si="93"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W84" s="55">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="X84" s="55">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-      <c r="Y84" s="56" t="e">
+      <c r="V85" s="54" t="e">
+        <f t="shared" ref="V85:V89" si="100">SUM(D85:F85)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W85" s="55">
+        <f t="shared" ref="W85:W89" si="101">SUM(G85:I85)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X85" s="55">
+        <f t="shared" ref="X85:X89" si="102">SUM(J85:L85)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A86" s="78"/>
+      <c r="B86" s="118">
+        <v>0</v>
+      </c>
+      <c r="C86" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E86" s="120"/>
+      <c r="F86" s="121"/>
+      <c r="G86" s="120"/>
+      <c r="H86" s="120"/>
+      <c r="I86" s="121"/>
+      <c r="J86" s="120">
+        <v>520</v>
+      </c>
+      <c r="K86" s="120">
+        <v>920</v>
+      </c>
+      <c r="L86" s="121">
+        <v>960</v>
+      </c>
+      <c r="M86" s="122">
+        <f>SUM(D86:L86)</f>
+        <v>4000</v>
+      </c>
+      <c r="N86" s="39"/>
+      <c r="O86" s="49"/>
+      <c r="P86" s="73"/>
+      <c r="Q86" s="40"/>
+      <c r="R86" s="51"/>
+      <c r="S86" s="52"/>
+      <c r="T86" s="52"/>
+      <c r="U86" s="53"/>
+      <c r="V86" s="54"/>
+      <c r="W86" s="55"/>
+      <c r="X86" s="55"/>
+      <c r="Y86" s="56"/>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A87" s="78"/>
+      <c r="B87" s="47">
+        <v>1</v>
+      </c>
+      <c r="C87" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="74"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="76"/>
+      <c r="G87" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H87" s="75">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I87" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J87" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K87" s="75">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L87" s="76">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M87" s="48">
+        <f t="shared" si="97"/>
+        <v>400</v>
+      </c>
+      <c r="N87" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O87" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P87" s="73">
+        <f t="shared" si="98"/>
+        <v>230</v>
+      </c>
+      <c r="Q87" s="40">
+        <f t="shared" si="99"/>
+        <v>570</v>
+      </c>
+      <c r="R87" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S87" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T87" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V87" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W87" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X87" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y87" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B85" s="165" t="s">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B88" s="47">
+        <v>2</v>
+      </c>
+      <c r="C88" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D88" s="74">
+        <v>1400</v>
+      </c>
+      <c r="E88" s="75"/>
+      <c r="F88" s="76"/>
+      <c r="G88" s="50">
+        <v>400</v>
+      </c>
+      <c r="H88" s="75">
+        <v>400</v>
+      </c>
+      <c r="I88" s="49">
+        <v>0</v>
+      </c>
+      <c r="J88" s="50">
+        <v>400</v>
+      </c>
+      <c r="K88" s="75">
+        <v>400</v>
+      </c>
+      <c r="L88" s="76">
+        <v>600</v>
+      </c>
+      <c r="M88" s="48">
+        <f t="shared" si="97"/>
+        <v>90</v>
+      </c>
+      <c r="N88" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O88" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P88" s="73">
+        <f t="shared" si="98"/>
+        <v>40</v>
+      </c>
+      <c r="Q88" s="40">
+        <f t="shared" si="99"/>
+        <v>70</v>
+      </c>
+      <c r="R88" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S88" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T88" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V88" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W88" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X88" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y88" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B89" s="183" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" s="184"/>
+      <c r="D89" s="87">
+        <f>SUM(D87:D88)</f>
+        <v>1400</v>
+      </c>
+      <c r="E89" s="87">
+        <f t="shared" ref="E89:L89" si="103">SUM(E87:E88)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="87">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="87">
+        <f t="shared" si="103"/>
+        <v>2280</v>
+      </c>
+      <c r="H89" s="87">
+        <f t="shared" si="103"/>
+        <v>1000</v>
+      </c>
+      <c r="I89" s="87">
+        <f t="shared" si="103"/>
+        <v>2120</v>
+      </c>
+      <c r="J89" s="87">
+        <f t="shared" si="103"/>
+        <v>3800</v>
+      </c>
+      <c r="K89" s="87">
+        <f t="shared" si="103"/>
+        <v>3400</v>
+      </c>
+      <c r="L89" s="87">
+        <f t="shared" si="103"/>
+        <v>5600</v>
+      </c>
+      <c r="M89" s="123">
+        <f>SUM(M86:M88)</f>
+        <v>4490</v>
+      </c>
+      <c r="N89" s="59">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O89" s="58">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P89" s="73">
+        <f t="shared" si="98"/>
+        <v>270</v>
+      </c>
+      <c r="Q89" s="40">
+        <f t="shared" si="99"/>
+        <v>640</v>
+      </c>
+      <c r="R89" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S89" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T89" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V89" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W89" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X89" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y89" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B90" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C85" s="166"/>
-      <c r="D85" s="89">
-        <f>SUM(D80,D84)</f>
+      <c r="C90" s="173"/>
+      <c r="D90" s="89">
+        <f>SUM(D85,D89)</f>
         <v>2720</v>
       </c>
-      <c r="E85" s="89">
-        <f t="shared" ref="E85:L85" si="97">SUM(E80,E84)</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="89">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="89">
-        <f t="shared" si="97"/>
+      <c r="E90" s="89">
+        <f t="shared" ref="E90:L90" si="104">SUM(E85,E89)</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="89">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="G90" s="89">
+        <f t="shared" si="104"/>
         <v>9420</v>
       </c>
-      <c r="H85" s="89">
-        <f t="shared" si="97"/>
+      <c r="H90" s="89">
+        <f t="shared" si="104"/>
         <v>8657</v>
       </c>
-      <c r="I85" s="89">
-        <f t="shared" si="97"/>
+      <c r="I90" s="89">
+        <f t="shared" si="104"/>
         <v>12777</v>
       </c>
-      <c r="J85" s="89">
-        <f t="shared" si="97"/>
+      <c r="J90" s="89">
+        <f t="shared" si="104"/>
         <v>15097</v>
       </c>
-      <c r="K85" s="89">
-        <f t="shared" si="97"/>
+      <c r="K90" s="89">
+        <f t="shared" si="104"/>
         <v>13084</v>
       </c>
-      <c r="L85" s="89">
-        <f t="shared" si="97"/>
+      <c r="L90" s="89">
+        <f t="shared" si="104"/>
         <v>18819</v>
       </c>
-      <c r="M85" s="60">
+      <c r="M90" s="60">
         <f t="shared" si="0"/>
         <v>2014.35</v>
       </c>
-      <c r="N85" s="63">
-        <f>SUM(N5:N84)</f>
-        <v>0</v>
-      </c>
-      <c r="O85" s="61">
-        <f t="shared" ref="O85:Y85" si="98">SUM(O5:O84)</f>
-        <v>26198.770000000011</v>
-      </c>
-      <c r="P85" s="62">
-        <f t="shared" si="98"/>
-        <v>3461.95</v>
-      </c>
-      <c r="Q85" s="64">
-        <f t="shared" si="98"/>
-        <v>5539.1</v>
-      </c>
-      <c r="R85" s="65" t="e">
-        <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S85" s="66">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="T85" s="66">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="67" t="e">
-        <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V85" s="68" t="e">
-        <f t="shared" si="98"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W85" s="69">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="X85" s="69">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="Y85" s="70" t="e">
-        <f t="shared" si="98"/>
+      <c r="N90" s="63">
+        <f>SUM(N5:N89)</f>
+        <v>0</v>
+      </c>
+      <c r="O90" s="61">
+        <f t="shared" ref="O90:Y90" si="105">SUM(O5:O89)</f>
+        <v>27856.920000000016</v>
+      </c>
+      <c r="P90" s="62">
+        <f t="shared" si="105"/>
+        <v>3522.7</v>
+      </c>
+      <c r="Q90" s="64">
+        <f t="shared" si="105"/>
+        <v>5611.95</v>
+      </c>
+      <c r="R90" s="65" t="e">
+        <f t="shared" si="105"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S90" s="66">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="T90" s="66">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="67" t="e">
+        <f t="shared" si="105"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V90" s="68" t="e">
+        <f t="shared" si="105"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W90" s="69">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="X90" s="69">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="70" t="e">
+        <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B89:C89"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B80:C80"/>
     <mergeCell ref="B85:C85"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B84:C84"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -9231,24 +9585,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="190" t="s">
+      <c r="C3" s="185" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="191"/>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="194" t="s">
+      <c r="D3" s="186"/>
+      <c r="E3" s="186"/>
+      <c r="F3" s="186"/>
+      <c r="G3" s="187"/>
+      <c r="H3" s="189" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="195"/>
-      <c r="K3" s="196" t="s">
+      <c r="I3" s="190"/>
+      <c r="K3" s="191" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="196"/>
-      <c r="O3" s="196"/>
+      <c r="L3" s="191"/>
+      <c r="M3" s="191"/>
+      <c r="N3" s="191"/>
+      <c r="O3" s="191"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="109"/>
@@ -9291,24 +9645,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="92">
-        <v>548</v>
+        <v>598</v>
       </c>
       <c r="E5" s="79">
-        <v>1656</v>
+        <v>1724</v>
       </c>
       <c r="F5" s="79">
         <v>590</v>
       </c>
       <c r="G5" s="112">
         <f>SUM(D5:F5)</f>
-        <v>2794</v>
+        <v>2912</v>
       </c>
       <c r="H5" s="105">
         <v>10000</v>
       </c>
       <c r="I5" s="106">
         <f>G5-H5</f>
-        <v>-7206</v>
+        <v>-7088</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -9333,11 +9687,11 @@
       </c>
       <c r="D6" s="114">
         <f>D5*40</f>
-        <v>21920</v>
+        <v>23920</v>
       </c>
       <c r="E6" s="115">
         <f>E5*40</f>
-        <v>66240</v>
+        <v>68960</v>
       </c>
       <c r="F6" s="115">
         <f>F5*40</f>
@@ -9345,7 +9699,7 @@
       </c>
       <c r="G6" s="116">
         <f>SUM(D6:F6)</f>
-        <v>111760</v>
+        <v>116480</v>
       </c>
       <c r="H6" s="107">
         <f>H5*40</f>
@@ -9353,7 +9707,7 @@
       </c>
       <c r="I6" s="108">
         <f>G6-H6</f>
-        <v>-288240</v>
+        <v>-283520</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -9418,11 +9772,11 @@
       </c>
       <c r="D9" s="117">
         <f>D8-D5</f>
-        <v>-548</v>
+        <v>-598</v>
       </c>
       <c r="E9" s="117">
         <f>E8-E5</f>
-        <v>-1656</v>
+        <v>-1724</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -9460,20 +9814,20 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="193" t="s">
+      <c r="C11" s="188" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="193"/>
-      <c r="F11" s="193" t="s">
+      <c r="D11" s="188"/>
+      <c r="F11" s="188" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="193"/>
+      <c r="G11" s="188"/>
       <c r="H11" t="s">
         <v>158</v>
       </c>
       <c r="I11">
         <f>D5/20</f>
-        <v>27.4</v>
+        <v>29.9</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
@@ -9504,7 +9858,7 @@
       </c>
       <c r="G12" s="101">
         <f>D12+G5</f>
-        <v>3294.9</v>
+        <v>3412.9</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -9536,7 +9890,7 @@
       </c>
       <c r="G13" s="101">
         <f>G12*40</f>
-        <v>131796</v>
+        <v>136516</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -9566,10 +9920,10 @@
       <c r="M17" s="139">
         <v>11562</v>
       </c>
-      <c r="N17" s="148">
+      <c r="N17" s="147">
         <v>13270</v>
       </c>
-      <c r="O17" s="149">
+      <c r="O17" s="148">
         <f>N17-M5</f>
         <v>-338</v>
       </c>
@@ -9587,7 +9941,7 @@
       <c r="N18" s="5">
         <v>14352</v>
       </c>
-      <c r="O18" s="149">
+      <c r="O18" s="148">
         <f>N18-M6</f>
         <v>-343</v>
       </c>
@@ -9605,7 +9959,7 @@
       <c r="N19" s="5">
         <v>1010</v>
       </c>
-      <c r="O19" s="149">
+      <c r="O19" s="148">
         <f t="shared" ref="O19:O23" si="1">N19-M7</f>
         <v>-325</v>
       </c>
@@ -9623,7 +9977,7 @@
       <c r="N20" s="5">
         <v>12294</v>
       </c>
-      <c r="O20" s="149">
+      <c r="O20" s="148">
         <f t="shared" si="1"/>
         <v>-361</v>
       </c>
@@ -9641,7 +9995,7 @@
       <c r="N21" s="5">
         <v>6522</v>
       </c>
-      <c r="O21" s="149">
+      <c r="O21" s="148">
         <f t="shared" si="1"/>
         <v>-695</v>
       </c>
@@ -9659,7 +10013,7 @@
       <c r="N22" s="5">
         <v>9539</v>
       </c>
-      <c r="O22" s="149">
+      <c r="O22" s="148">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -9677,7 +10031,7 @@
       <c r="N23" s="5">
         <v>57991</v>
       </c>
-      <c r="O23" s="149">
+      <c r="O23" s="148">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -9758,13 +10112,13 @@
       <c r="D1" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="150" t="s">
+      <c r="J1" s="149" t="s">
         <v>132</v>
       </c>
-      <c r="K1" s="150" t="s">
+      <c r="K1" s="149" t="s">
         <v>130</v>
       </c>
     </row>
@@ -9838,6 +10192,9 @@
       <c r="K5" s="81" t="s">
         <v>138</v>
       </c>
+      <c r="L5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
@@ -9852,6 +10209,9 @@
       </c>
       <c r="K6" s="81" t="s">
         <v>138</v>
+      </c>
+      <c r="L6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7373A0C1-CA51-4D68-BC3A-453D2E96F8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D24A10-36F9-49A6-BF1E-336A170313A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="180">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -517,13 +517,52 @@
     <t>Sana C &amp; C</t>
   </si>
   <si>
-    <t>Rambo BT</t>
-  </si>
-  <si>
     <t>Aslam Super Mart</t>
   </si>
   <si>
     <t>4 Reason</t>
+  </si>
+  <si>
+    <t>Jalal Sons Behria Orchard</t>
+  </si>
+  <si>
+    <t>Shehwar Mega Mart</t>
+  </si>
+  <si>
+    <t>Vip</t>
+  </si>
+  <si>
+    <t>Rainbow Shadra</t>
+  </si>
+  <si>
+    <t>Gourmet Food Badami Bagh</t>
+  </si>
+  <si>
+    <t>Gourmet Food Begum Kot</t>
+  </si>
+  <si>
+    <t>Gourmet Food Imamia Colony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gourmet Food Bilal Ganj </t>
+  </si>
+  <si>
+    <t>Gourmet Food Islam Pura</t>
+  </si>
+  <si>
+    <t>Gourmet Food Kareem Park</t>
+  </si>
+  <si>
+    <t>Gourmet Food Kot Abdul malik</t>
+  </si>
+  <si>
+    <t>Gourmet Food Krishan Nager</t>
+  </si>
+  <si>
+    <t>Gourmet Food Lakshman</t>
+  </si>
+  <si>
+    <t>Gourmet Food Shadra</t>
   </si>
 </sst>
 </file>
@@ -1424,7 +1463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1912,6 +1951,13 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2440,7 +2486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y90"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2782,7 +2828,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M90" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M99" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2790,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O89" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O98" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2802,15 +2848,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R89" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R98" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S89" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S98" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T89" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T98" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2958,7 +3004,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N89" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N98" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3398,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U89" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U98" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3414,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y89" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y98" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4074,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y85" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y94" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7138,7 +7184,7 @@
         <v>400</v>
       </c>
       <c r="M61" s="152">
-        <f t="shared" ref="M61:M84" si="81">SUM(D61:L61)/40</f>
+        <f t="shared" ref="M61:M93" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
       <c r="N61" s="39">
@@ -7150,11 +7196,11 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P84" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" ref="P61:P93" si="82">SUM(G61:I61)/20</f>
         <v>14</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q84" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" ref="Q61:Q93" si="83">SUM(J61:L61)/20</f>
         <v>30</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -7170,23 +7216,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U84" si="84">SUM(R61:T61)</f>
+        <f t="shared" ref="U61:U93" si="84">SUM(R61:T61)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V84" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" ref="V61:V93" si="85">SUM(D61:F61)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W84" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" ref="W61:W93" si="86">SUM(G61:I61)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X84" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" ref="X61:X93" si="87">SUM(J61:L61)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y84" si="88">SUM(V61:X61)</f>
+        <f t="shared" ref="Y61:Y93" si="88">SUM(V61:X61)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -8623,31 +8669,31 @@
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="150" t="s">
-        <v>165</v>
-      </c>
-      <c r="D79" s="146"/>
-      <c r="E79" s="146"/>
-      <c r="F79" s="146"/>
-      <c r="G79" s="146">
+      <c r="C79" s="192" t="s">
+        <v>164</v>
+      </c>
+      <c r="D79" s="193"/>
+      <c r="E79" s="193"/>
+      <c r="F79" s="193"/>
+      <c r="G79" s="193">
         <v>314</v>
       </c>
-      <c r="H79" s="146">
+      <c r="H79" s="193">
         <v>353</v>
       </c>
-      <c r="I79" s="159">
+      <c r="I79" s="194">
         <v>388</v>
       </c>
-      <c r="J79" s="146">
+      <c r="J79" s="193">
         <v>350</v>
       </c>
-      <c r="K79" s="146">
+      <c r="K79" s="193">
         <v>311</v>
       </c>
-      <c r="L79" s="146">
+      <c r="L79" s="193">
         <v>396</v>
       </c>
-      <c r="M79" s="159">
+      <c r="M79" s="152">
         <f t="shared" si="81"/>
         <v>52.8</v>
       </c>
@@ -8705,33 +8751,33 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="150" t="s">
-        <v>166</v>
-      </c>
-      <c r="D80" s="146">
-        <v>40</v>
-      </c>
-      <c r="E80" s="146"/>
-      <c r="F80" s="146"/>
-      <c r="G80" s="146">
-        <v>40</v>
-      </c>
-      <c r="H80" s="146">
-        <v>0</v>
-      </c>
-      <c r="I80" s="159">
+      <c r="C80" s="192" t="s">
+        <v>165</v>
+      </c>
+      <c r="D80" s="193">
+        <v>40</v>
+      </c>
+      <c r="E80" s="193"/>
+      <c r="F80" s="193"/>
+      <c r="G80" s="193">
+        <v>40</v>
+      </c>
+      <c r="H80" s="193">
+        <v>0</v>
+      </c>
+      <c r="I80" s="194">
         <v>120</v>
       </c>
-      <c r="J80" s="146">
+      <c r="J80" s="193">
         <v>200</v>
       </c>
-      <c r="K80" s="146">
-        <v>0</v>
-      </c>
-      <c r="L80" s="146">
+      <c r="K80" s="193">
+        <v>0</v>
+      </c>
+      <c r="L80" s="193">
         <v>200</v>
       </c>
-      <c r="M80" s="159">
+      <c r="M80" s="152">
         <f t="shared" si="81"/>
         <v>15</v>
       </c>
@@ -8789,17 +8835,32 @@
       <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="151"/>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="50"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="152"/>
-      <c r="J81" s="50"/>
-      <c r="K81" s="50"/>
-      <c r="L81" s="50"/>
-      <c r="M81" s="152"/>
+      <c r="C81" s="150" t="s">
+        <v>170</v>
+      </c>
+      <c r="D81" s="146"/>
+      <c r="E81" s="146"/>
+      <c r="F81" s="146"/>
+      <c r="G81" s="146">
+        <v>40</v>
+      </c>
+      <c r="H81" s="146">
+        <v>40</v>
+      </c>
+      <c r="I81" s="159"/>
+      <c r="J81" s="146">
+        <v>40</v>
+      </c>
+      <c r="K81" s="146">
+        <v>40</v>
+      </c>
+      <c r="L81" s="146">
+        <v>40</v>
+      </c>
+      <c r="M81" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
       <c r="N81" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -8810,11 +8871,11 @@
       </c>
       <c r="P81" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q81" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R81" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8854,17 +8915,32 @@
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="151"/>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="50"/>
-      <c r="H82" s="50"/>
-      <c r="I82" s="152"/>
-      <c r="J82" s="50"/>
-      <c r="K82" s="50"/>
-      <c r="L82" s="50"/>
-      <c r="M82" s="152"/>
+      <c r="C82" s="150" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="146"/>
+      <c r="E82" s="146"/>
+      <c r="F82" s="146"/>
+      <c r="G82" s="146">
+        <v>80</v>
+      </c>
+      <c r="H82" s="146">
+        <v>80</v>
+      </c>
+      <c r="I82" s="159"/>
+      <c r="J82" s="146">
+        <v>80</v>
+      </c>
+      <c r="K82" s="146">
+        <v>80</v>
+      </c>
+      <c r="L82" s="146">
+        <v>80</v>
+      </c>
+      <c r="M82" s="159">
+        <f t="shared" si="81"/>
+        <v>10</v>
+      </c>
       <c r="N82" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -8875,11 +8951,11 @@
       </c>
       <c r="P82" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q82" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R82" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8919,17 +8995,32 @@
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="151"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="50"/>
-      <c r="H83" s="50"/>
-      <c r="I83" s="152"/>
-      <c r="J83" s="50"/>
-      <c r="K83" s="50"/>
-      <c r="L83" s="50"/>
-      <c r="M83" s="152"/>
+      <c r="C83" s="150" t="s">
+        <v>172</v>
+      </c>
+      <c r="D83" s="146"/>
+      <c r="E83" s="146"/>
+      <c r="F83" s="146"/>
+      <c r="G83" s="146">
+        <v>40</v>
+      </c>
+      <c r="H83" s="146">
+        <v>40</v>
+      </c>
+      <c r="I83" s="159"/>
+      <c r="J83" s="146">
+        <v>40</v>
+      </c>
+      <c r="K83" s="146">
+        <v>40</v>
+      </c>
+      <c r="L83" s="146">
+        <v>40</v>
+      </c>
+      <c r="M83" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
       <c r="N83" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -8940,11 +9031,11 @@
       </c>
       <c r="P83" s="73">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q83" s="40">
         <f t="shared" si="90"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R83" s="51" t="e">
         <f t="shared" si="4"/>
@@ -8981,195 +9072,116 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="78"/>
-      <c r="B84" s="47">
+      <c r="B84" s="47"/>
+      <c r="C84" s="150" t="s">
+        <v>173</v>
+      </c>
+      <c r="D84" s="146"/>
+      <c r="E84" s="146"/>
+      <c r="F84" s="146"/>
+      <c r="G84" s="146">
         <v>80</v>
       </c>
-      <c r="C84" s="151"/>
-      <c r="D84" s="50"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="50"/>
-      <c r="H84" s="50"/>
-      <c r="I84" s="152"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="50"/>
-      <c r="L84" s="50"/>
-      <c r="M84" s="152">
+      <c r="H84" s="146">
+        <v>80</v>
+      </c>
+      <c r="I84" s="159"/>
+      <c r="J84" s="146">
+        <v>80</v>
+      </c>
+      <c r="K84" s="146">
+        <v>80</v>
+      </c>
+      <c r="L84" s="146">
+        <v>80</v>
+      </c>
+      <c r="M84" s="159">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N84" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O84" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P84" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="R84" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S84" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T84" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U84" s="53" t="e">
-        <f t="shared" si="84"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V84" s="54" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W84" s="55">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="X84" s="55">
-        <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="Y84" s="56" t="e">
-        <f t="shared" si="88"/>
-        <v>#VALUE!</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N84" s="39"/>
+      <c r="O84" s="49"/>
+      <c r="P84" s="73"/>
+      <c r="Q84" s="40"/>
+      <c r="R84" s="51"/>
+      <c r="S84" s="52"/>
+      <c r="T84" s="52"/>
+      <c r="U84" s="53"/>
+      <c r="V84" s="54"/>
+      <c r="W84" s="55"/>
+      <c r="X84" s="55"/>
+      <c r="Y84" s="56"/>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
-      <c r="B85" s="170" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="171"/>
-      <c r="D85" s="88">
-        <f t="shared" ref="D85:L85" si="96">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E85" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="88">
-        <f t="shared" si="96"/>
-        <v>7140</v>
-      </c>
-      <c r="H85" s="88">
-        <f t="shared" si="96"/>
-        <v>7657</v>
-      </c>
-      <c r="I85" s="88">
-        <f t="shared" si="96"/>
-        <v>10657</v>
-      </c>
-      <c r="J85" s="88">
-        <f t="shared" si="96"/>
-        <v>11297</v>
-      </c>
-      <c r="K85" s="88">
-        <f t="shared" si="96"/>
-        <v>9684</v>
-      </c>
-      <c r="L85" s="88">
-        <f t="shared" si="96"/>
-        <v>13219</v>
-      </c>
-      <c r="M85" s="48">
-        <f t="shared" ref="M85:M88" si="97">SUM(D85:L85)/40</f>
-        <v>1524.35</v>
-      </c>
-      <c r="N85" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O85" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P85" s="73">
-        <f t="shared" ref="P85:P89" si="98">SUM(G85:I85)/20</f>
-        <v>1272.7</v>
-      </c>
-      <c r="Q85" s="40">
-        <f t="shared" ref="Q85:Q89" si="99">SUM(J85:L85)/20</f>
-        <v>1710</v>
-      </c>
-      <c r="R85" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S85" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T85" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U85" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V85" s="54" t="e">
-        <f t="shared" ref="V85:V89" si="100">SUM(D85:F85)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W85" s="55">
-        <f t="shared" ref="W85:W89" si="101">SUM(G85:I85)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X85" s="55">
-        <f t="shared" ref="X85:X89" si="102">SUM(J85:L85)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y85" s="56" t="e">
-        <f t="shared" si="44"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B85" s="47"/>
+      <c r="C85" s="150" t="s">
+        <v>174</v>
+      </c>
+      <c r="D85" s="146"/>
+      <c r="E85" s="146"/>
+      <c r="F85" s="146"/>
+      <c r="G85" s="146">
+        <v>40</v>
+      </c>
+      <c r="H85" s="146">
+        <v>40</v>
+      </c>
+      <c r="I85" s="159"/>
+      <c r="J85" s="146">
+        <v>40</v>
+      </c>
+      <c r="K85" s="146">
+        <v>40</v>
+      </c>
+      <c r="L85" s="146">
+        <v>40</v>
+      </c>
+      <c r="M85" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N85" s="39"/>
+      <c r="O85" s="49"/>
+      <c r="P85" s="73"/>
+      <c r="Q85" s="40"/>
+      <c r="R85" s="51"/>
+      <c r="S85" s="52"/>
+      <c r="T85" s="52"/>
+      <c r="U85" s="53"/>
+      <c r="V85" s="54"/>
+      <c r="W85" s="55"/>
+      <c r="X85" s="55"/>
+      <c r="Y85" s="56"/>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
-      <c r="B86" s="118">
-        <v>0</v>
-      </c>
-      <c r="C86" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D86" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E86" s="120"/>
-      <c r="F86" s="121"/>
-      <c r="G86" s="120"/>
-      <c r="H86" s="120"/>
-      <c r="I86" s="121"/>
-      <c r="J86" s="120">
-        <v>520</v>
-      </c>
-      <c r="K86" s="120">
-        <v>920</v>
-      </c>
-      <c r="L86" s="121">
-        <v>960</v>
-      </c>
-      <c r="M86" s="122">
-        <f>SUM(D86:L86)</f>
-        <v>4000</v>
+      <c r="B86" s="47"/>
+      <c r="C86" s="150" t="s">
+        <v>175</v>
+      </c>
+      <c r="D86" s="146"/>
+      <c r="E86" s="146"/>
+      <c r="F86" s="146"/>
+      <c r="G86" s="146">
+        <v>40</v>
+      </c>
+      <c r="H86" s="146">
+        <v>40</v>
+      </c>
+      <c r="I86" s="159"/>
+      <c r="J86" s="146">
+        <v>40</v>
+      </c>
+      <c r="K86" s="146">
+        <v>40</v>
+      </c>
+      <c r="L86" s="146">
+        <v>40</v>
+      </c>
+      <c r="M86" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
       </c>
       <c r="N86" s="39"/>
       <c r="O86" s="49"/>
@@ -9186,376 +9198,821 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
-      <c r="B87" s="47">
+      <c r="B87" s="47"/>
+      <c r="C87" s="150" t="s">
+        <v>176</v>
+      </c>
+      <c r="D87" s="146"/>
+      <c r="E87" s="146"/>
+      <c r="F87" s="146"/>
+      <c r="G87" s="146">
+        <v>40</v>
+      </c>
+      <c r="H87" s="146">
+        <v>40</v>
+      </c>
+      <c r="I87" s="159"/>
+      <c r="J87" s="146">
+        <v>40</v>
+      </c>
+      <c r="K87" s="146">
+        <v>40</v>
+      </c>
+      <c r="L87" s="146">
+        <v>40</v>
+      </c>
+      <c r="M87" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N87" s="39"/>
+      <c r="O87" s="49"/>
+      <c r="P87" s="73"/>
+      <c r="Q87" s="40"/>
+      <c r="R87" s="51"/>
+      <c r="S87" s="52"/>
+      <c r="T87" s="52"/>
+      <c r="U87" s="53"/>
+      <c r="V87" s="54"/>
+      <c r="W87" s="55"/>
+      <c r="X87" s="55"/>
+      <c r="Y87" s="56"/>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A88" s="78"/>
+      <c r="B88" s="47"/>
+      <c r="C88" s="150" t="s">
+        <v>177</v>
+      </c>
+      <c r="D88" s="146"/>
+      <c r="E88" s="146"/>
+      <c r="F88" s="146"/>
+      <c r="G88" s="146">
+        <v>40</v>
+      </c>
+      <c r="H88" s="146">
+        <v>40</v>
+      </c>
+      <c r="I88" s="159"/>
+      <c r="J88" s="146">
+        <v>40</v>
+      </c>
+      <c r="K88" s="146">
+        <v>40</v>
+      </c>
+      <c r="L88" s="146">
+        <v>40</v>
+      </c>
+      <c r="M88" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N88" s="39"/>
+      <c r="O88" s="49"/>
+      <c r="P88" s="73"/>
+      <c r="Q88" s="40"/>
+      <c r="R88" s="51"/>
+      <c r="S88" s="52"/>
+      <c r="T88" s="52"/>
+      <c r="U88" s="53"/>
+      <c r="V88" s="54"/>
+      <c r="W88" s="55"/>
+      <c r="X88" s="55"/>
+      <c r="Y88" s="56"/>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A89" s="78"/>
+      <c r="B89" s="47"/>
+      <c r="C89" s="150" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" s="146"/>
+      <c r="E89" s="146"/>
+      <c r="F89" s="146"/>
+      <c r="G89" s="146">
+        <v>40</v>
+      </c>
+      <c r="H89" s="146">
+        <v>40</v>
+      </c>
+      <c r="I89" s="159"/>
+      <c r="J89" s="146">
+        <v>40</v>
+      </c>
+      <c r="K89" s="146">
+        <v>40</v>
+      </c>
+      <c r="L89" s="146">
+        <v>40</v>
+      </c>
+      <c r="M89" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N89" s="39"/>
+      <c r="O89" s="49"/>
+      <c r="P89" s="73"/>
+      <c r="Q89" s="40"/>
+      <c r="R89" s="51"/>
+      <c r="S89" s="52"/>
+      <c r="T89" s="52"/>
+      <c r="U89" s="53"/>
+      <c r="V89" s="54"/>
+      <c r="W89" s="55"/>
+      <c r="X89" s="55"/>
+      <c r="Y89" s="56"/>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A90" s="78"/>
+      <c r="B90" s="47"/>
+      <c r="C90" s="150" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" s="146"/>
+      <c r="E90" s="146"/>
+      <c r="F90" s="146"/>
+      <c r="G90" s="146">
+        <v>40</v>
+      </c>
+      <c r="H90" s="146">
+        <v>40</v>
+      </c>
+      <c r="I90" s="159"/>
+      <c r="J90" s="146">
+        <v>40</v>
+      </c>
+      <c r="K90" s="146">
+        <v>40</v>
+      </c>
+      <c r="L90" s="146">
+        <v>40</v>
+      </c>
+      <c r="M90" s="159">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N90" s="39"/>
+      <c r="O90" s="49"/>
+      <c r="P90" s="73"/>
+      <c r="Q90" s="40"/>
+      <c r="R90" s="51"/>
+      <c r="S90" s="52"/>
+      <c r="T90" s="52"/>
+      <c r="U90" s="53"/>
+      <c r="V90" s="54"/>
+      <c r="W90" s="55"/>
+      <c r="X90" s="55"/>
+      <c r="Y90" s="56"/>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A91" s="78"/>
+      <c r="B91" s="47"/>
+      <c r="C91" s="150" t="s">
+        <v>169</v>
+      </c>
+      <c r="D91" s="146"/>
+      <c r="E91" s="146"/>
+      <c r="F91" s="146"/>
+      <c r="G91" s="146">
+        <v>84</v>
+      </c>
+      <c r="H91" s="146">
+        <v>84</v>
+      </c>
+      <c r="I91" s="159"/>
+      <c r="J91" s="146">
+        <v>168</v>
+      </c>
+      <c r="K91" s="146">
+        <v>126</v>
+      </c>
+      <c r="L91" s="146">
+        <v>252</v>
+      </c>
+      <c r="M91" s="159">
+        <f t="shared" si="81"/>
+        <v>17.850000000000001</v>
+      </c>
+      <c r="N91" s="39"/>
+      <c r="O91" s="49"/>
+      <c r="P91" s="73"/>
+      <c r="Q91" s="40"/>
+      <c r="R91" s="51"/>
+      <c r="S91" s="52"/>
+      <c r="T91" s="52"/>
+      <c r="U91" s="53"/>
+      <c r="V91" s="54"/>
+      <c r="W91" s="55"/>
+      <c r="X91" s="55"/>
+      <c r="Y91" s="56"/>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A92" s="78"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="151"/>
+      <c r="D92" s="50"/>
+      <c r="E92" s="50"/>
+      <c r="F92" s="50"/>
+      <c r="G92" s="50"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="152"/>
+      <c r="J92" s="50"/>
+      <c r="K92" s="50"/>
+      <c r="L92" s="50"/>
+      <c r="M92" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N92" s="39"/>
+      <c r="O92" s="49"/>
+      <c r="P92" s="73"/>
+      <c r="Q92" s="40"/>
+      <c r="R92" s="51"/>
+      <c r="S92" s="52"/>
+      <c r="T92" s="52"/>
+      <c r="U92" s="53"/>
+      <c r="V92" s="54"/>
+      <c r="W92" s="55"/>
+      <c r="X92" s="55"/>
+      <c r="Y92" s="56"/>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A93" s="78"/>
+      <c r="B93" s="47">
+        <v>80</v>
+      </c>
+      <c r="C93" s="151"/>
+      <c r="D93" s="50"/>
+      <c r="E93" s="50"/>
+      <c r="F93" s="50"/>
+      <c r="G93" s="50"/>
+      <c r="H93" s="50"/>
+      <c r="I93" s="152"/>
+      <c r="J93" s="50"/>
+      <c r="K93" s="50"/>
+      <c r="L93" s="50"/>
+      <c r="M93" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N93" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O93" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P93" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q93" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R93" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S93" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V93" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W93" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X93" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y93" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A94" s="78"/>
+      <c r="B94" s="170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="171"/>
+      <c r="D94" s="88">
+        <f t="shared" ref="D94:L94" si="96">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E94" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="F94" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="G94" s="88">
+        <f t="shared" si="96"/>
+        <v>7140</v>
+      </c>
+      <c r="H94" s="88">
+        <f t="shared" si="96"/>
+        <v>7657</v>
+      </c>
+      <c r="I94" s="88">
+        <f t="shared" si="96"/>
+        <v>10657</v>
+      </c>
+      <c r="J94" s="88">
+        <f t="shared" si="96"/>
+        <v>11297</v>
+      </c>
+      <c r="K94" s="88">
+        <f t="shared" si="96"/>
+        <v>9684</v>
+      </c>
+      <c r="L94" s="88">
+        <f t="shared" si="96"/>
+        <v>13219</v>
+      </c>
+      <c r="M94" s="48">
+        <f t="shared" ref="M94:M97" si="97">SUM(D94:L94)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N94" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O94" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P94" s="73">
+        <f t="shared" ref="P94:P98" si="98">SUM(G94:I94)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q94" s="40">
+        <f t="shared" ref="Q94:Q98" si="99">SUM(J94:L94)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R94" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S94" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T94" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U94" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V94" s="54" t="e">
+        <f t="shared" ref="V94:V98" si="100">SUM(D94:F94)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W94" s="55">
+        <f t="shared" ref="W94:W98" si="101">SUM(G94:I94)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X94" s="55">
+        <f t="shared" ref="X94:X98" si="102">SUM(J94:L94)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y94" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A95" s="78"/>
+      <c r="B95" s="118">
+        <v>0</v>
+      </c>
+      <c r="C95" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E95" s="120"/>
+      <c r="F95" s="121"/>
+      <c r="G95" s="120"/>
+      <c r="H95" s="120"/>
+      <c r="I95" s="121"/>
+      <c r="J95" s="120">
+        <v>520</v>
+      </c>
+      <c r="K95" s="120">
+        <v>920</v>
+      </c>
+      <c r="L95" s="121">
+        <v>960</v>
+      </c>
+      <c r="M95" s="122">
+        <f>SUM(D95:L95)</f>
+        <v>4000</v>
+      </c>
+      <c r="N95" s="39"/>
+      <c r="O95" s="49"/>
+      <c r="P95" s="73"/>
+      <c r="Q95" s="40"/>
+      <c r="R95" s="51"/>
+      <c r="S95" s="52"/>
+      <c r="T95" s="52"/>
+      <c r="U95" s="53"/>
+      <c r="V95" s="54"/>
+      <c r="W95" s="55"/>
+      <c r="X95" s="55"/>
+      <c r="Y95" s="56"/>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A96" s="78"/>
+      <c r="B96" s="47">
         <v>1</v>
       </c>
-      <c r="C87" s="57" t="s">
+      <c r="C96" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D87" s="74"/>
-      <c r="E87" s="75"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="50">
+      <c r="D96" s="74"/>
+      <c r="E96" s="75"/>
+      <c r="F96" s="76"/>
+      <c r="G96" s="50">
         <f>280+1600</f>
         <v>1880</v>
       </c>
-      <c r="H87" s="75">
+      <c r="H96" s="75">
         <f>0+600</f>
         <v>600</v>
       </c>
-      <c r="I87" s="49">
+      <c r="I96" s="49">
         <f>320+1800</f>
         <v>2120</v>
       </c>
-      <c r="J87" s="50">
+      <c r="J96" s="50">
         <f>600+2800</f>
         <v>3400</v>
       </c>
-      <c r="K87" s="75">
+      <c r="K96" s="75">
         <f>600+2400</f>
         <v>3000</v>
       </c>
-      <c r="L87" s="76">
+      <c r="L96" s="76">
         <f>2200+2800</f>
         <v>5000</v>
       </c>
-      <c r="M87" s="48">
+      <c r="M96" s="48">
         <f t="shared" si="97"/>
         <v>400</v>
       </c>
-      <c r="N87" s="39">
+      <c r="N96" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O87" s="49">
+      <c r="O96" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P87" s="73">
+      <c r="P96" s="73">
         <f t="shared" si="98"/>
         <v>230</v>
       </c>
-      <c r="Q87" s="40">
+      <c r="Q96" s="40">
         <f t="shared" si="99"/>
         <v>570</v>
       </c>
-      <c r="R87" s="51" t="e">
+      <c r="R96" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S87" s="52">
+      <c r="S96" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T87" s="52">
+      <c r="T96" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U87" s="53" t="e">
+      <c r="U96" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V87" s="54" t="e">
+      <c r="V96" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W87" s="55">
+      <c r="W96" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X87" s="55">
+      <c r="X96" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y87" s="56" t="e">
+      <c r="Y96" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B88" s="47">
+    <row r="97" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B97" s="47">
         <v>2</v>
       </c>
-      <c r="C88" s="57" t="s">
+      <c r="C97" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D88" s="74">
+      <c r="D97" s="74">
         <v>1400</v>
       </c>
-      <c r="E88" s="75"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="50">
+      <c r="E97" s="75"/>
+      <c r="F97" s="76"/>
+      <c r="G97" s="50">
         <v>400</v>
       </c>
-      <c r="H88" s="75">
+      <c r="H97" s="75">
         <v>400</v>
       </c>
-      <c r="I88" s="49">
-        <v>0</v>
-      </c>
-      <c r="J88" s="50">
+      <c r="I97" s="49">
+        <v>0</v>
+      </c>
+      <c r="J97" s="50">
         <v>400</v>
       </c>
-      <c r="K88" s="75">
+      <c r="K97" s="75">
         <v>400</v>
       </c>
-      <c r="L88" s="76">
+      <c r="L97" s="76">
         <v>600</v>
       </c>
-      <c r="M88" s="48">
+      <c r="M97" s="48">
         <f t="shared" si="97"/>
         <v>90</v>
       </c>
-      <c r="N88" s="39">
+      <c r="N97" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O88" s="49">
+      <c r="O97" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P88" s="73">
+      <c r="P97" s="73">
         <f t="shared" si="98"/>
         <v>40</v>
       </c>
-      <c r="Q88" s="40">
+      <c r="Q97" s="40">
         <f t="shared" si="99"/>
         <v>70</v>
       </c>
-      <c r="R88" s="51" t="e">
+      <c r="R97" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S88" s="52">
+      <c r="S97" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T88" s="52">
+      <c r="T97" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U88" s="53" t="e">
+      <c r="U97" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V88" s="54" t="e">
+      <c r="V97" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W88" s="55">
+      <c r="W97" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X88" s="55">
+      <c r="X97" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y88" s="56" t="e">
+      <c r="Y97" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B89" s="183" t="s">
+    <row r="98" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B98" s="183" t="s">
         <v>93</v>
       </c>
-      <c r="C89" s="184"/>
-      <c r="D89" s="87">
-        <f>SUM(D87:D88)</f>
+      <c r="C98" s="184"/>
+      <c r="D98" s="87">
+        <f>SUM(D96:D97)</f>
         <v>1400</v>
       </c>
-      <c r="E89" s="87">
-        <f t="shared" ref="E89:L89" si="103">SUM(E87:E88)</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="87">
+      <c r="E98" s="87">
+        <f t="shared" ref="E98:L98" si="103">SUM(E96:E97)</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="87">
         <f t="shared" si="103"/>
         <v>0</v>
       </c>
-      <c r="G89" s="87">
+      <c r="G98" s="87">
         <f t="shared" si="103"/>
         <v>2280</v>
       </c>
-      <c r="H89" s="87">
+      <c r="H98" s="87">
         <f t="shared" si="103"/>
         <v>1000</v>
       </c>
-      <c r="I89" s="87">
+      <c r="I98" s="87">
         <f t="shared" si="103"/>
         <v>2120</v>
       </c>
-      <c r="J89" s="87">
+      <c r="J98" s="87">
         <f t="shared" si="103"/>
         <v>3800</v>
       </c>
-      <c r="K89" s="87">
+      <c r="K98" s="87">
         <f t="shared" si="103"/>
         <v>3400</v>
       </c>
-      <c r="L89" s="87">
+      <c r="L98" s="87">
         <f t="shared" si="103"/>
         <v>5600</v>
       </c>
-      <c r="M89" s="123">
-        <f>SUM(M86:M88)</f>
+      <c r="M98" s="123">
+        <f>SUM(M95:M97)</f>
         <v>4490</v>
       </c>
-      <c r="N89" s="59">
+      <c r="N98" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O89" s="58">
+      <c r="O98" s="58">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P89" s="73">
+      <c r="P98" s="73">
         <f t="shared" si="98"/>
         <v>270</v>
       </c>
-      <c r="Q89" s="40">
+      <c r="Q98" s="40">
         <f t="shared" si="99"/>
         <v>640</v>
       </c>
-      <c r="R89" s="51" t="e">
+      <c r="R98" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S89" s="52">
+      <c r="S98" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T89" s="52">
+      <c r="T98" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U89" s="53" t="e">
+      <c r="U98" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V89" s="54" t="e">
+      <c r="V98" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W89" s="55">
+      <c r="W98" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X89" s="55">
+      <c r="X98" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y89" s="56" t="e">
+      <c r="Y98" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="172" t="s">
+    <row r="99" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B99" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C90" s="173"/>
-      <c r="D90" s="89">
-        <f>SUM(D85,D89)</f>
+      <c r="C99" s="173"/>
+      <c r="D99" s="89">
+        <f>SUM(D94,D98)</f>
         <v>2720</v>
       </c>
-      <c r="E90" s="89">
-        <f t="shared" ref="E90:L90" si="104">SUM(E85,E89)</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="89">
+      <c r="E99" s="89">
+        <f t="shared" ref="E99:L99" si="104">SUM(E94,E98)</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="89">
         <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="G90" s="89">
+      <c r="G99" s="89">
         <f t="shared" si="104"/>
         <v>9420</v>
       </c>
-      <c r="H90" s="89">
+      <c r="H99" s="89">
         <f t="shared" si="104"/>
         <v>8657</v>
       </c>
-      <c r="I90" s="89">
+      <c r="I99" s="89">
         <f t="shared" si="104"/>
         <v>12777</v>
       </c>
-      <c r="J90" s="89">
+      <c r="J99" s="89">
         <f t="shared" si="104"/>
         <v>15097</v>
       </c>
-      <c r="K90" s="89">
+      <c r="K99" s="89">
         <f t="shared" si="104"/>
         <v>13084</v>
       </c>
-      <c r="L90" s="89">
+      <c r="L99" s="89">
         <f t="shared" si="104"/>
         <v>18819</v>
       </c>
-      <c r="M90" s="60">
+      <c r="M99" s="60">
         <f t="shared" si="0"/>
         <v>2014.35</v>
       </c>
-      <c r="N90" s="63">
-        <f>SUM(N5:N89)</f>
-        <v>0</v>
-      </c>
-      <c r="O90" s="61">
-        <f t="shared" ref="O90:Y90" si="105">SUM(O5:O89)</f>
+      <c r="N99" s="63">
+        <f>SUM(N5:N98)</f>
+        <v>0</v>
+      </c>
+      <c r="O99" s="61">
+        <f t="shared" ref="O99:Y99" si="105">SUM(O5:O98)</f>
         <v>27856.920000000016</v>
       </c>
-      <c r="P90" s="62">
+      <c r="P99" s="62">
         <f t="shared" si="105"/>
-        <v>3522.7</v>
-      </c>
-      <c r="Q90" s="64">
+        <v>3538.7</v>
+      </c>
+      <c r="Q99" s="64">
         <f t="shared" si="105"/>
-        <v>5611.95</v>
-      </c>
-      <c r="R90" s="65" t="e">
+        <v>5635.95</v>
+      </c>
+      <c r="R99" s="65" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S90" s="66">
+      <c r="S99" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="T90" s="66">
+      <c r="T99" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="U90" s="67" t="e">
+      <c r="U99" s="67" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V90" s="68" t="e">
+      <c r="V99" s="68" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W90" s="69">
+      <c r="W99" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="X90" s="69">
+      <c r="X99" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="Y90" s="70" t="e">
+      <c r="Y99" s="70" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B99:C99"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B98:C98"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B94:C94"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -10094,7 +10551,7 @@
     <col min="4" max="4" width="5.6328125" customWidth="1"/>
     <col min="6" max="6" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.81640625" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -10223,10 +10680,13 @@
         <v>133</v>
       </c>
       <c r="J7" s="81">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K7" s="81" t="s">
         <v>139</v>
+      </c>
+      <c r="L7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -10238,7 +10698,7 @@
         <v>163</v>
       </c>
       <c r="J8" s="81">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K8" s="81" t="s">
         <v>139</v>
@@ -10250,13 +10710,16 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="I9" s="81" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J9" s="81">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K9" s="81" t="s">
         <v>139</v>
+      </c>
+      <c r="L9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -10268,7 +10731,7 @@
         <v>133</v>
       </c>
       <c r="J10" s="81">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K10" s="81" t="s">
         <v>139</v>
@@ -10279,45 +10742,73 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
+      <c r="I11" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" s="81">
+        <v>3</v>
+      </c>
+      <c r="K11" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
+      <c r="I12" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="J12" s="81">
+        <v>11</v>
+      </c>
+      <c r="K12" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
+      <c r="I13" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="81">
+        <v>80</v>
+      </c>
+      <c r="K13" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="I14" s="81"/>
+      <c r="I14" s="81" t="s">
+        <v>168</v>
+      </c>
       <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="K14" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
+      <c r="I15" s="81" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="81">
+        <v>12</v>
+      </c>
+      <c r="K15" s="81" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D24A10-36F9-49A6-BF1E-336A170313A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2235F7-9044-41AD-90F6-56053F7D3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1463,7 +1463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1856,6 +1856,45 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1892,45 +1931,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,13 +1951,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2494,13 +2487,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="160">
+      <c r="B1" s="173">
         <v>46186</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2522,10 +2515,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="182" t="s">
+      <c r="A2" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="174" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2558,13 +2551,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="174"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="176"/>
-      <c r="P2" s="177" t="s">
+      <c r="M2" s="162"/>
+      <c r="N2" s="163"/>
+      <c r="O2" s="164"/>
+      <c r="P2" s="165" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="178"/>
+      <c r="Q2" s="166"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2583,8 +2576,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="182"/>
-      <c r="B3" s="162"/>
+      <c r="A3" s="170"/>
+      <c r="B3" s="175"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2615,29 +2608,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="179" t="s">
+      <c r="M3" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="180"/>
-      <c r="O3" s="181"/>
+      <c r="N3" s="168"/>
+      <c r="O3" s="169"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="164" t="s">
+      <c r="R3" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="165"/>
-      <c r="T3" s="165"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="167" t="s">
+      <c r="S3" s="178"/>
+      <c r="T3" s="178"/>
+      <c r="U3" s="179"/>
+      <c r="V3" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="168"/>
-      <c r="X3" s="168"/>
-      <c r="Y3" s="169"/>
+      <c r="W3" s="181"/>
+      <c r="X3" s="181"/>
+      <c r="Y3" s="182"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="182"/>
-      <c r="B4" s="163"/>
+      <c r="A4" s="170"/>
+      <c r="B4" s="176"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8669,28 +8662,28 @@
       <c r="B79" s="47">
         <v>75</v>
       </c>
-      <c r="C79" s="192" t="s">
+      <c r="C79" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="D79" s="193"/>
-      <c r="E79" s="193"/>
-      <c r="F79" s="193"/>
-      <c r="G79" s="193">
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50">
         <v>314</v>
       </c>
-      <c r="H79" s="193">
+      <c r="H79" s="50">
         <v>353</v>
       </c>
-      <c r="I79" s="194">
+      <c r="I79" s="152">
         <v>388</v>
       </c>
-      <c r="J79" s="193">
+      <c r="J79" s="50">
         <v>350</v>
       </c>
-      <c r="K79" s="193">
+      <c r="K79" s="50">
         <v>311</v>
       </c>
-      <c r="L79" s="193">
+      <c r="L79" s="50">
         <v>396</v>
       </c>
       <c r="M79" s="152">
@@ -8751,30 +8744,30 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="192" t="s">
+      <c r="C80" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="D80" s="193">
-        <v>40</v>
-      </c>
-      <c r="E80" s="193"/>
-      <c r="F80" s="193"/>
-      <c r="G80" s="193">
-        <v>40</v>
-      </c>
-      <c r="H80" s="193">
-        <v>0</v>
-      </c>
-      <c r="I80" s="194">
+      <c r="D80" s="50">
+        <v>40</v>
+      </c>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50">
+        <v>40</v>
+      </c>
+      <c r="H80" s="50">
+        <v>0</v>
+      </c>
+      <c r="I80" s="152">
         <v>120</v>
       </c>
-      <c r="J80" s="193">
+      <c r="J80" s="50">
         <v>200</v>
       </c>
-      <c r="K80" s="193">
-        <v>0</v>
-      </c>
-      <c r="L80" s="193">
+      <c r="K80" s="50">
+        <v>0</v>
+      </c>
+      <c r="L80" s="50">
         <v>200</v>
       </c>
       <c r="M80" s="152">
@@ -9506,10 +9499,10 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
-      <c r="B94" s="170" t="s">
+      <c r="B94" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="C94" s="171"/>
+      <c r="C94" s="184"/>
       <c r="D94" s="88">
         <f t="shared" ref="D94:L94" si="96">SUM(D6:D60)</f>
         <v>1320</v>
@@ -9813,10 +9806,10 @@
       </c>
     </row>
     <row r="98" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="183" t="s">
+      <c r="B98" s="171" t="s">
         <v>93</v>
       </c>
-      <c r="C98" s="184"/>
+      <c r="C98" s="172"/>
       <c r="D98" s="87">
         <f>SUM(D96:D97)</f>
         <v>1400</v>
@@ -9907,10 +9900,10 @@
       </c>
     </row>
     <row r="99" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B99" s="172" t="s">
+      <c r="B99" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="C99" s="173"/>
+      <c r="C99" s="161"/>
       <c r="D99" s="89">
         <f>SUM(D94,D98)</f>
         <v>2720</v>
@@ -10002,17 +9995,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B94:C94"/>
     <mergeCell ref="B99:C99"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B94:C94"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -10102,24 +10095,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="92">
-        <v>598</v>
+        <v>701</v>
       </c>
       <c r="E5" s="79">
-        <v>1724</v>
+        <v>1802</v>
       </c>
       <c r="F5" s="79">
         <v>590</v>
       </c>
       <c r="G5" s="112">
         <f>SUM(D5:F5)</f>
-        <v>2912</v>
+        <v>3093</v>
       </c>
       <c r="H5" s="105">
         <v>10000</v>
       </c>
       <c r="I5" s="106">
         <f>G5-H5</f>
-        <v>-7088</v>
+        <v>-6907</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -10144,11 +10137,11 @@
       </c>
       <c r="D6" s="114">
         <f>D5*40</f>
-        <v>23920</v>
+        <v>28040</v>
       </c>
       <c r="E6" s="115">
         <f>E5*40</f>
-        <v>68960</v>
+        <v>72080</v>
       </c>
       <c r="F6" s="115">
         <f>F5*40</f>
@@ -10156,7 +10149,7 @@
       </c>
       <c r="G6" s="116">
         <f>SUM(D6:F6)</f>
-        <v>116480</v>
+        <v>123720</v>
       </c>
       <c r="H6" s="107">
         <f>H5*40</f>
@@ -10164,7 +10157,7 @@
       </c>
       <c r="I6" s="108">
         <f>G6-H6</f>
-        <v>-283520</v>
+        <v>-276280</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -10229,11 +10222,11 @@
       </c>
       <c r="D9" s="117">
         <f>D8-D5</f>
-        <v>-598</v>
+        <v>-701</v>
       </c>
       <c r="E9" s="117">
         <f>E8-E5</f>
-        <v>-1724</v>
+        <v>-1802</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -10284,7 +10277,7 @@
       </c>
       <c r="I11">
         <f>D5/20</f>
-        <v>29.9</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
@@ -10315,7 +10308,7 @@
       </c>
       <c r="G12" s="101">
         <f>D12+G5</f>
-        <v>3412.9</v>
+        <v>3593.9</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -10347,7 +10340,7 @@
       </c>
       <c r="G13" s="101">
         <f>G12*40</f>
-        <v>136516</v>
+        <v>143756</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2235F7-9044-41AD-90F6-56053F7D3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633D7642-AC6E-470E-AF44-43B96832A85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="192">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -439,9 +439,6 @@
     <t>Raheem iqbal</t>
   </si>
   <si>
-    <t>On The Way</t>
-  </si>
-  <si>
     <t>Pending</t>
   </si>
   <si>
@@ -563,6 +560,45 @@
   </si>
   <si>
     <t>Gourmet Food Shadra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naimat khana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons H Block </t>
+  </si>
+  <si>
+    <t>Rainbow BT</t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Sana Cash &amp; Carry</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA Rahber</t>
+  </si>
+  <si>
+    <t>Gourmet Food Bahria Town</t>
+  </si>
+  <si>
+    <t>Jalal Sons Bahria Orchard</t>
+  </si>
+  <si>
+    <t>on the way</t>
+  </si>
+  <si>
+    <t>Manawan Risen</t>
+  </si>
+  <si>
+    <t>Altaf C &amp; C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jalal Sons Lake City </t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -667,7 +703,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -740,6 +776,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="58">
     <border>
@@ -1463,7 +1505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1856,6 +1898,54 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1895,42 +1985,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,6 +2005,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2461,14 +2529,14 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="156" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="155" t="s">
         <v>160</v>
-      </c>
-      <c r="C24" s="155" t="s">
-        <v>161</v>
       </c>
       <c r="D24" s="155"/>
       <c r="E24" s="155" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2479,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2487,13 +2555,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="173">
+      <c r="B1" s="164">
         <v>46186</v>
       </c>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2515,10 +2583,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="186" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="165" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2551,13 +2619,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="162"/>
-      <c r="N2" s="163"/>
-      <c r="O2" s="164"/>
-      <c r="P2" s="165" t="s">
+      <c r="M2" s="178"/>
+      <c r="N2" s="179"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="166"/>
+      <c r="Q2" s="182"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2576,8 +2644,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="170"/>
-      <c r="B3" s="175"/>
+      <c r="A3" s="186"/>
+      <c r="B3" s="166"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2608,29 +2676,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="168"/>
-      <c r="O3" s="169"/>
+      <c r="N3" s="184"/>
+      <c r="O3" s="185"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="177" t="s">
+      <c r="R3" s="168" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="178"/>
-      <c r="T3" s="178"/>
-      <c r="U3" s="179"/>
-      <c r="V3" s="180" t="s">
+      <c r="S3" s="169"/>
+      <c r="T3" s="169"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="181"/>
-      <c r="X3" s="181"/>
-      <c r="Y3" s="182"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="173"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="170"/>
-      <c r="B4" s="176"/>
+      <c r="A4" s="186"/>
+      <c r="B4" s="167"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2821,7 +2889,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M99" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M106" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2829,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O98" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O105" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2841,15 +2909,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R98" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R105" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S98" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S105" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T98" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T105" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -2997,7 +3065,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N98" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N105" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3437,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U98" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U105" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3453,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y98" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y105" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4113,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y94" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y101" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7153,7 +7221,7 @@
         <v>57</v>
       </c>
       <c r="C61" s="151" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
@@ -7177,7 +7245,7 @@
         <v>400</v>
       </c>
       <c r="M61" s="152">
-        <f t="shared" ref="M61:M93" si="81">SUM(D61:L61)/40</f>
+        <f t="shared" ref="M61:M100" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
       <c r="N61" s="39">
@@ -7189,11 +7257,11 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P93" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" ref="P61:P100" si="82">SUM(G61:I61)/20</f>
         <v>14</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q93" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" ref="Q61:Q100" si="83">SUM(J61:L61)/20</f>
         <v>30</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -7209,23 +7277,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U93" si="84">SUM(R61:T61)</f>
+        <f t="shared" ref="U61:U100" si="84">SUM(R61:T61)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V93" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" ref="V61:V100" si="85">SUM(D61:F61)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W93" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" ref="W61:W100" si="86">SUM(G61:I61)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X93" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" ref="X61:X100" si="87">SUM(J61:L61)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y93" si="88">SUM(V61:X61)</f>
+        <f t="shared" ref="Y61:Y100" si="88">SUM(V61:X61)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7237,7 +7305,7 @@
         <v>58</v>
       </c>
       <c r="C62" s="151" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
@@ -7321,7 +7389,7 @@
         <v>59</v>
       </c>
       <c r="C63" s="151" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
@@ -7405,7 +7473,7 @@
         <v>60</v>
       </c>
       <c r="C64" s="151" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
@@ -7489,7 +7557,7 @@
         <v>61</v>
       </c>
       <c r="C65" s="151" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D65" s="75"/>
       <c r="E65" s="75"/>
@@ -7573,7 +7641,7 @@
         <v>62</v>
       </c>
       <c r="C66" s="151" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D66" s="75"/>
       <c r="E66" s="75"/>
@@ -7657,7 +7725,7 @@
         <v>63</v>
       </c>
       <c r="C67" s="151" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D67" s="75"/>
       <c r="E67" s="75"/>
@@ -7741,7 +7809,7 @@
         <v>64</v>
       </c>
       <c r="C68" s="151" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D68" s="75"/>
       <c r="E68" s="75"/>
@@ -7825,7 +7893,7 @@
         <v>65</v>
       </c>
       <c r="C69" s="151" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
@@ -7909,7 +7977,7 @@
         <v>66</v>
       </c>
       <c r="C70" s="151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
@@ -7993,7 +8061,7 @@
         <v>67</v>
       </c>
       <c r="C71" s="151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
@@ -8077,7 +8145,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="151" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
@@ -8161,7 +8229,7 @@
         <v>69</v>
       </c>
       <c r="C73" s="151" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D73" s="75"/>
       <c r="E73" s="75"/>
@@ -8245,7 +8313,7 @@
         <v>70</v>
       </c>
       <c r="C74" s="158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D74" s="75"/>
       <c r="E74" s="75"/>
@@ -8329,7 +8397,7 @@
         <v>71</v>
       </c>
       <c r="C75" s="158" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D75" s="75"/>
       <c r="E75" s="50"/>
@@ -8413,7 +8481,7 @@
         <v>72</v>
       </c>
       <c r="C76" s="158" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D76" s="75"/>
       <c r="E76" s="50"/>
@@ -8497,7 +8565,7 @@
         <v>73</v>
       </c>
       <c r="C77" s="158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D77" s="75"/>
       <c r="E77" s="50"/>
@@ -8581,7 +8649,7 @@
         <v>74</v>
       </c>
       <c r="C78" s="158" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D78" s="75"/>
       <c r="E78" s="50"/>
@@ -8663,7 +8731,7 @@
         <v>75</v>
       </c>
       <c r="C79" s="151" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D79" s="50"/>
       <c r="E79" s="50"/>
@@ -8744,33 +8812,33 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="151" t="s">
-        <v>165</v>
-      </c>
-      <c r="D80" s="50">
-        <v>40</v>
-      </c>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50">
-        <v>40</v>
-      </c>
-      <c r="H80" s="50">
-        <v>0</v>
-      </c>
-      <c r="I80" s="152">
+      <c r="C80" s="199" t="s">
+        <v>164</v>
+      </c>
+      <c r="D80" s="200">
+        <v>40</v>
+      </c>
+      <c r="E80" s="200"/>
+      <c r="F80" s="200"/>
+      <c r="G80" s="200">
+        <v>40</v>
+      </c>
+      <c r="H80" s="200">
+        <v>0</v>
+      </c>
+      <c r="I80" s="201">
         <v>120</v>
       </c>
-      <c r="J80" s="50">
+      <c r="J80" s="200">
         <v>200</v>
       </c>
-      <c r="K80" s="50">
-        <v>0</v>
-      </c>
-      <c r="L80" s="50">
+      <c r="K80" s="200">
+        <v>0</v>
+      </c>
+      <c r="L80" s="200">
         <v>200</v>
       </c>
-      <c r="M80" s="152">
+      <c r="M80" s="201">
         <f t="shared" si="81"/>
         <v>15</v>
       </c>
@@ -8828,29 +8896,29 @@
       <c r="B81" s="47">
         <v>77</v>
       </c>
-      <c r="C81" s="150" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="146"/>
-      <c r="E81" s="146"/>
-      <c r="F81" s="146"/>
-      <c r="G81" s="146">
-        <v>40</v>
-      </c>
-      <c r="H81" s="146">
-        <v>40</v>
-      </c>
-      <c r="I81" s="159"/>
-      <c r="J81" s="146">
-        <v>40</v>
-      </c>
-      <c r="K81" s="146">
-        <v>40</v>
-      </c>
-      <c r="L81" s="146">
-        <v>40</v>
-      </c>
-      <c r="M81" s="159">
+      <c r="C81" s="151" t="s">
+        <v>169</v>
+      </c>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
+      <c r="G81" s="50">
+        <v>40</v>
+      </c>
+      <c r="H81" s="50">
+        <v>40</v>
+      </c>
+      <c r="I81" s="152"/>
+      <c r="J81" s="50">
+        <v>40</v>
+      </c>
+      <c r="K81" s="50">
+        <v>40</v>
+      </c>
+      <c r="L81" s="50">
+        <v>40</v>
+      </c>
+      <c r="M81" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -8908,29 +8976,29 @@
       <c r="B82" s="47">
         <v>78</v>
       </c>
-      <c r="C82" s="150" t="s">
-        <v>171</v>
-      </c>
-      <c r="D82" s="146"/>
-      <c r="E82" s="146"/>
-      <c r="F82" s="146"/>
-      <c r="G82" s="146">
-        <v>80</v>
-      </c>
-      <c r="H82" s="146">
-        <v>80</v>
-      </c>
-      <c r="I82" s="159"/>
-      <c r="J82" s="146">
-        <v>80</v>
-      </c>
-      <c r="K82" s="146">
-        <v>80</v>
-      </c>
-      <c r="L82" s="146">
-        <v>80</v>
-      </c>
-      <c r="M82" s="159">
+      <c r="C82" s="151" t="s">
+        <v>170</v>
+      </c>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
+      <c r="G82" s="50">
+        <v>80</v>
+      </c>
+      <c r="H82" s="50">
+        <v>80</v>
+      </c>
+      <c r="I82" s="152"/>
+      <c r="J82" s="50">
+        <v>80</v>
+      </c>
+      <c r="K82" s="50">
+        <v>80</v>
+      </c>
+      <c r="L82" s="50">
+        <v>80</v>
+      </c>
+      <c r="M82" s="152">
         <f t="shared" si="81"/>
         <v>10</v>
       </c>
@@ -8988,29 +9056,29 @@
       <c r="B83" s="47">
         <v>79</v>
       </c>
-      <c r="C83" s="150" t="s">
-        <v>172</v>
-      </c>
-      <c r="D83" s="146"/>
-      <c r="E83" s="146"/>
-      <c r="F83" s="146"/>
-      <c r="G83" s="146">
-        <v>40</v>
-      </c>
-      <c r="H83" s="146">
-        <v>40</v>
-      </c>
-      <c r="I83" s="159"/>
-      <c r="J83" s="146">
-        <v>40</v>
-      </c>
-      <c r="K83" s="146">
-        <v>40</v>
-      </c>
-      <c r="L83" s="146">
-        <v>40</v>
-      </c>
-      <c r="M83" s="159">
+      <c r="C83" s="151" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50">
+        <v>40</v>
+      </c>
+      <c r="H83" s="50">
+        <v>40</v>
+      </c>
+      <c r="I83" s="152"/>
+      <c r="J83" s="50">
+        <v>40</v>
+      </c>
+      <c r="K83" s="50">
+        <v>40</v>
+      </c>
+      <c r="L83" s="50">
+        <v>40</v>
+      </c>
+      <c r="M83" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9065,30 +9133,32 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" s="78"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="150" t="s">
-        <v>173</v>
-      </c>
-      <c r="D84" s="146"/>
-      <c r="E84" s="146"/>
-      <c r="F84" s="146"/>
-      <c r="G84" s="146">
-        <v>80</v>
-      </c>
-      <c r="H84" s="146">
-        <v>80</v>
-      </c>
-      <c r="I84" s="159"/>
-      <c r="J84" s="146">
-        <v>80</v>
-      </c>
-      <c r="K84" s="146">
-        <v>80</v>
-      </c>
-      <c r="L84" s="146">
-        <v>80</v>
-      </c>
-      <c r="M84" s="159">
+      <c r="B84" s="47">
+        <v>80</v>
+      </c>
+      <c r="C84" s="151" t="s">
+        <v>172</v>
+      </c>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
+      <c r="G84" s="50">
+        <v>80</v>
+      </c>
+      <c r="H84" s="50">
+        <v>80</v>
+      </c>
+      <c r="I84" s="152"/>
+      <c r="J84" s="50">
+        <v>80</v>
+      </c>
+      <c r="K84" s="50">
+        <v>80</v>
+      </c>
+      <c r="L84" s="50">
+        <v>80</v>
+      </c>
+      <c r="M84" s="152">
         <f t="shared" si="81"/>
         <v>10</v>
       </c>
@@ -9107,30 +9177,32 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
-      <c r="B85" s="47"/>
-      <c r="C85" s="150" t="s">
-        <v>174</v>
-      </c>
-      <c r="D85" s="146"/>
-      <c r="E85" s="146"/>
-      <c r="F85" s="146"/>
-      <c r="G85" s="146">
-        <v>40</v>
-      </c>
-      <c r="H85" s="146">
-        <v>40</v>
-      </c>
-      <c r="I85" s="159"/>
-      <c r="J85" s="146">
-        <v>40</v>
-      </c>
-      <c r="K85" s="146">
-        <v>40</v>
-      </c>
-      <c r="L85" s="146">
-        <v>40</v>
-      </c>
-      <c r="M85" s="159">
+      <c r="B85" s="47">
+        <v>81</v>
+      </c>
+      <c r="C85" s="151" t="s">
+        <v>173</v>
+      </c>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
+      <c r="G85" s="50">
+        <v>40</v>
+      </c>
+      <c r="H85" s="50">
+        <v>40</v>
+      </c>
+      <c r="I85" s="152"/>
+      <c r="J85" s="50">
+        <v>40</v>
+      </c>
+      <c r="K85" s="50">
+        <v>40</v>
+      </c>
+      <c r="L85" s="50">
+        <v>40</v>
+      </c>
+      <c r="M85" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9149,30 +9221,32 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="150" t="s">
-        <v>175</v>
-      </c>
-      <c r="D86" s="146"/>
-      <c r="E86" s="146"/>
-      <c r="F86" s="146"/>
-      <c r="G86" s="146">
-        <v>40</v>
-      </c>
-      <c r="H86" s="146">
-        <v>40</v>
-      </c>
-      <c r="I86" s="159"/>
-      <c r="J86" s="146">
-        <v>40</v>
-      </c>
-      <c r="K86" s="146">
-        <v>40</v>
-      </c>
-      <c r="L86" s="146">
-        <v>40</v>
-      </c>
-      <c r="M86" s="159">
+      <c r="B86" s="47">
+        <v>82</v>
+      </c>
+      <c r="C86" s="151" t="s">
+        <v>174</v>
+      </c>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50">
+        <v>40</v>
+      </c>
+      <c r="H86" s="50">
+        <v>40</v>
+      </c>
+      <c r="I86" s="152"/>
+      <c r="J86" s="50">
+        <v>40</v>
+      </c>
+      <c r="K86" s="50">
+        <v>40</v>
+      </c>
+      <c r="L86" s="50">
+        <v>40</v>
+      </c>
+      <c r="M86" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9191,30 +9265,32 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="150" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="146"/>
-      <c r="E87" s="146"/>
-      <c r="F87" s="146"/>
-      <c r="G87" s="146">
-        <v>40</v>
-      </c>
-      <c r="H87" s="146">
-        <v>40</v>
-      </c>
-      <c r="I87" s="159"/>
-      <c r="J87" s="146">
-        <v>40</v>
-      </c>
-      <c r="K87" s="146">
-        <v>40</v>
-      </c>
-      <c r="L87" s="146">
-        <v>40</v>
-      </c>
-      <c r="M87" s="159">
+      <c r="B87" s="47">
+        <v>83</v>
+      </c>
+      <c r="C87" s="151" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50">
+        <v>40</v>
+      </c>
+      <c r="H87" s="50">
+        <v>40</v>
+      </c>
+      <c r="I87" s="152"/>
+      <c r="J87" s="50">
+        <v>40</v>
+      </c>
+      <c r="K87" s="50">
+        <v>40</v>
+      </c>
+      <c r="L87" s="50">
+        <v>40</v>
+      </c>
+      <c r="M87" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9233,30 +9309,32 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="78"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="150" t="s">
-        <v>177</v>
-      </c>
-      <c r="D88" s="146"/>
-      <c r="E88" s="146"/>
-      <c r="F88" s="146"/>
-      <c r="G88" s="146">
-        <v>40</v>
-      </c>
-      <c r="H88" s="146">
-        <v>40</v>
-      </c>
-      <c r="I88" s="159"/>
-      <c r="J88" s="146">
-        <v>40</v>
-      </c>
-      <c r="K88" s="146">
-        <v>40</v>
-      </c>
-      <c r="L88" s="146">
-        <v>40</v>
-      </c>
-      <c r="M88" s="159">
+      <c r="B88" s="47">
+        <v>84</v>
+      </c>
+      <c r="C88" s="151" t="s">
+        <v>176</v>
+      </c>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50">
+        <v>40</v>
+      </c>
+      <c r="H88" s="50">
+        <v>40</v>
+      </c>
+      <c r="I88" s="152"/>
+      <c r="J88" s="50">
+        <v>40</v>
+      </c>
+      <c r="K88" s="50">
+        <v>40</v>
+      </c>
+      <c r="L88" s="50">
+        <v>40</v>
+      </c>
+      <c r="M88" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9275,30 +9353,32 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
-      <c r="B89" s="47"/>
-      <c r="C89" s="150" t="s">
-        <v>178</v>
-      </c>
-      <c r="D89" s="146"/>
-      <c r="E89" s="146"/>
-      <c r="F89" s="146"/>
-      <c r="G89" s="146">
-        <v>40</v>
-      </c>
-      <c r="H89" s="146">
-        <v>40</v>
-      </c>
-      <c r="I89" s="159"/>
-      <c r="J89" s="146">
-        <v>40</v>
-      </c>
-      <c r="K89" s="146">
-        <v>40</v>
-      </c>
-      <c r="L89" s="146">
-        <v>40</v>
-      </c>
-      <c r="M89" s="159">
+      <c r="B89" s="47">
+        <v>85</v>
+      </c>
+      <c r="C89" s="151" t="s">
+        <v>177</v>
+      </c>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50">
+        <v>40</v>
+      </c>
+      <c r="H89" s="50">
+        <v>40</v>
+      </c>
+      <c r="I89" s="152"/>
+      <c r="J89" s="50">
+        <v>40</v>
+      </c>
+      <c r="K89" s="50">
+        <v>40</v>
+      </c>
+      <c r="L89" s="50">
+        <v>40</v>
+      </c>
+      <c r="M89" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9317,30 +9397,32 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
-      <c r="B90" s="47"/>
-      <c r="C90" s="150" t="s">
-        <v>179</v>
-      </c>
-      <c r="D90" s="146"/>
-      <c r="E90" s="146"/>
-      <c r="F90" s="146"/>
-      <c r="G90" s="146">
-        <v>40</v>
-      </c>
-      <c r="H90" s="146">
-        <v>40</v>
-      </c>
-      <c r="I90" s="159"/>
-      <c r="J90" s="146">
-        <v>40</v>
-      </c>
-      <c r="K90" s="146">
-        <v>40</v>
-      </c>
-      <c r="L90" s="146">
-        <v>40</v>
-      </c>
-      <c r="M90" s="159">
+      <c r="B90" s="47">
+        <v>86</v>
+      </c>
+      <c r="C90" s="151" t="s">
+        <v>178</v>
+      </c>
+      <c r="D90" s="50"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="50"/>
+      <c r="G90" s="50">
+        <v>40</v>
+      </c>
+      <c r="H90" s="50">
+        <v>40</v>
+      </c>
+      <c r="I90" s="152"/>
+      <c r="J90" s="50">
+        <v>40</v>
+      </c>
+      <c r="K90" s="50">
+        <v>40</v>
+      </c>
+      <c r="L90" s="50">
+        <v>40</v>
+      </c>
+      <c r="M90" s="152">
         <f t="shared" si="81"/>
         <v>5</v>
       </c>
@@ -9359,30 +9441,32 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
-      <c r="B91" s="47"/>
-      <c r="C91" s="150" t="s">
-        <v>169</v>
-      </c>
-      <c r="D91" s="146"/>
-      <c r="E91" s="146"/>
-      <c r="F91" s="146"/>
-      <c r="G91" s="146">
+      <c r="B91" s="47">
+        <v>87</v>
+      </c>
+      <c r="C91" s="151" t="s">
+        <v>168</v>
+      </c>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50">
         <v>84</v>
       </c>
-      <c r="H91" s="146">
+      <c r="H91" s="50">
         <v>84</v>
       </c>
-      <c r="I91" s="159"/>
-      <c r="J91" s="146">
+      <c r="I91" s="152"/>
+      <c r="J91" s="50">
         <v>168</v>
       </c>
-      <c r="K91" s="146">
+      <c r="K91" s="50">
         <v>126</v>
       </c>
-      <c r="L91" s="146">
+      <c r="L91" s="50">
         <v>252</v>
       </c>
-      <c r="M91" s="159">
+      <c r="M91" s="152">
         <f t="shared" si="81"/>
         <v>17.850000000000001</v>
       </c>
@@ -9401,20 +9485,36 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="78"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="151"/>
-      <c r="D92" s="50"/>
-      <c r="E92" s="50"/>
-      <c r="F92" s="50"/>
-      <c r="G92" s="50"/>
-      <c r="H92" s="50"/>
-      <c r="I92" s="152"/>
-      <c r="J92" s="50"/>
-      <c r="K92" s="50"/>
-      <c r="L92" s="50"/>
+      <c r="B92" s="47">
+        <v>88</v>
+      </c>
+      <c r="C92" s="150" t="s">
+        <v>183</v>
+      </c>
+      <c r="D92" s="146">
+        <v>80</v>
+      </c>
+      <c r="E92" s="146"/>
+      <c r="F92" s="146"/>
+      <c r="G92" s="146">
+        <v>80</v>
+      </c>
+      <c r="H92" s="146">
+        <v>80</v>
+      </c>
+      <c r="I92" s="159"/>
+      <c r="J92" s="146">
+        <v>80</v>
+      </c>
+      <c r="K92" s="146">
+        <v>80</v>
+      </c>
+      <c r="L92" s="146">
+        <v>80</v>
+      </c>
       <c r="M92" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N92" s="39"/>
       <c r="O92" s="49"/>
@@ -9432,194 +9532,117 @@
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="78"/>
       <c r="B93" s="47">
-        <v>80</v>
-      </c>
-      <c r="C93" s="151"/>
-      <c r="D93" s="50"/>
-      <c r="E93" s="50"/>
-      <c r="F93" s="50"/>
-      <c r="G93" s="50"/>
-      <c r="H93" s="50"/>
-      <c r="I93" s="152"/>
-      <c r="J93" s="50"/>
-      <c r="K93" s="50"/>
-      <c r="L93" s="50"/>
+        <v>89</v>
+      </c>
+      <c r="C93" s="150" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="146"/>
+      <c r="E93" s="146"/>
+      <c r="F93" s="146"/>
+      <c r="G93" s="146">
+        <v>80</v>
+      </c>
+      <c r="H93" s="146">
+        <v>80</v>
+      </c>
+      <c r="I93" s="159"/>
+      <c r="J93" s="146">
+        <v>80</v>
+      </c>
+      <c r="K93" s="146">
+        <v>80</v>
+      </c>
+      <c r="L93" s="146">
+        <v>80</v>
+      </c>
       <c r="M93" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N93" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O93" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P93" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="R93" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S93" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T93" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U93" s="53" t="e">
-        <f t="shared" si="84"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V93" s="54" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W93" s="55">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="X93" s="55">
-        <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="Y93" s="56" t="e">
-        <f t="shared" si="88"/>
-        <v>#VALUE!</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N93" s="39"/>
+      <c r="O93" s="49"/>
+      <c r="P93" s="73"/>
+      <c r="Q93" s="40"/>
+      <c r="R93" s="51"/>
+      <c r="S93" s="52"/>
+      <c r="T93" s="52"/>
+      <c r="U93" s="53"/>
+      <c r="V93" s="54"/>
+      <c r="W93" s="55"/>
+      <c r="X93" s="55"/>
+      <c r="Y93" s="56"/>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
-      <c r="B94" s="183" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94" s="184"/>
-      <c r="D94" s="88">
-        <f t="shared" ref="D94:L94" si="96">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E94" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="G94" s="88">
-        <f t="shared" si="96"/>
-        <v>7140</v>
-      </c>
-      <c r="H94" s="88">
-        <f t="shared" si="96"/>
-        <v>7657</v>
-      </c>
-      <c r="I94" s="88">
-        <f t="shared" si="96"/>
-        <v>10657</v>
-      </c>
-      <c r="J94" s="88">
-        <f t="shared" si="96"/>
-        <v>11297</v>
-      </c>
-      <c r="K94" s="88">
-        <f t="shared" si="96"/>
-        <v>9684</v>
-      </c>
-      <c r="L94" s="88">
-        <f t="shared" si="96"/>
-        <v>13219</v>
-      </c>
-      <c r="M94" s="48">
-        <f t="shared" ref="M94:M97" si="97">SUM(D94:L94)/40</f>
-        <v>1524.35</v>
-      </c>
-      <c r="N94" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O94" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P94" s="73">
-        <f t="shared" ref="P94:P98" si="98">SUM(G94:I94)/20</f>
-        <v>1272.7</v>
-      </c>
-      <c r="Q94" s="40">
-        <f t="shared" ref="Q94:Q98" si="99">SUM(J94:L94)/20</f>
-        <v>1710</v>
-      </c>
-      <c r="R94" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S94" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T94" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U94" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V94" s="54" t="e">
-        <f t="shared" ref="V94:V98" si="100">SUM(D94:F94)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W94" s="55">
-        <f t="shared" ref="W94:W98" si="101">SUM(G94:I94)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X94" s="55">
-        <f t="shared" ref="X94:X98" si="102">SUM(J94:L94)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y94" s="56" t="e">
-        <f t="shared" si="44"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B94" s="47">
+        <v>90</v>
+      </c>
+      <c r="C94" s="150" t="s">
+        <v>185</v>
+      </c>
+      <c r="D94" s="146"/>
+      <c r="E94" s="146"/>
+      <c r="F94" s="146"/>
+      <c r="G94" s="146">
+        <v>80</v>
+      </c>
+      <c r="H94" s="146">
+        <v>80</v>
+      </c>
+      <c r="I94" s="159"/>
+      <c r="J94" s="146">
+        <v>80</v>
+      </c>
+      <c r="K94" s="146">
+        <v>80</v>
+      </c>
+      <c r="L94" s="146">
+        <v>80</v>
+      </c>
+      <c r="M94" s="152">
+        <f t="shared" si="81"/>
+        <v>10</v>
+      </c>
+      <c r="N94" s="39"/>
+      <c r="O94" s="49"/>
+      <c r="P94" s="73"/>
+      <c r="Q94" s="40"/>
+      <c r="R94" s="51"/>
+      <c r="S94" s="52"/>
+      <c r="T94" s="52"/>
+      <c r="U94" s="53"/>
+      <c r="V94" s="54"/>
+      <c r="W94" s="55"/>
+      <c r="X94" s="55"/>
+      <c r="Y94" s="56"/>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="78"/>
-      <c r="B95" s="118">
-        <v>0</v>
-      </c>
-      <c r="C95" s="57" t="s">
+      <c r="B95" s="47">
         <v>91</v>
       </c>
-      <c r="D95" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E95" s="120"/>
-      <c r="F95" s="121"/>
-      <c r="G95" s="120"/>
-      <c r="H95" s="120"/>
-      <c r="I95" s="121"/>
-      <c r="J95" s="120">
-        <v>520</v>
-      </c>
-      <c r="K95" s="120">
-        <v>920</v>
-      </c>
-      <c r="L95" s="121">
-        <v>960</v>
-      </c>
-      <c r="M95" s="122">
-        <f>SUM(D95:L95)</f>
-        <v>4000</v>
+      <c r="C95" s="150" t="s">
+        <v>186</v>
+      </c>
+      <c r="D95" s="146"/>
+      <c r="E95" s="146"/>
+      <c r="F95" s="146"/>
+      <c r="G95" s="146"/>
+      <c r="H95" s="146"/>
+      <c r="I95" s="159"/>
+      <c r="J95" s="146">
+        <v>40</v>
+      </c>
+      <c r="K95" s="146">
+        <v>40</v>
+      </c>
+      <c r="L95" s="146">
+        <v>40</v>
+      </c>
+      <c r="M95" s="152">
+        <f t="shared" si="81"/>
+        <v>3</v>
       </c>
       <c r="N95" s="39"/>
       <c r="O95" s="49"/>
@@ -9637,375 +9660,732 @@
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="78"/>
       <c r="B96" s="47">
+        <v>92</v>
+      </c>
+      <c r="C96" s="150" t="s">
+        <v>166</v>
+      </c>
+      <c r="D96" s="146"/>
+      <c r="E96" s="146"/>
+      <c r="F96" s="146"/>
+      <c r="G96" s="146">
+        <v>80</v>
+      </c>
+      <c r="H96" s="146">
+        <v>80</v>
+      </c>
+      <c r="I96" s="159"/>
+      <c r="J96" s="146">
+        <v>80</v>
+      </c>
+      <c r="K96" s="146">
+        <v>80</v>
+      </c>
+      <c r="L96" s="146">
+        <v>80</v>
+      </c>
+      <c r="M96" s="152">
+        <f t="shared" si="81"/>
+        <v>10</v>
+      </c>
+      <c r="N96" s="39"/>
+      <c r="O96" s="49"/>
+      <c r="P96" s="73"/>
+      <c r="Q96" s="40"/>
+      <c r="R96" s="51"/>
+      <c r="S96" s="52"/>
+      <c r="T96" s="52"/>
+      <c r="U96" s="53"/>
+      <c r="V96" s="54"/>
+      <c r="W96" s="55"/>
+      <c r="X96" s="55"/>
+      <c r="Y96" s="56"/>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A97" s="78"/>
+      <c r="B97" s="47">
+        <v>93</v>
+      </c>
+      <c r="C97" s="196" t="s">
+        <v>181</v>
+      </c>
+      <c r="D97" s="197"/>
+      <c r="E97" s="197"/>
+      <c r="F97" s="197"/>
+      <c r="G97" s="197">
+        <v>80</v>
+      </c>
+      <c r="H97" s="197">
+        <v>80</v>
+      </c>
+      <c r="I97" s="198"/>
+      <c r="J97" s="197">
+        <v>80</v>
+      </c>
+      <c r="K97" s="197">
+        <v>120</v>
+      </c>
+      <c r="L97" s="197">
+        <v>80</v>
+      </c>
+      <c r="M97" s="152">
+        <f t="shared" si="81"/>
+        <v>11</v>
+      </c>
+      <c r="N97" s="39"/>
+      <c r="O97" s="49"/>
+      <c r="P97" s="73"/>
+      <c r="Q97" s="40"/>
+      <c r="R97" s="51"/>
+      <c r="S97" s="52"/>
+      <c r="T97" s="52"/>
+      <c r="U97" s="53"/>
+      <c r="V97" s="54"/>
+      <c r="W97" s="55"/>
+      <c r="X97" s="55"/>
+      <c r="Y97" s="56"/>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A98" s="78"/>
+      <c r="B98" s="47">
+        <v>94</v>
+      </c>
+      <c r="C98" s="151"/>
+      <c r="D98" s="50"/>
+      <c r="E98" s="50"/>
+      <c r="F98" s="50"/>
+      <c r="G98" s="50"/>
+      <c r="H98" s="50"/>
+      <c r="I98" s="152"/>
+      <c r="J98" s="50"/>
+      <c r="K98" s="50"/>
+      <c r="L98" s="50"/>
+      <c r="M98" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N98" s="39"/>
+      <c r="O98" s="49"/>
+      <c r="P98" s="73"/>
+      <c r="Q98" s="40"/>
+      <c r="R98" s="51"/>
+      <c r="S98" s="52"/>
+      <c r="T98" s="52"/>
+      <c r="U98" s="53"/>
+      <c r="V98" s="54"/>
+      <c r="W98" s="55"/>
+      <c r="X98" s="55"/>
+      <c r="Y98" s="56"/>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A99" s="78"/>
+      <c r="B99" s="47">
+        <v>95</v>
+      </c>
+      <c r="C99" s="151"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="152"/>
+      <c r="J99" s="50"/>
+      <c r="K99" s="50"/>
+      <c r="L99" s="50"/>
+      <c r="M99" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N99" s="39"/>
+      <c r="O99" s="49"/>
+      <c r="P99" s="73"/>
+      <c r="Q99" s="40"/>
+      <c r="R99" s="51"/>
+      <c r="S99" s="52"/>
+      <c r="T99" s="52"/>
+      <c r="U99" s="53"/>
+      <c r="V99" s="54"/>
+      <c r="W99" s="55"/>
+      <c r="X99" s="55"/>
+      <c r="Y99" s="56"/>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A100" s="78"/>
+      <c r="B100" s="47">
+        <v>96</v>
+      </c>
+      <c r="C100" s="151"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="152"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="50"/>
+      <c r="L100" s="50"/>
+      <c r="M100" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N100" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O100" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P100" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R100" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S100" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T100" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V100" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W100" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X100" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y100" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A101" s="78"/>
+      <c r="B101" s="174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" s="175"/>
+      <c r="D101" s="88">
+        <f t="shared" ref="D101:L101" si="96">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E101" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="88">
+        <f t="shared" si="96"/>
+        <v>7140</v>
+      </c>
+      <c r="H101" s="88">
+        <f t="shared" si="96"/>
+        <v>7657</v>
+      </c>
+      <c r="I101" s="88">
+        <f t="shared" si="96"/>
+        <v>10657</v>
+      </c>
+      <c r="J101" s="88">
+        <f t="shared" si="96"/>
+        <v>11297</v>
+      </c>
+      <c r="K101" s="88">
+        <f t="shared" si="96"/>
+        <v>9684</v>
+      </c>
+      <c r="L101" s="88">
+        <f t="shared" si="96"/>
+        <v>13219</v>
+      </c>
+      <c r="M101" s="48">
+        <f t="shared" ref="M101:M104" si="97">SUM(D101:L101)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N101" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O101" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P101" s="73">
+        <f t="shared" ref="P101:P105" si="98">SUM(G101:I101)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q101" s="40">
+        <f t="shared" ref="Q101:Q105" si="99">SUM(J101:L101)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R101" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S101" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T101" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U101" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V101" s="54" t="e">
+        <f t="shared" ref="V101:V105" si="100">SUM(D101:F101)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W101" s="55">
+        <f t="shared" ref="W101:W105" si="101">SUM(G101:I101)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X101" s="55">
+        <f t="shared" ref="X101:X105" si="102">SUM(J101:L101)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A102" s="78"/>
+      <c r="B102" s="118">
+        <v>0</v>
+      </c>
+      <c r="C102" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D102" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="120"/>
+      <c r="F102" s="121"/>
+      <c r="G102" s="120"/>
+      <c r="H102" s="120"/>
+      <c r="I102" s="121"/>
+      <c r="J102" s="120">
+        <v>520</v>
+      </c>
+      <c r="K102" s="120">
+        <v>920</v>
+      </c>
+      <c r="L102" s="121">
+        <v>960</v>
+      </c>
+      <c r="M102" s="122">
+        <f>SUM(D102:L102)</f>
+        <v>4000</v>
+      </c>
+      <c r="N102" s="39"/>
+      <c r="O102" s="49"/>
+      <c r="P102" s="73"/>
+      <c r="Q102" s="40"/>
+      <c r="R102" s="51"/>
+      <c r="S102" s="52"/>
+      <c r="T102" s="52"/>
+      <c r="U102" s="53"/>
+      <c r="V102" s="54"/>
+      <c r="W102" s="55"/>
+      <c r="X102" s="55"/>
+      <c r="Y102" s="56"/>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A103" s="78"/>
+      <c r="B103" s="47">
         <v>1</v>
       </c>
-      <c r="C96" s="57" t="s">
+      <c r="C103" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D96" s="74"/>
-      <c r="E96" s="75"/>
-      <c r="F96" s="76"/>
-      <c r="G96" s="50">
+      <c r="D103" s="74"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="76"/>
+      <c r="G103" s="50">
         <f>280+1600</f>
         <v>1880</v>
       </c>
-      <c r="H96" s="75">
+      <c r="H103" s="75">
         <f>0+600</f>
         <v>600</v>
       </c>
-      <c r="I96" s="49">
+      <c r="I103" s="49">
         <f>320+1800</f>
         <v>2120</v>
       </c>
-      <c r="J96" s="50">
+      <c r="J103" s="50">
         <f>600+2800</f>
         <v>3400</v>
       </c>
-      <c r="K96" s="75">
+      <c r="K103" s="75">
         <f>600+2400</f>
         <v>3000</v>
       </c>
-      <c r="L96" s="76">
+      <c r="L103" s="76">
         <f>2200+2800</f>
         <v>5000</v>
       </c>
-      <c r="M96" s="48">
+      <c r="M103" s="48">
         <f t="shared" si="97"/>
         <v>400</v>
       </c>
-      <c r="N96" s="39">
+      <c r="N103" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O96" s="49">
+      <c r="O103" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P96" s="73">
+      <c r="P103" s="73">
         <f t="shared" si="98"/>
         <v>230</v>
       </c>
-      <c r="Q96" s="40">
+      <c r="Q103" s="40">
         <f t="shared" si="99"/>
         <v>570</v>
       </c>
-      <c r="R96" s="51" t="e">
+      <c r="R103" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S96" s="52">
+      <c r="S103" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T96" s="52">
+      <c r="T103" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U96" s="53" t="e">
+      <c r="U103" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V96" s="54" t="e">
+      <c r="V103" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W96" s="55">
+      <c r="W103" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X96" s="55">
+      <c r="X103" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y96" s="56" t="e">
+      <c r="Y103" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="97" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B97" s="47">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B104" s="47">
         <v>2</v>
       </c>
-      <c r="C97" s="57" t="s">
+      <c r="C104" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D97" s="74">
+      <c r="D104" s="74">
         <v>1400</v>
       </c>
-      <c r="E97" s="75"/>
-      <c r="F97" s="76"/>
-      <c r="G97" s="50">
+      <c r="E104" s="75"/>
+      <c r="F104" s="76"/>
+      <c r="G104" s="50">
         <v>400</v>
       </c>
-      <c r="H97" s="75">
+      <c r="H104" s="75">
         <v>400</v>
       </c>
-      <c r="I97" s="49">
-        <v>0</v>
-      </c>
-      <c r="J97" s="50">
+      <c r="I104" s="49">
+        <v>0</v>
+      </c>
+      <c r="J104" s="50">
         <v>400</v>
       </c>
-      <c r="K97" s="75">
+      <c r="K104" s="75">
         <v>400</v>
       </c>
-      <c r="L97" s="76">
+      <c r="L104" s="76">
         <v>600</v>
       </c>
-      <c r="M97" s="48">
+      <c r="M104" s="48">
         <f t="shared" si="97"/>
         <v>90</v>
       </c>
-      <c r="N97" s="39">
+      <c r="N104" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O97" s="49">
+      <c r="O104" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P97" s="73">
+      <c r="P104" s="73">
         <f t="shared" si="98"/>
         <v>40</v>
       </c>
-      <c r="Q97" s="40">
+      <c r="Q104" s="40">
         <f t="shared" si="99"/>
         <v>70</v>
       </c>
-      <c r="R97" s="51" t="e">
+      <c r="R104" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S97" s="52">
+      <c r="S104" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T97" s="52">
+      <c r="T104" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U97" s="53" t="e">
+      <c r="U104" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V97" s="54" t="e">
+      <c r="V104" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W97" s="55">
+      <c r="W104" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X97" s="55">
+      <c r="X104" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y97" s="56" t="e">
+      <c r="Y104" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="98" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="171" t="s">
+    <row r="105" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B105" s="187" t="s">
         <v>93</v>
       </c>
-      <c r="C98" s="172"/>
-      <c r="D98" s="87">
-        <f>SUM(D96:D97)</f>
+      <c r="C105" s="188"/>
+      <c r="D105" s="87">
+        <f>SUM(D103:D104)</f>
         <v>1400</v>
       </c>
-      <c r="E98" s="87">
-        <f t="shared" ref="E98:L98" si="103">SUM(E96:E97)</f>
-        <v>0</v>
-      </c>
-      <c r="F98" s="87">
+      <c r="E105" s="87">
+        <f t="shared" ref="E105:L105" si="103">SUM(E103:E104)</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="87">
         <f t="shared" si="103"/>
         <v>0</v>
       </c>
-      <c r="G98" s="87">
+      <c r="G105" s="87">
         <f t="shared" si="103"/>
         <v>2280</v>
       </c>
-      <c r="H98" s="87">
+      <c r="H105" s="87">
         <f t="shared" si="103"/>
         <v>1000</v>
       </c>
-      <c r="I98" s="87">
+      <c r="I105" s="87">
         <f t="shared" si="103"/>
         <v>2120</v>
       </c>
-      <c r="J98" s="87">
+      <c r="J105" s="87">
         <f t="shared" si="103"/>
         <v>3800</v>
       </c>
-      <c r="K98" s="87">
+      <c r="K105" s="87">
         <f t="shared" si="103"/>
         <v>3400</v>
       </c>
-      <c r="L98" s="87">
+      <c r="L105" s="87">
         <f t="shared" si="103"/>
         <v>5600</v>
       </c>
-      <c r="M98" s="123">
-        <f>SUM(M95:M97)</f>
+      <c r="M105" s="123">
+        <f>SUM(M102:M104)</f>
         <v>4490</v>
       </c>
-      <c r="N98" s="59">
+      <c r="N105" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O98" s="58">
+      <c r="O105" s="58">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P98" s="73">
+      <c r="P105" s="73">
         <f t="shared" si="98"/>
         <v>270</v>
       </c>
-      <c r="Q98" s="40">
+      <c r="Q105" s="40">
         <f t="shared" si="99"/>
         <v>640</v>
       </c>
-      <c r="R98" s="51" t="e">
+      <c r="R105" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S98" s="52">
+      <c r="S105" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T98" s="52">
+      <c r="T105" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U98" s="53" t="e">
+      <c r="U105" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V98" s="54" t="e">
+      <c r="V105" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W98" s="55">
+      <c r="W105" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X98" s="55">
+      <c r="X105" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y98" s="56" t="e">
+      <c r="Y105" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B99" s="160" t="s">
+    <row r="106" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B106" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="C99" s="161"/>
-      <c r="D99" s="89">
-        <f>SUM(D94,D98)</f>
+      <c r="C106" s="177"/>
+      <c r="D106" s="89">
+        <f>SUM(D101,D105)</f>
         <v>2720</v>
       </c>
-      <c r="E99" s="89">
-        <f t="shared" ref="E99:L99" si="104">SUM(E94,E98)</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="89">
+      <c r="E106" s="89">
+        <f t="shared" ref="E106:L106" si="104">SUM(E101,E105)</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="89">
         <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="G99" s="89">
+      <c r="G106" s="89">
         <f t="shared" si="104"/>
         <v>9420</v>
       </c>
-      <c r="H99" s="89">
+      <c r="H106" s="89">
         <f t="shared" si="104"/>
         <v>8657</v>
       </c>
-      <c r="I99" s="89">
+      <c r="I106" s="89">
         <f t="shared" si="104"/>
         <v>12777</v>
       </c>
-      <c r="J99" s="89">
+      <c r="J106" s="89">
         <f t="shared" si="104"/>
         <v>15097</v>
       </c>
-      <c r="K99" s="89">
+      <c r="K106" s="89">
         <f t="shared" si="104"/>
         <v>13084</v>
       </c>
-      <c r="L99" s="89">
+      <c r="L106" s="89">
         <f t="shared" si="104"/>
         <v>18819</v>
       </c>
-      <c r="M99" s="60">
+      <c r="M106" s="60">
         <f t="shared" si="0"/>
         <v>2014.35</v>
       </c>
-      <c r="N99" s="63">
-        <f>SUM(N5:N98)</f>
-        <v>0</v>
-      </c>
-      <c r="O99" s="61">
-        <f t="shared" ref="O99:Y99" si="105">SUM(O5:O98)</f>
+      <c r="N106" s="63">
+        <f>SUM(N5:N105)</f>
+        <v>0</v>
+      </c>
+      <c r="O106" s="61">
+        <f t="shared" ref="O106:Y106" si="105">SUM(O5:O105)</f>
         <v>27856.920000000016</v>
       </c>
-      <c r="P99" s="62">
+      <c r="P106" s="62">
         <f t="shared" si="105"/>
         <v>3538.7</v>
       </c>
-      <c r="Q99" s="64">
+      <c r="Q106" s="64">
         <f t="shared" si="105"/>
         <v>5635.95</v>
       </c>
-      <c r="R99" s="65" t="e">
+      <c r="R106" s="65" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S99" s="66">
+      <c r="S106" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="T99" s="66">
+      <c r="T106" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="U99" s="67" t="e">
+      <c r="U106" s="67" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V99" s="68" t="e">
+      <c r="V106" s="68" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W99" s="69">
+      <c r="W106" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="X99" s="69">
+      <c r="X106" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="Y99" s="70" t="e">
+      <c r="Y106" s="70" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B105:C105"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B101:C101"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -10035,24 +10415,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="189" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="186"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="189" t="s">
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="191"/>
+      <c r="H3" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="190"/>
-      <c r="K3" s="191" t="s">
+      <c r="I3" s="194"/>
+      <c r="K3" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
+      <c r="L3" s="195"/>
+      <c r="M3" s="195"/>
+      <c r="N3" s="195"/>
+      <c r="O3" s="195"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="109"/>
@@ -10095,24 +10475,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="92">
-        <v>701</v>
+        <v>727</v>
       </c>
       <c r="E5" s="79">
-        <v>1802</v>
+        <v>1858</v>
       </c>
       <c r="F5" s="79">
         <v>590</v>
       </c>
       <c r="G5" s="112">
         <f>SUM(D5:F5)</f>
-        <v>3093</v>
+        <v>3175</v>
       </c>
       <c r="H5" s="105">
         <v>10000</v>
       </c>
       <c r="I5" s="106">
         <f>G5-H5</f>
-        <v>-6907</v>
+        <v>-6825</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -10137,11 +10517,11 @@
       </c>
       <c r="D6" s="114">
         <f>D5*40</f>
-        <v>28040</v>
+        <v>29080</v>
       </c>
       <c r="E6" s="115">
         <f>E5*40</f>
-        <v>72080</v>
+        <v>74320</v>
       </c>
       <c r="F6" s="115">
         <f>F5*40</f>
@@ -10149,7 +10529,7 @@
       </c>
       <c r="G6" s="116">
         <f>SUM(D6:F6)</f>
-        <v>123720</v>
+        <v>127000</v>
       </c>
       <c r="H6" s="107">
         <f>H5*40</f>
@@ -10157,7 +10537,7 @@
       </c>
       <c r="I6" s="108">
         <f>G6-H6</f>
-        <v>-276280</v>
+        <v>-273000</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -10222,11 +10602,11 @@
       </c>
       <c r="D9" s="117">
         <f>D8-D5</f>
-        <v>-701</v>
+        <v>-727</v>
       </c>
       <c r="E9" s="117">
         <f>E8-E5</f>
-        <v>-1802</v>
+        <v>-1858</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -10264,20 +10644,20 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="188" t="s">
+      <c r="C11" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="188"/>
-      <c r="F11" s="188" t="s">
+      <c r="D11" s="192"/>
+      <c r="F11" s="192" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="188"/>
+      <c r="G11" s="192"/>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I11">
         <f>D5/20</f>
-        <v>35.049999999999997</v>
+        <v>36.35</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
@@ -10308,7 +10688,7 @@
       </c>
       <c r="G12" s="101">
         <f>D12+G5</f>
-        <v>3593.9</v>
+        <v>3675.9</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -10340,7 +10720,7 @@
       </c>
       <c r="G13" s="101">
         <f>G12*40</f>
-        <v>143756</v>
+        <v>147036</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -10536,7 +10916,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -10585,11 +10965,11 @@
       <c r="J2" s="81">
         <v>20</v>
       </c>
-      <c r="K2" s="81" t="s">
-        <v>138</v>
+      <c r="K2" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -10603,11 +10983,11 @@
       <c r="J3" s="81">
         <v>22</v>
       </c>
-      <c r="K3" s="81" t="s">
-        <v>138</v>
+      <c r="K3" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -10621,11 +11001,11 @@
       <c r="J4" s="81">
         <v>114</v>
       </c>
-      <c r="K4" s="81" t="s">
-        <v>138</v>
+      <c r="K4" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -10639,11 +11019,11 @@
       <c r="J5" s="81">
         <v>60</v>
       </c>
-      <c r="K5" s="81" t="s">
-        <v>138</v>
+      <c r="K5" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -10657,11 +11037,11 @@
       <c r="J6" s="81">
         <v>15</v>
       </c>
-      <c r="K6" s="81" t="s">
-        <v>138</v>
+      <c r="K6" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -10675,11 +11055,11 @@
       <c r="J7" s="81">
         <v>60</v>
       </c>
-      <c r="K7" s="81" t="s">
-        <v>139</v>
+      <c r="K7" s="161" t="s">
+        <v>182</v>
       </c>
       <c r="L7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -10687,32 +11067,36 @@
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
       <c r="I8" s="81" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J8" s="81">
-        <v>13</v>
-      </c>
-      <c r="K8" s="81" t="s">
-        <v>139</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="K8" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L8" s="160"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="I9" s="81" t="s">
-        <v>169</v>
+      <c r="I9" s="163" t="s">
+        <v>162</v>
       </c>
       <c r="J9" s="81">
-        <v>18</v>
-      </c>
-      <c r="K9" s="81" t="s">
-        <v>139</v>
-      </c>
-      <c r="L9" t="s">
-        <v>159</v>
+        <v>13</v>
+      </c>
+      <c r="K9" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L9" s="160" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -10720,14 +11104,17 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="163" t="s">
         <v>133</v>
       </c>
       <c r="J10" s="81">
         <v>22</v>
       </c>
-      <c r="K10" s="81" t="s">
-        <v>139</v>
+      <c r="K10" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L10" s="160" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -10735,14 +11122,17 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="81" t="s">
-        <v>166</v>
+      <c r="I11" s="163" t="s">
+        <v>165</v>
       </c>
       <c r="J11" s="81">
         <v>3</v>
       </c>
-      <c r="K11" s="81" t="s">
-        <v>139</v>
+      <c r="K11" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" s="160" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -10750,14 +11140,17 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="81" t="s">
-        <v>167</v>
+      <c r="I12" s="163" t="s">
+        <v>166</v>
       </c>
       <c r="J12" s="81">
         <v>11</v>
       </c>
-      <c r="K12" s="81" t="s">
-        <v>139</v>
+      <c r="K12" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L12" s="160" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -10765,14 +11158,17 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="I13" s="81" t="s">
-        <v>133</v>
+      <c r="I13" s="163" t="s">
+        <v>181</v>
       </c>
       <c r="J13" s="81">
-        <v>80</v>
-      </c>
-      <c r="K13" s="81" t="s">
-        <v>139</v>
+        <v>12</v>
+      </c>
+      <c r="K13" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" s="160" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -10780,12 +11176,17 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
+      <c r="H14" t="s">
+        <v>191</v>
+      </c>
       <c r="I14" s="81" t="s">
-        <v>168</v>
-      </c>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="J14" s="81">
+        <v>80</v>
+      </c>
+      <c r="K14" s="162" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -10793,14 +11194,17 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
+      <c r="H15" t="s">
+        <v>191</v>
+      </c>
       <c r="I15" s="81" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J15" s="81">
-        <v>12</v>
-      </c>
-      <c r="K15" s="81" t="s">
-        <v>139</v>
+        <v>18</v>
+      </c>
+      <c r="K15" s="162" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -10808,27 +11212,48 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
+      <c r="H16" t="s">
+        <v>191</v>
+      </c>
+      <c r="I16" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="81">
+        <v>38</v>
+      </c>
+      <c r="K16" s="162" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
+      <c r="I17" s="81" t="s">
+        <v>179</v>
+      </c>
+      <c r="J17" s="81">
+        <v>45</v>
+      </c>
+      <c r="K17" s="162" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
+      <c r="I18" s="81" t="s">
+        <v>180</v>
+      </c>
+      <c r="J18" s="81">
+        <v>3</v>
+      </c>
+      <c r="K18" s="162" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
@@ -10837,22 +11262,70 @@
       <c r="D19" s="83"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
+      <c r="K19" s="162"/>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="84"/>
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
+      <c r="H20" t="s">
+        <v>191</v>
+      </c>
+      <c r="I20" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="J20" s="81">
+        <v>10</v>
+      </c>
+      <c r="K20" s="162" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I21" s="160" t="s">
+        <v>189</v>
+      </c>
+      <c r="J21" s="160">
+        <v>5</v>
+      </c>
+      <c r="K21" s="162" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H22" t="s">
+        <v>191</v>
+      </c>
+      <c r="I22" s="160" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22" s="160">
+        <v>5</v>
+      </c>
+      <c r="K22" s="162" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H23" t="s">
+        <v>191</v>
+      </c>
+      <c r="I23" s="160" t="s">
+        <v>190</v>
+      </c>
+      <c r="J23" s="160">
+        <v>8</v>
+      </c>
+      <c r="K23" s="162" t="s">
+        <v>138</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80DF3CCA-0793-4D04-8BF6-1A26354907F3}">
           <x14:formula1>
             <xm:f>Sheet1!$B$10:$B$22</xm:f>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633D7642-AC6E-470E-AF44-43B96832A85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB07E09-F59E-42D6-B944-D7EC0C3263A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="193">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Iqbal Town </t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1508,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1910,102 +1913,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2013,12 +1920,101 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2555,13 +2551,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="164">
+      <c r="B1" s="167">
         <v>46186</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2583,10 +2579,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="189" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="168" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2619,13 +2615,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="178"/>
-      <c r="N2" s="179"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="181" t="s">
+      <c r="M2" s="181"/>
+      <c r="N2" s="182"/>
+      <c r="O2" s="183"/>
+      <c r="P2" s="184" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="182"/>
+      <c r="Q2" s="185"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2644,8 +2640,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="186"/>
-      <c r="B3" s="166"/>
+      <c r="A3" s="189"/>
+      <c r="B3" s="169"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2676,29 +2672,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="183" t="s">
+      <c r="M3" s="186" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="184"/>
-      <c r="O3" s="185"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="188"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="168" t="s">
+      <c r="R3" s="171" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="169"/>
-      <c r="T3" s="169"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="171" t="s">
+      <c r="S3" s="172"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="173"/>
+      <c r="V3" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="173"/>
+      <c r="W3" s="175"/>
+      <c r="X3" s="175"/>
+      <c r="Y3" s="176"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="186"/>
-      <c r="B4" s="167"/>
+      <c r="A4" s="189"/>
+      <c r="B4" s="170"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -8812,33 +8808,33 @@
       <c r="B80" s="47">
         <v>76</v>
       </c>
-      <c r="C80" s="199" t="s">
+      <c r="C80" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="D80" s="200">
-        <v>40</v>
-      </c>
-      <c r="E80" s="200"/>
-      <c r="F80" s="200"/>
-      <c r="G80" s="200">
-        <v>40</v>
-      </c>
-      <c r="H80" s="200">
-        <v>0</v>
-      </c>
-      <c r="I80" s="201">
+      <c r="D80" s="50">
+        <v>40</v>
+      </c>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50">
+        <v>40</v>
+      </c>
+      <c r="H80" s="50">
+        <v>0</v>
+      </c>
+      <c r="I80" s="152">
         <v>120</v>
       </c>
-      <c r="J80" s="200">
+      <c r="J80" s="50">
         <v>200</v>
       </c>
-      <c r="K80" s="200">
-        <v>0</v>
-      </c>
-      <c r="L80" s="200">
+      <c r="K80" s="50">
+        <v>0</v>
+      </c>
+      <c r="L80" s="50">
         <v>200</v>
       </c>
-      <c r="M80" s="201">
+      <c r="M80" s="152">
         <f t="shared" si="81"/>
         <v>15</v>
       </c>
@@ -9706,26 +9702,26 @@
       <c r="B97" s="47">
         <v>93</v>
       </c>
-      <c r="C97" s="196" t="s">
+      <c r="C97" s="164" t="s">
         <v>181</v>
       </c>
-      <c r="D97" s="197"/>
-      <c r="E97" s="197"/>
-      <c r="F97" s="197"/>
-      <c r="G97" s="197">
-        <v>80</v>
-      </c>
-      <c r="H97" s="197">
-        <v>80</v>
-      </c>
-      <c r="I97" s="198"/>
-      <c r="J97" s="197">
-        <v>80</v>
-      </c>
-      <c r="K97" s="197">
+      <c r="D97" s="165"/>
+      <c r="E97" s="165"/>
+      <c r="F97" s="165"/>
+      <c r="G97" s="165">
+        <v>80</v>
+      </c>
+      <c r="H97" s="165">
+        <v>80</v>
+      </c>
+      <c r="I97" s="166"/>
+      <c r="J97" s="165">
+        <v>80</v>
+      </c>
+      <c r="K97" s="165">
         <v>120</v>
       </c>
-      <c r="L97" s="197">
+      <c r="L97" s="165">
         <v>80</v>
       </c>
       <c r="M97" s="152">
@@ -9879,10 +9875,10 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="78"/>
-      <c r="B101" s="174" t="s">
+      <c r="B101" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="C101" s="175"/>
+      <c r="C101" s="178"/>
       <c r="D101" s="88">
         <f t="shared" ref="D101:L101" si="96">SUM(D6:D60)</f>
         <v>1320</v>
@@ -10186,10 +10182,10 @@
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B105" s="187" t="s">
+      <c r="B105" s="190" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="188"/>
+      <c r="C105" s="191"/>
       <c r="D105" s="87">
         <f>SUM(D103:D104)</f>
         <v>1400</v>
@@ -10280,10 +10276,10 @@
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B106" s="176" t="s">
+      <c r="B106" s="179" t="s">
         <v>11</v>
       </c>
-      <c r="C106" s="177"/>
+      <c r="C106" s="180"/>
       <c r="D106" s="89">
         <f>SUM(D101,D105)</f>
         <v>2720</v>
@@ -10415,24 +10411,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="189" t="s">
+      <c r="C3" s="192" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="193" t="s">
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="196" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="194"/>
-      <c r="K3" s="195" t="s">
+      <c r="I3" s="197"/>
+      <c r="K3" s="198" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="195"/>
-      <c r="M3" s="195"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="195"/>
+      <c r="L3" s="198"/>
+      <c r="M3" s="198"/>
+      <c r="N3" s="198"/>
+      <c r="O3" s="198"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="109"/>
@@ -10644,14 +10640,14 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="192" t="s">
+      <c r="C11" s="195" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="192"/>
-      <c r="F11" s="192" t="s">
+      <c r="D11" s="195"/>
+      <c r="F11" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="192"/>
+      <c r="G11" s="195"/>
       <c r="H11" t="s">
         <v>157</v>
       </c>
@@ -10916,7 +10912,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43751F5-4C5F-4082-9A98-9CA12EDC5193}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
@@ -11318,6 +11314,31 @@
         <v>8</v>
       </c>
       <c r="K23" s="162" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H24" t="s">
+        <v>191</v>
+      </c>
+      <c r="I24" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" s="160">
+        <v>65</v>
+      </c>
+      <c r="K24" s="162" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I25" s="160" t="s">
+        <v>192</v>
+      </c>
+      <c r="J25" s="160">
+        <v>14</v>
+      </c>
+      <c r="K25" s="162" t="s">
         <v>138</v>
       </c>
     </row>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB07E09-F59E-42D6-B944-D7EC0C3263A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1D3042-47B3-4477-90AF-956ADA72F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="207">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -586,9 +586,6 @@
     <t>Jalal Sons Bahria Orchard</t>
   </si>
   <si>
-    <t>on the way</t>
-  </si>
-  <si>
     <t>Manawan Risen</t>
   </si>
   <si>
@@ -602,6 +599,51 @@
   </si>
   <si>
     <t xml:space="preserve">Raheem Iqbal Town </t>
+  </si>
+  <si>
+    <t>Gourmet Food Lider Pind LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food Bankers Co operative</t>
+  </si>
+  <si>
+    <t>Gourmet Food CANTT GIRJA CHOWK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food BHATTHA CHOWK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA FF BLOCK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA H BLOCK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA K BLOCK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA XX-3 BLOCK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food DHA Z BLOCK LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food NADRA ABAD LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food NISHAT COLONY LHR</t>
+  </si>
+  <si>
+    <t>Gourmet Food PUNJAB SOCIETY GHAZI ROAD LHR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on thy way </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Behria Orchard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalal Sons Lake City </t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2015,6 +2057,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2543,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y106"/>
+  <dimension ref="A1:Y124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2885,7 +2936,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M106" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M124" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2893,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O105" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O123" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2905,15 +2956,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R105" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R123" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S105" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S123" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T105" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T123" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -3061,7 +3112,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N105" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N123" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3501,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U105" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U123" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3517,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y105" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y123" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4177,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y101" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y119" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7241,7 +7292,7 @@
         <v>400</v>
       </c>
       <c r="M61" s="152">
-        <f t="shared" ref="M61:M100" si="81">SUM(D61:L61)/40</f>
+        <f t="shared" ref="M61:M118" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
       <c r="N61" s="39">
@@ -7253,11 +7304,11 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P100" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" ref="P61:P118" si="82">SUM(G61:I61)/20</f>
         <v>14</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q100" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" ref="Q61:Q118" si="83">SUM(J61:L61)/20</f>
         <v>30</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -7273,23 +7324,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U100" si="84">SUM(R61:T61)</f>
+        <f t="shared" ref="U61:U118" si="84">SUM(R61:T61)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V100" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" ref="V61:V118" si="85">SUM(D61:F61)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W100" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" ref="W61:W118" si="86">SUM(G61:I61)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X100" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" ref="X61:X118" si="87">SUM(J61:L61)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y100" si="88">SUM(V61:X61)</f>
+        <f t="shared" ref="Y61:Y118" si="88">SUM(V61:X61)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9742,23 +9793,37 @@
       <c r="Y97" s="56"/>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A98" s="78"/>
+      <c r="A98" s="78">
+        <v>46202</v>
+      </c>
       <c r="B98" s="47">
         <v>94</v>
       </c>
-      <c r="C98" s="151"/>
+      <c r="C98" s="151" t="s">
+        <v>192</v>
+      </c>
       <c r="D98" s="50"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
-      <c r="G98" s="50"/>
-      <c r="H98" s="50"/>
+      <c r="G98" s="50">
+        <v>40</v>
+      </c>
+      <c r="H98" s="50">
+        <v>40</v>
+      </c>
       <c r="I98" s="152"/>
-      <c r="J98" s="50"/>
-      <c r="K98" s="50"/>
-      <c r="L98" s="50"/>
+      <c r="J98" s="50">
+        <v>40</v>
+      </c>
+      <c r="K98" s="50">
+        <v>40</v>
+      </c>
+      <c r="L98" s="50">
+        <v>40</v>
+      </c>
       <c r="M98" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N98" s="39"/>
       <c r="O98" s="49"/>
@@ -9774,23 +9839,37 @@
       <c r="Y98" s="56"/>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A99" s="78"/>
+      <c r="A99" s="78">
+        <v>46202</v>
+      </c>
       <c r="B99" s="47">
         <v>95</v>
       </c>
-      <c r="C99" s="151"/>
+      <c r="C99" s="151" t="s">
+        <v>193</v>
+      </c>
       <c r="D99" s="50"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
-      <c r="H99" s="50"/>
+      <c r="G99" s="50">
+        <v>80</v>
+      </c>
+      <c r="H99" s="50">
+        <v>80</v>
+      </c>
       <c r="I99" s="152"/>
-      <c r="J99" s="50"/>
-      <c r="K99" s="50"/>
-      <c r="L99" s="50"/>
+      <c r="J99" s="50">
+        <v>80</v>
+      </c>
+      <c r="K99" s="50">
+        <v>80</v>
+      </c>
+      <c r="L99" s="50">
+        <v>80</v>
+      </c>
       <c r="M99" s="152">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N99" s="39"/>
       <c r="O99" s="49"/>
@@ -9806,11 +9885,15 @@
       <c r="Y99" s="56"/>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A100" s="78"/>
+      <c r="A100" s="78">
+        <v>46202</v>
+      </c>
       <c r="B100" s="47">
         <v>96</v>
       </c>
-      <c r="C100" s="151"/>
+      <c r="C100" s="151" t="s">
+        <v>194</v>
+      </c>
       <c r="D100" s="50"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
@@ -9824,178 +9907,97 @@
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="N100" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O100" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P100" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="R100" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S100" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T100" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U100" s="53" t="e">
-        <f t="shared" si="84"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V100" s="54" t="e">
-        <f t="shared" si="85"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W100" s="55">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-      <c r="X100" s="55">
-        <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-      <c r="Y100" s="56" t="e">
-        <f t="shared" si="88"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="N100" s="39"/>
+      <c r="O100" s="49"/>
+      <c r="P100" s="73"/>
+      <c r="Q100" s="40"/>
+      <c r="R100" s="51"/>
+      <c r="S100" s="52"/>
+      <c r="T100" s="52"/>
+      <c r="U100" s="53"/>
+      <c r="V100" s="54"/>
+      <c r="W100" s="55"/>
+      <c r="X100" s="55"/>
+      <c r="Y100" s="56"/>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A101" s="78"/>
-      <c r="B101" s="177" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101" s="178"/>
-      <c r="D101" s="88">
-        <f t="shared" ref="D101:L101" si="96">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E101" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="G101" s="88">
-        <f t="shared" si="96"/>
-        <v>7140</v>
-      </c>
-      <c r="H101" s="88">
-        <f t="shared" si="96"/>
-        <v>7657</v>
-      </c>
-      <c r="I101" s="88">
-        <f t="shared" si="96"/>
-        <v>10657</v>
-      </c>
-      <c r="J101" s="88">
-        <f t="shared" si="96"/>
-        <v>11297</v>
-      </c>
-      <c r="K101" s="88">
-        <f t="shared" si="96"/>
-        <v>9684</v>
-      </c>
-      <c r="L101" s="88">
-        <f t="shared" si="96"/>
-        <v>13219</v>
-      </c>
-      <c r="M101" s="48">
-        <f t="shared" ref="M101:M104" si="97">SUM(D101:L101)/40</f>
-        <v>1524.35</v>
-      </c>
-      <c r="N101" s="39">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="O101" s="49">
-        <f t="shared" si="1"/>
-        <v>331.63</v>
-      </c>
-      <c r="P101" s="73">
-        <f t="shared" ref="P101:P105" si="98">SUM(G101:I101)/20</f>
-        <v>1272.7</v>
-      </c>
-      <c r="Q101" s="40">
-        <f t="shared" ref="Q101:Q105" si="99">SUM(J101:L101)/20</f>
-        <v>1710</v>
-      </c>
-      <c r="R101" s="51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S101" s="52">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T101" s="52">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U101" s="53" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V101" s="54" t="e">
-        <f t="shared" ref="V101:V105" si="100">SUM(D101:F101)*$V$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W101" s="55">
-        <f t="shared" ref="W101:W105" si="101">SUM(G101:I101)*$W$3</f>
-        <v>0</v>
-      </c>
-      <c r="X101" s="55">
-        <f t="shared" ref="X101:X105" si="102">SUM(J101:L101)*$X$3</f>
-        <v>0</v>
-      </c>
-      <c r="Y101" s="56" t="e">
-        <f t="shared" si="44"/>
-        <v>#VALUE!</v>
-      </c>
+      <c r="A101" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B101" s="47">
+        <v>97</v>
+      </c>
+      <c r="C101" s="151" t="s">
+        <v>195</v>
+      </c>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50">
+        <v>40</v>
+      </c>
+      <c r="H101" s="50">
+        <v>40</v>
+      </c>
+      <c r="I101" s="152"/>
+      <c r="J101" s="50">
+        <v>40</v>
+      </c>
+      <c r="K101" s="50">
+        <v>40</v>
+      </c>
+      <c r="L101" s="50">
+        <v>40</v>
+      </c>
+      <c r="M101" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N101" s="39"/>
+      <c r="O101" s="49"/>
+      <c r="P101" s="73"/>
+      <c r="Q101" s="40"/>
+      <c r="R101" s="51"/>
+      <c r="S101" s="52"/>
+      <c r="T101" s="52"/>
+      <c r="U101" s="53"/>
+      <c r="V101" s="54"/>
+      <c r="W101" s="55"/>
+      <c r="X101" s="55"/>
+      <c r="Y101" s="56"/>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A102" s="78"/>
-      <c r="B102" s="118">
-        <v>0</v>
-      </c>
-      <c r="C102" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D102" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E102" s="120"/>
-      <c r="F102" s="121"/>
-      <c r="G102" s="120"/>
-      <c r="H102" s="120"/>
-      <c r="I102" s="121"/>
-      <c r="J102" s="120">
-        <v>520</v>
-      </c>
-      <c r="K102" s="120">
-        <v>920</v>
-      </c>
-      <c r="L102" s="121">
-        <v>960</v>
-      </c>
-      <c r="M102" s="122">
-        <f>SUM(D102:L102)</f>
-        <v>4000</v>
+      <c r="A102" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B102" s="47">
+        <v>98</v>
+      </c>
+      <c r="C102" s="151" t="s">
+        <v>196</v>
+      </c>
+      <c r="D102" s="50"/>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50"/>
+      <c r="G102" s="50">
+        <v>80</v>
+      </c>
+      <c r="H102" s="50">
+        <v>80</v>
+      </c>
+      <c r="I102" s="152"/>
+      <c r="J102" s="50">
+        <v>80</v>
+      </c>
+      <c r="K102" s="50">
+        <v>80</v>
+      </c>
+      <c r="L102" s="50">
+        <v>80</v>
+      </c>
+      <c r="M102" s="152">
+        <f t="shared" si="81"/>
+        <v>10</v>
       </c>
       <c r="N102" s="39"/>
       <c r="O102" s="49"/>
@@ -10011,377 +10013,1193 @@
       <c r="Y102" s="56"/>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A103" s="78"/>
+      <c r="A103" s="78">
+        <v>46202</v>
+      </c>
       <c r="B103" s="47">
+        <v>99</v>
+      </c>
+      <c r="C103" s="151" t="s">
+        <v>197</v>
+      </c>
+      <c r="D103" s="50"/>
+      <c r="E103" s="50"/>
+      <c r="F103" s="50"/>
+      <c r="G103" s="50">
+        <v>40</v>
+      </c>
+      <c r="H103" s="50">
+        <v>40</v>
+      </c>
+      <c r="I103" s="152"/>
+      <c r="J103" s="50">
+        <v>40</v>
+      </c>
+      <c r="K103" s="50">
+        <v>40</v>
+      </c>
+      <c r="L103" s="50">
+        <v>40</v>
+      </c>
+      <c r="M103" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N103" s="39"/>
+      <c r="O103" s="49"/>
+      <c r="P103" s="73"/>
+      <c r="Q103" s="40"/>
+      <c r="R103" s="51"/>
+      <c r="S103" s="52"/>
+      <c r="T103" s="52"/>
+      <c r="U103" s="53"/>
+      <c r="V103" s="54"/>
+      <c r="W103" s="55"/>
+      <c r="X103" s="55"/>
+      <c r="Y103" s="56"/>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A104" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B104" s="47">
+        <v>100</v>
+      </c>
+      <c r="C104" s="151" t="s">
+        <v>198</v>
+      </c>
+      <c r="D104" s="50"/>
+      <c r="E104" s="50"/>
+      <c r="F104" s="50"/>
+      <c r="G104" s="50">
+        <v>40</v>
+      </c>
+      <c r="H104" s="50">
+        <v>40</v>
+      </c>
+      <c r="I104" s="152"/>
+      <c r="J104" s="50">
+        <v>40</v>
+      </c>
+      <c r="K104" s="50">
+        <v>40</v>
+      </c>
+      <c r="L104" s="50">
+        <v>40</v>
+      </c>
+      <c r="M104" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N104" s="39"/>
+      <c r="O104" s="49"/>
+      <c r="P104" s="73"/>
+      <c r="Q104" s="40"/>
+      <c r="R104" s="51"/>
+      <c r="S104" s="52"/>
+      <c r="T104" s="52"/>
+      <c r="U104" s="53"/>
+      <c r="V104" s="54"/>
+      <c r="W104" s="55"/>
+      <c r="X104" s="55"/>
+      <c r="Y104" s="56"/>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A105" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B105" s="47">
+        <v>101</v>
+      </c>
+      <c r="C105" s="151" t="s">
+        <v>199</v>
+      </c>
+      <c r="D105" s="50"/>
+      <c r="E105" s="50"/>
+      <c r="F105" s="50"/>
+      <c r="G105" s="50">
+        <v>40</v>
+      </c>
+      <c r="H105" s="50">
+        <v>40</v>
+      </c>
+      <c r="I105" s="152"/>
+      <c r="J105" s="50">
+        <v>40</v>
+      </c>
+      <c r="K105" s="50">
+        <v>40</v>
+      </c>
+      <c r="L105" s="50">
+        <v>40</v>
+      </c>
+      <c r="M105" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N105" s="39"/>
+      <c r="O105" s="49"/>
+      <c r="P105" s="73"/>
+      <c r="Q105" s="40"/>
+      <c r="R105" s="51"/>
+      <c r="S105" s="52"/>
+      <c r="T105" s="52"/>
+      <c r="U105" s="53"/>
+      <c r="V105" s="54"/>
+      <c r="W105" s="55"/>
+      <c r="X105" s="55"/>
+      <c r="Y105" s="56"/>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A106" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B106" s="47">
+        <v>102</v>
+      </c>
+      <c r="C106" s="151" t="s">
+        <v>200</v>
+      </c>
+      <c r="D106" s="50"/>
+      <c r="E106" s="50"/>
+      <c r="F106" s="50"/>
+      <c r="G106" s="50">
+        <v>40</v>
+      </c>
+      <c r="H106" s="50">
+        <v>40</v>
+      </c>
+      <c r="I106" s="152"/>
+      <c r="J106" s="50">
+        <v>40</v>
+      </c>
+      <c r="K106" s="50">
+        <v>40</v>
+      </c>
+      <c r="L106" s="50">
+        <v>40</v>
+      </c>
+      <c r="M106" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N106" s="39"/>
+      <c r="O106" s="49"/>
+      <c r="P106" s="73"/>
+      <c r="Q106" s="40"/>
+      <c r="R106" s="51"/>
+      <c r="S106" s="52"/>
+      <c r="T106" s="52"/>
+      <c r="U106" s="53"/>
+      <c r="V106" s="54"/>
+      <c r="W106" s="55"/>
+      <c r="X106" s="55"/>
+      <c r="Y106" s="56"/>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A107" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B107" s="47">
+        <v>103</v>
+      </c>
+      <c r="C107" s="151" t="s">
+        <v>201</v>
+      </c>
+      <c r="D107" s="50"/>
+      <c r="E107" s="50"/>
+      <c r="F107" s="50"/>
+      <c r="G107" s="50">
+        <v>40</v>
+      </c>
+      <c r="H107" s="50">
+        <v>40</v>
+      </c>
+      <c r="I107" s="152"/>
+      <c r="J107" s="50">
+        <v>40</v>
+      </c>
+      <c r="K107" s="50">
+        <v>40</v>
+      </c>
+      <c r="L107" s="50">
+        <v>40</v>
+      </c>
+      <c r="M107" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N107" s="39"/>
+      <c r="O107" s="49"/>
+      <c r="P107" s="73"/>
+      <c r="Q107" s="40"/>
+      <c r="R107" s="51"/>
+      <c r="S107" s="52"/>
+      <c r="T107" s="52"/>
+      <c r="U107" s="53"/>
+      <c r="V107" s="54"/>
+      <c r="W107" s="55"/>
+      <c r="X107" s="55"/>
+      <c r="Y107" s="56"/>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A108" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B108" s="47">
+        <v>104</v>
+      </c>
+      <c r="C108" s="151" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" s="50"/>
+      <c r="E108" s="50"/>
+      <c r="F108" s="50"/>
+      <c r="G108" s="50">
+        <v>40</v>
+      </c>
+      <c r="H108" s="50">
+        <v>40</v>
+      </c>
+      <c r="I108" s="152"/>
+      <c r="J108" s="50">
+        <v>40</v>
+      </c>
+      <c r="K108" s="50">
+        <v>40</v>
+      </c>
+      <c r="L108" s="50">
+        <v>40</v>
+      </c>
+      <c r="M108" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N108" s="39"/>
+      <c r="O108" s="49"/>
+      <c r="P108" s="73"/>
+      <c r="Q108" s="40"/>
+      <c r="R108" s="51"/>
+      <c r="S108" s="52"/>
+      <c r="T108" s="52"/>
+      <c r="U108" s="53"/>
+      <c r="V108" s="54"/>
+      <c r="W108" s="55"/>
+      <c r="X108" s="55"/>
+      <c r="Y108" s="56"/>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A109" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B109" s="47">
+        <v>105</v>
+      </c>
+      <c r="C109" s="151" t="s">
+        <v>203</v>
+      </c>
+      <c r="D109" s="50"/>
+      <c r="E109" s="50"/>
+      <c r="F109" s="50"/>
+      <c r="G109" s="50">
+        <v>80</v>
+      </c>
+      <c r="H109" s="50">
+        <v>80</v>
+      </c>
+      <c r="I109" s="152"/>
+      <c r="J109" s="50">
+        <v>80</v>
+      </c>
+      <c r="K109" s="50">
+        <v>80</v>
+      </c>
+      <c r="L109" s="50">
+        <v>80</v>
+      </c>
+      <c r="M109" s="152">
+        <f t="shared" si="81"/>
+        <v>10</v>
+      </c>
+      <c r="N109" s="39"/>
+      <c r="O109" s="49"/>
+      <c r="P109" s="73"/>
+      <c r="Q109" s="40"/>
+      <c r="R109" s="51"/>
+      <c r="S109" s="52"/>
+      <c r="T109" s="52"/>
+      <c r="U109" s="53"/>
+      <c r="V109" s="54"/>
+      <c r="W109" s="55"/>
+      <c r="X109" s="55"/>
+      <c r="Y109" s="56"/>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A110" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B110" s="47">
+        <v>106</v>
+      </c>
+      <c r="C110" s="151" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" s="50"/>
+      <c r="E110" s="50"/>
+      <c r="F110" s="50"/>
+      <c r="G110" s="50">
+        <v>160</v>
+      </c>
+      <c r="H110" s="50">
+        <v>280</v>
+      </c>
+      <c r="I110" s="152"/>
+      <c r="J110" s="50">
+        <v>280</v>
+      </c>
+      <c r="K110" s="50">
+        <v>280</v>
+      </c>
+      <c r="L110" s="50">
+        <v>520</v>
+      </c>
+      <c r="M110" s="152">
+        <f t="shared" si="81"/>
+        <v>38</v>
+      </c>
+      <c r="N110" s="39"/>
+      <c r="O110" s="49"/>
+      <c r="P110" s="73"/>
+      <c r="Q110" s="40"/>
+      <c r="R110" s="51"/>
+      <c r="S110" s="52"/>
+      <c r="T110" s="52"/>
+      <c r="U110" s="53"/>
+      <c r="V110" s="54"/>
+      <c r="W110" s="55"/>
+      <c r="X110" s="55"/>
+      <c r="Y110" s="56"/>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A111" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B111" s="47">
+        <v>107</v>
+      </c>
+      <c r="C111" s="151" t="s">
+        <v>205</v>
+      </c>
+      <c r="D111" s="50"/>
+      <c r="E111" s="50"/>
+      <c r="F111" s="50"/>
+      <c r="G111" s="50"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="152"/>
+      <c r="J111" s="50">
+        <v>40</v>
+      </c>
+      <c r="K111" s="50">
+        <v>40</v>
+      </c>
+      <c r="L111" s="50">
+        <v>120</v>
+      </c>
+      <c r="M111" s="152">
+        <f t="shared" si="81"/>
+        <v>5</v>
+      </c>
+      <c r="N111" s="39"/>
+      <c r="O111" s="49"/>
+      <c r="P111" s="73"/>
+      <c r="Q111" s="40"/>
+      <c r="R111" s="51"/>
+      <c r="S111" s="52"/>
+      <c r="T111" s="52"/>
+      <c r="U111" s="53"/>
+      <c r="V111" s="54"/>
+      <c r="W111" s="55"/>
+      <c r="X111" s="55"/>
+      <c r="Y111" s="56"/>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A112" s="78">
+        <v>46202</v>
+      </c>
+      <c r="B112" s="47">
+        <v>108</v>
+      </c>
+      <c r="C112" s="151" t="s">
+        <v>206</v>
+      </c>
+      <c r="D112" s="50"/>
+      <c r="E112" s="50"/>
+      <c r="F112" s="50"/>
+      <c r="G112" s="50">
+        <v>80</v>
+      </c>
+      <c r="H112" s="50">
+        <v>40</v>
+      </c>
+      <c r="I112" s="152"/>
+      <c r="J112" s="50">
+        <v>80</v>
+      </c>
+      <c r="K112" s="50">
+        <v>40</v>
+      </c>
+      <c r="L112" s="50">
+        <v>80</v>
+      </c>
+      <c r="M112" s="152">
+        <f t="shared" si="81"/>
+        <v>8</v>
+      </c>
+      <c r="N112" s="39"/>
+      <c r="O112" s="49"/>
+      <c r="P112" s="73"/>
+      <c r="Q112" s="40"/>
+      <c r="R112" s="51"/>
+      <c r="S112" s="52"/>
+      <c r="T112" s="52"/>
+      <c r="U112" s="53"/>
+      <c r="V112" s="54"/>
+      <c r="W112" s="55"/>
+      <c r="X112" s="55"/>
+      <c r="Y112" s="56"/>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A113" s="78"/>
+      <c r="B113" s="47">
+        <v>109</v>
+      </c>
+      <c r="C113" s="151"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="50"/>
+      <c r="G113" s="50"/>
+      <c r="H113" s="50"/>
+      <c r="I113" s="152"/>
+      <c r="J113" s="50"/>
+      <c r="K113" s="50"/>
+      <c r="L113" s="50"/>
+      <c r="M113" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N113" s="39"/>
+      <c r="O113" s="49"/>
+      <c r="P113" s="73"/>
+      <c r="Q113" s="40"/>
+      <c r="R113" s="51"/>
+      <c r="S113" s="52"/>
+      <c r="T113" s="52"/>
+      <c r="U113" s="53"/>
+      <c r="V113" s="54"/>
+      <c r="W113" s="55"/>
+      <c r="X113" s="55"/>
+      <c r="Y113" s="56"/>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A114" s="78"/>
+      <c r="B114" s="47">
+        <v>110</v>
+      </c>
+      <c r="C114" s="151"/>
+      <c r="D114" s="50"/>
+      <c r="E114" s="50"/>
+      <c r="F114" s="50"/>
+      <c r="G114" s="50"/>
+      <c r="H114" s="50"/>
+      <c r="I114" s="152"/>
+      <c r="J114" s="50"/>
+      <c r="K114" s="50"/>
+      <c r="L114" s="50"/>
+      <c r="M114" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N114" s="39"/>
+      <c r="O114" s="49"/>
+      <c r="P114" s="73"/>
+      <c r="Q114" s="40"/>
+      <c r="R114" s="51"/>
+      <c r="S114" s="52"/>
+      <c r="T114" s="52"/>
+      <c r="U114" s="53"/>
+      <c r="V114" s="54"/>
+      <c r="W114" s="55"/>
+      <c r="X114" s="55"/>
+      <c r="Y114" s="56"/>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A115" s="78"/>
+      <c r="B115" s="47">
+        <v>111</v>
+      </c>
+      <c r="C115" s="151"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="50"/>
+      <c r="F115" s="50"/>
+      <c r="G115" s="50"/>
+      <c r="H115" s="50"/>
+      <c r="I115" s="152"/>
+      <c r="J115" s="50"/>
+      <c r="K115" s="50"/>
+      <c r="L115" s="50"/>
+      <c r="M115" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N115" s="39"/>
+      <c r="O115" s="49"/>
+      <c r="P115" s="73"/>
+      <c r="Q115" s="40"/>
+      <c r="R115" s="51"/>
+      <c r="S115" s="52"/>
+      <c r="T115" s="52"/>
+      <c r="U115" s="53"/>
+      <c r="V115" s="54"/>
+      <c r="W115" s="55"/>
+      <c r="X115" s="55"/>
+      <c r="Y115" s="56"/>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A116" s="78"/>
+      <c r="B116" s="47">
+        <v>112</v>
+      </c>
+      <c r="C116" s="151"/>
+      <c r="D116" s="50"/>
+      <c r="E116" s="50"/>
+      <c r="F116" s="50"/>
+      <c r="G116" s="50"/>
+      <c r="H116" s="50"/>
+      <c r="I116" s="152"/>
+      <c r="J116" s="50"/>
+      <c r="K116" s="50"/>
+      <c r="L116" s="50"/>
+      <c r="M116" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N116" s="39"/>
+      <c r="O116" s="49"/>
+      <c r="P116" s="73"/>
+      <c r="Q116" s="40"/>
+      <c r="R116" s="51"/>
+      <c r="S116" s="52"/>
+      <c r="T116" s="52"/>
+      <c r="U116" s="53"/>
+      <c r="V116" s="54"/>
+      <c r="W116" s="55"/>
+      <c r="X116" s="55"/>
+      <c r="Y116" s="56"/>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A117" s="78"/>
+      <c r="B117" s="47"/>
+      <c r="C117" s="151"/>
+      <c r="D117" s="50"/>
+      <c r="E117" s="50"/>
+      <c r="F117" s="50"/>
+      <c r="G117" s="50"/>
+      <c r="H117" s="50"/>
+      <c r="I117" s="152"/>
+      <c r="J117" s="50"/>
+      <c r="K117" s="50"/>
+      <c r="L117" s="50"/>
+      <c r="M117" s="152"/>
+      <c r="N117" s="39"/>
+      <c r="O117" s="49"/>
+      <c r="P117" s="73"/>
+      <c r="Q117" s="40"/>
+      <c r="R117" s="51"/>
+      <c r="S117" s="52"/>
+      <c r="T117" s="52"/>
+      <c r="U117" s="53"/>
+      <c r="V117" s="54"/>
+      <c r="W117" s="55"/>
+      <c r="X117" s="55"/>
+      <c r="Y117" s="56"/>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A118" s="78"/>
+      <c r="B118" s="47">
+        <v>96</v>
+      </c>
+      <c r="C118" s="151"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="50"/>
+      <c r="F118" s="50"/>
+      <c r="G118" s="50"/>
+      <c r="H118" s="50"/>
+      <c r="I118" s="152"/>
+      <c r="J118" s="50"/>
+      <c r="K118" s="50"/>
+      <c r="L118" s="50"/>
+      <c r="M118" s="152">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="N118" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O118" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P118" s="73">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Q118" s="40">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="R118" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S118" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T118" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U118" s="53" t="e">
+        <f t="shared" si="84"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V118" s="54" t="e">
+        <f t="shared" si="85"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W118" s="55">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="X118" s="55">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="Y118" s="56" t="e">
+        <f t="shared" si="88"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A119" s="78"/>
+      <c r="B119" s="177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="178"/>
+      <c r="D119" s="88">
+        <f t="shared" ref="D119:L119" si="96">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E119" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="88">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="88">
+        <f t="shared" si="96"/>
+        <v>7140</v>
+      </c>
+      <c r="H119" s="88">
+        <f t="shared" si="96"/>
+        <v>7657</v>
+      </c>
+      <c r="I119" s="88">
+        <f t="shared" si="96"/>
+        <v>10657</v>
+      </c>
+      <c r="J119" s="88">
+        <f t="shared" si="96"/>
+        <v>11297</v>
+      </c>
+      <c r="K119" s="88">
+        <f t="shared" si="96"/>
+        <v>9684</v>
+      </c>
+      <c r="L119" s="88">
+        <f t="shared" si="96"/>
+        <v>13219</v>
+      </c>
+      <c r="M119" s="48">
+        <f t="shared" ref="M119:M122" si="97">SUM(D119:L119)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N119" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O119" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P119" s="73">
+        <f t="shared" ref="P119:P123" si="98">SUM(G119:I119)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q119" s="40">
+        <f t="shared" ref="Q119:Q123" si="99">SUM(J119:L119)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R119" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S119" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T119" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U119" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V119" s="54" t="e">
+        <f t="shared" ref="V119:V123" si="100">SUM(D119:F119)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W119" s="55">
+        <f t="shared" ref="W119:W123" si="101">SUM(G119:I119)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X119" s="55">
+        <f t="shared" ref="X119:X123" si="102">SUM(J119:L119)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y119" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A120" s="78"/>
+      <c r="B120" s="118">
+        <v>0</v>
+      </c>
+      <c r="C120" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D120" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E120" s="120"/>
+      <c r="F120" s="121"/>
+      <c r="G120" s="120"/>
+      <c r="H120" s="120"/>
+      <c r="I120" s="121"/>
+      <c r="J120" s="120">
+        <v>520</v>
+      </c>
+      <c r="K120" s="120">
+        <v>920</v>
+      </c>
+      <c r="L120" s="121">
+        <v>960</v>
+      </c>
+      <c r="M120" s="122">
+        <f>SUM(D120:L120)</f>
+        <v>4000</v>
+      </c>
+      <c r="N120" s="39"/>
+      <c r="O120" s="49"/>
+      <c r="P120" s="73"/>
+      <c r="Q120" s="40"/>
+      <c r="R120" s="51"/>
+      <c r="S120" s="52"/>
+      <c r="T120" s="52"/>
+      <c r="U120" s="53"/>
+      <c r="V120" s="54"/>
+      <c r="W120" s="55"/>
+      <c r="X120" s="55"/>
+      <c r="Y120" s="56"/>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A121" s="78"/>
+      <c r="B121" s="47">
         <v>1</v>
       </c>
-      <c r="C103" s="57" t="s">
+      <c r="C121" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D103" s="74"/>
-      <c r="E103" s="75"/>
-      <c r="F103" s="76"/>
-      <c r="G103" s="50">
+      <c r="D121" s="74"/>
+      <c r="E121" s="75"/>
+      <c r="F121" s="76"/>
+      <c r="G121" s="50">
         <f>280+1600</f>
         <v>1880</v>
       </c>
-      <c r="H103" s="75">
+      <c r="H121" s="75">
         <f>0+600</f>
         <v>600</v>
       </c>
-      <c r="I103" s="49">
+      <c r="I121" s="49">
         <f>320+1800</f>
         <v>2120</v>
       </c>
-      <c r="J103" s="50">
+      <c r="J121" s="50">
         <f>600+2800</f>
         <v>3400</v>
       </c>
-      <c r="K103" s="75">
+      <c r="K121" s="75">
         <f>600+2400</f>
         <v>3000</v>
       </c>
-      <c r="L103" s="76">
+      <c r="L121" s="76">
         <f>2200+2800</f>
         <v>5000</v>
       </c>
-      <c r="M103" s="48">
+      <c r="M121" s="48">
         <f t="shared" si="97"/>
         <v>400</v>
       </c>
-      <c r="N103" s="39">
+      <c r="N121" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O103" s="49">
+      <c r="O121" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P103" s="73">
+      <c r="P121" s="73">
         <f t="shared" si="98"/>
         <v>230</v>
       </c>
-      <c r="Q103" s="40">
+      <c r="Q121" s="40">
         <f t="shared" si="99"/>
         <v>570</v>
       </c>
-      <c r="R103" s="51" t="e">
+      <c r="R121" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S103" s="52">
+      <c r="S121" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T103" s="52">
+      <c r="T121" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U103" s="53" t="e">
+      <c r="U121" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V103" s="54" t="e">
+      <c r="V121" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W103" s="55">
+      <c r="W121" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X103" s="55">
+      <c r="X121" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y103" s="56" t="e">
+      <c r="Y121" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="B104" s="47">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B122" s="47">
         <v>2</v>
       </c>
-      <c r="C104" s="57" t="s">
+      <c r="C122" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D104" s="74">
+      <c r="D122" s="74">
         <v>1400</v>
       </c>
-      <c r="E104" s="75"/>
-      <c r="F104" s="76"/>
-      <c r="G104" s="50">
+      <c r="E122" s="75"/>
+      <c r="F122" s="76"/>
+      <c r="G122" s="50">
         <v>400</v>
       </c>
-      <c r="H104" s="75">
+      <c r="H122" s="75">
         <v>400</v>
       </c>
-      <c r="I104" s="49">
-        <v>0</v>
-      </c>
-      <c r="J104" s="50">
+      <c r="I122" s="49">
+        <v>0</v>
+      </c>
+      <c r="J122" s="50">
         <v>400</v>
       </c>
-      <c r="K104" s="75">
+      <c r="K122" s="75">
         <v>400</v>
       </c>
-      <c r="L104" s="76">
+      <c r="L122" s="76">
         <v>600</v>
       </c>
-      <c r="M104" s="48">
+      <c r="M122" s="48">
         <f t="shared" si="97"/>
         <v>90</v>
       </c>
-      <c r="N104" s="39">
+      <c r="N122" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O104" s="49">
+      <c r="O122" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P104" s="73">
+      <c r="P122" s="73">
         <f t="shared" si="98"/>
         <v>40</v>
       </c>
-      <c r="Q104" s="40">
+      <c r="Q122" s="40">
         <f t="shared" si="99"/>
         <v>70</v>
       </c>
-      <c r="R104" s="51" t="e">
+      <c r="R122" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S104" s="52">
+      <c r="S122" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T104" s="52">
+      <c r="T122" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U104" s="53" t="e">
+      <c r="U122" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V104" s="54" t="e">
+      <c r="V122" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W104" s="55">
+      <c r="W122" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X104" s="55">
+      <c r="X122" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y104" s="56" t="e">
+      <c r="Y122" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B105" s="190" t="s">
+    <row r="123" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B123" s="190" t="s">
         <v>93</v>
       </c>
-      <c r="C105" s="191"/>
-      <c r="D105" s="87">
-        <f>SUM(D103:D104)</f>
+      <c r="C123" s="191"/>
+      <c r="D123" s="87">
+        <f>SUM(D121:D122)</f>
         <v>1400</v>
       </c>
-      <c r="E105" s="87">
-        <f t="shared" ref="E105:L105" si="103">SUM(E103:E104)</f>
-        <v>0</v>
-      </c>
-      <c r="F105" s="87">
+      <c r="E123" s="87">
+        <f t="shared" ref="E123:L123" si="103">SUM(E121:E122)</f>
+        <v>0</v>
+      </c>
+      <c r="F123" s="87">
         <f t="shared" si="103"/>
         <v>0</v>
       </c>
-      <c r="G105" s="87">
+      <c r="G123" s="87">
         <f t="shared" si="103"/>
         <v>2280</v>
       </c>
-      <c r="H105" s="87">
+      <c r="H123" s="87">
         <f t="shared" si="103"/>
         <v>1000</v>
       </c>
-      <c r="I105" s="87">
+      <c r="I123" s="87">
         <f t="shared" si="103"/>
         <v>2120</v>
       </c>
-      <c r="J105" s="87">
+      <c r="J123" s="87">
         <f t="shared" si="103"/>
         <v>3800</v>
       </c>
-      <c r="K105" s="87">
+      <c r="K123" s="87">
         <f t="shared" si="103"/>
         <v>3400</v>
       </c>
-      <c r="L105" s="87">
+      <c r="L123" s="87">
         <f t="shared" si="103"/>
         <v>5600</v>
       </c>
-      <c r="M105" s="123">
-        <f>SUM(M102:M104)</f>
+      <c r="M123" s="123">
+        <f>SUM(M120:M122)</f>
         <v>4490</v>
       </c>
-      <c r="N105" s="59">
+      <c r="N123" s="59">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O105" s="58">
+      <c r="O123" s="58">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
-      <c r="P105" s="73">
+      <c r="P123" s="73">
         <f t="shared" si="98"/>
         <v>270</v>
       </c>
-      <c r="Q105" s="40">
+      <c r="Q123" s="40">
         <f t="shared" si="99"/>
         <v>640</v>
       </c>
-      <c r="R105" s="51" t="e">
+      <c r="R123" s="51" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S105" s="52">
+      <c r="S123" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T105" s="52">
+      <c r="T123" s="52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U105" s="53" t="e">
+      <c r="U123" s="53" t="e">
         <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V105" s="54" t="e">
+      <c r="V123" s="54" t="e">
         <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W105" s="55">
+      <c r="W123" s="55">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="X105" s="55">
+      <c r="X123" s="55">
         <f t="shared" si="102"/>
         <v>0</v>
       </c>
-      <c r="Y105" s="56" t="e">
+      <c r="Y123" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B106" s="179" t="s">
+    <row r="124" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B124" s="179" t="s">
         <v>11</v>
       </c>
-      <c r="C106" s="180"/>
-      <c r="D106" s="89">
-        <f>SUM(D101,D105)</f>
+      <c r="C124" s="180"/>
+      <c r="D124" s="89">
+        <f>SUM(D119,D123)</f>
         <v>2720</v>
       </c>
-      <c r="E106" s="89">
-        <f t="shared" ref="E106:L106" si="104">SUM(E101,E105)</f>
-        <v>0</v>
-      </c>
-      <c r="F106" s="89">
+      <c r="E124" s="89">
+        <f t="shared" ref="E124:L124" si="104">SUM(E119,E123)</f>
+        <v>0</v>
+      </c>
+      <c r="F124" s="89">
         <f t="shared" si="104"/>
         <v>0</v>
       </c>
-      <c r="G106" s="89">
+      <c r="G124" s="89">
         <f t="shared" si="104"/>
         <v>9420</v>
       </c>
-      <c r="H106" s="89">
+      <c r="H124" s="89">
         <f t="shared" si="104"/>
         <v>8657</v>
       </c>
-      <c r="I106" s="89">
+      <c r="I124" s="89">
         <f t="shared" si="104"/>
         <v>12777</v>
       </c>
-      <c r="J106" s="89">
+      <c r="J124" s="89">
         <f t="shared" si="104"/>
         <v>15097</v>
       </c>
-      <c r="K106" s="89">
+      <c r="K124" s="89">
         <f t="shared" si="104"/>
         <v>13084</v>
       </c>
-      <c r="L106" s="89">
+      <c r="L124" s="89">
         <f t="shared" si="104"/>
         <v>18819</v>
       </c>
-      <c r="M106" s="60">
+      <c r="M124" s="60">
         <f t="shared" si="0"/>
         <v>2014.35</v>
       </c>
-      <c r="N106" s="63">
-        <f>SUM(N5:N105)</f>
-        <v>0</v>
-      </c>
-      <c r="O106" s="61">
-        <f t="shared" ref="O106:Y106" si="105">SUM(O5:O105)</f>
+      <c r="N124" s="63">
+        <f>SUM(N5:N123)</f>
+        <v>0</v>
+      </c>
+      <c r="O124" s="61">
+        <f t="shared" ref="O124:Y124" si="105">SUM(O5:O123)</f>
         <v>27856.920000000016</v>
       </c>
-      <c r="P106" s="62">
+      <c r="P124" s="62">
         <f t="shared" si="105"/>
         <v>3538.7</v>
       </c>
-      <c r="Q106" s="64">
+      <c r="Q124" s="64">
         <f t="shared" si="105"/>
         <v>5635.95</v>
       </c>
-      <c r="R106" s="65" t="e">
+      <c r="R124" s="65" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S106" s="66">
+      <c r="S124" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="T106" s="66">
+      <c r="T124" s="66">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="U106" s="67" t="e">
+      <c r="U124" s="67" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="V106" s="68" t="e">
+      <c r="V124" s="68" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
-      <c r="W106" s="69">
+      <c r="W124" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="X106" s="69">
+      <c r="X124" s="69">
         <f t="shared" si="105"/>
         <v>0</v>
       </c>
-      <c r="Y106" s="70" t="e">
+      <c r="Y124" s="70" t="e">
         <f t="shared" si="105"/>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B124:C124"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B123:C123"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B119:C119"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -10471,24 +11289,24 @@
         <v>58</v>
       </c>
       <c r="D5" s="92">
-        <v>727</v>
+        <v>757</v>
       </c>
       <c r="E5" s="79">
-        <v>1858</v>
+        <v>1979</v>
       </c>
       <c r="F5" s="79">
         <v>590</v>
       </c>
       <c r="G5" s="112">
         <f>SUM(D5:F5)</f>
-        <v>3175</v>
+        <v>3326</v>
       </c>
       <c r="H5" s="105">
         <v>10000</v>
       </c>
       <c r="I5" s="106">
         <f>G5-H5</f>
-        <v>-6825</v>
+        <v>-6674</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -10513,11 +11331,11 @@
       </c>
       <c r="D6" s="114">
         <f>D5*40</f>
-        <v>29080</v>
+        <v>30280</v>
       </c>
       <c r="E6" s="115">
         <f>E5*40</f>
-        <v>74320</v>
+        <v>79160</v>
       </c>
       <c r="F6" s="115">
         <f>F5*40</f>
@@ -10525,7 +11343,7 @@
       </c>
       <c r="G6" s="116">
         <f>SUM(D6:F6)</f>
-        <v>127000</v>
+        <v>133040</v>
       </c>
       <c r="H6" s="107">
         <f>H5*40</f>
@@ -10533,7 +11351,7 @@
       </c>
       <c r="I6" s="108">
         <f>G6-H6</f>
-        <v>-273000</v>
+        <v>-266960</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -10598,11 +11416,11 @@
       </c>
       <c r="D9" s="117">
         <f>D8-D5</f>
-        <v>-727</v>
+        <v>-757</v>
       </c>
       <c r="E9" s="117">
         <f>E8-E5</f>
-        <v>-1858</v>
+        <v>-1979</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -10653,7 +11471,7 @@
       </c>
       <c r="I11">
         <f>D5/20</f>
-        <v>36.35</v>
+        <v>37.85</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>7</v>
@@ -10684,7 +11502,7 @@
       </c>
       <c r="G12" s="101">
         <f>D12+G5</f>
-        <v>3675.9</v>
+        <v>3826.9</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -10716,7 +11534,7 @@
       </c>
       <c r="G13" s="101">
         <f>G12*40</f>
-        <v>147036</v>
+        <v>153076</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -11173,16 +11991,19 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="H14" t="s">
-        <v>191</v>
-      </c>
-      <c r="I14" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="I14" s="161" t="s">
         <v>133</v>
       </c>
       <c r="J14" s="81">
-        <v>80</v>
-      </c>
-      <c r="K14" s="162" t="s">
-        <v>187</v>
+        <v>70</v>
+      </c>
+      <c r="K14" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="200" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -11191,7 +12012,7 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="H15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I15" s="81" t="s">
         <v>167</v>
@@ -11209,19 +12030,22 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="H16" t="s">
-        <v>191</v>
-      </c>
-      <c r="I16" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="161" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="81">
         <v>38</v>
       </c>
-      <c r="K16" s="162" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K16" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L16" s="201" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -11236,7 +12060,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -11251,7 +12075,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
@@ -11260,16 +12084,13 @@
       <c r="J19" s="81"/>
       <c r="K19" s="162"/>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="84"/>
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
-      <c r="H20" t="s">
-        <v>191</v>
-      </c>
       <c r="I20" s="81" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J20" s="81">
         <v>10</v>
@@ -11278,9 +12099,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I21" s="160" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J21" s="160">
         <v>5</v>
@@ -11289,38 +12110,41 @@
         <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H22" t="s">
-        <v>191</v>
-      </c>
-      <c r="I22" s="160" t="s">
+        <v>190</v>
+      </c>
+      <c r="I22" s="199" t="s">
         <v>165</v>
       </c>
       <c r="J22" s="160">
         <v>5</v>
       </c>
-      <c r="K22" s="162" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K22" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H23" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="160" t="s">
         <v>190</v>
+      </c>
+      <c r="I23" s="199" t="s">
+        <v>189</v>
       </c>
       <c r="J23" s="160">
         <v>8</v>
       </c>
-      <c r="K23" s="162" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="H24" t="s">
-        <v>191</v>
-      </c>
+      <c r="K23" s="161" t="s">
+        <v>182</v>
+      </c>
+      <c r="L23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I24" s="160" t="s">
         <v>79</v>
       </c>
@@ -11328,18 +12152,18 @@
         <v>65</v>
       </c>
       <c r="K24" s="162" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="I25" s="160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J25" s="160">
         <v>14</v>
       </c>
       <c r="K25" s="162" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F1D3042-47B3-4477-90AF-956ADA72F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC83A0D-523F-4FAF-8483-ACFA88F6FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1550,7 +1550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1962,6 +1962,51 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1998,45 +2043,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2057,15 +2063,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2602,13 +2599,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="167">
+      <c r="B1" s="182">
         <v>46186</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="182"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2630,10 +2627,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="179" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="183" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2666,13 +2663,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="181"/>
-      <c r="N2" s="182"/>
-      <c r="O2" s="183"/>
-      <c r="P2" s="184" t="s">
+      <c r="M2" s="171"/>
+      <c r="N2" s="172"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="185"/>
+      <c r="Q2" s="175"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2691,8 +2688,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="189"/>
-      <c r="B3" s="169"/>
+      <c r="A3" s="179"/>
+      <c r="B3" s="184"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2723,29 +2720,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="186" t="s">
+      <c r="M3" s="176" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="187"/>
-      <c r="O3" s="188"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="178"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="171" t="s">
+      <c r="R3" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="172"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="173"/>
-      <c r="V3" s="174" t="s">
+      <c r="S3" s="187"/>
+      <c r="T3" s="187"/>
+      <c r="U3" s="188"/>
+      <c r="V3" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="175"/>
-      <c r="X3" s="175"/>
-      <c r="Y3" s="176"/>
+      <c r="W3" s="190"/>
+      <c r="X3" s="190"/>
+      <c r="Y3" s="191"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="189"/>
-      <c r="B4" s="170"/>
+      <c r="A4" s="179"/>
+      <c r="B4" s="185"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -10429,26 +10426,26 @@
       <c r="B112" s="47">
         <v>108</v>
       </c>
-      <c r="C112" s="151" t="s">
+      <c r="C112" s="164" t="s">
         <v>206</v>
       </c>
-      <c r="D112" s="50"/>
-      <c r="E112" s="50"/>
-      <c r="F112" s="50"/>
-      <c r="G112" s="50">
-        <v>80</v>
-      </c>
-      <c r="H112" s="50">
-        <v>40</v>
-      </c>
-      <c r="I112" s="152"/>
-      <c r="J112" s="50">
-        <v>80</v>
-      </c>
-      <c r="K112" s="50">
-        <v>40</v>
-      </c>
-      <c r="L112" s="50">
+      <c r="D112" s="165"/>
+      <c r="E112" s="165"/>
+      <c r="F112" s="165"/>
+      <c r="G112" s="165">
+        <v>80</v>
+      </c>
+      <c r="H112" s="165">
+        <v>40</v>
+      </c>
+      <c r="I112" s="166"/>
+      <c r="J112" s="165">
+        <v>80</v>
+      </c>
+      <c r="K112" s="165">
+        <v>40</v>
+      </c>
+      <c r="L112" s="165">
         <v>80</v>
       </c>
       <c r="M112" s="152">
@@ -10693,10 +10690,10 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" s="78"/>
-      <c r="B119" s="177" t="s">
+      <c r="B119" s="192" t="s">
         <v>11</v>
       </c>
-      <c r="C119" s="178"/>
+      <c r="C119" s="193"/>
       <c r="D119" s="88">
         <f t="shared" ref="D119:L119" si="96">SUM(D6:D60)</f>
         <v>1320</v>
@@ -11000,10 +10997,10 @@
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B123" s="190" t="s">
+      <c r="B123" s="180" t="s">
         <v>93</v>
       </c>
-      <c r="C123" s="191"/>
+      <c r="C123" s="181"/>
       <c r="D123" s="87">
         <f>SUM(D121:D122)</f>
         <v>1400</v>
@@ -11094,10 +11091,10 @@
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B124" s="179" t="s">
+      <c r="B124" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C124" s="180"/>
+      <c r="C124" s="170"/>
       <c r="D124" s="89">
         <f>SUM(D119,D123)</f>
         <v>2720</v>
@@ -11189,17 +11186,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B119:C119"/>
     <mergeCell ref="B124:C124"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B119:C119"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11229,24 +11226,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="192" t="s">
+      <c r="C3" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="193"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="196" t="s">
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="197"/>
-      <c r="K3" s="198" t="s">
+      <c r="I3" s="199"/>
+      <c r="K3" s="200" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="198"/>
-      <c r="M3" s="198"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="198"/>
+      <c r="L3" s="200"/>
+      <c r="M3" s="200"/>
+      <c r="N3" s="200"/>
+      <c r="O3" s="200"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="109"/>
@@ -11458,14 +11455,14 @@
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="195" t="s">
+      <c r="C11" s="197" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="195"/>
-      <c r="F11" s="195" t="s">
+      <c r="D11" s="197"/>
+      <c r="F11" s="197" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="195"/>
+      <c r="G11" s="197"/>
       <c r="H11" t="s">
         <v>157</v>
       </c>
@@ -12002,7 +11999,7 @@
       <c r="K14" s="161" t="s">
         <v>182</v>
       </c>
-      <c r="L14" s="200" t="s">
+      <c r="L14" s="160" t="s">
         <v>158</v>
       </c>
     </row>
@@ -12041,7 +12038,7 @@
       <c r="K16" s="161" t="s">
         <v>182</v>
       </c>
-      <c r="L16" s="201" t="s">
+      <c r="L16" s="168" t="s">
         <v>158</v>
       </c>
     </row>
@@ -12114,7 +12111,7 @@
       <c r="H22" t="s">
         <v>190</v>
       </c>
-      <c r="I22" s="199" t="s">
+      <c r="I22" s="167" t="s">
         <v>165</v>
       </c>
       <c r="J22" s="160">
@@ -12131,7 +12128,7 @@
       <c r="H23" t="s">
         <v>190</v>
       </c>
-      <c r="I23" s="199" t="s">
+      <c r="I23" s="167" t="s">
         <v>189</v>
       </c>
       <c r="J23" s="160">

--- a/LMT Orders.xlsx
+++ b/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC83A0D-523F-4FAF-8483-ACFA88F6FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD122D3-5B11-4587-B57D-7CE6B948E41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="218">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -644,6 +644,39 @@
   </si>
   <si>
     <t xml:space="preserve">Jalal Sons Lake City </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Iqbal Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Central Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Ghazi Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Ferozpur Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Ismail Nager Lahore</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Kahna </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Muslim Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Muslim Town Ayubia </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Pak Arab Society </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Walton Road </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gourmet Food Youhaba Abad</t>
   </si>
 </sst>
 </file>
@@ -2591,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y124"/>
+  <dimension ref="A1:Y137"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
@@ -2933,7 +2966,7 @@
         <v>800</v>
       </c>
       <c r="M6" s="48">
-        <f t="shared" ref="M6:M124" si="0">SUM(D6:L6)/40</f>
+        <f t="shared" ref="M6:M137" si="0">SUM(D6:L6)/40</f>
         <v>140</v>
       </c>
       <c r="N6" s="39">
@@ -2941,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="49">
-        <f t="shared" ref="O6:O123" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
+        <f t="shared" ref="O6:O136" si="1">SUMPRODUCT($D$3:$L$3,$D$6:$L$6)/1000</f>
         <v>331.63</v>
       </c>
       <c r="P6" s="73">
@@ -2953,15 +2986,15 @@
         <v>120</v>
       </c>
       <c r="R6" s="51" t="e">
-        <f t="shared" ref="R6:R123" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
+        <f t="shared" ref="R6:R136" si="4">SUMPRODUCT($D$4:$F$4,$D$6:$F$6)*$R$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="S6" s="52">
-        <f t="shared" ref="S6:S123" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
+        <f t="shared" ref="S6:S136" si="5">SUMPRODUCT($G$4:$I$4,$G$6:$I$6)*$S$3</f>
         <v>0</v>
       </c>
       <c r="T6" s="52">
-        <f t="shared" ref="T6:T123" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
+        <f t="shared" ref="T6:T136" si="6">SUMPRODUCT($J$4:$L$4,$J$6:$L$6)*$T$3</f>
         <v>0</v>
       </c>
       <c r="U6" s="53" t="e">
@@ -3109,7 +3142,7 @@
         <v>35</v>
       </c>
       <c r="N8" s="39">
-        <f t="shared" ref="N8:N123" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
+        <f t="shared" ref="N8:N136" si="18">SUMPRODUCT($D$4:$L$4,$D$6:$L$6)</f>
         <v>0</v>
       </c>
       <c r="O8" s="49">
@@ -3549,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="U13" s="53" t="e">
-        <f t="shared" ref="U13:U123" si="19">SUM(R13:T13)</f>
+        <f t="shared" ref="U13:U136" si="19">SUM(R13:T13)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V13" s="54" t="e">
@@ -3565,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="56" t="e">
-        <f t="shared" ref="Y13:Y123" si="20">SUM(V13:X13)</f>
+        <f t="shared" ref="Y13:Y136" si="20">SUM(V13:X13)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4225,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="56" t="e">
-        <f t="shared" ref="Y21:Y119" si="44">SUM(V21:X21)</f>
+        <f t="shared" ref="Y21:Y132" si="44">SUM(V21:X21)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -7289,7 +7322,7 @@
         <v>400</v>
       </c>
       <c r="M61" s="152">
-        <f t="shared" ref="M61:M118" si="81">SUM(D61:L61)/40</f>
+        <f t="shared" ref="M61:M83" si="81">SUM(D61:L61)/40</f>
         <v>22</v>
       </c>
       <c r="N61" s="39">
@@ -7301,11 +7334,11 @@
         <v>331.63</v>
       </c>
       <c r="P61" s="73">
-        <f t="shared" ref="P61:P118" si="82">SUM(G61:I61)/20</f>
+        <f t="shared" ref="P61:P78" si="82">SUM(G61:I61)/20</f>
         <v>14</v>
       </c>
       <c r="Q61" s="40">
-        <f t="shared" ref="Q61:Q118" si="83">SUM(J61:L61)/20</f>
+        <f t="shared" ref="Q61:Q78" si="83">SUM(J61:L61)/20</f>
         <v>30</v>
       </c>
       <c r="R61" s="51" t="e">
@@ -7321,23 +7354,23 @@
         <v>0</v>
       </c>
       <c r="U61" s="53" t="e">
-        <f t="shared" ref="U61:U118" si="84">SUM(R61:T61)</f>
+        <f t="shared" ref="U61:U78" si="84">SUM(R61:T61)</f>
         <v>#VALUE!</v>
       </c>
       <c r="V61" s="54" t="e">
-        <f t="shared" ref="V61:V118" si="85">SUM(D61:F61)*$V$3</f>
+        <f t="shared" ref="V61:V78" si="85">SUM(D61:F61)*$V$3</f>
         <v>#VALUE!</v>
       </c>
       <c r="W61" s="55">
-        <f t="shared" ref="W61:W118" si="86">SUM(G61:I61)*$W$3</f>
+        <f t="shared" ref="W61:W78" si="86">SUM(G61:I61)*$W$3</f>
         <v>0</v>
       </c>
       <c r="X61" s="55">
-        <f t="shared" ref="X61:X118" si="87">SUM(J61:L61)*$X$3</f>
+        <f t="shared" ref="X61:X78" si="87">SUM(J61:L61)*$X$3</f>
         <v>0</v>
       </c>
       <c r="Y61" s="56" t="e">
-        <f t="shared" ref="Y61:Y118" si="88">SUM(V61:X61)</f>
+        <f t="shared" ref="Y61:Y78" si="88">SUM(V61:X61)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -9203,21 +9236,57 @@
         <v>80</v>
       </c>
       <c r="M84" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="M84:M131" si="96">SUM(D84:L84)/40</f>
         <v>10</v>
       </c>
-      <c r="N84" s="39"/>
-      <c r="O84" s="49"/>
-      <c r="P84" s="73"/>
-      <c r="Q84" s="40"/>
-      <c r="R84" s="51"/>
-      <c r="S84" s="52"/>
-      <c r="T84" s="52"/>
-      <c r="U84" s="53"/>
-      <c r="V84" s="54"/>
-      <c r="W84" s="55"/>
-      <c r="X84" s="55"/>
-      <c r="Y84" s="56"/>
+      <c r="N84" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O84" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P84" s="73">
+        <f t="shared" ref="P84:P131" si="97">SUM(G84:I84)/20</f>
+        <v>8</v>
+      </c>
+      <c r="Q84" s="40">
+        <f t="shared" ref="Q84:Q131" si="98">SUM(J84:L84)/20</f>
+        <v>12</v>
+      </c>
+      <c r="R84" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S84" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T84" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U84" s="53" t="e">
+        <f t="shared" ref="U84:U131" si="99">SUM(R84:T84)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V84" s="54" t="e">
+        <f t="shared" ref="V84:V131" si="100">SUM(D84:F84)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W84" s="55">
+        <f t="shared" ref="W84:W131" si="101">SUM(G84:I84)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X84" s="55">
+        <f t="shared" ref="X84:X131" si="102">SUM(J84:L84)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="56" t="e">
+        <f t="shared" ref="Y84:Y131" si="103">SUM(V84:X84)</f>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" s="78"/>
@@ -9247,21 +9316,57 @@
         <v>40</v>
       </c>
       <c r="M85" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N85" s="39"/>
-      <c r="O85" s="49"/>
-      <c r="P85" s="73"/>
-      <c r="Q85" s="40"/>
-      <c r="R85" s="51"/>
-      <c r="S85" s="52"/>
-      <c r="T85" s="52"/>
-      <c r="U85" s="53"/>
-      <c r="V85" s="54"/>
-      <c r="W85" s="55"/>
-      <c r="X85" s="55"/>
-      <c r="Y85" s="56"/>
+      <c r="N85" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O85" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P85" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q85" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R85" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S85" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T85" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U85" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V85" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W85" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X85" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y85" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" s="78"/>
@@ -9291,21 +9396,57 @@
         <v>40</v>
       </c>
       <c r="M86" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N86" s="39"/>
-      <c r="O86" s="49"/>
-      <c r="P86" s="73"/>
-      <c r="Q86" s="40"/>
-      <c r="R86" s="51"/>
-      <c r="S86" s="52"/>
-      <c r="T86" s="52"/>
-      <c r="U86" s="53"/>
-      <c r="V86" s="54"/>
-      <c r="W86" s="55"/>
-      <c r="X86" s="55"/>
-      <c r="Y86" s="56"/>
+      <c r="N86" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O86" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P86" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q86" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R86" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S86" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T86" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U86" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V86" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W86" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X86" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y86" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" s="78"/>
@@ -9335,21 +9476,57 @@
         <v>40</v>
       </c>
       <c r="M87" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N87" s="39"/>
-      <c r="O87" s="49"/>
-      <c r="P87" s="73"/>
-      <c r="Q87" s="40"/>
-      <c r="R87" s="51"/>
-      <c r="S87" s="52"/>
-      <c r="T87" s="52"/>
-      <c r="U87" s="53"/>
-      <c r="V87" s="54"/>
-      <c r="W87" s="55"/>
-      <c r="X87" s="55"/>
-      <c r="Y87" s="56"/>
+      <c r="N87" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O87" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P87" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q87" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R87" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S87" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T87" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V87" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W87" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X87" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y87" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" s="78"/>
@@ -9379,21 +9556,57 @@
         <v>40</v>
       </c>
       <c r="M88" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N88" s="39"/>
-      <c r="O88" s="49"/>
-      <c r="P88" s="73"/>
-      <c r="Q88" s="40"/>
-      <c r="R88" s="51"/>
-      <c r="S88" s="52"/>
-      <c r="T88" s="52"/>
-      <c r="U88" s="53"/>
-      <c r="V88" s="54"/>
-      <c r="W88" s="55"/>
-      <c r="X88" s="55"/>
-      <c r="Y88" s="56"/>
+      <c r="N88" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O88" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P88" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q88" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R88" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S88" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T88" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V88" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W88" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X88" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y88" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" s="78"/>
@@ -9423,21 +9636,57 @@
         <v>40</v>
       </c>
       <c r="M89" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N89" s="39"/>
-      <c r="O89" s="49"/>
-      <c r="P89" s="73"/>
-      <c r="Q89" s="40"/>
-      <c r="R89" s="51"/>
-      <c r="S89" s="52"/>
-      <c r="T89" s="52"/>
-      <c r="U89" s="53"/>
-      <c r="V89" s="54"/>
-      <c r="W89" s="55"/>
-      <c r="X89" s="55"/>
-      <c r="Y89" s="56"/>
+      <c r="N89" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O89" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P89" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q89" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R89" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S89" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T89" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V89" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W89" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X89" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y89" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" s="78"/>
@@ -9467,21 +9716,57 @@
         <v>40</v>
       </c>
       <c r="M90" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N90" s="39"/>
-      <c r="O90" s="49"/>
-      <c r="P90" s="73"/>
-      <c r="Q90" s="40"/>
-      <c r="R90" s="51"/>
-      <c r="S90" s="52"/>
-      <c r="T90" s="52"/>
-      <c r="U90" s="53"/>
-      <c r="V90" s="54"/>
-      <c r="W90" s="55"/>
-      <c r="X90" s="55"/>
-      <c r="Y90" s="56"/>
+      <c r="N90" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O90" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P90" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q90" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R90" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S90" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T90" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V90" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W90" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X90" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" s="78"/>
@@ -9511,21 +9796,57 @@
         <v>252</v>
       </c>
       <c r="M91" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>17.850000000000001</v>
       </c>
-      <c r="N91" s="39"/>
-      <c r="O91" s="49"/>
-      <c r="P91" s="73"/>
-      <c r="Q91" s="40"/>
-      <c r="R91" s="51"/>
-      <c r="S91" s="52"/>
-      <c r="T91" s="52"/>
-      <c r="U91" s="53"/>
-      <c r="V91" s="54"/>
-      <c r="W91" s="55"/>
-      <c r="X91" s="55"/>
-      <c r="Y91" s="56"/>
+      <c r="N91" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O91" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P91" s="73">
+        <f t="shared" si="97"/>
+        <v>8.4</v>
+      </c>
+      <c r="Q91" s="40">
+        <f t="shared" si="98"/>
+        <v>27.3</v>
+      </c>
+      <c r="R91" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S91" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T91" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U91" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V91" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W91" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X91" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" s="78"/>
@@ -9557,21 +9878,57 @@
         <v>80</v>
       </c>
       <c r="M92" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>12</v>
       </c>
-      <c r="N92" s="39"/>
-      <c r="O92" s="49"/>
-      <c r="P92" s="73"/>
-      <c r="Q92" s="40"/>
-      <c r="R92" s="51"/>
-      <c r="S92" s="52"/>
-      <c r="T92" s="52"/>
-      <c r="U92" s="53"/>
-      <c r="V92" s="54"/>
-      <c r="W92" s="55"/>
-      <c r="X92" s="55"/>
-      <c r="Y92" s="56"/>
+      <c r="N92" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O92" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P92" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q92" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R92" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S92" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T92" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V92" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W92" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X92" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y92" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" s="78"/>
@@ -9601,21 +9958,57 @@
         <v>80</v>
       </c>
       <c r="M93" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N93" s="39"/>
-      <c r="O93" s="49"/>
-      <c r="P93" s="73"/>
-      <c r="Q93" s="40"/>
-      <c r="R93" s="51"/>
-      <c r="S93" s="52"/>
-      <c r="T93" s="52"/>
-      <c r="U93" s="53"/>
-      <c r="V93" s="54"/>
-      <c r="W93" s="55"/>
-      <c r="X93" s="55"/>
-      <c r="Y93" s="56"/>
+      <c r="N93" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O93" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P93" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q93" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R93" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S93" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T93" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V93" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W93" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X93" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y93" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" s="78"/>
@@ -9645,21 +10038,57 @@
         <v>80</v>
       </c>
       <c r="M94" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N94" s="39"/>
-      <c r="O94" s="49"/>
-      <c r="P94" s="73"/>
-      <c r="Q94" s="40"/>
-      <c r="R94" s="51"/>
-      <c r="S94" s="52"/>
-      <c r="T94" s="52"/>
-      <c r="U94" s="53"/>
-      <c r="V94" s="54"/>
-      <c r="W94" s="55"/>
-      <c r="X94" s="55"/>
-      <c r="Y94" s="56"/>
+      <c r="N94" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O94" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P94" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q94" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R94" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S94" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T94" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U94" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V94" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W94" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X94" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y94" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" s="78"/>
@@ -9685,21 +10114,57 @@
         <v>40</v>
       </c>
       <c r="M95" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>3</v>
       </c>
-      <c r="N95" s="39"/>
-      <c r="O95" s="49"/>
-      <c r="P95" s="73"/>
-      <c r="Q95" s="40"/>
-      <c r="R95" s="51"/>
-      <c r="S95" s="52"/>
-      <c r="T95" s="52"/>
-      <c r="U95" s="53"/>
-      <c r="V95" s="54"/>
-      <c r="W95" s="55"/>
-      <c r="X95" s="55"/>
-      <c r="Y95" s="56"/>
+      <c r="N95" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O95" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P95" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q95" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R95" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S95" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T95" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V95" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W95" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X95" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y95" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" s="78"/>
@@ -9729,21 +10194,57 @@
         <v>80</v>
       </c>
       <c r="M96" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N96" s="39"/>
-      <c r="O96" s="49"/>
-      <c r="P96" s="73"/>
-      <c r="Q96" s="40"/>
-      <c r="R96" s="51"/>
-      <c r="S96" s="52"/>
-      <c r="T96" s="52"/>
-      <c r="U96" s="53"/>
-      <c r="V96" s="54"/>
-      <c r="W96" s="55"/>
-      <c r="X96" s="55"/>
-      <c r="Y96" s="56"/>
+      <c r="N96" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O96" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P96" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q96" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R96" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S96" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T96" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V96" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W96" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X96" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y96" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" s="78"/>
@@ -9773,21 +10274,57 @@
         <v>80</v>
       </c>
       <c r="M97" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>11</v>
       </c>
-      <c r="N97" s="39"/>
-      <c r="O97" s="49"/>
-      <c r="P97" s="73"/>
-      <c r="Q97" s="40"/>
-      <c r="R97" s="51"/>
-      <c r="S97" s="52"/>
-      <c r="T97" s="52"/>
-      <c r="U97" s="53"/>
-      <c r="V97" s="54"/>
-      <c r="W97" s="55"/>
-      <c r="X97" s="55"/>
-      <c r="Y97" s="56"/>
+      <c r="N97" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O97" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P97" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q97" s="40">
+        <f t="shared" si="98"/>
+        <v>14</v>
+      </c>
+      <c r="R97" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S97" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T97" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U97" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V97" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W97" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X97" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y97" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" s="78">
@@ -9819,21 +10356,57 @@
         <v>40</v>
       </c>
       <c r="M98" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N98" s="39"/>
-      <c r="O98" s="49"/>
-      <c r="P98" s="73"/>
-      <c r="Q98" s="40"/>
-      <c r="R98" s="51"/>
-      <c r="S98" s="52"/>
-      <c r="T98" s="52"/>
-      <c r="U98" s="53"/>
-      <c r="V98" s="54"/>
-      <c r="W98" s="55"/>
-      <c r="X98" s="55"/>
-      <c r="Y98" s="56"/>
+      <c r="N98" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O98" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P98" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q98" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R98" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S98" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T98" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U98" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V98" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W98" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X98" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y98" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" s="78">
@@ -9865,21 +10438,57 @@
         <v>80</v>
       </c>
       <c r="M99" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N99" s="39"/>
-      <c r="O99" s="49"/>
-      <c r="P99" s="73"/>
-      <c r="Q99" s="40"/>
-      <c r="R99" s="51"/>
-      <c r="S99" s="52"/>
-      <c r="T99" s="52"/>
-      <c r="U99" s="53"/>
-      <c r="V99" s="54"/>
-      <c r="W99" s="55"/>
-      <c r="X99" s="55"/>
-      <c r="Y99" s="56"/>
+      <c r="N99" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O99" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P99" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q99" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R99" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S99" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T99" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U99" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V99" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W99" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X99" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y99" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" s="78">
@@ -9901,21 +10510,57 @@
       <c r="K100" s="50"/>
       <c r="L100" s="50"/>
       <c r="M100" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N100" s="39"/>
-      <c r="O100" s="49"/>
-      <c r="P100" s="73"/>
-      <c r="Q100" s="40"/>
-      <c r="R100" s="51"/>
-      <c r="S100" s="52"/>
-      <c r="T100" s="52"/>
-      <c r="U100" s="53"/>
-      <c r="V100" s="54"/>
-      <c r="W100" s="55"/>
-      <c r="X100" s="55"/>
-      <c r="Y100" s="56"/>
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N100" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O100" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P100" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R100" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S100" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T100" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U100" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V100" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W100" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X100" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y100" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" s="78">
@@ -9947,21 +10592,57 @@
         <v>40</v>
       </c>
       <c r="M101" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N101" s="39"/>
-      <c r="O101" s="49"/>
-      <c r="P101" s="73"/>
-      <c r="Q101" s="40"/>
-      <c r="R101" s="51"/>
-      <c r="S101" s="52"/>
-      <c r="T101" s="52"/>
-      <c r="U101" s="53"/>
-      <c r="V101" s="54"/>
-      <c r="W101" s="55"/>
-      <c r="X101" s="55"/>
-      <c r="Y101" s="56"/>
+      <c r="N101" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O101" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P101" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q101" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R101" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S101" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T101" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U101" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V101" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W101" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X101" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" s="78">
@@ -9993,21 +10674,57 @@
         <v>80</v>
       </c>
       <c r="M102" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N102" s="39"/>
-      <c r="O102" s="49"/>
-      <c r="P102" s="73"/>
-      <c r="Q102" s="40"/>
-      <c r="R102" s="51"/>
-      <c r="S102" s="52"/>
-      <c r="T102" s="52"/>
-      <c r="U102" s="53"/>
-      <c r="V102" s="54"/>
-      <c r="W102" s="55"/>
-      <c r="X102" s="55"/>
-      <c r="Y102" s="56"/>
+      <c r="N102" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O102" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P102" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q102" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R102" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S102" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T102" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U102" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V102" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W102" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X102" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y102" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" s="78">
@@ -10039,21 +10756,57 @@
         <v>40</v>
       </c>
       <c r="M103" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N103" s="39"/>
-      <c r="O103" s="49"/>
-      <c r="P103" s="73"/>
-      <c r="Q103" s="40"/>
-      <c r="R103" s="51"/>
-      <c r="S103" s="52"/>
-      <c r="T103" s="52"/>
-      <c r="U103" s="53"/>
-      <c r="V103" s="54"/>
-      <c r="W103" s="55"/>
-      <c r="X103" s="55"/>
-      <c r="Y103" s="56"/>
+      <c r="N103" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O103" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P103" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q103" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R103" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S103" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T103" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U103" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V103" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W103" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X103" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y103" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" s="78">
@@ -10085,21 +10838,57 @@
         <v>40</v>
       </c>
       <c r="M104" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N104" s="39"/>
-      <c r="O104" s="49"/>
-      <c r="P104" s="73"/>
-      <c r="Q104" s="40"/>
-      <c r="R104" s="51"/>
-      <c r="S104" s="52"/>
-      <c r="T104" s="52"/>
-      <c r="U104" s="53"/>
-      <c r="V104" s="54"/>
-      <c r="W104" s="55"/>
-      <c r="X104" s="55"/>
-      <c r="Y104" s="56"/>
+      <c r="N104" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O104" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P104" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q104" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R104" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S104" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T104" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U104" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V104" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W104" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X104" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y104" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" s="78">
@@ -10131,21 +10920,57 @@
         <v>40</v>
       </c>
       <c r="M105" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N105" s="39"/>
-      <c r="O105" s="49"/>
-      <c r="P105" s="73"/>
-      <c r="Q105" s="40"/>
-      <c r="R105" s="51"/>
-      <c r="S105" s="52"/>
-      <c r="T105" s="52"/>
-      <c r="U105" s="53"/>
-      <c r="V105" s="54"/>
-      <c r="W105" s="55"/>
-      <c r="X105" s="55"/>
-      <c r="Y105" s="56"/>
+      <c r="N105" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O105" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P105" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q105" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R105" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S105" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T105" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U105" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V105" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W105" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X105" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y105" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" s="78">
@@ -10177,21 +11002,57 @@
         <v>40</v>
       </c>
       <c r="M106" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N106" s="39"/>
-      <c r="O106" s="49"/>
-      <c r="P106" s="73"/>
-      <c r="Q106" s="40"/>
-      <c r="R106" s="51"/>
-      <c r="S106" s="52"/>
-      <c r="T106" s="52"/>
-      <c r="U106" s="53"/>
-      <c r="V106" s="54"/>
-      <c r="W106" s="55"/>
-      <c r="X106" s="55"/>
-      <c r="Y106" s="56"/>
+      <c r="N106" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O106" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P106" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q106" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R106" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S106" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T106" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U106" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V106" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W106" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X106" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y106" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" s="78">
@@ -10223,21 +11084,57 @@
         <v>40</v>
       </c>
       <c r="M107" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N107" s="39"/>
-      <c r="O107" s="49"/>
-      <c r="P107" s="73"/>
-      <c r="Q107" s="40"/>
-      <c r="R107" s="51"/>
-      <c r="S107" s="52"/>
-      <c r="T107" s="52"/>
-      <c r="U107" s="53"/>
-      <c r="V107" s="54"/>
-      <c r="W107" s="55"/>
-      <c r="X107" s="55"/>
-      <c r="Y107" s="56"/>
+      <c r="N107" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O107" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P107" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q107" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R107" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S107" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T107" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U107" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V107" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W107" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X107" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y107" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" s="78">
@@ -10269,21 +11166,57 @@
         <v>40</v>
       </c>
       <c r="M108" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N108" s="39"/>
-      <c r="O108" s="49"/>
-      <c r="P108" s="73"/>
-      <c r="Q108" s="40"/>
-      <c r="R108" s="51"/>
-      <c r="S108" s="52"/>
-      <c r="T108" s="52"/>
-      <c r="U108" s="53"/>
-      <c r="V108" s="54"/>
-      <c r="W108" s="55"/>
-      <c r="X108" s="55"/>
-      <c r="Y108" s="56"/>
+      <c r="N108" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O108" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P108" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q108" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R108" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S108" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T108" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U108" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V108" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W108" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X108" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y108" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" s="78">
@@ -10315,21 +11248,57 @@
         <v>80</v>
       </c>
       <c r="M109" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>10</v>
       </c>
-      <c r="N109" s="39"/>
-      <c r="O109" s="49"/>
-      <c r="P109" s="73"/>
-      <c r="Q109" s="40"/>
-      <c r="R109" s="51"/>
-      <c r="S109" s="52"/>
-      <c r="T109" s="52"/>
-      <c r="U109" s="53"/>
-      <c r="V109" s="54"/>
-      <c r="W109" s="55"/>
-      <c r="X109" s="55"/>
-      <c r="Y109" s="56"/>
+      <c r="N109" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O109" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P109" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q109" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R109" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S109" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T109" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U109" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V109" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W109" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X109" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y109" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" s="78">
@@ -10361,21 +11330,57 @@
         <v>520</v>
       </c>
       <c r="M110" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>38</v>
       </c>
-      <c r="N110" s="39"/>
-      <c r="O110" s="49"/>
-      <c r="P110" s="73"/>
-      <c r="Q110" s="40"/>
-      <c r="R110" s="51"/>
-      <c r="S110" s="52"/>
-      <c r="T110" s="52"/>
-      <c r="U110" s="53"/>
-      <c r="V110" s="54"/>
-      <c r="W110" s="55"/>
-      <c r="X110" s="55"/>
-      <c r="Y110" s="56"/>
+      <c r="N110" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P110" s="73">
+        <f t="shared" si="97"/>
+        <v>22</v>
+      </c>
+      <c r="Q110" s="40">
+        <f t="shared" si="98"/>
+        <v>54</v>
+      </c>
+      <c r="R110" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S110" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T110" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U110" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V110" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W110" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X110" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y110" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" s="78">
@@ -10403,21 +11408,57 @@
         <v>120</v>
       </c>
       <c r="M111" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="N111" s="39"/>
-      <c r="O111" s="49"/>
-      <c r="P111" s="73"/>
-      <c r="Q111" s="40"/>
-      <c r="R111" s="51"/>
-      <c r="S111" s="52"/>
-      <c r="T111" s="52"/>
-      <c r="U111" s="53"/>
-      <c r="V111" s="54"/>
-      <c r="W111" s="55"/>
-      <c r="X111" s="55"/>
-      <c r="Y111" s="56"/>
+      <c r="N111" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O111" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P111" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q111" s="40">
+        <f t="shared" si="98"/>
+        <v>10</v>
+      </c>
+      <c r="R111" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S111" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T111" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U111" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V111" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W111" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X111" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y111" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" s="78">
@@ -10449,195 +11490,500 @@
         <v>80</v>
       </c>
       <c r="M112" s="152">
-        <f t="shared" si="81"/>
+        <f t="shared" si="96"/>
         <v>8</v>
       </c>
-      <c r="N112" s="39"/>
-      <c r="O112" s="49"/>
-      <c r="P112" s="73"/>
-      <c r="Q112" s="40"/>
-      <c r="R112" s="51"/>
-      <c r="S112" s="52"/>
-      <c r="T112" s="52"/>
-      <c r="U112" s="53"/>
-      <c r="V112" s="54"/>
-      <c r="W112" s="55"/>
-      <c r="X112" s="55"/>
-      <c r="Y112" s="56"/>
+      <c r="N112" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O112" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P112" s="73">
+        <f t="shared" si="97"/>
+        <v>6</v>
+      </c>
+      <c r="Q112" s="40">
+        <f t="shared" si="98"/>
+        <v>10</v>
+      </c>
+      <c r="R112" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S112" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T112" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U112" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V112" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W112" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X112" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y112" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A113" s="78"/>
+      <c r="A113" s="78">
+        <v>46203</v>
+      </c>
       <c r="B113" s="47">
         <v>109</v>
       </c>
-      <c r="C113" s="151"/>
-      <c r="D113" s="50"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="50"/>
-      <c r="G113" s="50"/>
-      <c r="H113" s="50"/>
-      <c r="I113" s="152"/>
-      <c r="J113" s="50"/>
-      <c r="K113" s="50"/>
-      <c r="L113" s="50"/>
+      <c r="C113" s="150" t="s">
+        <v>207</v>
+      </c>
+      <c r="D113" s="146"/>
+      <c r="E113" s="146"/>
+      <c r="F113" s="146"/>
+      <c r="G113" s="146">
+        <v>40</v>
+      </c>
+      <c r="H113" s="146">
+        <v>40</v>
+      </c>
+      <c r="I113" s="159"/>
+      <c r="J113" s="146">
+        <v>40</v>
+      </c>
+      <c r="K113" s="146">
+        <v>40</v>
+      </c>
+      <c r="L113" s="146">
+        <v>40</v>
+      </c>
       <c r="M113" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N113" s="39"/>
-      <c r="O113" s="49"/>
-      <c r="P113" s="73"/>
-      <c r="Q113" s="40"/>
-      <c r="R113" s="51"/>
-      <c r="S113" s="52"/>
-      <c r="T113" s="52"/>
-      <c r="U113" s="53"/>
-      <c r="V113" s="54"/>
-      <c r="W113" s="55"/>
-      <c r="X113" s="55"/>
-      <c r="Y113" s="56"/>
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N113" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O113" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P113" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q113" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R113" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S113" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T113" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U113" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V113" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W113" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X113" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y113" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A114" s="78"/>
+      <c r="A114" s="78">
+        <v>46203</v>
+      </c>
       <c r="B114" s="47">
         <v>110</v>
       </c>
-      <c r="C114" s="151"/>
-      <c r="D114" s="50"/>
-      <c r="E114" s="50"/>
-      <c r="F114" s="50"/>
-      <c r="G114" s="50"/>
-      <c r="H114" s="50"/>
-      <c r="I114" s="152"/>
-      <c r="J114" s="50"/>
-      <c r="K114" s="50"/>
-      <c r="L114" s="50"/>
+      <c r="C114" s="150" t="s">
+        <v>208</v>
+      </c>
+      <c r="D114" s="146"/>
+      <c r="E114" s="146"/>
+      <c r="F114" s="146"/>
+      <c r="G114" s="146">
+        <v>80</v>
+      </c>
+      <c r="H114" s="146">
+        <v>80</v>
+      </c>
+      <c r="I114" s="159"/>
+      <c r="J114" s="146">
+        <v>80</v>
+      </c>
+      <c r="K114" s="146">
+        <v>80</v>
+      </c>
+      <c r="L114" s="146">
+        <v>80</v>
+      </c>
       <c r="M114" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N114" s="39"/>
-      <c r="O114" s="49"/>
-      <c r="P114" s="73"/>
-      <c r="Q114" s="40"/>
-      <c r="R114" s="51"/>
-      <c r="S114" s="52"/>
-      <c r="T114" s="52"/>
-      <c r="U114" s="53"/>
-      <c r="V114" s="54"/>
-      <c r="W114" s="55"/>
-      <c r="X114" s="55"/>
-      <c r="Y114" s="56"/>
+        <f t="shared" si="96"/>
+        <v>10</v>
+      </c>
+      <c r="N114" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O114" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P114" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q114" s="40">
+        <f t="shared" si="98"/>
+        <v>12</v>
+      </c>
+      <c r="R114" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S114" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T114" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U114" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V114" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W114" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X114" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y114" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A115" s="78"/>
+      <c r="A115" s="78">
+        <v>46203</v>
+      </c>
       <c r="B115" s="47">
         <v>111</v>
       </c>
-      <c r="C115" s="151"/>
-      <c r="D115" s="50"/>
-      <c r="E115" s="50"/>
-      <c r="F115" s="50"/>
-      <c r="G115" s="50"/>
-      <c r="H115" s="50"/>
-      <c r="I115" s="152"/>
-      <c r="J115" s="50"/>
-      <c r="K115" s="50"/>
-      <c r="L115" s="50"/>
+      <c r="C115" s="150" t="s">
+        <v>209</v>
+      </c>
+      <c r="D115" s="146"/>
+      <c r="E115" s="146"/>
+      <c r="F115" s="146"/>
+      <c r="G115" s="146">
+        <v>40</v>
+      </c>
+      <c r="H115" s="146">
+        <v>40</v>
+      </c>
+      <c r="I115" s="159"/>
+      <c r="J115" s="146">
+        <v>40</v>
+      </c>
+      <c r="K115" s="146">
+        <v>40</v>
+      </c>
+      <c r="L115" s="146">
+        <v>40</v>
+      </c>
       <c r="M115" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N115" s="39"/>
-      <c r="O115" s="49"/>
-      <c r="P115" s="73"/>
-      <c r="Q115" s="40"/>
-      <c r="R115" s="51"/>
-      <c r="S115" s="52"/>
-      <c r="T115" s="52"/>
-      <c r="U115" s="53"/>
-      <c r="V115" s="54"/>
-      <c r="W115" s="55"/>
-      <c r="X115" s="55"/>
-      <c r="Y115" s="56"/>
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N115" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O115" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P115" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q115" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R115" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S115" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T115" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U115" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V115" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W115" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X115" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y115" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A116" s="78"/>
+      <c r="A116" s="78">
+        <v>46203</v>
+      </c>
       <c r="B116" s="47">
         <v>112</v>
       </c>
-      <c r="C116" s="151"/>
-      <c r="D116" s="50"/>
-      <c r="E116" s="50"/>
-      <c r="F116" s="50"/>
-      <c r="G116" s="50"/>
-      <c r="H116" s="50"/>
-      <c r="I116" s="152"/>
-      <c r="J116" s="50"/>
-      <c r="K116" s="50"/>
-      <c r="L116" s="50"/>
+      <c r="C116" s="150" t="s">
+        <v>210</v>
+      </c>
+      <c r="D116" s="146"/>
+      <c r="E116" s="146"/>
+      <c r="F116" s="146"/>
+      <c r="G116" s="146">
+        <v>40</v>
+      </c>
+      <c r="H116" s="146">
+        <v>40</v>
+      </c>
+      <c r="I116" s="159"/>
+      <c r="J116" s="146">
+        <v>40</v>
+      </c>
+      <c r="K116" s="146">
+        <v>40</v>
+      </c>
+      <c r="L116" s="146">
+        <v>40</v>
+      </c>
       <c r="M116" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="N116" s="39"/>
-      <c r="O116" s="49"/>
-      <c r="P116" s="73"/>
-      <c r="Q116" s="40"/>
-      <c r="R116" s="51"/>
-      <c r="S116" s="52"/>
-      <c r="T116" s="52"/>
-      <c r="U116" s="53"/>
-      <c r="V116" s="54"/>
-      <c r="W116" s="55"/>
-      <c r="X116" s="55"/>
-      <c r="Y116" s="56"/>
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N116" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O116" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P116" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q116" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R116" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S116" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T116" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U116" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V116" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W116" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X116" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y116" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A117" s="78"/>
-      <c r="B117" s="47"/>
-      <c r="C117" s="151"/>
-      <c r="D117" s="50"/>
-      <c r="E117" s="50"/>
-      <c r="F117" s="50"/>
-      <c r="G117" s="50"/>
-      <c r="H117" s="50"/>
-      <c r="I117" s="152"/>
-      <c r="J117" s="50"/>
-      <c r="K117" s="50"/>
-      <c r="L117" s="50"/>
-      <c r="M117" s="152"/>
-      <c r="N117" s="39"/>
-      <c r="O117" s="49"/>
-      <c r="P117" s="73"/>
-      <c r="Q117" s="40"/>
-      <c r="R117" s="51"/>
-      <c r="S117" s="52"/>
-      <c r="T117" s="52"/>
-      <c r="U117" s="53"/>
-      <c r="V117" s="54"/>
-      <c r="W117" s="55"/>
-      <c r="X117" s="55"/>
-      <c r="Y117" s="56"/>
+      <c r="A117" s="78">
+        <v>46203</v>
+      </c>
+      <c r="B117" s="47">
+        <v>113</v>
+      </c>
+      <c r="C117" s="150" t="s">
+        <v>211</v>
+      </c>
+      <c r="D117" s="146"/>
+      <c r="E117" s="146"/>
+      <c r="F117" s="146"/>
+      <c r="G117" s="146">
+        <v>40</v>
+      </c>
+      <c r="H117" s="146">
+        <v>40</v>
+      </c>
+      <c r="I117" s="159"/>
+      <c r="J117" s="146">
+        <v>40</v>
+      </c>
+      <c r="K117" s="146">
+        <v>40</v>
+      </c>
+      <c r="L117" s="146">
+        <v>40</v>
+      </c>
+      <c r="M117" s="152">
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N117" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O117" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P117" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q117" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R117" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S117" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T117" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U117" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V117" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W117" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X117" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y117" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A118" s="78"/>
+      <c r="A118" s="78">
+        <v>46203</v>
+      </c>
       <c r="B118" s="47">
-        <v>96</v>
-      </c>
-      <c r="C118" s="151"/>
-      <c r="D118" s="50"/>
-      <c r="E118" s="50"/>
-      <c r="F118" s="50"/>
-      <c r="G118" s="50"/>
-      <c r="H118" s="50"/>
-      <c r="I118" s="152"/>
-      <c r="J118" s="50"/>
-      <c r="K118" s="50"/>
-      <c r="L118" s="50"/>
+        <v>114</v>
+      </c>
+      <c r="C118" s="150" t="s">
+        <v>212</v>
+      </c>
+      <c r="D118" s="146"/>
+      <c r="E118" s="146"/>
+      <c r="F118" s="146"/>
+      <c r="G118" s="146">
+        <v>40</v>
+      </c>
+      <c r="H118" s="146">
+        <v>40</v>
+      </c>
+      <c r="I118" s="159"/>
+      <c r="J118" s="146">
+        <v>40</v>
+      </c>
+      <c r="K118" s="146">
+        <v>40</v>
+      </c>
+      <c r="L118" s="146">
+        <v>40</v>
+      </c>
       <c r="M118" s="152">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <f t="shared" si="96"/>
+        <v>5</v>
       </c>
       <c r="N118" s="39">
         <f t="shared" si="18"/>
@@ -10648,12 +11994,12 @@
         <v>331.63</v>
       </c>
       <c r="P118" s="73">
-        <f t="shared" si="82"/>
-        <v>0</v>
+        <f t="shared" si="97"/>
+        <v>4</v>
       </c>
       <c r="Q118" s="40">
-        <f t="shared" si="83"/>
-        <v>0</v>
+        <f t="shared" si="98"/>
+        <v>6</v>
       </c>
       <c r="R118" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10668,71 +12014,58 @@
         <v>0</v>
       </c>
       <c r="U118" s="53" t="e">
-        <f t="shared" si="84"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V118" s="54" t="e">
-        <f t="shared" si="85"/>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="W118" s="55">
-        <f t="shared" si="86"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="X118" s="55">
-        <f t="shared" si="87"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="Y118" s="56" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="103"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A119" s="78"/>
-      <c r="B119" s="192" t="s">
-        <v>11</v>
-      </c>
-      <c r="C119" s="193"/>
-      <c r="D119" s="88">
-        <f t="shared" ref="D119:L119" si="96">SUM(D6:D60)</f>
-        <v>1320</v>
-      </c>
-      <c r="E119" s="88">
+      <c r="A119" s="78">
+        <v>46203</v>
+      </c>
+      <c r="B119" s="47">
+        <v>115</v>
+      </c>
+      <c r="C119" s="150" t="s">
+        <v>213</v>
+      </c>
+      <c r="D119" s="146"/>
+      <c r="E119" s="146"/>
+      <c r="F119" s="146"/>
+      <c r="G119" s="146">
+        <v>40</v>
+      </c>
+      <c r="H119" s="146">
+        <v>40</v>
+      </c>
+      <c r="I119" s="159"/>
+      <c r="J119" s="146">
+        <v>40</v>
+      </c>
+      <c r="K119" s="146">
+        <v>40</v>
+      </c>
+      <c r="L119" s="146">
+        <v>40</v>
+      </c>
+      <c r="M119" s="152">
         <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="F119" s="88">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-      <c r="G119" s="88">
-        <f t="shared" si="96"/>
-        <v>7140</v>
-      </c>
-      <c r="H119" s="88">
-        <f t="shared" si="96"/>
-        <v>7657</v>
-      </c>
-      <c r="I119" s="88">
-        <f t="shared" si="96"/>
-        <v>10657</v>
-      </c>
-      <c r="J119" s="88">
-        <f t="shared" si="96"/>
-        <v>11297</v>
-      </c>
-      <c r="K119" s="88">
-        <f t="shared" si="96"/>
-        <v>9684</v>
-      </c>
-      <c r="L119" s="88">
-        <f t="shared" si="96"/>
-        <v>13219</v>
-      </c>
-      <c r="M119" s="48">
-        <f t="shared" ref="M119:M122" si="97">SUM(D119:L119)/40</f>
-        <v>1524.35</v>
+        <v>5</v>
       </c>
       <c r="N119" s="39">
         <f t="shared" si="18"/>
@@ -10743,12 +12076,12 @@
         <v>331.63</v>
       </c>
       <c r="P119" s="73">
-        <f t="shared" ref="P119:P123" si="98">SUM(G119:I119)/20</f>
-        <v>1272.7</v>
+        <f t="shared" si="97"/>
+        <v>4</v>
       </c>
       <c r="Q119" s="40">
-        <f t="shared" ref="Q119:Q123" si="99">SUM(J119:L119)/20</f>
-        <v>1710</v>
+        <f t="shared" si="98"/>
+        <v>6</v>
       </c>
       <c r="R119" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10763,106 +12096,140 @@
         <v>0</v>
       </c>
       <c r="U119" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V119" s="54" t="e">
-        <f t="shared" ref="V119:V123" si="100">SUM(D119:F119)*$V$3</f>
+        <f t="shared" si="100"/>
         <v>#VALUE!</v>
       </c>
       <c r="W119" s="55">
-        <f t="shared" ref="W119:W123" si="101">SUM(G119:I119)*$W$3</f>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="X119" s="55">
-        <f t="shared" ref="X119:X123" si="102">SUM(J119:L119)*$X$3</f>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="Y119" s="56" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="103"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A120" s="78"/>
-      <c r="B120" s="118">
-        <v>0</v>
-      </c>
-      <c r="C120" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="D120" s="119">
-        <v>1600</v>
-      </c>
-      <c r="E120" s="120"/>
-      <c r="F120" s="121"/>
-      <c r="G120" s="120"/>
-      <c r="H120" s="120"/>
-      <c r="I120" s="121"/>
-      <c r="J120" s="120">
-        <v>520</v>
-      </c>
-      <c r="K120" s="120">
-        <v>920</v>
-      </c>
-      <c r="L120" s="121">
-        <v>960</v>
-      </c>
-      <c r="M120" s="122">
-        <f>SUM(D120:L120)</f>
-        <v>4000</v>
-      </c>
-      <c r="N120" s="39"/>
-      <c r="O120" s="49"/>
-      <c r="P120" s="73"/>
-      <c r="Q120" s="40"/>
-      <c r="R120" s="51"/>
-      <c r="S120" s="52"/>
-      <c r="T120" s="52"/>
-      <c r="U120" s="53"/>
-      <c r="V120" s="54"/>
-      <c r="W120" s="55"/>
-      <c r="X120" s="55"/>
-      <c r="Y120" s="56"/>
+      <c r="A120" s="78">
+        <v>46203</v>
+      </c>
+      <c r="B120" s="47">
+        <v>116</v>
+      </c>
+      <c r="C120" s="150" t="s">
+        <v>214</v>
+      </c>
+      <c r="D120" s="146"/>
+      <c r="E120" s="146"/>
+      <c r="F120" s="146"/>
+      <c r="G120" s="146">
+        <v>40</v>
+      </c>
+      <c r="H120" s="146">
+        <v>40</v>
+      </c>
+      <c r="I120" s="159"/>
+      <c r="J120" s="146">
+        <v>40</v>
+      </c>
+      <c r="K120" s="146">
+        <v>40</v>
+      </c>
+      <c r="L120" s="146">
+        <v>40</v>
+      </c>
+      <c r="M120" s="152">
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N120" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O120" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P120" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q120" s="40">
+        <f t="shared" si="98"/>
+        <v>6</v>
+      </c>
+      <c r="R120" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S120" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T120" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U120" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V120" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W120" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X120" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y120" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A121" s="78"/>
+      <c r="A121" s="78">
+        <v>46203</v>
+      </c>
       <c r="B121" s="47">
-        <v>1</v>
-      </c>
-      <c r="C121" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D121" s="74"/>
-      <c r="E121" s="75"/>
-      <c r="F121" s="76"/>
-      <c r="G121" s="50">
-        <f>280+1600</f>
-        <v>1880</v>
-      </c>
-      <c r="H121" s="75">
-        <f>0+600</f>
-        <v>600</v>
-      </c>
-      <c r="I121" s="49">
-        <f>320+1800</f>
-        <v>2120</v>
-      </c>
-      <c r="J121" s="50">
-        <f>600+2800</f>
-        <v>3400</v>
-      </c>
-      <c r="K121" s="75">
-        <f>600+2400</f>
-        <v>3000</v>
-      </c>
-      <c r="L121" s="76">
-        <f>2200+2800</f>
-        <v>5000</v>
-      </c>
-      <c r="M121" s="48">
-        <f t="shared" si="97"/>
-        <v>400</v>
+        <v>117</v>
+      </c>
+      <c r="C121" s="150" t="s">
+        <v>215</v>
+      </c>
+      <c r="D121" s="146"/>
+      <c r="E121" s="146"/>
+      <c r="F121" s="146"/>
+      <c r="G121" s="146">
+        <v>80</v>
+      </c>
+      <c r="H121" s="146">
+        <v>80</v>
+      </c>
+      <c r="I121" s="159"/>
+      <c r="J121" s="146">
+        <v>80</v>
+      </c>
+      <c r="K121" s="146">
+        <v>80</v>
+      </c>
+      <c r="L121" s="146">
+        <v>80</v>
+      </c>
+      <c r="M121" s="152">
+        <f t="shared" si="96"/>
+        <v>10</v>
       </c>
       <c r="N121" s="39">
         <f t="shared" si="18"/>
@@ -10873,12 +12240,12 @@
         <v>331.63</v>
       </c>
       <c r="P121" s="73">
+        <f t="shared" si="97"/>
+        <v>8</v>
+      </c>
+      <c r="Q121" s="40">
         <f t="shared" si="98"/>
-        <v>230</v>
-      </c>
-      <c r="Q121" s="40">
-        <f t="shared" si="99"/>
-        <v>570</v>
+        <v>12</v>
       </c>
       <c r="R121" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10893,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V121" s="54" t="e">
@@ -10909,43 +12276,42 @@
         <v>0</v>
       </c>
       <c r="Y121" s="56" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="103"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A122" s="78">
+        <v>46203</v>
+      </c>
       <c r="B122" s="47">
-        <v>2</v>
-      </c>
-      <c r="C122" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="D122" s="74">
-        <v>1400</v>
-      </c>
-      <c r="E122" s="75"/>
-      <c r="F122" s="76"/>
-      <c r="G122" s="50">
-        <v>400</v>
-      </c>
-      <c r="H122" s="75">
-        <v>400</v>
-      </c>
-      <c r="I122" s="49">
-        <v>0</v>
-      </c>
-      <c r="J122" s="50">
-        <v>400</v>
-      </c>
-      <c r="K122" s="75">
-        <v>400</v>
-      </c>
-      <c r="L122" s="76">
-        <v>600</v>
-      </c>
-      <c r="M122" s="48">
-        <f t="shared" si="97"/>
-        <v>90</v>
+        <v>118</v>
+      </c>
+      <c r="C122" s="150" t="s">
+        <v>216</v>
+      </c>
+      <c r="D122" s="146"/>
+      <c r="E122" s="146"/>
+      <c r="F122" s="146"/>
+      <c r="G122" s="146">
+        <v>40</v>
+      </c>
+      <c r="H122" s="146">
+        <v>40</v>
+      </c>
+      <c r="I122" s="159"/>
+      <c r="J122" s="146">
+        <v>40</v>
+      </c>
+      <c r="K122" s="146">
+        <v>40</v>
+      </c>
+      <c r="L122" s="146">
+        <v>40</v>
+      </c>
+      <c r="M122" s="152">
+        <f t="shared" si="96"/>
+        <v>5</v>
       </c>
       <c r="N122" s="39">
         <f t="shared" si="18"/>
@@ -10956,12 +12322,12 @@
         <v>331.63</v>
       </c>
       <c r="P122" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q122" s="40">
         <f t="shared" si="98"/>
-        <v>40</v>
-      </c>
-      <c r="Q122" s="40">
-        <f t="shared" si="99"/>
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="R122" s="51" t="e">
         <f t="shared" si="4"/>
@@ -10976,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V122" s="54" t="e">
@@ -10992,70 +12358,58 @@
         <v>0</v>
       </c>
       <c r="Y122" s="56" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="123" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B123" s="180" t="s">
-        <v>93</v>
-      </c>
-      <c r="C123" s="181"/>
-      <c r="D123" s="87">
-        <f>SUM(D121:D122)</f>
-        <v>1400</v>
-      </c>
-      <c r="E123" s="87">
-        <f t="shared" ref="E123:L123" si="103">SUM(E121:E122)</f>
-        <v>0</v>
-      </c>
-      <c r="F123" s="87">
         <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="G123" s="87">
-        <f t="shared" si="103"/>
-        <v>2280</v>
-      </c>
-      <c r="H123" s="87">
-        <f t="shared" si="103"/>
-        <v>1000</v>
-      </c>
-      <c r="I123" s="87">
-        <f t="shared" si="103"/>
-        <v>2120</v>
-      </c>
-      <c r="J123" s="87">
-        <f t="shared" si="103"/>
-        <v>3800</v>
-      </c>
-      <c r="K123" s="87">
-        <f t="shared" si="103"/>
-        <v>3400</v>
-      </c>
-      <c r="L123" s="87">
-        <f t="shared" si="103"/>
-        <v>5600</v>
-      </c>
-      <c r="M123" s="123">
-        <f>SUM(M120:M122)</f>
-        <v>4490</v>
-      </c>
-      <c r="N123" s="59">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A123" s="78">
+        <v>46203</v>
+      </c>
+      <c r="B123" s="47">
+        <v>119</v>
+      </c>
+      <c r="C123" s="150" t="s">
+        <v>217</v>
+      </c>
+      <c r="D123" s="146"/>
+      <c r="E123" s="146"/>
+      <c r="F123" s="146"/>
+      <c r="G123" s="146">
+        <v>40</v>
+      </c>
+      <c r="H123" s="146">
+        <v>40</v>
+      </c>
+      <c r="I123" s="159"/>
+      <c r="J123" s="146">
+        <v>40</v>
+      </c>
+      <c r="K123" s="146">
+        <v>40</v>
+      </c>
+      <c r="L123" s="146">
+        <v>40</v>
+      </c>
+      <c r="M123" s="152">
+        <f t="shared" si="96"/>
+        <v>5</v>
+      </c>
+      <c r="N123" s="39">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="O123" s="58">
+      <c r="O123" s="49">
         <f t="shared" si="1"/>
         <v>331.63</v>
       </c>
       <c r="P123" s="73">
+        <f t="shared" si="97"/>
+        <v>4</v>
+      </c>
+      <c r="Q123" s="40">
         <f t="shared" si="98"/>
-        <v>270</v>
-      </c>
-      <c r="Q123" s="40">
-        <f t="shared" si="99"/>
-        <v>640</v>
+        <v>6</v>
       </c>
       <c r="R123" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11070,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="U123" s="53" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="99"/>
         <v>#VALUE!</v>
       </c>
       <c r="V123" s="54" t="e">
@@ -11086,101 +12440,1031 @@
         <v>0</v>
       </c>
       <c r="Y123" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A124" s="78"/>
+      <c r="B124" s="118"/>
+      <c r="C124" s="151"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="50"/>
+      <c r="G124" s="50"/>
+      <c r="H124" s="50"/>
+      <c r="I124" s="152"/>
+      <c r="J124" s="50"/>
+      <c r="K124" s="50"/>
+      <c r="L124" s="50"/>
+      <c r="M124" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N124" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O124" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P124" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q124" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R124" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S124" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T124" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U124" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V124" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W124" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X124" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y124" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A125" s="78"/>
+      <c r="B125" s="118"/>
+      <c r="C125" s="151"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
+      <c r="F125" s="50"/>
+      <c r="G125" s="50"/>
+      <c r="H125" s="50"/>
+      <c r="I125" s="152"/>
+      <c r="J125" s="50"/>
+      <c r="K125" s="50"/>
+      <c r="L125" s="50"/>
+      <c r="M125" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N125" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O125" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P125" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q125" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R125" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S125" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T125" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U125" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V125" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W125" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X125" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y125" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A126" s="78"/>
+      <c r="B126" s="118"/>
+      <c r="C126" s="151"/>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50"/>
+      <c r="F126" s="50"/>
+      <c r="G126" s="50"/>
+      <c r="H126" s="50"/>
+      <c r="I126" s="152"/>
+      <c r="J126" s="50"/>
+      <c r="K126" s="50"/>
+      <c r="L126" s="50"/>
+      <c r="M126" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N126" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O126" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P126" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q126" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R126" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S126" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T126" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U126" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V126" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W126" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X126" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y126" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A127" s="78"/>
+      <c r="B127" s="118"/>
+      <c r="C127" s="151"/>
+      <c r="D127" s="50"/>
+      <c r="E127" s="50"/>
+      <c r="F127" s="50"/>
+      <c r="G127" s="50"/>
+      <c r="H127" s="50"/>
+      <c r="I127" s="152"/>
+      <c r="J127" s="50"/>
+      <c r="K127" s="50"/>
+      <c r="L127" s="50"/>
+      <c r="M127" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N127" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O127" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P127" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R127" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S127" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T127" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U127" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V127" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W127" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X127" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y127" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A128" s="78"/>
+      <c r="B128" s="118"/>
+      <c r="C128" s="151"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="50"/>
+      <c r="F128" s="50"/>
+      <c r="G128" s="50"/>
+      <c r="H128" s="50"/>
+      <c r="I128" s="152"/>
+      <c r="J128" s="50"/>
+      <c r="K128" s="50"/>
+      <c r="L128" s="50"/>
+      <c r="M128" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N128" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O128" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P128" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q128" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R128" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S128" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T128" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U128" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V128" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W128" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X128" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y128" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A129" s="78"/>
+      <c r="B129" s="118"/>
+      <c r="C129" s="151"/>
+      <c r="D129" s="50"/>
+      <c r="E129" s="50"/>
+      <c r="F129" s="50"/>
+      <c r="G129" s="50"/>
+      <c r="H129" s="50"/>
+      <c r="I129" s="152"/>
+      <c r="J129" s="50"/>
+      <c r="K129" s="50"/>
+      <c r="L129" s="50"/>
+      <c r="M129" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N129" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O129" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P129" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q129" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R129" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S129" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T129" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U129" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V129" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W129" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X129" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y129" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A130" s="78"/>
+      <c r="B130" s="118"/>
+      <c r="C130" s="151"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="50"/>
+      <c r="F130" s="50"/>
+      <c r="G130" s="50"/>
+      <c r="H130" s="50"/>
+      <c r="I130" s="152"/>
+      <c r="J130" s="50"/>
+      <c r="K130" s="50"/>
+      <c r="L130" s="50"/>
+      <c r="M130" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N130" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O130" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P130" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q130" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R130" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S130" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T130" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U130" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V130" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W130" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X130" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y130" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A131" s="78"/>
+      <c r="B131" s="118"/>
+      <c r="C131" s="151"/>
+      <c r="D131" s="50"/>
+      <c r="E131" s="50"/>
+      <c r="F131" s="50"/>
+      <c r="G131" s="50"/>
+      <c r="H131" s="50"/>
+      <c r="I131" s="152"/>
+      <c r="J131" s="50"/>
+      <c r="K131" s="50"/>
+      <c r="L131" s="50"/>
+      <c r="M131" s="152">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="N131" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O131" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P131" s="73">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="Q131" s="40">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="R131" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S131" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T131" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U131" s="53" t="e">
+        <f t="shared" si="99"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V131" s="54" t="e">
+        <f t="shared" si="100"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W131" s="55">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="X131" s="55">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="Y131" s="56" t="e">
+        <f t="shared" si="103"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A132" s="78"/>
+      <c r="B132" s="192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="193"/>
+      <c r="D132" s="88">
+        <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
+        <v>1320</v>
+      </c>
+      <c r="E132" s="88">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="88">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="88">
+        <f t="shared" si="104"/>
+        <v>7140</v>
+      </c>
+      <c r="H132" s="88">
+        <f t="shared" si="104"/>
+        <v>7657</v>
+      </c>
+      <c r="I132" s="88">
+        <f t="shared" si="104"/>
+        <v>10657</v>
+      </c>
+      <c r="J132" s="88">
+        <f t="shared" si="104"/>
+        <v>11297</v>
+      </c>
+      <c r="K132" s="88">
+        <f t="shared" si="104"/>
+        <v>9684</v>
+      </c>
+      <c r="L132" s="88">
+        <f t="shared" si="104"/>
+        <v>13219</v>
+      </c>
+      <c r="M132" s="48">
+        <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
+        <v>1524.35</v>
+      </c>
+      <c r="N132" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O132" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P132" s="73">
+        <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
+        <v>1272.7</v>
+      </c>
+      <c r="Q132" s="40">
+        <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
+        <v>1710</v>
+      </c>
+      <c r="R132" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S132" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T132" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U132" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V132" s="54" t="e">
+        <f t="shared" ref="V132:V136" si="108">SUM(D132:F132)*$V$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W132" s="55">
+        <f t="shared" ref="W132:W136" si="109">SUM(G132:I132)*$W$3</f>
+        <v>0</v>
+      </c>
+      <c r="X132" s="55">
+        <f t="shared" ref="X132:X136" si="110">SUM(J132:L132)*$X$3</f>
+        <v>0</v>
+      </c>
+      <c r="Y132" s="56" t="e">
+        <f t="shared" si="44"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A133" s="78"/>
+      <c r="B133" s="118">
+        <v>0</v>
+      </c>
+      <c r="C133" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D133" s="119">
+        <v>1600</v>
+      </c>
+      <c r="E133" s="120"/>
+      <c r="F133" s="121"/>
+      <c r="G133" s="120"/>
+      <c r="H133" s="120"/>
+      <c r="I133" s="121"/>
+      <c r="J133" s="120">
+        <v>520</v>
+      </c>
+      <c r="K133" s="120">
+        <v>920</v>
+      </c>
+      <c r="L133" s="121">
+        <v>960</v>
+      </c>
+      <c r="M133" s="122">
+        <f>SUM(D133:L133)</f>
+        <v>4000</v>
+      </c>
+      <c r="N133" s="39"/>
+      <c r="O133" s="49"/>
+      <c r="P133" s="73"/>
+      <c r="Q133" s="40"/>
+      <c r="R133" s="51"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
+      <c r="U133" s="53"/>
+      <c r="V133" s="54"/>
+      <c r="W133" s="55"/>
+      <c r="X133" s="55"/>
+      <c r="Y133" s="56"/>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A134" s="78"/>
+      <c r="B134" s="47">
+        <v>1</v>
+      </c>
+      <c r="C134" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" s="74"/>
+      <c r="E134" s="75"/>
+      <c r="F134" s="76"/>
+      <c r="G134" s="50">
+        <f>280+1600</f>
+        <v>1880</v>
+      </c>
+      <c r="H134" s="75">
+        <f>0+600</f>
+        <v>600</v>
+      </c>
+      <c r="I134" s="49">
+        <f>320+1800</f>
+        <v>2120</v>
+      </c>
+      <c r="J134" s="50">
+        <f>600+2800</f>
+        <v>3400</v>
+      </c>
+      <c r="K134" s="75">
+        <f>600+2400</f>
+        <v>3000</v>
+      </c>
+      <c r="L134" s="76">
+        <f>2200+2800</f>
+        <v>5000</v>
+      </c>
+      <c r="M134" s="48">
+        <f t="shared" si="105"/>
+        <v>400</v>
+      </c>
+      <c r="N134" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O134" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P134" s="73">
+        <f t="shared" si="106"/>
+        <v>230</v>
+      </c>
+      <c r="Q134" s="40">
+        <f t="shared" si="107"/>
+        <v>570</v>
+      </c>
+      <c r="R134" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S134" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T134" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U134" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V134" s="54" t="e">
+        <f t="shared" si="108"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W134" s="55">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="X134" s="55">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Y134" s="56" t="e">
         <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B124" s="169" t="s">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="B135" s="47">
+        <v>2</v>
+      </c>
+      <c r="C135" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135" s="74">
+        <v>1400</v>
+      </c>
+      <c r="E135" s="75"/>
+      <c r="F135" s="76"/>
+      <c r="G135" s="50">
+        <v>400</v>
+      </c>
+      <c r="H135" s="75">
+        <v>400</v>
+      </c>
+      <c r="I135" s="49">
+        <v>0</v>
+      </c>
+      <c r="J135" s="50">
+        <v>400</v>
+      </c>
+      <c r="K135" s="75">
+        <v>400</v>
+      </c>
+      <c r="L135" s="76">
+        <v>600</v>
+      </c>
+      <c r="M135" s="48">
+        <f t="shared" si="105"/>
+        <v>90</v>
+      </c>
+      <c r="N135" s="39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O135" s="49">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P135" s="73">
+        <f t="shared" si="106"/>
+        <v>40</v>
+      </c>
+      <c r="Q135" s="40">
+        <f t="shared" si="107"/>
+        <v>70</v>
+      </c>
+      <c r="R135" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S135" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T135" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U135" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V135" s="54" t="e">
+        <f t="shared" si="108"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W135" s="55">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="X135" s="55">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Y135" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B136" s="180" t="s">
+        <v>93</v>
+      </c>
+      <c r="C136" s="181"/>
+      <c r="D136" s="87">
+        <f>SUM(D134:D135)</f>
+        <v>1400</v>
+      </c>
+      <c r="E136" s="87">
+        <f t="shared" ref="E136:L136" si="111">SUM(E134:E135)</f>
+        <v>0</v>
+      </c>
+      <c r="F136" s="87">
+        <f t="shared" si="111"/>
+        <v>0</v>
+      </c>
+      <c r="G136" s="87">
+        <f t="shared" si="111"/>
+        <v>2280</v>
+      </c>
+      <c r="H136" s="87">
+        <f t="shared" si="111"/>
+        <v>1000</v>
+      </c>
+      <c r="I136" s="87">
+        <f t="shared" si="111"/>
+        <v>2120</v>
+      </c>
+      <c r="J136" s="87">
+        <f t="shared" si="111"/>
+        <v>3800</v>
+      </c>
+      <c r="K136" s="87">
+        <f t="shared" si="111"/>
+        <v>3400</v>
+      </c>
+      <c r="L136" s="87">
+        <f t="shared" si="111"/>
+        <v>5600</v>
+      </c>
+      <c r="M136" s="123">
+        <f>SUM(M133:M135)</f>
+        <v>4490</v>
+      </c>
+      <c r="N136" s="59">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O136" s="58">
+        <f t="shared" si="1"/>
+        <v>331.63</v>
+      </c>
+      <c r="P136" s="73">
+        <f t="shared" si="106"/>
+        <v>270</v>
+      </c>
+      <c r="Q136" s="40">
+        <f t="shared" si="107"/>
+        <v>640</v>
+      </c>
+      <c r="R136" s="51" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S136" s="52">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T136" s="52">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U136" s="53" t="e">
+        <f t="shared" si="19"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V136" s="54" t="e">
+        <f t="shared" si="108"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W136" s="55">
+        <f t="shared" si="109"/>
+        <v>0</v>
+      </c>
+      <c r="X136" s="55">
+        <f t="shared" si="110"/>
+        <v>0</v>
+      </c>
+      <c r="Y136" s="56" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B137" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="C124" s="170"/>
-      <c r="D124" s="89">
-        <f>SUM(D119,D123)</f>
+      <c r="C137" s="170"/>
+      <c r="D137" s="89">
+        <f>SUM(D132,D136)</f>
         <v>2720</v>
       </c>
-      <c r="E124" s="89">
-        <f t="shared" ref="E124:L124" si="104">SUM(E119,E123)</f>
-        <v>0</v>
-      </c>
-      <c r="F124" s="89">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="G124" s="89">
-        <f t="shared" si="104"/>
+      <c r="E137" s="89">
+        <f t="shared" ref="E137:L137" si="112">SUM(E132,E136)</f>
+        <v>0</v>
+      </c>
+      <c r="F137" s="89">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="G137" s="89">
+        <f t="shared" si="112"/>
         <v>9420</v>
       </c>
-      <c r="H124" s="89">
-        <f t="shared" si="104"/>
+      <c r="H137" s="89">
+        <f t="shared" si="112"/>
         <v>8657</v>
       </c>
-      <c r="I124" s="89">
-        <f t="shared" si="104"/>
+      <c r="I137" s="89">
+        <f t="shared" si="112"/>
         <v>12777</v>
       </c>
-      <c r="J124" s="89">
-        <f t="shared" si="104"/>
+      <c r="J137" s="89">
+        <f t="shared" si="112"/>
         <v>15097</v>
       </c>
-      <c r="K124" s="89">
-        <f t="shared" si="104"/>
+      <c r="K137" s="89">
+        <f t="shared" si="112"/>
         <v>13084</v>
       </c>
-      <c r="L124" s="89">
-        <f t="shared" si="104"/>
+      <c r="L137" s="89">
+        <f t="shared" si="112"/>
         <v>18819</v>
       </c>
-      <c r="M124" s="60">
+      <c r="M137" s="60">
         <f t="shared" si="0"/>
         <v>2014.35</v>
       </c>
-      <c r="N124" s="63">
-        <f>SUM(N5:N123)</f>
-        <v>0</v>
-      </c>
-      <c r="O124" s="61">
-        <f t="shared" ref="O124:Y124" si="105">SUM(O5:O123)</f>
-        <v>27856.920000000016</v>
-      </c>
-      <c r="P124" s="62">
-        <f t="shared" si="105"/>
-        <v>3538.7</v>
-      </c>
-      <c r="Q124" s="64">
-        <f t="shared" si="105"/>
-        <v>5635.95</v>
-      </c>
-      <c r="R124" s="65" t="e">
-        <f t="shared" si="105"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="S124" s="66">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="T124" s="66">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="U124" s="67" t="e">
-        <f t="shared" si="105"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V124" s="68" t="e">
-        <f t="shared" si="105"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="W124" s="69">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="X124" s="69">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="Y124" s="70" t="e">
-        <f t="shared" si="105"/>
+      <c r="N137" s="63">
+        <f>SUM(N5:N136)</f>
+        <v>0</v>
+      </c>
+      <c r="O137" s="61">
+        <f t="shared" ref="O137:Y137" si="113">SUM(O5:O136)</f>
+        <v>43443.529999999948</v>
+      </c>
+      <c r="P137" s="62">
+        <f t="shared" si="113"/>
+        <v>3755.1000000000004</v>
+      </c>
+      <c r="Q137" s="64">
+        <f t="shared" si="113"/>
+        <v>6015.25</v>
+      </c>
+      <c r="R137" s="65" t="e">
+        <f t="shared" si="113"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S137" s="66">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="T137" s="66">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="U137" s="67" t="e">
+        <f t="shared" si="113"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V137" s="68" t="e">
+        <f t="shared" si="113"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="W137" s="69">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="X137" s="69">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="Y137" s="70" t="e">
+        <f t="shared" si="113"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -11190,13 +13474,13 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B136:C136"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
